--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -524,7 +524,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -580,7 +579,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -11182,12 +11180,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Cloud hosting. Provider and region not chosen. Nearest Supabase region is Frankfurt.</t>
+          <t>Cloud hosting on Supabase, region West EU (Ireland).</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Open: pick region</t>
+          <t>Confirmed 30 Sep 2026</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -524,6 +524,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -579,6 +580,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -593,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12">
@@ -613,7 +615,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +645,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -659,10 +661,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Partly built, no tagged test</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>R1b</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>3</v>
       </c>
     </row>
@@ -677,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P116"/>
+  <dimension ref="A1:P117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1397,7 +1409,7 @@
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>15_accounts (7)</t>
+          <t>15_accounts (7); 28_platform_console (16); browser: platform-console</t>
         </is>
       </c>
       <c r="O9" s="10" t="inlineStr">
@@ -1405,7 +1417,11 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P9" s="10" t="inlineStr"/>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>Platform console /platform (wave 2 item 2): extend trial, activate or extend paid period, suspend, change plan, cancel; each with a reason, logged in subscription_history with the operator.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -1470,20 +1486,24 @@
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>row-level security; platform staff have no tenant profile</t>
+          <t>platform_list_tenants (hotel account data only); operators have no hotel, so row-level security shows them no hotel rows</t>
         </is>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28_platform_console (7); browser: platform-console</t>
         </is>
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
-          <t>Built, no tagged test</t>
-        </is>
-      </c>
-      <c r="P10" s="10" t="inlineStr"/>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>Corrected 6 Oct 2026: before wave 2 item 2 there was no platform staff role at all; the earlier "Built, no tagged test" was wrong.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -1722,22 +1742,22 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>ADM-001</t>
+          <t>PLT-013</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Platform &amp; Tenancy</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>ADM-01</t>
+          <t>/platform</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>A hotel administrator adds staff to the hotel.</t>
+          <t>Platform operators are separate sign-ins that belong to no hotel, added only by the database owner; the platform console and every platform function need the operator list and a session that passed two-step sign-in.</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -1757,37 +1777,37 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>adm.user.manage</t>
+          <t>platform operator list; aal2</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>Rule: Role assignment</t>
+          <t>Decisions of 6 Oct 2026 (wave 2 item 2)</t>
         </is>
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>an administrator and a new auth user created by an Edge Function</t>
+          <t>a platform operator signed in with password only</t>
         </is>
       </c>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t>the administrator registers the user</t>
+          <t>they open the console or call a platform function</t>
         </is>
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>the user joins the hotel; a person who already belongs to a hotel cannot be taken over</t>
+          <t>it is refused until they confirm with their authenticator app; hotel accounts are always refused</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>register_invited_user (the Edge Function creates the auth user and sends the invite)</t>
+          <t>app.require_platform, app.add_platform_operator, platform_* functions</t>
         </is>
       </c>
       <c r="N14" s="10" t="inlineStr">
         <is>
-          <t>10_security (1)</t>
+          <t>28_platform_console (14); browser: platform-console</t>
         </is>
       </c>
       <c r="O14" s="10" t="inlineStr">
@@ -1795,16 +1815,12 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P14" s="10" t="inlineStr">
-        <is>
-          <t>Invites are sent by a Vercel server function (not an Edge Function).</t>
-        </is>
-      </c>
+      <c r="P14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>ADM-002</t>
+          <t>ADM-001</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -1814,12 +1830,12 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>ADM-02</t>
+          <t>ADM-01</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Only administrators assign roles, per property or hotel-wide; the last administrator cannot be removed.</t>
+          <t>A hotel administrator adds staff to the hotel.</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -1839,7 +1855,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>adm.role.assign</t>
+          <t>adm.user.manage</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
@@ -1849,27 +1865,27 @@
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>a hotel with one System Administrator</t>
+          <t>an administrator and a new auth user created by an Edge Function</t>
         </is>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>that person is removed or disabled</t>
+          <t>the administrator registers the user</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>the change is refused with E_LAST_ADMIN; platform roles can never be assigned by a hotel</t>
+          <t>the user joins the hotel; a person who already belongs to a hotel cannot be taken over</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>assign_role, remove_role, set_user_status</t>
+          <t>register_invited_user (the Edge Function creates the auth user and sends the invite)</t>
         </is>
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>10_security (2); 15_accounts (3); 27_medium_fixes (2)</t>
+          <t>10_security (1)</t>
         </is>
       </c>
       <c r="O15" s="10" t="inlineStr">
@@ -1877,12 +1893,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P15" s="10" t="inlineStr"/>
+      <c r="P15" s="10" t="inlineStr">
+        <is>
+          <t>Invites are sent by a Vercel server function (not an Edge Function).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>ADM-003</t>
+          <t>ADM-002</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1892,12 +1912,12 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>ADM-01</t>
+          <t>ADM-02</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>A disabled user loses all access immediately.</t>
+          <t>Only administrators assign roles, per property or hotel-wide; the last administrator cannot be removed.</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -1917,37 +1937,37 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>adm.user.manage</t>
+          <t>adm.role.assign</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Role assignment</t>
         </is>
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>a cashier who leaves the company</t>
+          <t>a hotel with one System Administrator</t>
         </is>
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>an administrator disables the user</t>
+          <t>that person is removed or disabled</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>every action the user tries is refused with E_PERM</t>
+          <t>the change is refused with E_LAST_ADMIN; platform roles can never be assigned by a hotel</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>set_user_status; grant_level checks profile status</t>
+          <t>assign_role, remove_role, set_user_status</t>
         </is>
       </c>
       <c r="N16" s="10" t="inlineStr">
         <is>
-          <t>15_accounts (2)</t>
+          <t>10_security (2); 15_accounts (3); 27_medium_fixes (2)</t>
         </is>
       </c>
       <c r="O16" s="10" t="inlineStr">
@@ -1960,7 +1980,7 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>ADM-004</t>
+          <t>ADM-003</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1970,12 +1990,12 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>ADM-02</t>
+          <t>ADM-01</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Custom roles cannot hold more than their creator holds.</t>
+          <t>A disabled user loses all access immediately.</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
@@ -1995,37 +2015,37 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>adm.role.manage</t>
+          <t>adm.user.manage</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Rule: Role assignment</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>an administrator without payment rights</t>
+          <t>a cashier who leaves the company</t>
         </is>
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>they add fin.payment.post to a custom role</t>
+          <t>an administrator disables the user</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>the change is refused with E_ESCALATION; system roles cannot be edited</t>
+          <t>every action the user tries is refused with E_PERM</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>role_perm_no_escalation trigger; roles policies</t>
+          <t>set_user_status; grant_level checks profile status</t>
         </is>
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>10_security (1); 15_accounts (1)</t>
+          <t>15_accounts (2)</t>
         </is>
       </c>
       <c r="O17" s="10" t="inlineStr">
@@ -2038,7 +2058,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>ADM-005</t>
+          <t>ADM-004</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -2053,12 +2073,12 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Limit-based permissions (grant level L) use a per-role amount; no limit means zero.</t>
+          <t>Custom roles cannot hold more than their creator holds.</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>BR-015, BR-017</t>
+          <t>BR-017</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
@@ -2073,37 +2093,37 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>adm.config.manage</t>
+          <t>adm.role.manage</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>Rule: Limits</t>
+          <t>Rule: Role assignment</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>a role with level L on discount and a limit of 5,000</t>
+          <t>an administrator without payment rights</t>
         </is>
       </c>
       <c r="K18" s="10" t="inlineStr">
         <is>
-          <t>the user applies a discount of 8,000</t>
+          <t>they add fin.payment.post to a custom role</t>
         </is>
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>the discount waits for approval</t>
+          <t>the change is refused with E_ESCALATION; system roles cannot be edited</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>approval_limits, approval_limit()</t>
+          <t>role_perm_no_escalation trigger; roles policies</t>
         </is>
       </c>
       <c r="N18" s="10" t="inlineStr">
         <is>
-          <t>10_security (1)</t>
+          <t>10_security (1); 15_accounts (1)</t>
         </is>
       </c>
       <c r="O18" s="10" t="inlineStr">
@@ -2116,7 +2136,7 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>ADM-006</t>
+          <t>ADM-005</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -2126,17 +2146,17 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>ADM-03</t>
+          <t>ADM-02</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>The audit trail cannot be changed or deleted by anyone, and is visible to permitted roles only.</t>
+          <t>Limit-based permissions (grant level L) use a per-role amount; no limit means zero.</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>BR-014, BR-018</t>
+          <t>BR-015, BR-017</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
@@ -2151,37 +2171,37 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>adm.audit.view</t>
+          <t>adm.config.manage</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>Rule: Immutability, Audit log access</t>
+          <t>Rule: Limits</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>audit events exist</t>
+          <t>a role with level L on discount and a limit of 5,000</t>
         </is>
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>anyone, including the database owner, updates or deletes one</t>
+          <t>the user applies a discount of 8,000</t>
         </is>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>the change is refused with E_IMMUTABLE</t>
+          <t>the discount waits for approval</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>audit_events triggers; audit_read policy</t>
+          <t>approval_limits, approval_limit()</t>
         </is>
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>10_security (1); 16_structure (6); upgrade (2)</t>
+          <t>10_security (1)</t>
         </is>
       </c>
       <c r="O19" s="10" t="inlineStr">
@@ -2194,7 +2214,7 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>ADM-007</t>
+          <t>ADM-006</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -2204,17 +2224,17 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>(all)</t>
+          <t>ADM-03</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Sensitive actions require a reason and write an audit event with actor, time, before and after.</t>
+          <t>The audit trail cannot be changed or deleted by anyone, and is visible to permitted roles only.</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>BR-018</t>
+          <t>BR-014, BR-018</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
@@ -2229,37 +2249,37 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>(all S permissions)</t>
+          <t>adm.audit.view</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>Rule: Reasons</t>
+          <t>Rule: Immutability, Audit log access</t>
         </is>
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>a sensitive action (cancel, rate override, refund, block, reopen, override condition)</t>
+          <t>audit events exist</t>
         </is>
       </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
-          <t>it is performed</t>
+          <t>anyone, including the database owner, updates or deletes one</t>
         </is>
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>a reason is required and an audit event is written</t>
+          <t>the change is refused with E_IMMUTABLE</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>app.audit calls in each function</t>
+          <t>audit_events triggers; audit_read policy</t>
         </is>
       </c>
       <c r="N20" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>10_security (1); 16_structure (6); upgrade (2)</t>
         </is>
       </c>
       <c r="O20" s="10" t="inlineStr">
@@ -2272,7 +2292,7 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>ADM-008</t>
+          <t>ADM-007</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -2282,22 +2302,22 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>(bell icon)</t>
+          <t>(all)</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Staff get in-app notifications for approvals, tasks and exceptions, and can mark them read.</t>
+          <t>Sensitive actions require a reason and write an audit event with actor, time, before and after.</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>BR-017</t>
+          <t>BR-018</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -2307,37 +2327,37 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>(own)</t>
+          <t>(all S permissions)</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Reasons</t>
         </is>
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>an approval is requested</t>
+          <t>a sensitive action (cancel, rate override, refund, block, reopen, override condition)</t>
         </is>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>the requester submits it</t>
+          <t>it is performed</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>users holding the approve permission get a notification; each user sees only their own</t>
+          <t>a reason is required and an audit event is written</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
-          <t>notifications, notify_permission, notify_user</t>
+          <t>app.audit calls in each function</t>
         </is>
       </c>
       <c r="N21" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (1); 16_structure (3)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O21" s="10" t="inlineStr">
@@ -2350,7 +2370,7 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>ADM-009</t>
+          <t>ADM-008</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -2360,17 +2380,17 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>(exports)</t>
+          <t>(bell icon)</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Authorised users export data.</t>
+          <t>Staff get in-app notifications for approvals, tasks and exceptions, and can mark them read.</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>BR-020</t>
+          <t>BR-017</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
@@ -2385,7 +2405,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>data.export, rep.export</t>
+          <t>(own)</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -2395,69 +2415,65 @@
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>an authorised user</t>
+          <t>an approval is requested</t>
         </is>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>they export a report</t>
+          <t>the requester submits it</t>
         </is>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>a file is produced and the export is audited</t>
+          <t>users holding the approve permission get a notification; each user sees only their own</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>(needs an Edge Function or client-side export)</t>
+          <t>notifications, notify_permission, notify_user</t>
         </is>
       </c>
       <c r="N22" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12_ledger (1); 16_structure (3)</t>
         </is>
       </c>
       <c r="O22" s="10" t="inlineStr">
         <is>
-          <t>Built, no tagged test</t>
-        </is>
-      </c>
-      <c r="P22" s="10" t="inlineStr">
-        <is>
-          <t>export_data (audited), Reports &gt; Export.</t>
-        </is>
-      </c>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>SET-001</t>
+          <t>ADM-009</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>SET-01</t>
+          <t>(exports)</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Property profile can be edited, but the business date and base currency cannot.</t>
+          <t>Authorised users export data.</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>BR-002</t>
+          <t>BR-020</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -2467,50 +2483,54 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>setup.property.manage</t>
+          <t>data.export, rep.export</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>Rule: Business date</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>a property with postings</t>
+          <t>an authorised user</t>
         </is>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>an administrator edits the profile</t>
+          <t>they export a report</t>
         </is>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>name, contact, rollover time and inspection setting change; business date and base currency are refused</t>
+          <t>a file is produced and the export is audited</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>column grants on properties</t>
+          <t>(needs an Edge Function or client-side export)</t>
         </is>
       </c>
       <c r="N23" s="10" t="inlineStr">
         <is>
-          <t>10_security (3); 16_structure (1)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="10" t="inlineStr">
         <is>
-          <t>Built+tested</t>
-        </is>
-      </c>
-      <c r="P23" s="10" t="inlineStr"/>
+          <t>Built, no tagged test</t>
+        </is>
+      </c>
+      <c r="P23" s="10" t="inlineStr">
+        <is>
+          <t>export_data (audited), Reports &gt; Export.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>SET-002</t>
+          <t>SET-001</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -2520,17 +2540,17 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>SET-02</t>
+          <t>SET-01</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Room types with occupancy limits and an overbooking allowance.</t>
+          <t>Property profile can be edited, but the business date and base currency cannot.</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>BR-004</t>
+          <t>BR-002</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
@@ -2545,42 +2565,42 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>setup.roomtype.manage</t>
+          <t>setup.property.manage</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Business date</t>
         </is>
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>an administrator</t>
+          <t>a property with postings</t>
         </is>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>they add a room type</t>
+          <t>an administrator edits the profile</t>
         </is>
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>it appears in availability and booking</t>
+          <t>name, contact, rollover time and inspection setting change; business date and base currency are refused</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>room_types (direct write with RLS)</t>
+          <t>column grants on properties</t>
         </is>
       </c>
       <c r="N24" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10_security (3); 16_structure (1)</t>
         </is>
       </c>
       <c r="O24" s="10" t="inlineStr">
         <is>
-          <t>Built, no tagged test</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P24" s="10" t="inlineStr"/>
@@ -2588,7 +2608,7 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>SET-003</t>
+          <t>SET-002</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -2598,17 +2618,17 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>SET-03</t>
+          <t>SET-02</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Room inventory per property; rooms can be retired but never deleted while in use.</t>
+          <t>Room types with occupancy limits and an overbooking allowance.</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>BR-004, BR-009</t>
+          <t>BR-004</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
@@ -2623,7 +2643,7 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>setup.room.manage</t>
+          <t>setup.roomtype.manage</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
@@ -2638,17 +2658,17 @@
       </c>
       <c r="K25" s="10" t="inlineStr">
         <is>
-          <t>they add rooms</t>
+          <t>they add a room type</t>
         </is>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>they start Ready and Vacant and count towards inventory; condition and occupancy cannot be written by hand</t>
+          <t>it appears in availability and booking</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>rooms; column grants</t>
+          <t>room_types (direct write with RLS)</t>
         </is>
       </c>
       <c r="N25" s="10" t="inlineStr">
@@ -2658,15 +2678,19 @@
       </c>
       <c r="O25" s="10" t="inlineStr">
         <is>
-          <t>Built, no tagged test</t>
-        </is>
-      </c>
-      <c r="P25" s="10" t="inlineStr"/>
+          <t>Partly built, no tagged test</t>
+        </is>
+      </c>
+      <c r="P25" s="10" t="inlineStr">
+        <is>
+          <t>Corrected 6 Oct 2026: room types and occupancy limits (save_room_type, max adults and children; Setup, Room types) exist; the overbooking allowance does not exist anywhere in the app.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>SET-004</t>
+          <t>SET-003</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -2676,17 +2700,17 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>SET-04</t>
+          <t>SET-03</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Rate plans with prices by room type, date range and weekday, and policies for cancellation, no-show and deposit.</t>
+          <t>Room inventory per property; rooms can be retired but never deleted while in use.</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>BR-004</t>
+          <t>BR-004, BR-009</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
@@ -2701,42 +2725,42 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>setup.rateplan.manage</t>
+          <t>setup.room.manage</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
-          <t>a rate plan with a cancellation rule of one night inside two days</t>
+          <t>an administrator</t>
         </is>
       </c>
       <c r="K26" s="10" t="inlineStr">
         <is>
-          <t>a guest cancels one day before arrival</t>
+          <t>they add rooms</t>
         </is>
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>one night is charged</t>
+          <t>they start Ready and Vacant and count towards inventory; condition and occupancy cannot be written by hand</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>rate_plans, rate_plan_prices, night_price, policy_fee</t>
+          <t>rooms; column grants</t>
         </is>
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (2)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="10" t="inlineStr">
         <is>
-          <t>Built+tested</t>
+          <t>Built, no tagged test</t>
         </is>
       </c>
       <c r="P26" s="10" t="inlineStr"/>
@@ -2744,7 +2768,7 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>SET-005</t>
+          <t>SET-004</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -2754,17 +2778,17 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>SET-05</t>
+          <t>SET-04</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Tax lines with rate, base (net or net plus prior taxes), applicable revenue groups and a verified flag.</t>
+          <t>Rate plans with prices by room type, date range and weekday, and policies for cancellation, no-show and deposit.</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-004</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
@@ -2779,37 +2803,37 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>setup.tax.manage</t>
+          <t>setup.rateplan.manage</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>service charge 10% then VAT 7.5% on price plus service charge</t>
+          <t>a rate plan with a cancellation rule of one night inside two days</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>a charge of 10,000 is posted</t>
+          <t>a guest cancels one day before arrival</t>
         </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>tax lines of 1,000 and 825 are posted; inclusive prices solve back to the same net</t>
+          <t>one night is charged</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>tax_rates, compute_taxes</t>
+          <t>rate_plans, rate_plan_prices, night_price, policy_fee</t>
         </is>
       </c>
       <c r="N27" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (1)</t>
+          <t>13_reservations (2)</t>
         </is>
       </c>
       <c r="O27" s="10" t="inlineStr">
@@ -2822,7 +2846,7 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>SET-006</t>
+          <t>SET-005</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -2837,7 +2861,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Charge codes and payment methods per property.</t>
+          <t>Tax lines with rate, base (net or net plus prior taxes), applicable revenue groups and a verified flag.</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -2862,37 +2886,37 @@
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>Rule: Payments in R1</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
-          <t>a property</t>
+          <t>service charge 10% then VAT 7.5% on price plus service charge</t>
         </is>
       </c>
       <c r="K28" s="10" t="inlineStr">
         <is>
-          <t>staff post a charge or a payment</t>
+          <t>a charge of 10,000 is posted</t>
         </is>
       </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
-          <t>only active codes and methods of that property are accepted</t>
+          <t>tax lines of 1,000 and 825 are posted; inclusive prices solve back to the same net</t>
         </is>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>charge_codes, payment_methods</t>
+          <t>tax_rates, compute_taxes</t>
         </is>
       </c>
       <c r="N28" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12_ledger (1)</t>
         </is>
       </c>
       <c r="O28" s="10" t="inlineStr">
         <is>
-          <t>Built, no tagged test</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P28" s="10" t="inlineStr"/>
@@ -2900,7 +2924,7 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>SET-007</t>
+          <t>SET-006</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -2915,7 +2939,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Exchange rates per property per day, entered by hand.</t>
+          <t>Charge codes and payment methods per property.</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
@@ -2925,7 +2949,7 @@
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
@@ -2935,42 +2959,42 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>setup.fx.manage</t>
+          <t>setup.tax.manage</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>Rule: Multi-currency; A10</t>
+          <t>Rule: Payments in R1</t>
         </is>
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>USD at 1,500</t>
+          <t>a property</t>
         </is>
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
-          <t>a guest pays USD 10</t>
+          <t>staff post a charge or a payment</t>
         </is>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>the row stores amount, currency, rate 1,500 and a base amount of 15,000; a currency without a rate is refused</t>
+          <t>only active codes and methods of that property are accepted</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
-          <t>set_exchange_rate, fx_rate</t>
+          <t>charge_codes, payment_methods</t>
         </is>
       </c>
       <c r="N29" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (1)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="10" t="inlineStr">
         <is>
-          <t>Built+tested</t>
+          <t>Built, no tagged test</t>
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr"/>
@@ -2978,7 +3002,7 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>SET-008</t>
+          <t>SET-007</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -2988,17 +3012,17 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>SET-01</t>
+          <t>SET-05</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Inspection can be switched off per property.</t>
+          <t>Exchange rates per property per day, entered by hand.</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>BR-011</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
@@ -3013,37 +3037,37 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>setup.property.manage</t>
+          <t>setup.fx.manage</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>Transition: Room Condition Cleaning to Ready</t>
+          <t>Rule: Multi-currency; A10</t>
         </is>
       </c>
       <c r="J30" s="10" t="inlineStr">
         <is>
-          <t>inspection_required is false</t>
+          <t>USD at 1,500</t>
         </is>
       </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>an attendant completes a task</t>
+          <t>a guest pays USD 10</t>
         </is>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>the room is Ready at once and the task closes itself</t>
+          <t>the row stores amount, currency, rate 1,500 and a base amount of 15,000; a currency without a rate is refused</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr">
         <is>
-          <t>complete_hk_task</t>
+          <t>set_exchange_rate, fx_rate</t>
         </is>
       </c>
       <c r="N30" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (1); 26_small_fixes (4)</t>
+          <t>12_ledger (1)</t>
         </is>
       </c>
       <c r="O30" s="10" t="inlineStr">
@@ -3056,32 +3080,32 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>RES-001</t>
+          <t>SET-008</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Reservations</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>RES-01, RES-04</t>
+          <t>SET-01</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Availability is calculated per room type and night from sellable rooms less held bookings.</t>
+          <t>Inspection can be switched off per property.</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>BR-004</t>
+          <t>BR-011</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -3091,37 +3115,37 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>res.availability.view</t>
+          <t>setup.property.manage</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>Rule: Room condition vs sellability</t>
+          <t>Transition: Room Condition Cleaning to Ready</t>
         </is>
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>three standard rooms and three bookings for a night</t>
+          <t>inspection_required is false</t>
         </is>
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
-          <t>staff search that night</t>
+          <t>an attendant completes a task</t>
         </is>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>availability is zero; approved blocks reduce sellable rooms; dirty rooms do not</t>
+          <t>the room is Ready at once and the task closes itself</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr">
         <is>
-          <t>get_availability, holds_inventory</t>
+          <t>complete_hk_task</t>
         </is>
       </c>
       <c r="N31" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (2)</t>
+          <t>17_more_features (1); 26_small_fixes (4)</t>
         </is>
       </c>
       <c r="O31" s="10" t="inlineStr">
@@ -3134,7 +3158,7 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>RES-002</t>
+          <t>RES-001</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -3144,17 +3168,17 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>RES-02</t>
+          <t>RES-01, RES-04</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Create a reservation for one room type and rate plan, priced night by night.</t>
+          <t>Availability is calculated per room type and night from sellable rooms less held bookings.</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>BR-004, BR-007</t>
+          <t>BR-004</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
@@ -3169,37 +3193,37 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>res.create</t>
+          <t>res.availability.view</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>Transition: Reservation new to Inquiry/Tentative/Confirmed</t>
+          <t>Rule: Room condition vs sellability</t>
         </is>
       </c>
       <c r="J32" s="10" t="inlineStr">
         <is>
-          <t>a room type with a rate</t>
+          <t>three standard rooms and three bookings for a night</t>
         </is>
       </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>staff create a two-night booking</t>
+          <t>staff search that night</t>
         </is>
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>nights are priced from the rate plan, a folio is opened, and the same idempotency key returns the same booking</t>
+          <t>availability is zero; approved blocks reduce sellable rooms; dirty rooms do not</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
-          <t>create_reservation</t>
+          <t>get_availability, holds_inventory</t>
         </is>
       </c>
       <c r="N32" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (3)</t>
+          <t>13_reservations (2)</t>
         </is>
       </c>
       <c r="O32" s="10" t="inlineStr">
@@ -3212,7 +3236,7 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>RES-003</t>
+          <t>RES-002</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -3227,12 +3251,12 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>A sold-out room type cannot be booked, and occupancy and stay-length limits are enforced.</t>
+          <t>Create a reservation for one room type and rate plan, priced night by night.</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>BR-004, BR-005</t>
+          <t>BR-004, BR-007</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
@@ -3252,32 +3276,32 @@
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Transition: Reservation new to Inquiry/Tentative/Confirmed</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>a sold-out night</t>
+          <t>a room type with a rate</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>staff book it</t>
+          <t>staff create a two-night booking</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
-          <t>the booking is refused with E_UNAVAILABLE; too many guests gives E_OCCUPANCY; past arrival gives E_DATES</t>
+          <t>nights are priced from the rate plan, a folio is opened, and the same idempotency key returns the same booking</t>
         </is>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>assert_available (advisory lock per property and room type)</t>
+          <t>create_reservation</t>
         </is>
       </c>
       <c r="N33" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (4)</t>
+          <t>13_reservations (3)</t>
         </is>
       </c>
       <c r="O33" s="10" t="inlineStr">
@@ -3290,7 +3314,7 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>RES-004</t>
+          <t>RES-003</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -3300,17 +3324,17 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>RES-03</t>
+          <t>RES-02</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Modify dates, room type, rate plan or guest count before check-in; the stay is repriced and inventory follows.</t>
+          <t>A sold-out room type cannot be booked, and occupancy and stay-length limits are enforced.</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>BR-004</t>
+          <t>BR-004, BR-005</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
@@ -3325,37 +3349,37 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>res.edit</t>
+          <t>res.create</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>Transition: Reservation edit</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>a confirmed booking</t>
+          <t>a sold-out night</t>
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>staff shorten it by a night</t>
+          <t>staff book it</t>
         </is>
       </c>
       <c r="L34" s="10" t="inlineStr">
         <is>
-          <t>the total is repriced and the night is released; an in-house booking cannot be edited this way</t>
+          <t>the booking is refused with E_UNAVAILABLE; too many guests gives E_OCCUPANCY; past arrival gives E_DATES</t>
         </is>
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
-          <t>modify_reservation</t>
+          <t>assert_available (advisory lock per property and room type)</t>
         </is>
       </c>
       <c r="N34" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (3)</t>
+          <t>13_reservations (4)</t>
         </is>
       </c>
       <c r="O34" s="10" t="inlineStr">
@@ -3368,7 +3392,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>RES-005</t>
+          <t>RES-004</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -3378,12 +3402,12 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>RES-02, RES-03</t>
+          <t>RES-03</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>A tentative booking holds inventory until its hold expires, then is released at the next roll; confirming ends the hold.</t>
+          <t>Modify dates, room type, rate plan or guest count before check-in; the stay is repriced and inventory follows.</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
@@ -3403,37 +3427,37 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>res.create, res.edit</t>
+          <t>res.edit</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>Transition: Tentative to Confirmed / Cancelled</t>
+          <t>Transition: Reservation edit</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>a tentative booking with a 1-hour hold</t>
+          <t>a confirmed booking</t>
         </is>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>the hold passes and the roll runs</t>
+          <t>staff shorten it by a night</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>the booking is cancelled with reason 'Hold expired' and inventory is free</t>
+          <t>the total is repriced and the night is released; an in-house booking cannot be edited this way</t>
         </is>
       </c>
       <c r="M35" s="10" t="inlineStr">
         <is>
-          <t>create_reservation, confirm_reservation, roll_business_date</t>
+          <t>modify_reservation</t>
         </is>
       </c>
       <c r="N35" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (5)</t>
+          <t>13_reservations (3)</t>
         </is>
       </c>
       <c r="O35" s="10" t="inlineStr">
@@ -3446,7 +3470,7 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>RES-006</t>
+          <t>RES-005</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -3456,17 +3480,17 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>RES-03</t>
+          <t>RES-02, RES-03</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Cancel with a reason; the fee follows the rate plan; only a permitted user can waive it.</t>
+          <t>A tentative booking holds inventory until its hold expires, then is released at the next roll; confirming ends the hold.</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>BR-004, BR-015</t>
+          <t>BR-004</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
@@ -3481,37 +3505,37 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>res.cancel, res.rate.override</t>
+          <t>res.create, res.edit</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>Transition: Confirmed to Cancelled</t>
+          <t>Transition: Tentative to Confirmed / Cancelled</t>
         </is>
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>a booking inside the free-cancellation window</t>
+          <t>a tentative booking with a 1-hour hold</t>
         </is>
       </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
-          <t>staff cancel it</t>
+          <t>the hold passes and the roll runs</t>
         </is>
       </c>
       <c r="L36" s="10" t="inlineStr">
         <is>
-          <t>one night's fee is posted to the folio; a cancellation outside the window is free; waiving the fee needs res.rate.override</t>
+          <t>the booking is cancelled with reason 'Hold expired' and inventory is free</t>
         </is>
       </c>
       <c r="M36" s="10" t="inlineStr">
         <is>
-          <t>cancel_reservation</t>
+          <t>create_reservation, confirm_reservation, roll_business_date</t>
         </is>
       </c>
       <c r="N36" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (8)</t>
+          <t>17_more_features (5)</t>
         </is>
       </c>
       <c r="O36" s="10" t="inlineStr">
@@ -3524,7 +3548,7 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>RES-007</t>
+          <t>RES-006</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -3534,17 +3558,17 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>RES-03, FO-01</t>
+          <t>RES-03</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>No-show can be marked by hand or by the automatic roll, with the fee from the rate plan.</t>
+          <t>Cancel with a reason; the fee follows the rate plan; only a permitted user can waive it.</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>BR-004</t>
+          <t>BR-004, BR-015</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
@@ -3559,37 +3583,37 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>res.noshow.mark</t>
+          <t>res.cancel, res.rate.override</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>Transition: Confirmed to No-show; A2</t>
+          <t>Transition: Confirmed to Cancelled</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>a confirmed booking whose arrival date is today</t>
+          <t>a booking inside the free-cancellation window</t>
         </is>
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
-          <t>staff mark it no-show, or the roll runs</t>
+          <t>staff cancel it</t>
         </is>
       </c>
       <c r="L37" s="10" t="inlineStr">
         <is>
-          <t>the booking is No-show, the fee is posted once and the room hold is released; a guest not yet due cannot be marked</t>
+          <t>one night's fee is posted to the folio; a cancellation outside the window is free; waiving the fee needs res.rate.override</t>
         </is>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
-          <t>mark_no_show, no_show_internal, roll_business_date</t>
+          <t>cancel_reservation</t>
         </is>
       </c>
       <c r="N37" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (5); 14_lifecycle (1)</t>
+          <t>13_reservations (8)</t>
         </is>
       </c>
       <c r="O37" s="10" t="inlineStr">
@@ -3602,7 +3626,7 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>RES-008</t>
+          <t>RES-007</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -3612,12 +3636,12 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>RES-03</t>
+          <t>RES-03, FO-01</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>Reinstate a cancelled or no-show booking when inventory allows.</t>
+          <t>No-show can be marked by hand or by the automatic roll, with the fee from the rate plan.</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
@@ -3627,7 +3651,7 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -3637,37 +3661,37 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>res.reinstate</t>
+          <t>res.noshow.mark</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>Transition: Cancelled/No-show to Confirmed</t>
+          <t>Transition: Confirmed to No-show; A2</t>
         </is>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>a cancelled booking with the room type still available</t>
+          <t>a confirmed booking whose arrival date is today</t>
         </is>
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
-          <t>a manager reinstates it with a reason</t>
+          <t>staff mark it no-show, or the roll runs</t>
         </is>
       </c>
       <c r="L38" s="10" t="inlineStr">
         <is>
-          <t>it is Confirmed again and its folio reopens; if the type is full it is refused</t>
+          <t>the booking is No-show, the fee is posted once and the room hold is released; a guest not yet due cannot be marked</t>
         </is>
       </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
-          <t>reinstate_reservation</t>
+          <t>mark_no_show, no_show_internal, roll_business_date</t>
         </is>
       </c>
       <c r="N38" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (2)</t>
+          <t>13_reservations (5); 14_lifecycle (1)</t>
         </is>
       </c>
       <c r="O38" s="10" t="inlineStr">
@@ -3680,7 +3704,7 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>RES-009</t>
+          <t>RES-008</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -3690,22 +3714,22 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>RES-02</t>
+          <t>RES-03</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Rate override needs its own permission and a reason, and is audited.</t>
+          <t>Reinstate a cancelled or no-show booking when inventory allows.</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>BR-015, BR-018</t>
+          <t>BR-004</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
@@ -3715,37 +3739,37 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>res.rate.override</t>
+          <t>res.reinstate</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>Rule: Reasons</t>
+          <t>Transition: Cancelled/No-show to Confirmed</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>a front desk officer without the permission</t>
+          <t>a cancelled booking with the room type still available</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>they set a custom rate</t>
+          <t>a manager reinstates it with a reason</t>
         </is>
       </c>
       <c r="L39" s="10" t="inlineStr">
         <is>
-          <t>the request is refused; a manager with a reason sets the rate and the override is audited</t>
+          <t>it is Confirmed again and its folio reopens; if the type is full it is refused</t>
         </is>
       </c>
       <c r="M39" s="10" t="inlineStr">
         <is>
-          <t>create_reservation, modify_reservation</t>
+          <t>reinstate_reservation</t>
         </is>
       </c>
       <c r="N39" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (3)</t>
+          <t>13_reservations (2)</t>
         </is>
       </c>
       <c r="O39" s="10" t="inlineStr">
@@ -3758,7 +3782,7 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>RES-010</t>
+          <t>RES-009</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -3773,12 +3797,12 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>A deposit rule on the rate plan sets the deposit required.</t>
+          <t>Rate override needs its own permission and a reason, and is audited.</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-015, BR-018</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
@@ -3793,37 +3817,37 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>res.deposit.request</t>
+          <t>res.rate.override</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Rule: Payments in R1</t>
+          <t>Rule: Reasons</t>
         </is>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>a rate plan asking for 50% deposit</t>
+          <t>a front desk officer without the permission</t>
         </is>
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>a two-night booking is made</t>
+          <t>they set a custom rate</t>
         </is>
       </c>
       <c r="L40" s="10" t="inlineStr">
         <is>
-          <t>the deposit required is half the stay and the guarantee type is deposit</t>
+          <t>the request is refused; a manager with a reason sets the rate and the override is audited</t>
         </is>
       </c>
       <c r="M40" s="10" t="inlineStr">
         <is>
-          <t>create_reservation</t>
+          <t>create_reservation, modify_reservation</t>
         </is>
       </c>
       <c r="N40" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>13_reservations (3)</t>
         </is>
       </c>
       <c r="O40" s="10" t="inlineStr">
@@ -3836,7 +3860,7 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>RES-011</t>
+          <t>RES-010</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -3851,12 +3875,12 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Corporate business is a booking source plus a free-text company name plus a corporate rate plan; no company entity in R1.</t>
+          <t>A deposit rule on the rate plan sets the deposit required.</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>BR-007, BR-024</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
@@ -3871,37 +3895,37 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>res.create</t>
+          <t>res.deposit.request</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>Rule: Payments in R1</t>
         </is>
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>a booking for a company</t>
+          <t>a rate plan asking for 50% deposit</t>
         </is>
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>staff choose source Corporate and type the company name</t>
+          <t>a two-night booking is made</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr">
         <is>
-          <t>the company name is saved with the booking and reports can filter on it</t>
+          <t>the deposit required is half the stay and the guarantee type is deposit</t>
         </is>
       </c>
       <c r="M41" s="10" t="inlineStr">
         <is>
-          <t>reservations.company_name, rate_plans.is_corporate</t>
+          <t>create_reservation</t>
         </is>
       </c>
       <c r="N41" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (2)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O41" s="10" t="inlineStr">
@@ -3914,7 +3938,7 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>RES-012</t>
+          <t>RES-011</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -3929,17 +3953,17 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>A group booking is several one-room reservations sharing a group record.</t>
+          <t>Corporate business is a booking source plus a free-text company name plus a corporate rate plan; no company entity in R1.</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>BR-007</t>
+          <t>BR-007, BR-024</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -3949,54 +3973,50 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>res.group.manage</t>
+          <t>res.create</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>a group with a contact and dates</t>
+          <t>a booking for a company</t>
         </is>
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>staff create reservations for the group</t>
+          <t>staff choose source Corporate and type the company name</t>
         </is>
       </c>
       <c r="L42" s="10" t="inlineStr">
         <is>
-          <t>each reservation links to the group; each room is booked and assigned on its own</t>
+          <t>the company name is saved with the booking and reports can filter on it</t>
         </is>
       </c>
       <c r="M42" s="10" t="inlineStr">
         <is>
-          <t>group_bookings, reservations.group_id</t>
+          <t>reservations.company_name, rate_plans.is_corporate</t>
         </is>
       </c>
       <c r="N42" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17_more_features (2)</t>
         </is>
       </c>
       <c r="O42" s="10" t="inlineStr">
         <is>
-          <t>Built (database only), no tagged test</t>
-        </is>
-      </c>
-      <c r="P42" s="10" t="inlineStr">
-        <is>
-          <t>save_group_booking exists and the booking form picks a group; there is no screen to create a group.</t>
-        </is>
-      </c>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>RES-013</t>
+          <t>RES-012</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
@@ -4006,17 +4026,17 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>RES-03</t>
+          <t>RES-02</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Additional guests and an arrival-ready flag on a booking.</t>
+          <t>A group booking is several one-room reservations sharing a group record.</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>BR-003</t>
+          <t>BR-007</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
@@ -4031,79 +4051,79 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>res.edit</t>
+          <t>res.group.manage</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>Rule: arrival-ready is a flag</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>a confirmed booking</t>
+          <t>a group with a contact and dates</t>
         </is>
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>staff add a second guest and set arrival-ready</t>
+          <t>staff create reservations for the group</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr">
         <is>
-          <t>both are saved; arrival-ready never changes the status</t>
+          <t>each reservation links to the group; each room is booked and assigned on its own</t>
         </is>
       </c>
       <c r="M43" s="10" t="inlineStr">
         <is>
-          <t>set_reservation_guests, set_arrival_ready</t>
+          <t>group_bookings, reservations.group_id</t>
         </is>
       </c>
       <c r="N43" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (2); 26_small_fixes (4)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="10" t="inlineStr">
         <is>
-          <t>Built+tested (database only)</t>
+          <t>Built (database only), no tagged test</t>
         </is>
       </c>
       <c r="P43" s="10" t="inlineStr">
         <is>
-          <t>set_arrival_ready exists; no screen shows the flag yet (skipped 6 Oct 2026).</t>
+          <t>save_group_booking exists and the booking form picks a group; there is no screen to create a group.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>FO-001</t>
+          <t>RES-013</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Front Office</t>
+          <t>Reservations</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>FO-01</t>
+          <t>RES-03</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>Arrivals due today or overdue, with guest, room type, guarantee and assigned room.</t>
+          <t>Additional guests and an arrival-ready flag on a booking.</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>BR-006</t>
+          <t>BR-003</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
@@ -4113,50 +4133,54 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>fo.board.view</t>
+          <t>res.edit</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: arrival-ready is a flag</t>
         </is>
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>a confirmed booking due today</t>
+          <t>a confirmed booking</t>
         </is>
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>staff open the board</t>
+          <t>staff add a second guest and set arrival-ready</t>
         </is>
       </c>
       <c r="L44" s="10" t="inlineStr">
         <is>
-          <t>it appears with the guest's name; after check-in it leaves the list</t>
+          <t>both are saved; arrival-ready never changes the status</t>
         </is>
       </c>
       <c r="M44" s="10" t="inlineStr">
         <is>
-          <t>v_arrivals</t>
+          <t>set_reservation_guests, set_arrival_ready</t>
         </is>
       </c>
       <c r="N44" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (2)</t>
+          <t>17_more_features (2); 26_small_fixes (4)</t>
         </is>
       </c>
       <c r="O44" s="10" t="inlineStr">
         <is>
-          <t>Built+tested</t>
-        </is>
-      </c>
-      <c r="P44" s="10" t="inlineStr"/>
+          <t>Built+tested (database only)</t>
+        </is>
+      </c>
+      <c r="P44" s="10" t="inlineStr">
+        <is>
+          <t>set_arrival_ready exists; no screen shows the flag yet (skipped 6 Oct 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>FO-002</t>
+          <t>FO-001</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -4171,7 +4195,7 @@
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>In-house guests with room, departure and balance; overdue departures flagged.</t>
+          <t>Arrivals due today or overdue, with guest, room type, guarantee and assigned room.</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
@@ -4201,7 +4225,7 @@
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>a guest in house</t>
+          <t>a confirmed booking due today</t>
         </is>
       </c>
       <c r="K45" s="10" t="inlineStr">
@@ -4211,17 +4235,17 @@
       </c>
       <c r="L45" s="10" t="inlineStr">
         <is>
-          <t>the guest appears with room number and balance</t>
+          <t>it appears with the guest's name; after check-in it leaves the list</t>
         </is>
       </c>
       <c r="M45" s="10" t="inlineStr">
         <is>
-          <t>v_in_house</t>
+          <t>v_arrivals</t>
         </is>
       </c>
       <c r="N45" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (1)</t>
+          <t>17_more_features (2)</t>
         </is>
       </c>
       <c r="O45" s="10" t="inlineStr">
@@ -4234,7 +4258,7 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>FO-003</t>
+          <t>FO-002</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -4244,17 +4268,17 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>FO-02</t>
+          <t>FO-01</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>Check-in guards: confirmed booking, arrival date reached, ID recorded, registration accepted, room ready and free, deposit paid.</t>
+          <t>In-house guests with room, departure and balance; overdue departures flagged.</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>BR-006, BR-011</t>
+          <t>BR-006</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
@@ -4269,54 +4293,50 @@
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>fo.checkin</t>
+          <t>fo.board.view</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>Transition: Confirmed to Checked In</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>a booking due today</t>
+          <t>a guest in house</t>
         </is>
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>staff check the guest in without ID, or into a dirty or occupied room, or without the deposit</t>
+          <t>staff open the board</t>
         </is>
       </c>
       <c r="L46" s="10" t="inlineStr">
         <is>
-          <t>each is refused with its own code; with everything in place the reservation is Checked In, the stay In-House and the room Occupied</t>
+          <t>the guest appears with room number and balance</t>
         </is>
       </c>
       <c r="M46" s="10" t="inlineStr">
         <is>
-          <t>check_in</t>
+          <t>v_in_house</t>
         </is>
       </c>
       <c r="N46" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (12); 27_medium_fixes (5); browser: medium-fixes</t>
+          <t>17_more_features (1)</t>
         </is>
       </c>
       <c r="O46" s="10" t="inlineStr">
         <is>
-          <t>Built+tested (known limit)</t>
-        </is>
-      </c>
-      <c r="P46" s="10" t="inlineStr">
-        <is>
-          <t>The check-in and walk-in screens force the registration card tick; a direct database call that omits it is not refused (decision 6 Oct 2026). Drawn signature later.</t>
-        </is>
-      </c>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>FO-004</t>
+          <t>FO-003</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -4331,12 +4351,12 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Walk-in check-in creates the booking and checks in in one step.</t>
+          <t>Check-in guards: confirmed booking, arrival date reached, ID recorded, registration accepted, room ready and free, deposit paid.</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>BR-006, BR-007</t>
+          <t>BR-006, BR-011</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
@@ -4351,50 +4371,54 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>fo.checkin.walkin</t>
+          <t>fo.checkin</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>Transition: (walk-in) to Checked In</t>
+          <t>Transition: Confirmed to Checked In</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>a free ready room</t>
+          <t>a booking due today</t>
         </is>
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>staff check in a walk-in guest</t>
+          <t>staff check the guest in without ID, or into a dirty or occupied room, or without the deposit</t>
         </is>
       </c>
       <c r="L47" s="10" t="inlineStr">
         <is>
-          <t>a confirmed walk-in booking is created and the guest is checked in</t>
+          <t>each is refused with its own code; with everything in place the reservation is Checked In, the stay In-House and the room Occupied</t>
         </is>
       </c>
       <c r="M47" s="10" t="inlineStr">
         <is>
-          <t>walk_in_check_in</t>
+          <t>check_in</t>
         </is>
       </c>
       <c r="N47" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (2)</t>
+          <t>13_reservations (12); 27_medium_fixes (5); browser: medium-fixes</t>
         </is>
       </c>
       <c r="O47" s="10" t="inlineStr">
         <is>
-          <t>Built+tested</t>
-        </is>
-      </c>
-      <c r="P47" s="10" t="inlineStr"/>
+          <t>Built+tested (known limit)</t>
+        </is>
+      </c>
+      <c r="P47" s="10" t="inlineStr">
+        <is>
+          <t>The check-in and walk-in screens force the registration card tick; a direct database call that omits it is not refused (decision 6 Oct 2026). Drawn signature later.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>FO-005</t>
+          <t>FO-004</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -4404,17 +4428,17 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>RES-03, FO-01</t>
+          <t>FO-02</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>Assign a room before arrival; two overlapping stays can never hold the same room.</t>
+          <t>Walk-in check-in creates the booking and checks in in one step.</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>BR-005</t>
+          <t>BR-006, BR-007</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
@@ -4429,32 +4453,32 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>fo.room.assign</t>
+          <t>fo.checkin.walkin</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>Transition: Room Assignment none to Held</t>
+          <t>Transition: (walk-in) to Checked In</t>
         </is>
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>a room held for a booking</t>
+          <t>a free ready room</t>
         </is>
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>staff assign it to an overlapping booking</t>
+          <t>staff check in a walk-in guest</t>
         </is>
       </c>
       <c r="L48" s="10" t="inlineStr">
         <is>
-          <t>the database refuses with E_ROOM_TAKEN; a room of the wrong type is refused with E_ROOM_TYPE</t>
+          <t>a confirmed walk-in booking is created and the guest is checked in</t>
         </is>
       </c>
       <c r="M48" s="10" t="inlineStr">
         <is>
-          <t>assign_room; exclusion constraint no_overlapping_room_use</t>
+          <t>walk_in_check_in</t>
         </is>
       </c>
       <c r="N48" s="10" t="inlineStr">
@@ -4472,7 +4496,7 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>FO-006</t>
+          <t>FO-005</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -4482,17 +4506,17 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>FO-04</t>
+          <t>RES-03, FO-01</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Move a guest to another room; the old room turns dirty with a turnover task; the stay and folio carry over.</t>
+          <t>Assign a room before arrival; two overlapping stays can never hold the same room.</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>BR-006, BR-010</t>
+          <t>BR-005</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
@@ -4507,37 +4531,37 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>fo.roommove</t>
+          <t>fo.room.assign</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>Transition: Room Assignment Active to Ended</t>
+          <t>Transition: Room Assignment none to Held</t>
         </is>
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>a guest in house and a ready room</t>
+          <t>a room held for a booking</t>
         </is>
       </c>
       <c r="K49" s="10" t="inlineStr">
         <is>
-          <t>staff move the guest with a reason</t>
+          <t>staff assign it to an overlapping booking</t>
         </is>
       </c>
       <c r="L49" s="10" t="inlineStr">
         <is>
-          <t>one active room at a time, old room dirty and vacant, new room occupied, task created; a dirty target is refused</t>
+          <t>the database refuses with E_ROOM_TAKEN; a room of the wrong type is refused with E_ROOM_TYPE</t>
         </is>
       </c>
       <c r="M49" s="10" t="inlineStr">
         <is>
-          <t>move_room</t>
+          <t>assign_room; exclusion constraint no_overlapping_room_use</t>
         </is>
       </c>
       <c r="N49" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (9)</t>
+          <t>13_reservations (2)</t>
         </is>
       </c>
       <c r="O49" s="10" t="inlineStr">
@@ -4550,7 +4574,7 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>FO-007</t>
+          <t>FO-006</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -4565,17 +4589,17 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>A move to a different room type reprices from tonight; a complimentary upgrade keeps the rate and needs its own permission.</t>
+          <t>Move a guest to another room; the old room turns dirty with a turnover task; the stay and folio carry over.</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>BR-006</t>
+          <t>BR-006, BR-010</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
@@ -4585,27 +4609,27 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>fo.roommove.complimentary</t>
+          <t>fo.roommove</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
-          <t>Transition: complimentary move</t>
+          <t>Transition: Room Assignment Active to Ended</t>
         </is>
       </c>
       <c r="J50" s="10" t="inlineStr">
         <is>
-          <t>a guest booked in a standard room</t>
+          <t>a guest in house and a ready room</t>
         </is>
       </c>
       <c r="K50" s="10" t="inlineStr">
         <is>
-          <t>a manager upgrades them free</t>
+          <t>staff move the guest with a reason</t>
         </is>
       </c>
       <c r="L50" s="10" t="inlineStr">
         <is>
-          <t>the booked rate stays but the night counts against deluxe inventory; a front desk officer is refused</t>
+          <t>one active room at a time, old room dirty and vacant, new room occupied, task created; a dirty target is refused</t>
         </is>
       </c>
       <c r="M50" s="10" t="inlineStr">
@@ -4615,7 +4639,7 @@
       </c>
       <c r="N50" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (1); 27_medium_fixes (13); browser: medium-fixes</t>
+          <t>13_reservations (9)</t>
         </is>
       </c>
       <c r="O50" s="10" t="inlineStr">
@@ -4623,16 +4647,12 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P50" s="10" t="inlineStr">
-        <is>
-          <t>Dearer room type: front desk charges the new rate; keeping it needs fo.upgrade.complimentary (SYSADMIN, GM, FOM), audited.</t>
-        </is>
-      </c>
+      <c r="P50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>FO-008</t>
+          <t>FO-007</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -4642,12 +4662,12 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>FO-01, RES-03</t>
+          <t>FO-04</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Extend or shorten a stay in house; extension checks inventory, the room and blocks.</t>
+          <t>A move to a different room type reprices from tonight; a complimentary upgrade keeps the rate and needs its own permission.</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
@@ -4657,7 +4677,7 @@
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
@@ -4667,37 +4687,37 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>fo.stay.extend</t>
+          <t>fo.roommove.complimentary</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>Transition: Stay extension</t>
+          <t>Transition: complimentary move</t>
         </is>
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>a guest in house and the room promised to another guest</t>
+          <t>a guest booked in a standard room</t>
         </is>
       </c>
       <c r="K51" s="10" t="inlineStr">
         <is>
-          <t>staff extend the stay</t>
+          <t>a manager upgrades them free</t>
         </is>
       </c>
       <c r="L51" s="10" t="inlineStr">
         <is>
-          <t>the extension is refused with E_ROOM_TAKEN; a free extension prices the new night; shortening removes unused nights</t>
+          <t>the booked rate stays but the night counts against deluxe inventory; a front desk officer is refused</t>
         </is>
       </c>
       <c r="M51" s="10" t="inlineStr">
         <is>
-          <t>extend_stay</t>
+          <t>move_room</t>
         </is>
       </c>
       <c r="N51" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (6); 26_small_fixes (7); browser: change-departure</t>
+          <t>13_reservations (1); 27_medium_fixes (13); browser: medium-fixes</t>
         </is>
       </c>
       <c r="O51" s="10" t="inlineStr">
@@ -4705,12 +4725,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P51" s="10" t="inlineStr"/>
+      <c r="P51" s="10" t="inlineStr">
+        <is>
+          <t>Dearer room type: front desk charges the new rate; keeping it needs fo.upgrade.complimentary (SYSADMIN, GM, FOM), audited.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>FO-009</t>
+          <t>FO-008</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -4720,17 +4744,17 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>FO-03</t>
+          <t>FO-01, RES-03</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Check-out needs a zero balance and no credit, or an approved exception; open folios stay open for collection.</t>
+          <t>Extend or shorten a stay in house; extension checks inventory, the room and blocks.</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>BR-006, BR-013</t>
+          <t>BR-006</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
@@ -4745,37 +4769,37 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>fo.checkout, fo.checkout.unsettled.approve</t>
+          <t>fo.stay.extend</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>Transition: In-House to Checked Out</t>
+          <t>Transition: Stay extension</t>
         </is>
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>a guest who owes money</t>
+          <t>a guest in house and the room promised to another guest</t>
         </is>
       </c>
       <c r="K52" s="10" t="inlineStr">
         <is>
-          <t>staff try to check them out</t>
+          <t>staff extend the stay</t>
         </is>
       </c>
       <c r="L52" s="10" t="inlineStr">
         <is>
-          <t>it is refused until a different person approves an exception; then the stay closes, the invoice shows the balance and the folio stays open; a credit balance must be refunded first</t>
+          <t>the extension is refused with E_ROOM_TAKEN; a free extension prices the new night; shortening removes unused nights</t>
         </is>
       </c>
       <c r="M52" s="10" t="inlineStr">
         <is>
-          <t>check_out, request_unsettled_checkout</t>
+          <t>extend_stay</t>
         </is>
       </c>
       <c r="N52" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (10)</t>
+          <t>13_reservations (6); 26_small_fixes (7); browser: change-departure</t>
         </is>
       </c>
       <c r="O52" s="10" t="inlineStr">
@@ -4788,7 +4812,7 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>FO-010</t>
+          <t>FO-009</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -4803,12 +4827,12 @@
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>Check-out sets the room Dirty and Vacant and creates a turnover task; leaving early releases the unused nights.</t>
+          <t>Check-out needs a zero balance and no credit, or an approved exception; open folios stay open for collection.</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>BR-010</t>
+          <t>BR-006, BR-013</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
@@ -4823,37 +4847,37 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>fo.checkout</t>
+          <t>fo.checkout, fo.checkout.unsettled.approve</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>Transition: Room Condition Ready to Dirty</t>
+          <t>Transition: In-House to Checked Out</t>
         </is>
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>a guest checks out</t>
+          <t>a guest who owes money</t>
         </is>
       </c>
       <c r="K53" s="10" t="inlineStr">
         <is>
-          <t>the check-out completes</t>
+          <t>staff try to check them out</t>
         </is>
       </c>
       <c r="L53" s="10" t="inlineStr">
         <is>
-          <t>the room is Dirty and Vacant, a turnover task exists, the folio closes and an invoice is issued</t>
+          <t>it is refused until a different person approves an exception; then the stay closes, the invoice shows the balance and the folio stays open; a credit balance must be refunded first</t>
         </is>
       </c>
       <c r="M53" s="10" t="inlineStr">
         <is>
-          <t>check_out, create_turnover_task</t>
+          <t>check_out, request_unsettled_checkout</t>
         </is>
       </c>
       <c r="N53" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (5)</t>
+          <t>13_reservations (10)</t>
         </is>
       </c>
       <c r="O53" s="10" t="inlineStr">
@@ -4866,7 +4890,7 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>FO-011</t>
+          <t>FO-010</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -4881,17 +4905,17 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Undo a check-out on the same business date.</t>
+          <t>Check-out sets the room Dirty and Vacant and creates a turnover task; leaving early releases the unused nights.</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>BR-006</t>
+          <t>BR-010</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -4901,32 +4925,32 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>fo.checkout.reverse</t>
+          <t>fo.checkout</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>Transition: Checked Out to Checked In</t>
+          <t>Transition: Room Condition Ready to Dirty</t>
         </is>
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>a guest checked out today and the room not yet being cleaned</t>
+          <t>a guest checks out</t>
         </is>
       </c>
       <c r="K54" s="10" t="inlineStr">
         <is>
-          <t>a manager undoes it with a reason</t>
+          <t>the check-out completes</t>
         </is>
       </c>
       <c r="L54" s="10" t="inlineStr">
         <is>
-          <t>the guest is in house, the room occupied, the task cancelled and the folio open; a front desk officer is refused</t>
+          <t>the room is Dirty and Vacant, a turnover task exists, the folio closes and an invoice is issued</t>
         </is>
       </c>
       <c r="M54" s="10" t="inlineStr">
         <is>
-          <t>undo_checkout</t>
+          <t>check_out, create_turnover_task</t>
         </is>
       </c>
       <c r="N54" s="10" t="inlineStr">
@@ -4944,7 +4968,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>FO-012</t>
+          <t>FO-011</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -4954,12 +4978,12 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>FO-02</t>
+          <t>FO-03</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>Void a check-in on the same business date when no charges are posted.</t>
+          <t>Undo a check-out on the same business date.</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
@@ -4984,32 +5008,32 @@
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
-          <t>Transition: Stay In-House to Voided</t>
+          <t>Transition: Checked Out to Checked In</t>
         </is>
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>a check-in made in error today</t>
+          <t>a guest checked out today and the room not yet being cleaned</t>
         </is>
       </c>
       <c r="K55" s="10" t="inlineStr">
         <is>
-          <t>a manager voids it with a reason</t>
+          <t>a manager undoes it with a reason</t>
         </is>
       </c>
       <c r="L55" s="10" t="inlineStr">
         <is>
-          <t>the stay is Voided, the booking Confirmed, the room vacant and held; the guest can be checked in again</t>
+          <t>the guest is in house, the room occupied, the task cancelled and the folio open; a front desk officer is refused</t>
         </is>
       </c>
       <c r="M55" s="10" t="inlineStr">
         <is>
-          <t>void_check_in</t>
+          <t>undo_checkout</t>
         </is>
       </c>
       <c r="N55" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (7)</t>
+          <t>13_reservations (5)</t>
         </is>
       </c>
       <c r="O55" s="10" t="inlineStr">
@@ -5022,7 +5046,7 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>FO-013</t>
+          <t>FO-012</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -5032,22 +5056,22 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>ROOM-01</t>
+          <t>FO-02</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Room board shows each room as occupied, vacant by condition, out of order or out of service.</t>
+          <t>Void a check-in on the same business date when no charges are posted.</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>BR-009</t>
+          <t>BR-006</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
@@ -5057,37 +5081,37 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>room.view</t>
+          <t>fo.checkout.reverse</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>Rule: Room condition vs sellability</t>
+          <t>Transition: Stay In-House to Voided</t>
         </is>
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>a guest in a room</t>
+          <t>a check-in made in error today</t>
         </is>
       </c>
       <c r="K56" s="10" t="inlineStr">
         <is>
-          <t>staff open the room board</t>
+          <t>a manager voids it with a reason</t>
         </is>
       </c>
       <c r="L56" s="10" t="inlineStr">
         <is>
-          <t>the room shows occupied</t>
+          <t>the stay is Voided, the booking Confirmed, the room vacant and held; the guest can be checked in again</t>
         </is>
       </c>
       <c r="M56" s="10" t="inlineStr">
         <is>
-          <t>v_room_board</t>
+          <t>void_check_in</t>
         </is>
       </c>
       <c r="N56" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (1)</t>
+          <t>17_more_features (7)</t>
         </is>
       </c>
       <c r="O56" s="10" t="inlineStr">
@@ -5100,27 +5124,27 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>GST-001</t>
+          <t>FO-013</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Guests</t>
+          <t>Front Office</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>GST-01, GST-02</t>
+          <t>ROOM-01</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>One guest profile per person across stays; search by name, phone, email or ID number.</t>
+          <t>Room board shows each room as occupied, vacant by condition, out of order or out of service.</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>BR-003, BR-008</t>
+          <t>BR-009</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
@@ -5135,37 +5159,37 @@
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>guest.view, guest.create, guest.edit</t>
+          <t>room.view</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Room condition vs sellability</t>
         </is>
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>guests exist</t>
+          <t>a guest in a room</t>
         </is>
       </c>
       <c r="K57" s="10" t="inlineStr">
         <is>
-          <t>front desk searches by surname</t>
+          <t>staff open the room board</t>
         </is>
       </c>
       <c r="L57" s="10" t="inlineStr">
         <is>
-          <t>the guest is found; a role without guest.view finds nothing</t>
+          <t>the room shows occupied</t>
         </is>
       </c>
       <c r="M57" s="10" t="inlineStr">
         <is>
-          <t>guests, search_guests</t>
+          <t>v_room_board</t>
         </is>
       </c>
       <c r="N57" s="10" t="inlineStr">
         <is>
-          <t>15_accounts (2)</t>
+          <t>17_more_features (1)</t>
         </is>
       </c>
       <c r="O57" s="10" t="inlineStr">
@@ -5178,7 +5202,7 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>GST-002</t>
+          <t>GST-001</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -5188,17 +5212,17 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>GST-02</t>
+          <t>GST-01, GST-02</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>ID documents are stored apart and shown only to roles that may see them.</t>
+          <t>One guest profile per person across stays; search by name, phone, email or ID number.</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>BR-017</t>
+          <t>BR-003, BR-008</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
@@ -5213,7 +5237,7 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>guest.idocs.view</t>
+          <t>guest.view, guest.create, guest.edit</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
@@ -5223,27 +5247,27 @@
       </c>
       <c r="J58" s="10" t="inlineStr">
         <is>
-          <t>a recorded passport number</t>
+          <t>guests exist</t>
         </is>
       </c>
       <c r="K58" s="10" t="inlineStr">
         <is>
-          <t>a reservation officer opens the guest</t>
+          <t>front desk searches by surname</t>
         </is>
       </c>
       <c r="L58" s="10" t="inlineStr">
         <is>
-          <t>they see the profile but no ID documents</t>
+          <t>the guest is found; a role without guest.view finds nothing</t>
         </is>
       </c>
       <c r="M58" s="10" t="inlineStr">
         <is>
-          <t>guest_documents policies</t>
+          <t>guests, search_guests</t>
         </is>
       </c>
       <c r="N58" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (2); 17_more_features (2); 24_id_photos (5)</t>
+          <t>15_accounts (2)</t>
         </is>
       </c>
       <c r="O58" s="10" t="inlineStr">
@@ -5256,7 +5280,7 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>GST-003</t>
+          <t>GST-002</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -5271,12 +5295,12 @@
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>Personal data never appears in audit records; only the names of changed fields do.</t>
+          <t>ID documents are stored apart and shown only to roles that may see them.</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>BR-018</t>
+          <t>BR-017</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
@@ -5291,37 +5315,37 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
+          <t>guest.idocs.view</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
-        <is>
-          <t>Rule: Personal data and the ledger</t>
-        </is>
-      </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>a phone number is changed</t>
+          <t>a recorded passport number</t>
         </is>
       </c>
       <c r="K59" s="10" t="inlineStr">
         <is>
-          <t>the audit trail is read</t>
+          <t>a reservation officer opens the guest</t>
         </is>
       </c>
       <c r="L59" s="10" t="inlineStr">
         <is>
-          <t>it says the phone changed, not what the number was</t>
+          <t>they see the profile but no ID documents</t>
         </is>
       </c>
       <c r="M59" s="10" t="inlineStr">
         <is>
-          <t>audit_change_pii</t>
+          <t>guest_documents policies</t>
         </is>
       </c>
       <c r="N59" s="10" t="inlineStr">
         <is>
-          <t>15_accounts (2)</t>
+          <t>13_reservations (2); 17_more_features (2); 24_id_photos (5)</t>
         </is>
       </c>
       <c r="O59" s="10" t="inlineStr">
@@ -5334,7 +5358,7 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>GST-004</t>
+          <t>GST-003</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -5349,17 +5373,17 @@
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Merge duplicate guest profiles; history moves to the kept profile.</t>
+          <t>Personal data never appears in audit records; only the names of changed fields do.</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>BR-003</t>
+          <t>BR-018</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
@@ -5369,37 +5393,37 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>guest.merge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Personal data and the ledger</t>
         </is>
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>two profiles for one person</t>
+          <t>a phone number is changed</t>
         </is>
       </c>
       <c r="K60" s="10" t="inlineStr">
         <is>
-          <t>a manager merges them with a reason</t>
+          <t>the audit trail is read</t>
         </is>
       </c>
       <c r="L60" s="10" t="inlineStr">
         <is>
-          <t>reservations and folios point to the kept profile and the duplicate is emptied</t>
+          <t>it says the phone changed, not what the number was</t>
         </is>
       </c>
       <c r="M60" s="10" t="inlineStr">
         <is>
-          <t>merge_guests</t>
+          <t>audit_change_pii</t>
         </is>
       </c>
       <c r="N60" s="10" t="inlineStr">
         <is>
-          <t>15_accounts (3)</t>
+          <t>15_accounts (2)</t>
         </is>
       </c>
       <c r="O60" s="10" t="inlineStr">
@@ -5412,7 +5436,7 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>GST-005</t>
+          <t>GST-004</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -5427,12 +5451,12 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>Anonymise a guest on request; the ledger and stay history stay intact.</t>
+          <t>Merge duplicate guest profiles; history moves to the kept profile.</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>BR-003, BR-014</t>
+          <t>BR-003</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
@@ -5452,32 +5476,32 @@
       </c>
       <c r="I61" s="10" t="inlineStr">
         <is>
-          <t>Rule: Personal data and the ledger</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>a guest with no current or upcoming stay</t>
+          <t>two profiles for one person</t>
         </is>
       </c>
       <c r="K61" s="10" t="inlineStr">
         <is>
-          <t>a manager anonymises them</t>
+          <t>a manager merges them with a reason</t>
         </is>
       </c>
       <c r="L61" s="10" t="inlineStr">
         <is>
-          <t>name, contact and documents are removed and cannot be restored from the app; reservations remain</t>
+          <t>reservations and folios point to the kept profile and the duplicate is emptied</t>
         </is>
       </c>
       <c r="M61" s="10" t="inlineStr">
         <is>
-          <t>anonymise_guest</t>
+          <t>merge_guests</t>
         </is>
       </c>
       <c r="N61" s="10" t="inlineStr">
         <is>
-          <t>15_accounts (8); upgrade (2)</t>
+          <t>15_accounts (3)</t>
         </is>
       </c>
       <c r="O61" s="10" t="inlineStr">
@@ -5490,7 +5514,7 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>GST-006</t>
+          <t>GST-005</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -5505,12 +5529,12 @@
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Feedback and complaints logged against a guest.</t>
+          <t>Anonymise a guest on request; the ledger and stay history stay intact.</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>BR-008</t>
+          <t>BR-003, BR-014</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
@@ -5525,42 +5549,42 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>guest.complaint.manage</t>
+          <t>guest.merge</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Personal data and the ledger</t>
         </is>
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>a guest complaint</t>
+          <t>a guest with no current or upcoming stay</t>
         </is>
       </c>
       <c r="K62" s="10" t="inlineStr">
         <is>
-          <t>staff log it</t>
+          <t>a manager anonymises them</t>
         </is>
       </c>
       <c r="L62" s="10" t="inlineStr">
         <is>
-          <t>it is saved with the guest and shown on the profile</t>
+          <t>name, contact and documents are removed and cannot be restored from the app; reservations remain</t>
         </is>
       </c>
       <c r="M62" s="10" t="inlineStr">
         <is>
-          <t>guest_feedback (direct write with RLS)</t>
+          <t>anonymise_guest</t>
         </is>
       </c>
       <c r="N62" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15_accounts (8); upgrade (2)</t>
         </is>
       </c>
       <c r="O62" s="10" t="inlineStr">
         <is>
-          <t>Built, no tagged test</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P62" s="10" t="inlineStr"/>
@@ -5568,32 +5592,32 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>ROOM-001</t>
+          <t>GST-006</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Rooms</t>
+          <t>Guests</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>ROOM-01, ROOM-02</t>
+          <t>GST-02</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>Room condition and occupancy are separate, are set only by the system or a controlled action, and cannot be written by hand.</t>
+          <t>Feedback and complaints logged against a guest.</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>BR-009</t>
+          <t>BR-008</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
@@ -5603,42 +5627,42 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>room.view</t>
+          <t>guest.complaint.manage</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>Rule: Room condition vs sellability</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>any user</t>
+          <t>a guest complaint</t>
         </is>
       </c>
       <c r="K63" s="10" t="inlineStr">
         <is>
-          <t>they try to update condition or occupancy directly</t>
+          <t>staff log it</t>
         </is>
       </c>
       <c r="L63" s="10" t="inlineStr">
         <is>
-          <t>the update is refused with permission denied</t>
+          <t>it is saved with the guest and shown on the profile</t>
         </is>
       </c>
       <c r="M63" s="10" t="inlineStr">
         <is>
-          <t>column grants; rooms</t>
+          <t>guest_feedback (direct write with RLS)</t>
         </is>
       </c>
       <c r="N63" s="10" t="inlineStr">
         <is>
-          <t>10_security (2)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="10" t="inlineStr">
         <is>
-          <t>Built+tested</t>
+          <t>Built, no tagged test</t>
         </is>
       </c>
       <c r="P63" s="10" t="inlineStr"/>
@@ -5646,7 +5670,7 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>ROOM-002</t>
+          <t>ROOM-001</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -5656,17 +5680,17 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>ROOM-03</t>
+          <t>ROOM-01, ROOM-02</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Out-of-order and out-of-service blocks; a request from maintenance needs approval, an approver's own request does not.</t>
+          <t>Room condition and occupancy are separate, are set only by the system or a controlled action, and cannot be written by hand.</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>BR-012</t>
+          <t>BR-009</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
@@ -5681,37 +5705,37 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>room.block.request, room.block.approve, room.block.release</t>
+          <t>room.view</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>Transition: Room Block</t>
+          <t>Rule: Room condition vs sellability</t>
         </is>
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>a maintenance officer requests a block</t>
+          <t>any user</t>
         </is>
       </c>
       <c r="K64" s="10" t="inlineStr">
         <is>
-          <t>a manager approves it</t>
+          <t>they try to update condition or occupancy directly</t>
         </is>
       </c>
       <c r="L64" s="10" t="inlineStr">
         <is>
-          <t>the room leaves availability for those nights; a requested block does not; releasing returns it</t>
+          <t>the update is refused with permission denied</t>
         </is>
       </c>
       <c r="M64" s="10" t="inlineStr">
         <is>
-          <t>request_room_block, decide_approval, release_room_block</t>
+          <t>column grants; rooms</t>
         </is>
       </c>
       <c r="N64" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (5)</t>
+          <t>10_security (2)</t>
         </is>
       </c>
       <c r="O64" s="10" t="inlineStr">
@@ -5724,7 +5748,7 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>ROOM-003</t>
+          <t>ROOM-002</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -5739,12 +5763,12 @@
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>A block cannot cover a night a guest is assigned, and cannot oversell the room type.</t>
+          <t>Out-of-order and out-of-service blocks; a request from maintenance needs approval, an approver's own request does not.</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>BR-005, BR-012</t>
+          <t>BR-012</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -5759,37 +5783,37 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>room.block.request</t>
+          <t>room.block.request, room.block.approve, room.block.release</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Transition: Room Block</t>
         </is>
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>a room assigned to a guest or the last room of a type</t>
+          <t>a maintenance officer requests a block</t>
         </is>
       </c>
       <c r="K65" s="10" t="inlineStr">
         <is>
-          <t>staff block it</t>
+          <t>a manager approves it</t>
         </is>
       </c>
       <c r="L65" s="10" t="inlineStr">
         <is>
-          <t>the block is refused with E_ROOM_TAKEN or E_OVERSOLD</t>
+          <t>the room leaves availability for those nights; a requested block does not; releasing returns it</t>
         </is>
       </c>
       <c r="M65" s="10" t="inlineStr">
         <is>
-          <t>request_room_block, assert_not_oversold</t>
+          <t>request_room_block, decide_approval, release_room_block</t>
         </is>
       </c>
       <c r="N65" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (1); 17_more_features (1)</t>
+          <t>14_lifecycle (5)</t>
         </is>
       </c>
       <c r="O65" s="10" t="inlineStr">
@@ -5802,7 +5826,7 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>ROOM-004</t>
+          <t>ROOM-003</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -5812,22 +5836,22 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>ROOM-02</t>
+          <t>ROOM-03</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>A supervisor can override a room's condition with a reason; it is audited.</t>
+          <t>A block cannot cover a night a guest is assigned, and cannot oversell the room type.</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>BR-018</t>
+          <t>BR-005, BR-012</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
@@ -5837,37 +5861,37 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>room.status.override</t>
+          <t>room.block.request</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
-          <t>Rule: Reasons</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>a dirty room a manager has inspected</t>
+          <t>a room assigned to a guest or the last room of a type</t>
         </is>
       </c>
       <c r="K66" s="10" t="inlineStr">
         <is>
-          <t>the manager marks it ready with a reason</t>
+          <t>staff block it</t>
         </is>
       </c>
       <c r="L66" s="10" t="inlineStr">
         <is>
-          <t>the room is Ready and the override is in the audit trail; front desk is refused</t>
+          <t>the block is refused with E_ROOM_TAKEN or E_OVERSOLD</t>
         </is>
       </c>
       <c r="M66" s="10" t="inlineStr">
         <is>
-          <t>set_room_condition</t>
+          <t>request_room_block, assert_not_oversold</t>
         </is>
       </c>
       <c r="N66" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (3); 26_small_fixes (1)</t>
+          <t>14_lifecycle (1); 17_more_features (1)</t>
         </is>
       </c>
       <c r="O66" s="10" t="inlineStr">
@@ -5880,32 +5904,32 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>HK-001</t>
+          <t>ROOM-004</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Housekeeping</t>
+          <t>Rooms</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>HK-01</t>
+          <t>ROOM-02</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>Check-out and room moves create a turnover task; the board lists open tasks.</t>
+          <t>A supervisor can override a room's condition with a reason; it is audited.</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>BR-010</t>
+          <t>BR-018</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
@@ -5915,37 +5939,37 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>hk.board.view</t>
+          <t>room.status.override</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
         <is>
-          <t>Transition: Ready to Dirty</t>
+          <t>Rule: Reasons</t>
         </is>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>a guest checks out</t>
+          <t>a dirty room a manager has inspected</t>
         </is>
       </c>
       <c r="K67" s="10" t="inlineStr">
         <is>
-          <t>the check-out completes</t>
+          <t>the manager marks it ready with a reason</t>
         </is>
       </c>
       <c r="L67" s="10" t="inlineStr">
         <is>
-          <t>a pending turnover task exists for the room; an older unfinished task is superseded</t>
+          <t>the room is Ready and the override is in the audit trail; front desk is refused</t>
         </is>
       </c>
       <c r="M67" s="10" t="inlineStr">
         <is>
-          <t>create_turnover_task, v_hk_board</t>
+          <t>set_room_condition</t>
         </is>
       </c>
       <c r="N67" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (3); 14_lifecycle (1)</t>
+          <t>14_lifecycle (3); 26_small_fixes (1)</t>
         </is>
       </c>
       <c r="O67" s="10" t="inlineStr">
@@ -5958,7 +5982,7 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>HK-002</t>
+          <t>HK-001</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -5968,12 +5992,12 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>HK-01, HK-02</t>
+          <t>HK-01</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Assign, start and complete cleaning tasks; an attendant sees only their own tasks.</t>
+          <t>Check-out and room moves create a turnover task; the board lists open tasks.</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
@@ -5993,37 +6017,37 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>hk.task.assign, hk.task.execute</t>
+          <t>hk.board.view</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>Transition: Dirty to Cleaning to Awaiting Inspection</t>
+          <t>Transition: Ready to Dirty</t>
         </is>
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
-          <t>a pending task</t>
+          <t>a guest checks out</t>
         </is>
       </c>
       <c r="K68" s="10" t="inlineStr">
         <is>
-          <t>a supervisor assigns it and the attendant starts and completes it</t>
+          <t>the check-out completes</t>
         </is>
       </c>
       <c r="L68" s="10" t="inlineStr">
         <is>
-          <t>the room goes Cleaning then Awaiting Inspection; an attendant cannot start another person's task</t>
+          <t>a pending turnover task exists for the room; an older unfinished task is superseded</t>
         </is>
       </c>
       <c r="M68" s="10" t="inlineStr">
         <is>
-          <t>assign_hk_task, start_hk_task, complete_hk_task</t>
+          <t>create_turnover_task, v_hk_board</t>
         </is>
       </c>
       <c r="N68" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (4); 17_more_features (2); 26_small_fixes (2)</t>
+          <t>13_reservations (3); 14_lifecycle (1)</t>
         </is>
       </c>
       <c r="O68" s="10" t="inlineStr">
@@ -6036,7 +6060,7 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>HK-003</t>
+          <t>HK-002</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -6046,17 +6070,17 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>HK-03</t>
+          <t>HK-01, HK-02</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>Inspection passes to Ready or fails with a reason and goes to rework.</t>
+          <t>Assign, start and complete cleaning tasks; an attendant sees only their own tasks.</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>BR-011</t>
+          <t>BR-010</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -6071,37 +6095,37 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>hk.inspect</t>
+          <t>hk.task.assign, hk.task.execute</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
         <is>
-          <t>Transition: Awaiting Inspection to Ready / Cleaning</t>
+          <t>Transition: Dirty to Cleaning to Awaiting Inspection</t>
         </is>
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>a completed task</t>
+          <t>a pending task</t>
         </is>
       </c>
       <c r="K69" s="10" t="inlineStr">
         <is>
-          <t>the inspector fails it with a reason</t>
+          <t>a supervisor assigns it and the attendant starts and completes it</t>
         </is>
       </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
-          <t>the room is Dirty, the task is in rework and the attendant is notified; a pass makes it Ready</t>
+          <t>the room goes Cleaning then Awaiting Inspection; an attendant cannot start another person's task</t>
         </is>
       </c>
       <c r="M69" s="10" t="inlineStr">
         <is>
-          <t>inspect_hk_task</t>
+          <t>assign_hk_task, start_hk_task, complete_hk_task</t>
         </is>
       </c>
       <c r="N69" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (5)</t>
+          <t>14_lifecycle (4); 17_more_features (2); 26_small_fixes (2)</t>
         </is>
       </c>
       <c r="O69" s="10" t="inlineStr">
@@ -6114,7 +6138,7 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>HK-004</t>
+          <t>HK-003</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -6129,12 +6153,12 @@
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Nobody inspects their own cleaning.</t>
+          <t>Inspection passes to Ready or fails with a reason and goes to rework.</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>BR-015</t>
+          <t>BR-011</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -6154,22 +6178,22 @@
       </c>
       <c r="I70" s="10" t="inlineStr">
         <is>
-          <t>Rule: Separation of duties</t>
+          <t>Transition: Awaiting Inspection to Ready / Cleaning</t>
         </is>
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
-          <t>a supervisor who cleaned a room</t>
+          <t>a completed task</t>
         </is>
       </c>
       <c r="K70" s="10" t="inlineStr">
         <is>
-          <t>they inspect it</t>
+          <t>the inspector fails it with a reason</t>
         </is>
       </c>
       <c r="L70" s="10" t="inlineStr">
         <is>
-          <t>it is refused with E_SOD</t>
+          <t>the room is Dirty, the task is in rework and the attendant is notified; a pass makes it Ready</t>
         </is>
       </c>
       <c r="M70" s="10" t="inlineStr">
@@ -6179,7 +6203,7 @@
       </c>
       <c r="N70" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (2)</t>
+          <t>14_lifecycle (5)</t>
         </is>
       </c>
       <c r="O70" s="10" t="inlineStr">
@@ -6192,7 +6216,7 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>HK-005</t>
+          <t>HK-004</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -6202,22 +6226,22 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>HK-01</t>
+          <t>HK-03</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>Stayover cleaning tasks are planned at the roll for guests staying on.</t>
+          <t>Nobody inspects their own cleaning.</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>BR-010</t>
+          <t>BR-015</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
@@ -6227,37 +6251,37 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>(system)</t>
+          <t>hk.inspect</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>Transition: stayover; Rule: Business date</t>
+          <t>Rule: Separation of duties</t>
         </is>
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>a guest in house who stays another night</t>
+          <t>a supervisor who cleaned a room</t>
         </is>
       </c>
       <c r="K71" s="10" t="inlineStr">
         <is>
-          <t>the roll runs</t>
+          <t>they inspect it</t>
         </is>
       </c>
       <c r="L71" s="10" t="inlineStr">
         <is>
-          <t>a stayover task exists for the new day; a departing guest gets none</t>
+          <t>it is refused with E_SOD</t>
         </is>
       </c>
       <c r="M71" s="10" t="inlineStr">
         <is>
-          <t>roll_business_date</t>
+          <t>inspect_hk_task</t>
         </is>
       </c>
       <c r="N71" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (1)</t>
+          <t>14_lifecycle (2)</t>
         </is>
       </c>
       <c r="O71" s="10" t="inlineStr">
@@ -6270,7 +6294,7 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>HK-006</t>
+          <t>HK-005</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -6280,17 +6304,17 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>(lost &amp; found)</t>
+          <t>HK-01</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Lost and found items are logged and tracked to return or disposal.</t>
+          <t>Stayover cleaning tasks are planned at the roll for guests staying on.</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-010</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -6305,37 +6329,37 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>hk.lostfound.manage</t>
+          <t>(system)</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Transition: stayover; Rule: Business date</t>
         </is>
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
-          <t>a found item</t>
+          <t>a guest in house who stays another night</t>
         </is>
       </c>
       <c r="K72" s="10" t="inlineStr">
         <is>
-          <t>housekeeping logs it</t>
+          <t>the roll runs</t>
         </is>
       </c>
       <c r="L72" s="10" t="inlineStr">
         <is>
-          <t>it is saved with room, date and status</t>
+          <t>a stayover task exists for the new day; a departing guest gets none</t>
         </is>
       </c>
       <c r="M72" s="10" t="inlineStr">
         <is>
-          <t>lost_found_items (direct write with RLS)</t>
+          <t>roll_business_date</t>
         </is>
       </c>
       <c r="N72" s="10" t="inlineStr">
         <is>
-          <t>16_structure (1)</t>
+          <t>14_lifecycle (1)</t>
         </is>
       </c>
       <c r="O72" s="10" t="inlineStr">
@@ -6348,32 +6372,32 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>MNT-001</t>
+          <t>HK-006</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Housekeeping</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>MNT-01, MNT-02</t>
+          <t>(lost &amp; found)</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>Tickets move from open to assigned, in progress, waiting, resolved and closed; waiting needs a reason.</t>
+          <t>Lost and found items are logged and tracked to return or disposal.</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>BR-012</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
@@ -6383,37 +6407,37 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>mnt.ticket.create, mnt.ticket.manage, mnt.ticket.work</t>
+          <t>hk.lostfound.manage</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>States: Maintenance Ticket</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>a ticket</t>
+          <t>a found item</t>
         </is>
       </c>
       <c r="K73" s="10" t="inlineStr">
         <is>
-          <t>it is assigned, started, paused with a reason, resumed and resolved</t>
+          <t>housekeeping logs it</t>
         </is>
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
-          <t>each step follows the allowed path and a ticket assigned to someone else cannot be started by another person</t>
+          <t>it is saved with room, date and status</t>
         </is>
       </c>
       <c r="M73" s="10" t="inlineStr">
         <is>
-          <t>create_ticket, assign_ticket, start_ticket, wait_ticket, resolve_ticket</t>
+          <t>lost_found_items (direct write with RLS)</t>
         </is>
       </c>
       <c r="N73" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (2)</t>
+          <t>16_structure (1)</t>
         </is>
       </c>
       <c r="O73" s="10" t="inlineStr">
@@ -6426,7 +6450,7 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>MNT-002</t>
+          <t>MNT-001</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -6436,17 +6460,17 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>MNT-02</t>
+          <t>MNT-01, MNT-02</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>The person who resolved a ticket cannot close it; closing releases its room block.</t>
+          <t>Tickets move from open to assigned, in progress, waiting, resolved and closed; waiting needs a reason.</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>BR-015, BR-012</t>
+          <t>BR-012</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -6461,37 +6485,37 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>mnt.ticket.close</t>
+          <t>mnt.ticket.create, mnt.ticket.manage, mnt.ticket.work</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>Rule: Separation of duties</t>
+          <t>States: Maintenance Ticket</t>
         </is>
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>a resolved ticket with a room block</t>
+          <t>a ticket</t>
         </is>
       </c>
       <c r="K74" s="10" t="inlineStr">
         <is>
-          <t>its resolver tries to close it, then a supervisor does</t>
+          <t>it is assigned, started, paused with a reason, resumed and resolved</t>
         </is>
       </c>
       <c r="L74" s="10" t="inlineStr">
         <is>
-          <t>the first is refused with E_SOD; the second closes it and releases the block</t>
+          <t>each step follows the allowed path and a ticket assigned to someone else cannot be started by another person</t>
         </is>
       </c>
       <c r="M74" s="10" t="inlineStr">
         <is>
-          <t>close_ticket</t>
+          <t>create_ticket, assign_ticket, start_ticket, wait_ticket, resolve_ticket</t>
         </is>
       </c>
       <c r="N74" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (4)</t>
+          <t>14_lifecycle (2)</t>
         </is>
       </c>
       <c r="O74" s="10" t="inlineStr">
@@ -6504,7 +6528,7 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>MNT-003</t>
+          <t>MNT-002</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -6519,17 +6543,17 @@
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>Tickets can be reopened or cancelled, each with a reason.</t>
+          <t>The person who resolved a ticket cannot close it; closing releases its room block.</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>BR-012</t>
+          <t>BR-015, BR-012</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
@@ -6539,37 +6563,37 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>mnt.ticket.manage, mnt.ticket.cancel</t>
+          <t>mnt.ticket.close</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>States: Maintenance Ticket</t>
+          <t>Rule: Separation of duties</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>a resolved ticket</t>
+          <t>a resolved ticket with a room block</t>
         </is>
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
-          <t>a maintenance officer reopens it or cancels it</t>
+          <t>its resolver tries to close it, then a supervisor does</t>
         </is>
       </c>
       <c r="L75" s="10" t="inlineStr">
         <is>
-          <t>the status changes and the reason is audited; housekeeping cannot cancel</t>
+          <t>the first is refused with E_SOD; the second closes it and releases the block</t>
         </is>
       </c>
       <c r="M75" s="10" t="inlineStr">
         <is>
-          <t>reopen_ticket, cancel_ticket</t>
+          <t>close_ticket</t>
         </is>
       </c>
       <c r="N75" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (4)</t>
+          <t>14_lifecycle (4)</t>
         </is>
       </c>
       <c r="O75" s="10" t="inlineStr">
@@ -6582,27 +6606,27 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>SVC-001</t>
+          <t>MNT-003</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>Guest Service</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>FO-01</t>
+          <t>MNT-02</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Guest requests are captured, assigned, progressed and completed.</t>
+          <t>Tickets can be reopened or cancelled, each with a reason.</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>BR-006</t>
+          <t>BR-012</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -6617,37 +6641,37 @@
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>svc.request.create, svc.request.manage</t>
+          <t>mnt.ticket.manage, mnt.ticket.cancel</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>Workflow WF05</t>
+          <t>States: Maintenance Ticket</t>
         </is>
       </c>
       <c r="J76" s="10" t="inlineStr">
         <is>
-          <t>a guest in house</t>
+          <t>a resolved ticket</t>
         </is>
       </c>
       <c r="K76" s="10" t="inlineStr">
         <is>
-          <t>staff log a request and it is assigned, started and completed</t>
+          <t>a maintenance officer reopens it or cancels it</t>
         </is>
       </c>
       <c r="L76" s="10" t="inlineStr">
         <is>
-          <t>it is tied to the guest's room and finishes once</t>
+          <t>the status changes and the reason is audited; housekeeping cannot cancel</t>
         </is>
       </c>
       <c r="M76" s="10" t="inlineStr">
         <is>
-          <t>create_service_request, assign_service_request, start_service_request, complete_service_request</t>
+          <t>reopen_ticket, cancel_ticket</t>
         </is>
       </c>
       <c r="N76" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (3)</t>
+          <t>17_more_features (4)</t>
         </is>
       </c>
       <c r="O76" s="10" t="inlineStr">
@@ -6660,7 +6684,7 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>SVC-002</t>
+          <t>SVC-001</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -6670,17 +6694,17 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>FO-01, FIN-01</t>
+          <t>FO-01</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>A chargeable request posts its charge, with tax, to the folio when completed.</t>
+          <t>Guest requests are captured, assigned, progressed and completed.</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-006</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
@@ -6695,7 +6719,7 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>svc.request.manage, fin.charge.post</t>
+          <t>svc.request.create, svc.request.manage</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
@@ -6705,22 +6729,22 @@
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>a chargeable laundry request of 3,000</t>
+          <t>a guest in house</t>
         </is>
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>it is completed</t>
+          <t>staff log a request and it is assigned, started and completed</t>
         </is>
       </c>
       <c r="L77" s="10" t="inlineStr">
         <is>
-          <t>3,000 plus tax is posted once to the guest's folio</t>
+          <t>it is tied to the guest's room and finishes once</t>
         </is>
       </c>
       <c r="M77" s="10" t="inlineStr">
         <is>
-          <t>complete_service_request</t>
+          <t>create_service_request, assign_service_request, start_service_request, complete_service_request</t>
         </is>
       </c>
       <c r="N77" s="10" t="inlineStr">
@@ -6738,22 +6762,22 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>FIN-001</t>
+          <t>SVC-002</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Guest Service</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>FIN-01</t>
+          <t>FO-01, FIN-01</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Charges post with their tax lines; prices can include or exclude tax; the remainder of a rounding goes on the last tax line.</t>
+          <t>A chargeable request posts its charge, with tax, to the folio when completed.</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
@@ -6763,7 +6787,7 @@
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
@@ -6773,37 +6797,37 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>fin.charge.post</t>
+          <t>svc.request.manage, fin.charge.post</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
         <is>
-          <t>Rule: Business date</t>
+          <t>Workflow WF05</t>
         </is>
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>service charge 10% and VAT 7.5%</t>
+          <t>a chargeable laundry request of 3,000</t>
         </is>
       </c>
       <c r="K78" s="10" t="inlineStr">
         <is>
-          <t>a charge of 10,000 or an inclusive 11,825 is posted</t>
+          <t>it is completed</t>
         </is>
       </c>
       <c r="L78" s="10" t="inlineStr">
         <is>
-          <t>the folio owes 11,825 with a net of 10,000 either way</t>
+          <t>3,000 plus tax is posted once to the guest's folio</t>
         </is>
       </c>
       <c r="M78" s="10" t="inlineStr">
         <is>
-          <t>post_charge, compute_taxes, insert_with_tax</t>
+          <t>complete_service_request</t>
         </is>
       </c>
       <c r="N78" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (6)</t>
+          <t>17_more_features (3)</t>
         </is>
       </c>
       <c r="O78" s="10" t="inlineStr">
@@ -6816,7 +6840,7 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>FIN-002</t>
+          <t>FIN-001</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
@@ -6831,7 +6855,7 @@
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>Payments and deposits are recorded against a folio with a method; payments are taken outside the system in R1.</t>
+          <t>Charges post with their tax lines; prices can include or exclude tax; the remainder of a rounding goes on the last tax line.</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
@@ -6851,37 +6875,37 @@
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>fin.payment.post, fin.deposit.take</t>
+          <t>fin.charge.post</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
         <is>
-          <t>Rule: Payments in R1</t>
+          <t>Rule: Business date</t>
         </is>
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>a folio with a balance</t>
+          <t>service charge 10% and VAT 7.5%</t>
         </is>
       </c>
       <c r="K79" s="10" t="inlineStr">
         <is>
-          <t>staff record a cash payment or a deposit</t>
+          <t>a charge of 10,000 or an inclusive 11,825 is posted</t>
         </is>
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
-          <t>the balance falls; a role without the matching permission is refused</t>
+          <t>the folio owes 11,825 with a net of 10,000 either way</t>
         </is>
       </c>
       <c r="M79" s="10" t="inlineStr">
         <is>
-          <t>post_payment</t>
+          <t>post_charge, compute_taxes, insert_with_tax</t>
         </is>
       </c>
       <c r="N79" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>12_ledger (6)</t>
         </is>
       </c>
       <c r="O79" s="10" t="inlineStr">
@@ -6894,7 +6918,7 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>FIN-003</t>
+          <t>FIN-002</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
@@ -6909,7 +6933,7 @@
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Foreign-currency postings store the amount, currency, exchange rate and base amount.</t>
+          <t>Payments and deposits are recorded against a folio with a method; payments are taken outside the system in R1.</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
@@ -6919,7 +6943,7 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
@@ -6929,32 +6953,32 @@
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>fin.payment.post</t>
+          <t>fin.payment.post, fin.deposit.take</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
-          <t>Rule: Multi-currency</t>
+          <t>Rule: Payments in R1</t>
         </is>
       </c>
       <c r="J80" s="10" t="inlineStr">
         <is>
-          <t>USD 10 at 1,500</t>
+          <t>a folio with a balance</t>
         </is>
       </c>
       <c r="K80" s="10" t="inlineStr">
         <is>
-          <t>it is posted</t>
+          <t>staff record a cash payment or a deposit</t>
         </is>
       </c>
       <c r="L80" s="10" t="inlineStr">
         <is>
-          <t>the row shows the rate and 15,000 in the base currency; the amount must respect the currency's decimals</t>
+          <t>the balance falls; a role without the matching permission is refused</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr">
         <is>
-          <t>insert_txn, fx_rate</t>
+          <t>post_payment</t>
         </is>
       </c>
       <c r="N80" s="10" t="inlineStr">
@@ -6972,7 +6996,7 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>FIN-004</t>
+          <t>FIN-003</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
@@ -6987,17 +7011,17 @@
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>A discount within the user's limit posts at once; above the limit it waits for an approver who is not the requester.</t>
+          <t>Foreign-currency postings store the amount, currency, exchange rate and base amount.</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>BR-015</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
@@ -7007,37 +7031,37 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>fin.discount.apply, fin.discount.approve</t>
+          <t>fin.payment.post</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
         <is>
-          <t>Rule: Limits; Separation of duties</t>
+          <t>Rule: Multi-currency</t>
         </is>
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>a front desk limit of 5,000</t>
+          <t>USD 10 at 1,500</t>
         </is>
       </c>
       <c r="K81" s="10" t="inlineStr">
         <is>
-          <t>they apply 3,000 then 8,000</t>
+          <t>it is posted</t>
         </is>
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>the first posts; the second is pending, does not change the balance and can be approved or rejected (with a reason) by a manager</t>
+          <t>the row shows the rate and 15,000 in the base currency; the amount must respect the currency's decimals</t>
         </is>
       </c>
       <c r="M81" s="10" t="inlineStr">
         <is>
-          <t>apply_discount, decide_approval</t>
+          <t>insert_txn, fx_rate</t>
         </is>
       </c>
       <c r="N81" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (6)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O81" s="10" t="inlineStr">
@@ -7050,7 +7074,7 @@
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>FIN-005</t>
+          <t>FIN-004</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -7065,7 +7089,7 @@
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>Adjustments, reversals and refunds always need a second person and stay within the approver's limit.</t>
+          <t>A discount within the user's limit posts at once; above the limit it waits for an approver who is not the requester.</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
@@ -7085,37 +7109,37 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>fin.adjust.post, fin.adjust.approve, fin.reverse.post, fin.refund.post, fin.refund.approve</t>
+          <t>fin.discount.apply, fin.discount.approve</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
         <is>
-          <t>Rule: Separation of duties, Limits</t>
+          <t>Rule: Limits; Separation of duties</t>
         </is>
       </c>
       <c r="J82" s="10" t="inlineStr">
         <is>
-          <t>an adjustment of 50,000 requested by a cashier</t>
+          <t>a front desk limit of 5,000</t>
         </is>
       </c>
       <c r="K82" s="10" t="inlineStr">
         <is>
-          <t>a manager with a 20,000 limit approves</t>
+          <t>they apply 3,000 then 8,000</t>
         </is>
       </c>
       <c r="L82" s="10" t="inlineStr">
         <is>
-          <t>it is refused with E_LIMIT; a senior approver can; nobody approves their own request</t>
+          <t>the first posts; the second is pending, does not change the balance and can be approved or rejected (with a reason) by a manager</t>
         </is>
       </c>
       <c r="M82" s="10" t="inlineStr">
         <is>
-          <t>request_adjustment, request_reversal, request_refund, decide_approval; check constraint approver_is_not_requester</t>
+          <t>apply_discount, decide_approval</t>
         </is>
       </c>
       <c r="N82" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>12_ledger (6)</t>
         </is>
       </c>
       <c r="O82" s="10" t="inlineStr">
@@ -7128,7 +7152,7 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>FIN-006</t>
+          <t>FIN-005</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -7143,12 +7167,12 @@
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>A posted transaction is never edited or deleted; corrections are linked reversal, adjustment or refund rows.</t>
+          <t>Adjustments, reversals and refunds always need a second person and stay within the approver's limit.</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>BR-014, BR-015</t>
+          <t>BR-015</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
@@ -7163,37 +7187,37 @@
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fin.adjust.post, fin.adjust.approve, fin.reverse.post, fin.refund.post, fin.refund.approve</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
         <is>
-          <t>Rule: Immutability</t>
+          <t>Rule: Separation of duties, Limits</t>
         </is>
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>a posted charge</t>
+          <t>an adjustment of 50,000 requested by a cashier</t>
         </is>
       </c>
       <c r="K83" s="10" t="inlineStr">
         <is>
-          <t>anyone, including the database owner, changes or deletes it</t>
+          <t>a manager with a 20,000 limit approves</t>
         </is>
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>the change is refused with E_IMMUTABLE; a reversal posts a linked row (with its tax lines) and a charge reverses only once</t>
+          <t>it is refused with E_LIMIT; a senior approver can; nobody approves their own request</t>
         </is>
       </c>
       <c r="M83" s="10" t="inlineStr">
         <is>
-          <t>txn_guard triggers; request_reversal</t>
+          <t>request_adjustment, request_reversal, request_refund, decide_approval; check constraint approver_is_not_requester</t>
         </is>
       </c>
       <c r="N83" s="10" t="inlineStr">
         <is>
-          <t>10_security (1); 12_ledger (13)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O83" s="10" t="inlineStr">
@@ -7206,7 +7230,7 @@
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>FIN-007</t>
+          <t>FIN-006</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -7221,12 +7245,12 @@
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>A refund cannot exceed the credit on the folio.</t>
+          <t>A posted transaction is never edited or deleted; corrections are linked reversal, adjustment or refund rows.</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>BR-015</t>
+          <t>BR-014, BR-015</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
@@ -7241,37 +7265,37 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>fin.refund.post</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Immutability</t>
         </is>
       </c>
       <c r="J84" s="10" t="inlineStr">
         <is>
-          <t>a folio with a small credit</t>
+          <t>a posted charge</t>
         </is>
       </c>
       <c r="K84" s="10" t="inlineStr">
         <is>
-          <t>staff request a bigger refund</t>
+          <t>anyone, including the database owner, changes or deletes it</t>
         </is>
       </c>
       <c r="L84" s="10" t="inlineStr">
         <is>
-          <t>it is refused with E_REFUND_LIMIT; a refund within the credit is approved and pays out</t>
+          <t>the change is refused with E_IMMUTABLE; a reversal posts a linked row (with its tax lines) and a charge reverses only once</t>
         </is>
       </c>
       <c r="M84" s="10" t="inlineStr">
         <is>
-          <t>request_refund</t>
+          <t>txn_guard triggers; request_reversal</t>
         </is>
       </c>
       <c r="N84" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>10_security (1); 12_ledger (13)</t>
         </is>
       </c>
       <c r="O84" s="10" t="inlineStr">
@@ -7284,7 +7308,7 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>FIN-008</t>
+          <t>FIN-007</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
@@ -7299,12 +7323,12 @@
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>Repeating the same request cannot double post (idempotency keys).</t>
+          <t>A refund cannot exceed the credit on the folio.</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-015</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
@@ -7319,32 +7343,32 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
+          <t>fin.refund.post</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>Rule: Offline-ready design; A12</t>
-        </is>
-      </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>a charge posted with a key</t>
+          <t>a folio with a small credit</t>
         </is>
       </c>
       <c r="K85" s="10" t="inlineStr">
         <is>
-          <t>the same request arrives again</t>
+          <t>staff request a bigger refund</t>
         </is>
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>the second returns the first and the balance is unchanged</t>
+          <t>it is refused with E_REFUND_LIMIT; a refund within the credit is approved and pays out</t>
         </is>
       </c>
       <c r="M85" s="10" t="inlineStr">
         <is>
-          <t>idempotency_key unique per tenant</t>
+          <t>request_refund</t>
         </is>
       </c>
       <c r="N85" s="10" t="inlineStr">
@@ -7362,7 +7386,7 @@
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>FIN-009</t>
+          <t>FIN-008</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
@@ -7377,7 +7401,7 @@
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Move a posted charge, with its tax, to another folio of the same booking; revenue does not change.</t>
+          <t>Repeating the same request cannot double post (idempotency keys).</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
@@ -7387,7 +7411,7 @@
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
@@ -7397,37 +7421,37 @@
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>fin.folio.transfer</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Offline-ready design; A12</t>
         </is>
       </c>
       <c r="J86" s="10" t="inlineStr">
         <is>
-          <t>a charge on the guest folio</t>
+          <t>a charge posted with a key</t>
         </is>
       </c>
       <c r="K86" s="10" t="inlineStr">
         <is>
-          <t>a manager transfers it to a company folio</t>
+          <t>the same request arrives again</t>
         </is>
       </c>
       <c r="L86" s="10" t="inlineStr">
         <is>
-          <t>the target owes the charge and tax, the source is relieved, the total is unchanged and the charge moves once</t>
+          <t>the second returns the first and the balance is unchanged</t>
         </is>
       </c>
       <c r="M86" s="10" t="inlineStr">
         <is>
-          <t>transfer_transaction</t>
+          <t>idempotency_key unique per tenant</t>
         </is>
       </c>
       <c r="N86" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (6)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O86" s="10" t="inlineStr">
@@ -7440,7 +7464,7 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>FIN-010</t>
+          <t>FIN-009</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
@@ -7455,7 +7479,7 @@
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Split folios per reservation.</t>
+          <t>Move a posted charge, with its tax, to another folio of the same booking; revenue does not change.</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
@@ -7475,7 +7499,7 @@
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>fin.folio.split</t>
+          <t>fin.folio.transfer</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
@@ -7485,27 +7509,27 @@
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>a reservation</t>
+          <t>a charge on the guest folio</t>
         </is>
       </c>
       <c r="K87" s="10" t="inlineStr">
         <is>
-          <t>staff add a Company folio</t>
+          <t>a manager transfers it to a company folio</t>
         </is>
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>charges can be posted to either folio and check-out settles both</t>
+          <t>the target owes the charge and tax, the source is relieved, the total is unchanged and the charge moves once</t>
         </is>
       </c>
       <c r="M87" s="10" t="inlineStr">
         <is>
-          <t>split_folio</t>
+          <t>transfer_transaction</t>
         </is>
       </c>
       <c r="N87" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (1)</t>
+          <t>12_ledger (6)</t>
         </is>
       </c>
       <c r="O87" s="10" t="inlineStr">
@@ -7518,7 +7542,7 @@
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>FIN-011</t>
+          <t>FIN-010</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -7533,17 +7557,17 @@
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>A folio closes only at a zero balance and reopens only for the accountant with a reason; a closed folio takes no postings.</t>
+          <t>Split folios per reservation.</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>BR-013, BR-015</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
@@ -7553,37 +7577,37 @@
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>fin.invoice.issue, fin.folio.reopen</t>
+          <t>fin.folio.split</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
         <is>
-          <t>Rule: Reasons</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J88" s="10" t="inlineStr">
         <is>
-          <t>a settled folio</t>
+          <t>a reservation</t>
         </is>
       </c>
       <c r="K88" s="10" t="inlineStr">
         <is>
-          <t>it is closed and then a posting is attempted</t>
+          <t>staff add a Company folio</t>
         </is>
       </c>
       <c r="L88" s="10" t="inlineStr">
         <is>
-          <t>the posting is refused with E_FOLIO_CLOSED; reopening needs the permission and a reason and is audited</t>
+          <t>charges can be posted to either folio and check-out settles both</t>
         </is>
       </c>
       <c r="M88" s="10" t="inlineStr">
         <is>
-          <t>close_folio, reopen_folio</t>
+          <t>split_folio</t>
         </is>
       </c>
       <c r="N88" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (5)</t>
+          <t>12_ledger (1)</t>
         </is>
       </c>
       <c r="O88" s="10" t="inlineStr">
@@ -7596,7 +7620,7 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>FIN-012</t>
+          <t>FIN-011</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
@@ -7606,17 +7630,17 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>FIN-01, FO-03</t>
+          <t>FIN-01</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>Invoices and receipts are numbered documents built from posted rows; they cannot be changed once issued.</t>
+          <t>A folio closes only at a zero balance and reopens only for the accountant with a reason; a closed folio takes no postings.</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-013, BR-015</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
@@ -7631,12 +7655,12 @@
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>fin.invoice.issue</t>
+          <t>fin.invoice.issue, fin.folio.reopen</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Reasons</t>
         </is>
       </c>
       <c r="J89" s="10" t="inlineStr">
@@ -7646,22 +7670,22 @@
       </c>
       <c r="K89" s="10" t="inlineStr">
         <is>
-          <t>an invoice is issued</t>
+          <t>it is closed and then a posting is attempted</t>
         </is>
       </c>
       <c r="L89" s="10" t="inlineStr">
         <is>
-          <t>the total, tax and balance match the folio and the invoice cannot be edited; interim receipts have their own number series</t>
+          <t>the posting is refused with E_FOLIO_CLOSED; reopening needs the permission and a reason and is audited</t>
         </is>
       </c>
       <c r="M89" s="10" t="inlineStr">
         <is>
-          <t>issue_invoice</t>
+          <t>close_folio, reopen_folio</t>
         </is>
       </c>
       <c r="N89" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (4); 17_more_features (4)</t>
+          <t>12_ledger (5)</t>
         </is>
       </c>
       <c r="O89" s="10" t="inlineStr">
@@ -7674,7 +7698,7 @@
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>FIN-013</t>
+          <t>FIN-012</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -7684,12 +7708,12 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>FIN-01</t>
+          <t>FIN-01, FO-03</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Balances are calculated from posted rows and never stored; pending approvals do not change them.</t>
+          <t>Invoices and receipts are numbered documents built from posted rows; they cannot be changed once issued.</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
@@ -7709,37 +7733,37 @@
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>fin.folio.view</t>
+          <t>fin.invoice.issue</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
         <is>
-          <t>Rule: Immutability</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J90" s="10" t="inlineStr">
         <is>
-          <t>a pending discount</t>
+          <t>a settled folio</t>
         </is>
       </c>
       <c r="K90" s="10" t="inlineStr">
         <is>
-          <t>the balance is read</t>
+          <t>an invoice is issued</t>
         </is>
       </c>
       <c r="L90" s="10" t="inlineStr">
         <is>
-          <t>it is unchanged until the approval posts</t>
+          <t>the total, tax and balance match the folio and the invoice cannot be edited; interim receipts have their own number series</t>
         </is>
       </c>
       <c r="M90" s="10" t="inlineStr">
         <is>
-          <t>v_folio_balances</t>
+          <t>issue_invoice</t>
         </is>
       </c>
       <c r="N90" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>12_ledger (4); 17_more_features (4)</t>
         </is>
       </c>
       <c r="O90" s="10" t="inlineStr">
@@ -7752,7 +7776,7 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>FIN-014</t>
+          <t>FIN-013</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
@@ -7767,7 +7791,7 @@
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>Every posting takes the open business date, and a past date is refused.</t>
+          <t>Balances are calculated from posted rows and never stored; pending approvals do not change them.</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
@@ -7787,37 +7811,37 @@
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fin.folio.view</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
         <is>
-          <t>Rule: Business date</t>
+          <t>Rule: Immutability</t>
         </is>
       </c>
       <c r="J91" s="10" t="inlineStr">
         <is>
-          <t>a posting for a past date</t>
+          <t>a pending discount</t>
         </is>
       </c>
       <c r="K91" s="10" t="inlineStr">
         <is>
-          <t>it is inserted</t>
+          <t>the balance is read</t>
         </is>
       </c>
       <c r="L91" s="10" t="inlineStr">
         <is>
-          <t>it is refused with E_DATE</t>
+          <t>it is unchanged until the approval posts</t>
         </is>
       </c>
       <c r="M91" s="10" t="inlineStr">
         <is>
-          <t>txn_guard</t>
+          <t>v_folio_balances</t>
         </is>
       </c>
       <c r="N91" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2); 14_lifecycle (1); upgrade (2)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O91" s="10" t="inlineStr">
@@ -7830,7 +7854,7 @@
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>FIN-015</t>
+          <t>FIN-014</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -7845,12 +7869,12 @@
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Folio visibility follows the role: managers see all folios, a reservation officer sees only those of their own bookings.</t>
+          <t>Every posting takes the open business date, and a past date is refused.</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>BR-017</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
@@ -7865,37 +7889,37 @@
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>fin.folio.view</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr">
         <is>
-          <t>Own-record scope</t>
+          <t>Rule: Business date</t>
         </is>
       </c>
       <c r="J92" s="10" t="inlineStr">
         <is>
-          <t>a reservation officer</t>
+          <t>a posting for a past date</t>
         </is>
       </c>
       <c r="K92" s="10" t="inlineStr">
         <is>
-          <t>they read a colleague's folio</t>
+          <t>it is inserted</t>
         </is>
       </c>
       <c r="L92" s="10" t="inlineStr">
         <is>
-          <t>they see nothing; they can still take a deposit</t>
+          <t>it is refused with E_DATE</t>
         </is>
       </c>
       <c r="M92" s="10" t="inlineStr">
         <is>
-          <t>can_see_folio</t>
+          <t>txn_guard</t>
         </is>
       </c>
       <c r="N92" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (6)</t>
+          <t>12_ledger (2); 14_lifecycle (1); upgrade (2)</t>
         </is>
       </c>
       <c r="O92" s="10" t="inlineStr">
@@ -7908,7 +7932,7 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>FIN-016</t>
+          <t>FIN-015</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
@@ -7918,67 +7942,67 @@
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>FIN-02</t>
+          <t>FIN-01</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>Cashier shifts and reconciliation by cashier, shift and method.</t>
+          <t>Folio visibility follows the role: managers see all folios, a reservation officer sees only those of their own bookings.</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
-          <t>BR-016</t>
+          <t>BR-017</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G93" s="10" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>fin.shift.manage, fin.shift.reconcile</t>
+          <t>fin.folio.view</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Own-record scope</t>
         </is>
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
-          <t>a cashier shift</t>
+          <t>a reservation officer</t>
         </is>
       </c>
       <c r="K93" s="10" t="inlineStr">
         <is>
-          <t>the shift is closed</t>
+          <t>they read a colleague's folio</t>
         </is>
       </c>
       <c r="L93" s="10" t="inlineStr">
         <is>
-          <t>payments reconcile by method</t>
+          <t>they see nothing; they can still take a deposit</t>
         </is>
       </c>
       <c r="M93" s="10" t="inlineStr">
         <is>
-          <t>(not in R1)</t>
+          <t>can_see_folio</t>
         </is>
       </c>
       <c r="N93" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12_ledger (6)</t>
         </is>
       </c>
       <c r="O93" s="10" t="inlineStr">
         <is>
-          <t>R1b</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P93" s="10" t="inlineStr"/>
@@ -7986,77 +8010,77 @@
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>DAY-001</t>
+          <t>FIN-016</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Business Date</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>(system)</t>
+          <t>FIN-02</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>The business date rolls automatically at each property's cut-off time.</t>
+          <t>Cashier shifts and reconciliation by cashier, shift and method.</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>BR-019</t>
+          <t>BR-016</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>audit.businessdate.view</t>
+          <t>fin.shift.manage, fin.shift.reconcile</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
         <is>
-          <t>Rule: Business date; A2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J94" s="10" t="inlineStr">
         <is>
-          <t>a property whose cut-off has passed</t>
+          <t>a cashier shift</t>
         </is>
       </c>
       <c r="K94" s="10" t="inlineStr">
         <is>
-          <t>the scheduler runs</t>
+          <t>the shift is closed</t>
         </is>
       </c>
       <c r="L94" s="10" t="inlineStr">
         <is>
-          <t>the date advances one day, up to three days per run; the roll is logged</t>
+          <t>payments reconcile by method</t>
         </is>
       </c>
       <c r="M94" s="10" t="inlineStr">
         <is>
-          <t>roll_business_date, run_due_rollovers (pg_cron)</t>
+          <t>(not in R1)</t>
         </is>
       </c>
       <c r="N94" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (4); upgrade (5)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O94" s="10" t="inlineStr">
         <is>
-          <t>Built+tested</t>
+          <t>R1b</t>
         </is>
       </c>
       <c r="P94" s="10" t="inlineStr"/>
@@ -8064,7 +8088,7 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>DAY-002</t>
+          <t>DAY-001</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
@@ -8079,12 +8103,12 @@
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>At the roll, each guest in house is charged the night's room rate and tax exactly once.</t>
+          <t>The business date rolls automatically at each property's cut-off time.</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-019</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
@@ -8099,37 +8123,37 @@
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>(system)</t>
+          <t>audit.businessdate.view</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr">
         <is>
-          <t>Rule: Business date</t>
+          <t>Rule: Business date; A2</t>
         </is>
       </c>
       <c r="J95" s="10" t="inlineStr">
         <is>
-          <t>two guests in house</t>
+          <t>a property whose cut-off has passed</t>
         </is>
       </c>
       <c r="K95" s="10" t="inlineStr">
         <is>
-          <t>the roll runs</t>
+          <t>the scheduler runs</t>
         </is>
       </c>
       <c r="L95" s="10" t="inlineStr">
         <is>
-          <t>each folio gets one room charge for the closing date, with tax; running it again for the same night cannot repeat it</t>
+          <t>the date advances one day, up to three days per run; the roll is logged</t>
         </is>
       </c>
       <c r="M95" s="10" t="inlineStr">
         <is>
-          <t>roll_business_date; idempotency keys room:&lt;reservation&gt;:&lt;date&gt;</t>
+          <t>roll_business_date, run_due_rollovers (pg_cron)</t>
         </is>
       </c>
       <c r="N95" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (3)</t>
+          <t>14_lifecycle (4); upgrade (5)</t>
         </is>
       </c>
       <c r="O95" s="10" t="inlineStr">
@@ -8142,7 +8166,7 @@
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>DAY-003</t>
+          <t>DAY-002</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
@@ -8157,7 +8181,7 @@
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>A guest still in house past departure is charged and extended a night if the room allows; otherwise managers are told.</t>
+          <t>At the roll, each guest in house is charged the night's room rate and tax exactly once.</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
@@ -8167,7 +8191,7 @@
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
@@ -8182,12 +8206,12 @@
       </c>
       <c r="I96" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Business date</t>
         </is>
       </c>
       <c r="J96" s="10" t="inlineStr">
         <is>
-          <t>a guest due out today who is still in house</t>
+          <t>two guests in house</t>
         </is>
       </c>
       <c r="K96" s="10" t="inlineStr">
@@ -8197,17 +8221,17 @@
       </c>
       <c r="L96" s="10" t="inlineStr">
         <is>
-          <t>the departure moves one day and the night is charged</t>
+          <t>each folio gets one room charge for the closing date, with tax; running it again for the same night cannot repeat it</t>
         </is>
       </c>
       <c r="M96" s="10" t="inlineStr">
         <is>
-          <t>roll_business_date</t>
+          <t>roll_business_date; idempotency keys room:&lt;reservation&gt;:&lt;date&gt;</t>
         </is>
       </c>
       <c r="N96" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (12); upgrade (2)</t>
+          <t>14_lifecycle (3)</t>
         </is>
       </c>
       <c r="O96" s="10" t="inlineStr">
@@ -8220,7 +8244,7 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>DAY-004</t>
+          <t>DAY-003</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
@@ -8235,7 +8259,7 @@
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>A failed roll changes nothing and notifies managers; other properties are not blocked.</t>
+          <t>A guest still in house past departure is charged and extended a night if the room allows; otherwise managers are told.</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
@@ -8245,7 +8269,7 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
@@ -8255,7 +8279,7 @@
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>audit.businessdate.view</t>
+          <t>(system)</t>
         </is>
       </c>
       <c r="I97" s="10" t="inlineStr">
@@ -8265,27 +8289,27 @@
       </c>
       <c r="J97" s="10" t="inlineStr">
         <is>
-          <t>a property whose roll fails</t>
+          <t>a guest due out today who is still in house</t>
         </is>
       </c>
       <c r="K97" s="10" t="inlineStr">
         <is>
-          <t>the scheduler runs</t>
+          <t>the roll runs</t>
         </is>
       </c>
       <c r="L97" s="10" t="inlineStr">
         <is>
-          <t>its date is unchanged and managers get a notification</t>
+          <t>the departure moves one day and the night is charged</t>
         </is>
       </c>
       <c r="M97" s="10" t="inlineStr">
         <is>
-          <t>run_due_rollovers</t>
+          <t>roll_business_date</t>
         </is>
       </c>
       <c r="N97" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (2)</t>
+          <t>14_lifecycle (12); upgrade (2)</t>
         </is>
       </c>
       <c r="O97" s="10" t="inlineStr">
@@ -8298,7 +8322,7 @@
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>DAY-005</t>
+          <t>DAY-004</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
@@ -8308,67 +8332,67 @@
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>FIN-03</t>
+          <t>(system)</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Night audit gates the roll from R2.</t>
+          <t>A failed roll changes nothing and notifies managers; other properties are not blocked.</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>BR-016</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>audit.night.run</t>
+          <t>audit.businessdate.view</t>
         </is>
       </c>
       <c r="I98" s="10" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J98" s="10" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>a property whose roll fails</t>
         </is>
       </c>
       <c r="K98" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>the scheduler runs</t>
         </is>
       </c>
       <c r="L98" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>its date is unchanged and managers get a notification</t>
         </is>
       </c>
       <c r="M98" s="10" t="inlineStr">
         <is>
-          <t>(not in R1)</t>
+          <t>run_due_rollovers</t>
         </is>
       </c>
       <c r="N98" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17_more_features (2)</t>
         </is>
       </c>
       <c r="O98" s="10" t="inlineStr">
         <is>
-          <t>R1b</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P98" s="10" t="inlineStr"/>
@@ -8376,7 +8400,7 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>DAY-006</t>
+          <t>DAY-005</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
@@ -8386,17 +8410,17 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>(system)</t>
+          <t>FIN-03</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>A same-day arrival and departure: decide whether a night or day-use charge applies.</t>
+          <t>Night audit gates the roll from R2.</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-016</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
@@ -8406,84 +8430,80 @@
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>(decision)</t>
+          <t>audit.night.run</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr">
         <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J99" s="10" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="K99" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J99" s="10" t="inlineStr">
-        <is>
-          <t>a guest checks in and out on the same business date</t>
-        </is>
-      </c>
-      <c r="K99" s="10" t="inlineStr">
-        <is>
-          <t>they leave before the roll</t>
-        </is>
-      </c>
       <c r="L99" s="10" t="inlineStr">
         <is>
-          <t>today no room charge is made; the desk can post a manual charge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M99" s="10" t="inlineStr">
         <is>
-          <t>check_out</t>
+          <t>(not in R1)</t>
         </is>
       </c>
       <c r="N99" s="10" t="inlineStr">
         <is>
-          <t>19_same_day (21); upgrade (2); browser: desk-journey</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O99" s="10" t="inlineStr">
         <is>
-          <t>Built+tested</t>
-        </is>
-      </c>
-      <c r="P99" s="10" t="inlineStr">
-        <is>
-          <t>Decided by Peter on 30 Sep 2026 (answer 5) and confirmed on 1 Oct 2026: same-day stays are charged one night; a manager can waive it with a reason.</t>
-        </is>
-      </c>
+          <t>R1b</t>
+        </is>
+      </c>
+      <c r="P99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>RPT-001</t>
+          <t>DAY-006</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Business Date</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>DASH-01, REP-01</t>
+          <t>(system)</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Occupancy, ADR and RevPAR use one definition: rooms sold over rooms available (out-of-order rooms excluded), revenue net of tax.</t>
+          <t>A same-day arrival and departure: decide whether a night or day-use charge applies.</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>BR-019</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
@@ -8493,37 +8513,37 @@
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>dash.view_exec, rep.ops.view</t>
+          <t>(decision)</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr">
         <is>
-          <t>KPI Dictionary</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J100" s="10" t="inlineStr">
         <is>
-          <t>a closed day</t>
+          <t>a guest checks in and out on the same business date</t>
         </is>
       </c>
       <c r="K100" s="10" t="inlineStr">
         <is>
-          <t>management opens the KPI view</t>
+          <t>they leave before the roll</t>
         </is>
       </c>
       <c r="L100" s="10" t="inlineStr">
         <is>
-          <t>occupancy, ADR and RevPAR equal sold, revenue and available as defined; tax is shown apart</t>
+          <t>today no room charge is made; the desk can post a manual charge</t>
         </is>
       </c>
       <c r="M100" s="10" t="inlineStr">
         <is>
-          <t>daily_stats, v_kpi_daily</t>
+          <t>check_out</t>
         </is>
       </c>
       <c r="N100" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (4)</t>
+          <t>19_same_day (21); upgrade (2); browser: desk-journey</t>
         </is>
       </c>
       <c r="O100" s="10" t="inlineStr">
@@ -8531,12 +8551,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P100" s="10" t="inlineStr"/>
+      <c r="P100" s="10" t="inlineStr">
+        <is>
+          <t>Decided by Peter on 30 Sep 2026 (answer 5) and confirmed on 1 Oct 2026: same-day stays are charged one night; a manager can waive it with a reason.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>RPT-002</t>
+          <t>RPT-001</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
@@ -8546,17 +8570,17 @@
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>DASH-02</t>
+          <t>DASH-01, REP-01</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>Live operations views: arrivals, in-house, room board, housekeeping board.</t>
+          <t>Occupancy, ADR and RevPAR use one definition: rooms sold over rooms available (out-of-order rooms excluded), revenue net of tax.</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>BR-006, BR-019</t>
+          <t>BR-019</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
@@ -8571,42 +8595,42 @@
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>dash.view_ops</t>
+          <t>dash.view_exec, rep.ops.view</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KPI Dictionary</t>
         </is>
       </c>
       <c r="J101" s="10" t="inlineStr">
         <is>
-          <t>activity in the hotel</t>
+          <t>a closed day</t>
         </is>
       </c>
       <c r="K101" s="10" t="inlineStr">
         <is>
-          <t>staff open the operations dashboard</t>
+          <t>management opens the KPI view</t>
         </is>
       </c>
       <c r="L101" s="10" t="inlineStr">
         <is>
-          <t>the views return only rows the user may see</t>
+          <t>occupancy, ADR and RevPAR equal sold, revenue and available as defined; tax is shown apart</t>
         </is>
       </c>
       <c r="M101" s="10" t="inlineStr">
         <is>
-          <t>v_arrivals, v_in_house, v_room_board, v_hk_board</t>
+          <t>daily_stats, v_kpi_daily</t>
         </is>
       </c>
       <c r="N101" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14_lifecycle (4)</t>
         </is>
       </c>
       <c r="O101" s="10" t="inlineStr">
         <is>
-          <t>Built, no tagged test</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P101" s="10" t="inlineStr"/>
@@ -8614,7 +8638,7 @@
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>RPT-003</t>
+          <t>RPT-002</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -8624,17 +8648,17 @@
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>REP-01, REP-02</t>
+          <t>DASH-02</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Every reported figure traces to ledger rows or operational records.</t>
+          <t>Live operations views: arrivals, in-house, room board, housekeeping board.</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>BR-020</t>
+          <t>BR-006, BR-019</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
@@ -8649,7 +8673,7 @@
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>rep.ops.view, rep.fin.view</t>
+          <t>dash.view_ops</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr">
@@ -8659,22 +8683,22 @@
       </c>
       <c r="J102" s="10" t="inlineStr">
         <is>
-          <t>a daily figure</t>
+          <t>activity in the hotel</t>
         </is>
       </c>
       <c r="K102" s="10" t="inlineStr">
         <is>
-          <t>an auditor recomputes it from folio_transactions</t>
+          <t>staff open the operations dashboard</t>
         </is>
       </c>
       <c r="L102" s="10" t="inlineStr">
         <is>
-          <t>the figures agree</t>
+          <t>the views return only rows the user may see</t>
         </is>
       </c>
       <c r="M102" s="10" t="inlineStr">
         <is>
-          <t>daily_stats computed from folio_transactions</t>
+          <t>v_arrivals, v_in_house, v_room_board, v_hk_board</t>
         </is>
       </c>
       <c r="N102" s="10" t="inlineStr">
@@ -8692,7 +8716,7 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>RPT-004</t>
+          <t>RPT-003</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
@@ -8707,12 +8731,12 @@
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>Report screens (occupancy trend, revenue by group, outstanding balances, cancellation and no-show rates).</t>
+          <t>Every reported figure traces to ledger rows or operational records.</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>BR-019</t>
+          <t>BR-020</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
@@ -8732,27 +8756,27 @@
       </c>
       <c r="I103" s="10" t="inlineStr">
         <is>
-          <t>KPI Dictionary</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
-          <t>a date range</t>
+          <t>a daily figure</t>
         </is>
       </c>
       <c r="K103" s="10" t="inlineStr">
         <is>
-          <t>a manager opens a report</t>
+          <t>an auditor recomputes it from folio_transactions</t>
         </is>
       </c>
       <c r="L103" s="10" t="inlineStr">
         <is>
-          <t>the numbers match the KPI definitions</t>
+          <t>the figures agree</t>
         </is>
       </c>
       <c r="M103" s="10" t="inlineStr">
         <is>
-          <t>(views for cancellation rate, ALOS and outstanding balances still to add)</t>
+          <t>daily_stats computed from folio_transactions</t>
         </is>
       </c>
       <c r="N103" s="10" t="inlineStr">
@@ -8765,36 +8789,32 @@
           <t>Built, no tagged test</t>
         </is>
       </c>
-      <c r="P103" s="10" t="inlineStr">
-        <is>
-          <t>Reports screen: KPIs, revenue by charge code, outstanding balances, payments, cancellations and stay length, balances by guest, export.</t>
-        </is>
-      </c>
+      <c r="P103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>NFR-001</t>
+          <t>RPT-004</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>(all)</t>
+          <t>REP-01, REP-02</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Every table has row-level security and tenant_id; security definer functions pin their search path.</t>
+          <t>Report screens (occupancy trend, revenue by group, outstanding balances, cancellation and no-show rates).</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>BR-017</t>
+          <t>BR-019</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
@@ -8809,50 +8829,54 @@
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
+          <t>rep.ops.view, rep.fin.view</t>
+        </is>
+      </c>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>KPI Dictionary</t>
+        </is>
+      </c>
+      <c r="J104" s="10" t="inlineStr">
+        <is>
+          <t>a date range</t>
+        </is>
+      </c>
+      <c r="K104" s="10" t="inlineStr">
+        <is>
+          <t>a manager opens a report</t>
+        </is>
+      </c>
+      <c r="L104" s="10" t="inlineStr">
+        <is>
+          <t>the numbers match the KPI definitions</t>
+        </is>
+      </c>
+      <c r="M104" s="10" t="inlineStr">
+        <is>
+          <t>(views for cancellation rate, ALOS and outstanding balances still to add)</t>
+        </is>
+      </c>
+      <c r="N104" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="10" t="inlineStr">
-        <is>
-          <t>Rule: Tenant isolation</t>
-        </is>
-      </c>
-      <c r="J104" s="10" t="inlineStr">
-        <is>
-          <t>a migration adds a table or function</t>
-        </is>
-      </c>
-      <c r="K104" s="10" t="inlineStr">
-        <is>
-          <t>the test suite runs</t>
-        </is>
-      </c>
-      <c r="L104" s="10" t="inlineStr">
-        <is>
-          <t>it fails if RLS, tenant_id or search_path is missing</t>
-        </is>
-      </c>
-      <c r="M104" s="10" t="inlineStr">
-        <is>
-          <t>structure tests</t>
-        </is>
-      </c>
-      <c r="N104" s="10" t="inlineStr">
-        <is>
-          <t>10_security (3)</t>
-        </is>
-      </c>
       <c r="O104" s="10" t="inlineStr">
         <is>
-          <t>Built+tested</t>
-        </is>
-      </c>
-      <c r="P104" s="10" t="inlineStr"/>
+          <t>Built, no tagged test</t>
+        </is>
+      </c>
+      <c r="P104" s="10" t="inlineStr">
+        <is>
+          <t>Reports screen: KPIs, revenue by charge code, outstanding balances, payments, cancellations and stay length, balances by guest, export.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>NFR-002</t>
+          <t>NFR-001</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
@@ -8867,12 +8891,12 @@
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>The browser can write directly only to plain configuration tables; ledger, reservations, stays, tasks and blocks change only through functions.</t>
+          <t>Every table has row-level security and tenant_id; security definer functions pin their search path.</t>
         </is>
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>BR-014, BR-017</t>
+          <t>BR-017</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
@@ -8892,32 +8916,32 @@
       </c>
       <c r="I105" s="10" t="inlineStr">
         <is>
-          <t>Rule: Immutability</t>
+          <t>Rule: Tenant isolation</t>
         </is>
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
-          <t>any user</t>
+          <t>a migration adds a table or function</t>
         </is>
       </c>
       <c r="K105" s="10" t="inlineStr">
         <is>
-          <t>they write to a ledger or state table</t>
+          <t>the test suite runs</t>
         </is>
       </c>
       <c r="L105" s="10" t="inlineStr">
         <is>
-          <t>permission denied; the list of directly writable tables is asserted by a test</t>
+          <t>it fails if RLS, tenant_id or search_path is missing</t>
         </is>
       </c>
       <c r="M105" s="10" t="inlineStr">
         <is>
-          <t>20260928001100_grants.sql</t>
+          <t>structure tests</t>
         </is>
       </c>
       <c r="N105" s="10" t="inlineStr">
         <is>
-          <t>10_security (2)</t>
+          <t>10_security (3)</t>
         </is>
       </c>
       <c r="O105" s="10" t="inlineStr">
@@ -8930,7 +8954,7 @@
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>NFR-003</t>
+          <t>NFR-002</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -8945,17 +8969,17 @@
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Create actions accept client-generated ids and idempotency keys so an offline queue can be added later.</t>
+          <t>The browser can write directly only to plain configuration tables; ledger, reservations, stays, tasks and blocks change only through functions.</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>BR-014, BR-017</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
@@ -8970,32 +8994,32 @@
       </c>
       <c r="I106" s="10" t="inlineStr">
         <is>
-          <t>Rule: Offline-ready design; A12</t>
+          <t>Rule: Immutability</t>
         </is>
       </c>
       <c r="J106" s="10" t="inlineStr">
         <is>
-          <t>a repeated create request</t>
+          <t>any user</t>
         </is>
       </c>
       <c r="K106" s="10" t="inlineStr">
         <is>
-          <t>it arrives twice</t>
+          <t>they write to a ledger or state table</t>
         </is>
       </c>
       <c r="L106" s="10" t="inlineStr">
         <is>
-          <t>only one record exists</t>
+          <t>permission denied; the list of directly writable tables is asserted by a test</t>
         </is>
       </c>
       <c r="M106" s="10" t="inlineStr">
         <is>
-          <t>idempotency keys; client ids allowed on insert</t>
+          <t>20260928001100_grants.sql</t>
         </is>
       </c>
       <c r="N106" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (1)</t>
+          <t>10_security (2)</t>
         </is>
       </c>
       <c r="O106" s="10" t="inlineStr">
@@ -9008,7 +9032,7 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>NFR-004</t>
+          <t>NFR-003</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
@@ -9023,17 +9047,17 @@
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>Money uses fixed decimals per currency (naira 2, CFA franc 0), never floating point.</t>
+          <t>Create actions accept client-generated ids and idempotency keys so an offline queue can be added later.</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
@@ -9048,32 +9072,32 @@
       </c>
       <c r="I107" s="10" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>Rule: Offline-ready design; A12</t>
         </is>
       </c>
       <c r="J107" s="10" t="inlineStr">
         <is>
-          <t>an amount with too many decimals</t>
+          <t>a repeated create request</t>
         </is>
       </c>
       <c r="K107" s="10" t="inlineStr">
         <is>
-          <t>it is posted</t>
+          <t>it arrives twice</t>
         </is>
       </c>
       <c r="L107" s="10" t="inlineStr">
         <is>
-          <t>it is refused with E_PRECISION</t>
+          <t>only one record exists</t>
         </is>
       </c>
       <c r="M107" s="10" t="inlineStr">
         <is>
-          <t>numeric(20,4), currencies.decimals</t>
+          <t>idempotency keys; client ids allowed on insert</t>
         </is>
       </c>
       <c r="N107" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>13_reservations (1)</t>
         </is>
       </c>
       <c r="O107" s="10" t="inlineStr">
@@ -9086,7 +9110,7 @@
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>NFR-005</t>
+          <t>NFR-004</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
@@ -9101,12 +9125,12 @@
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Business date and cut-off follow the property's timezone.</t>
+          <t>Money uses fixed decimals per currency (naira 2, CFA franc 0), never floating point.</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>BR-019</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
@@ -9126,32 +9150,32 @@
       </c>
       <c r="I108" s="10" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="J108" s="10" t="inlineStr">
         <is>
-          <t>a property in Lagos</t>
+          <t>an amount with too many decimals</t>
         </is>
       </c>
       <c r="K108" s="10" t="inlineStr">
         <is>
-          <t>it is created just before or after cut-off</t>
+          <t>it is posted</t>
         </is>
       </c>
       <c r="L108" s="10" t="inlineStr">
         <is>
-          <t>the business date is the local hotel day, not the server's day</t>
+          <t>it is refused with E_PRECISION</t>
         </is>
       </c>
       <c r="M108" s="10" t="inlineStr">
         <is>
-          <t>local_business_date</t>
+          <t>numeric(20,4), currencies.decimals</t>
         </is>
       </c>
       <c r="N108" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (1)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O108" s="10" t="inlineStr">
@@ -9164,72 +9188,72 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>DAY-006b</t>
+          <t>NFR-005</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>Business Date</t>
+          <t>Non-functional</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>/checkout/$id</t>
+          <t>(all)</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>A guest leaving on the arrival day is charged one night at check-out; a manager can waive it with a reason.</t>
+          <t>Business date and cut-off follow the property's timezone.</t>
         </is>
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
+          <t>BR-019</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G109" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H109" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F109" s="10" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G109" s="10" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H109" s="10" t="inlineStr">
-        <is>
-          <t>fo.checkout; fo.sameday.waive</t>
-        </is>
-      </c>
       <c r="I109" s="10" t="inlineStr">
         <is>
-          <t>Rule: DAY-006 decision</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="J109" s="10" t="inlineStr">
         <is>
-          <t>an in-house guest whose arrival and departure are today</t>
+          <t>a property in Lagos</t>
         </is>
       </c>
       <c r="K109" s="10" t="inlineStr">
         <is>
-          <t>they are checked out</t>
+          <t>it is created just before or after cut-off</t>
         </is>
       </c>
       <c r="L109" s="10" t="inlineStr">
         <is>
-          <t>one night (with tax) is posted unless a manager waives it with a reason</t>
+          <t>the business date is the local hotel day, not the server's day</t>
         </is>
       </c>
       <c r="M109" s="10" t="inlineStr">
         <is>
-          <t>preview_check_out_charge, check_out</t>
+          <t>local_business_date</t>
         </is>
       </c>
       <c r="N109" s="10" t="inlineStr">
         <is>
-          <t>21_same_day_checkout (28); upgrade (2)</t>
+          <t>17_more_features (1)</t>
         </is>
       </c>
       <c r="O109" s="10" t="inlineStr">
@@ -9242,22 +9266,22 @@
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>FIN-017</t>
+          <t>DAY-006b</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Business Date</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>/folios/$id</t>
+          <t>/checkout/$id</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>A payment matching one on the same bill (amount, currency, method, reference) within 10 minutes is refused unless the cashier confirms it with a reason; the refusal names the earlier payment and the confirmation is audited.</t>
+          <t>A guest leaving on the arrival day is charged one night at check-out; a manager can waive it with a reason.</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
@@ -9277,37 +9301,37 @@
       </c>
       <c r="H110" s="10" t="inlineStr">
         <is>
-          <t>fin.payment.post</t>
+          <t>fo.checkout; fo.sameday.waive</t>
         </is>
       </c>
       <c r="I110" s="10" t="inlineStr">
         <is>
-          <t>Setting duplicate_payment_window_minutes</t>
+          <t>Rule: DAY-006 decision</t>
         </is>
       </c>
       <c r="J110" s="10" t="inlineStr">
         <is>
-          <t>a payment recorded on a bill a few minutes ago</t>
+          <t>an in-house guest whose arrival and departure are today</t>
         </is>
       </c>
       <c r="K110" s="10" t="inlineStr">
         <is>
-          <t>the same payment is recorded again with a new key</t>
+          <t>they are checked out</t>
         </is>
       </c>
       <c r="L110" s="10" t="inlineStr">
         <is>
-          <t>it is refused naming the earlier payment; with a reason it is recorded and audited as payment_duplicate_confirmed</t>
+          <t>one night (with tax) is posted unless a manager waives it with a reason</t>
         </is>
       </c>
       <c r="M110" s="10" t="inlineStr">
         <is>
-          <t>post_payment</t>
+          <t>preview_check_out_charge, check_out</t>
         </is>
       </c>
       <c r="N110" s="10" t="inlineStr">
         <is>
-          <t>25_duplicate_payments (20); browser: duplicate-payment</t>
+          <t>21_same_day_checkout (28); upgrade (2)</t>
         </is>
       </c>
       <c r="O110" s="10" t="inlineStr">
@@ -9320,22 +9344,22 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>GST-007</t>
+          <t>FIN-017</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>Guests</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>/guests/$id; check-in; walk-in</t>
+          <t>/folios/$id</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>A photo or scan of an ID document is kept in private storage, shrunk and stripped of hidden data in the browser, and opened only through a 60-second link.</t>
+          <t>A payment matching one on the same bill (amount, currency, method, reference) within 10 minutes is refused unless the cashier confirms it with a reason; the refusal names the earlier payment and the confirmation is audited.</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
@@ -9355,37 +9379,37 @@
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>guest.document.file.upload / view / delete</t>
+          <t>fin.payment.post</t>
         </is>
       </c>
       <c r="I111" s="10" t="inlineStr">
         <is>
-          <t>SET-009 switch</t>
+          <t>Setting duplicate_payment_window_minutes</t>
         </is>
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
-          <t>a hotel that allows ID photos</t>
+          <t>a payment recorded on a bill a few minutes ago</t>
         </is>
       </c>
       <c r="K111" s="10" t="inlineStr">
         <is>
-          <t>front desk adds an ID photo</t>
+          <t>the same payment is recorded again with a new key</t>
         </is>
       </c>
       <c r="L111" s="10" t="inlineStr">
         <is>
-          <t>it is stored privately and opens only through a short-lived link</t>
+          <t>it is refused naming the earlier payment; with a reason it is recorded and audited as payment_duplicate_confirmed</t>
         </is>
       </c>
       <c r="M111" s="10" t="inlineStr">
         <is>
-          <t>begin_id_photo_upload, finish_id_photo_upload, open_id_photo</t>
+          <t>post_payment</t>
         </is>
       </c>
       <c r="N111" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (30)</t>
+          <t>25_duplicate_payments (20); browser: duplicate-payment</t>
         </is>
       </c>
       <c r="O111" s="10" t="inlineStr">
@@ -9398,7 +9422,7 @@
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>GST-008</t>
+          <t>GST-007</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
@@ -9408,12 +9432,12 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>/guests/$id</t>
+          <t>/guests/$id; check-in; walk-in</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>Every upload, view and deletion of an ID photo is audited with ids only, no personal data.</t>
+          <t>A photo or scan of an ID document is kept in private storage, shrunk and stripped of hidden data in the browser, and opened only through a 60-second link.</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
@@ -9433,37 +9457,37 @@
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>guest.document.file.upload / view / delete</t>
         </is>
       </c>
       <c r="I112" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SET-009 switch</t>
         </is>
       </c>
       <c r="J112" s="10" t="inlineStr">
         <is>
-          <t>an ID photo</t>
+          <t>a hotel that allows ID photos</t>
         </is>
       </c>
       <c r="K112" s="10" t="inlineStr">
         <is>
-          <t>it is uploaded, opened or deleted</t>
+          <t>front desk adds an ID photo</t>
         </is>
       </c>
       <c r="L112" s="10" t="inlineStr">
         <is>
-          <t>an audit row records who and which file, with no personal data</t>
+          <t>it is stored privately and opens only through a short-lived link</t>
         </is>
       </c>
       <c r="M112" s="10" t="inlineStr">
         <is>
-          <t>app.audit_id_photo</t>
+          <t>begin_id_photo_upload, finish_id_photo_upload, open_id_photo</t>
         </is>
       </c>
       <c r="N112" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (9)</t>
+          <t>24_id_photos (30)</t>
         </is>
       </c>
       <c r="O112" s="10" t="inlineStr">
@@ -9476,7 +9500,7 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>GST-009</t>
+          <t>GST-008</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -9491,7 +9515,7 @@
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>ID photos are removed from storage when the guest is anonymised or the document is removed, and move with the guest when two profiles are merged.</t>
+          <t>Every upload, view and deletion of an ID photo is audited with ids only, no personal data.</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
@@ -9521,27 +9545,27 @@
       </c>
       <c r="J113" s="10" t="inlineStr">
         <is>
-          <t>a guest with ID photos</t>
+          <t>an ID photo</t>
         </is>
       </c>
       <c r="K113" s="10" t="inlineStr">
         <is>
-          <t>the guest is anonymised, the document removed, or the profile merged</t>
+          <t>it is uploaded, opened or deleted</t>
         </is>
       </c>
       <c r="L113" s="10" t="inlineStr">
         <is>
-          <t>the files are removed, or move to the kept profile</t>
+          <t>an audit row records who and which file, with no personal data</t>
         </is>
       </c>
       <c r="M113" s="10" t="inlineStr">
         <is>
-          <t>anonymise_guest, merge_guests, delete_id_photo</t>
+          <t>app.audit_id_photo</t>
         </is>
       </c>
       <c r="N113" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (4)</t>
+          <t>24_id_photos (9)</t>
         </is>
       </c>
       <c r="O113" s="10" t="inlineStr">
@@ -9554,7 +9578,7 @@
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>GST-010</t>
+          <t>GST-009</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -9564,12 +9588,12 @@
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>(daily clean-up)</t>
+          <t>/guests/$id</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>ID photos are deleted automatically a set number of months (one setting, now 12) after the guest's last check-out, unless the guest has a booking that is not over.</t>
+          <t>ID photos are removed from storage when the guest is anonymised or the document is removed, and move with the guest when two profiles are merged.</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
@@ -9594,32 +9618,32 @@
       </c>
       <c r="I114" s="10" t="inlineStr">
         <is>
-          <t>Setting id_photo_keep_months; daily cron</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>a guest whose last check-out was more than the keep period ago</t>
+          <t>a guest with ID photos</t>
         </is>
       </c>
       <c r="K114" s="10" t="inlineStr">
         <is>
-          <t>the daily clean-up runs</t>
+          <t>the guest is anonymised, the document removed, or the profile merged</t>
         </is>
       </c>
       <c r="L114" s="10" t="inlineStr">
         <is>
-          <t>their ID photos are deleted</t>
+          <t>the files are removed, or move to the kept profile</t>
         </is>
       </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
-          <t>/api/cron/id-photo-cleanup</t>
+          <t>anonymise_guest, merge_guests, delete_id_photo</t>
         </is>
       </c>
       <c r="N114" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (5)</t>
+          <t>24_id_photos (4)</t>
         </is>
       </c>
       <c r="O114" s="10" t="inlineStr">
@@ -9632,22 +9656,22 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>ROOM-005</t>
+          <t>GST-010</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>Rooms</t>
+          <t>Guests</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>/rooms</t>
+          <t>(daily clean-up)</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>Rooms are added one at a time or several by number or by name, with a preview; labels are free text up to 30 characters, unique per hotel ignoring case and extra spaces, shown as typed and sorted in natural order.</t>
+          <t>ID photos are deleted automatically a set number of months (one setting, now 12) after the guest's last check-out, unless the guest has a booking that is not over.</t>
         </is>
       </c>
       <c r="E115" s="10" t="inlineStr">
@@ -9667,37 +9691,37 @@
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>setup.room.edit</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I115" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Setting id_photo_keep_months; daily cron</t>
         </is>
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>an administrator on the Rooms page</t>
+          <t>a guest whose last check-out was more than the keep period ago</t>
         </is>
       </c>
       <c r="K115" s="10" t="inlineStr">
         <is>
-          <t>they add rooms by number range or by names</t>
+          <t>the daily clean-up runs</t>
         </is>
       </c>
       <c r="L115" s="10" t="inlineStr">
         <is>
-          <t>valid new rooms are created, duplicates skipped and invalid names shown</t>
+          <t>their ID photos are deleted</t>
         </is>
       </c>
       <c r="M115" s="10" t="inlineStr">
         <is>
-          <t>add_rooms_range, add_rooms_named, save_room</t>
+          <t>/api/cron/id-photo-cleanup</t>
         </is>
       </c>
       <c r="N115" s="10" t="inlineStr">
         <is>
-          <t>23_room_labels (46); 26_small_fixes (1); browser: rooms-add</t>
+          <t>24_id_photos (5)</t>
         </is>
       </c>
       <c r="O115" s="10" t="inlineStr">
@@ -9710,80 +9734,158 @@
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
+          <t>ROOM-005</t>
+        </is>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>/rooms</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="inlineStr">
+        <is>
+          <t>Rooms are added one at a time or several by number or by name, with a preview; labels are free text up to 30 characters, unique per hotel ignoring case and extra spaces, shown as typed and sorted in natural order.</t>
+        </is>
+      </c>
+      <c r="E116" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G116" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H116" s="10" t="inlineStr">
+        <is>
+          <t>setup.room.edit</t>
+        </is>
+      </c>
+      <c r="I116" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J116" s="10" t="inlineStr">
+        <is>
+          <t>an administrator on the Rooms page</t>
+        </is>
+      </c>
+      <c r="K116" s="10" t="inlineStr">
+        <is>
+          <t>they add rooms by number range or by names</t>
+        </is>
+      </c>
+      <c r="L116" s="10" t="inlineStr">
+        <is>
+          <t>valid new rooms are created, duplicates skipped and invalid names shown</t>
+        </is>
+      </c>
+      <c r="M116" s="10" t="inlineStr">
+        <is>
+          <t>add_rooms_range, add_rooms_named, save_room</t>
+        </is>
+      </c>
+      <c r="N116" s="10" t="inlineStr">
+        <is>
+          <t>23_room_labels (46); 26_small_fixes (1); browser: rooms-add</t>
+        </is>
+      </c>
+      <c r="O116" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P116" s="10" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
           <t>SET-009</t>
         </is>
       </c>
-      <c r="B116" s="10" t="inlineStr">
+      <c r="B117" s="10" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="C116" s="10" t="inlineStr">
+      <c r="C117" s="10" t="inlineStr">
         <is>
           <t>/setup/property</t>
         </is>
       </c>
-      <c r="D116" s="10" t="inlineStr">
+      <c r="D117" s="10" t="inlineStr">
         <is>
           <t>Per hotel: "Allow ID photos" (off by default) and "Require ID photo at check-in" (only when allowed). While Allow is off, uploading and opening ID photos are refused.</t>
         </is>
       </c>
-      <c r="E116" s="10" t="inlineStr">
+      <c r="E117" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F116" s="10" t="inlineStr">
+      <c r="F117" s="10" t="inlineStr">
         <is>
           <t>Must</t>
         </is>
       </c>
-      <c r="G116" s="10" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H116" s="10" t="inlineStr">
+      <c r="G117" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H117" s="10" t="inlineStr">
         <is>
           <t>setup.property.edit</t>
         </is>
       </c>
-      <c r="I116" s="10" t="inlineStr">
+      <c r="I117" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J116" s="10" t="inlineStr">
+      <c r="J117" s="10" t="inlineStr">
         <is>
           <t>a hotel with ID photos off</t>
         </is>
       </c>
-      <c r="K116" s="10" t="inlineStr">
+      <c r="K117" s="10" t="inlineStr">
         <is>
           <t>staff try to add or open an ID photo</t>
         </is>
       </c>
-      <c r="L116" s="10" t="inlineStr">
+      <c r="L117" s="10" t="inlineStr">
         <is>
           <t>it is refused; when Require is on, check-in waits for an ID photo</t>
         </is>
       </c>
-      <c r="M116" s="10" t="inlineStr">
+      <c r="M117" s="10" t="inlineStr">
         <is>
           <t>set_id_photo_settings</t>
         </is>
       </c>
-      <c r="N116" s="10" t="inlineStr">
+      <c r="N117" s="10" t="inlineStr">
         <is>
           <t>24_id_photos (10)</t>
         </is>
       </c>
-      <c r="O116" s="10" t="inlineStr">
+      <c r="O117" s="10" t="inlineStr">
         <is>
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P116" s="10" t="inlineStr"/>
+      <c r="P117" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -601,27 +601,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Built (database only), no tagged test</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Built+tested</t>
+          <t>Built+tested (database only)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Built+tested (database only)</t>
+          <t>Built+tested (known limit)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -631,7 +631,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Built+tested (known limit)</t>
+          <t>Not built</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -641,40 +641,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Built, no tagged test</t>
+          <t>Partly built, no tagged test</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Not built</t>
+          <t>R1b</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Partly built, no tagged test</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R1b</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2513,12 +2493,12 @@
       </c>
       <c r="N23" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29_untagged_rows (5)</t>
         </is>
       </c>
       <c r="O23" s="10" t="inlineStr">
         <is>
-          <t>Built, no tagged test</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P23" s="10" t="inlineStr">
@@ -2755,12 +2735,12 @@
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29_untagged_rows (10)</t>
         </is>
       </c>
       <c r="O26" s="10" t="inlineStr">
         <is>
-          <t>Built, no tagged test</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P26" s="10" t="inlineStr"/>
@@ -2989,12 +2969,12 @@
       </c>
       <c r="N29" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29_untagged_rows (12)</t>
         </is>
       </c>
       <c r="O29" s="10" t="inlineStr">
         <is>
-          <t>Built, no tagged test</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr"/>
@@ -4081,12 +4061,12 @@
       </c>
       <c r="N43" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29_untagged_rows (7)</t>
         </is>
       </c>
       <c r="O43" s="10" t="inlineStr">
         <is>
-          <t>Built (database only), no tagged test</t>
+          <t>Built+tested (database only)</t>
         </is>
       </c>
       <c r="P43" s="10" t="inlineStr">
@@ -4163,7 +4143,7 @@
       </c>
       <c r="N44" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (2); 26_small_fixes (4)</t>
+          <t>17_more_features (2); 26_small_fixes (4); 29_untagged_rows (6)</t>
         </is>
       </c>
       <c r="O44" s="10" t="inlineStr">
@@ -5657,12 +5637,12 @@
       </c>
       <c r="N63" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29_untagged_rows (6)</t>
         </is>
       </c>
       <c r="O63" s="10" t="inlineStr">
         <is>
-          <t>Built, no tagged test</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P63" s="10" t="inlineStr"/>
@@ -8703,12 +8683,12 @@
       </c>
       <c r="N102" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29_untagged_rows (14)</t>
         </is>
       </c>
       <c r="O102" s="10" t="inlineStr">
         <is>
-          <t>Built, no tagged test</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P102" s="10" t="inlineStr"/>
@@ -8781,12 +8761,12 @@
       </c>
       <c r="N103" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29_untagged_rows (11)</t>
         </is>
       </c>
       <c r="O103" s="10" t="inlineStr">
         <is>
-          <t>Built, no tagged test</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P103" s="10" t="inlineStr"/>
@@ -8859,12 +8839,12 @@
       </c>
       <c r="N104" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29_untagged_rows (14)</t>
         </is>
       </c>
       <c r="O104" s="10" t="inlineStr">
         <is>
-          <t>Built, no tagged test</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P104" s="10" t="inlineStr">

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -2735,7 +2735,7 @@
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>29_untagged_rows (10)</t>
+          <t>29_untagged_rows (10); 30_retire_room_guard (8)</t>
         </is>
       </c>
       <c r="O26" s="10" t="inlineStr">
@@ -2743,7 +2743,11 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P26" s="10" t="inlineStr"/>
+      <c r="P26" s="10" t="inlineStr">
+        <is>
+          <t>A room with a guest in it right now cannot be retired; check the guest out first ([E_ROOM_OCCUPIED], decision of 6 Oct 2026). Retiring a room that is already retired is safe to repeat. Future bookings assigned to a retired room are not checked yet (open question).</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>(needs an Edge Function or client-side export)</t>
+          <t>export_data (rpt.export: System Administrator, General Manager, Accountant) returns bookings, ledger rows or guests for one property and at most a year, and writes an audit row (action export: who, what, which property, how many rows); the Export tab on Reports downloads it as CSV through src/lib/exports.functions.ts</t>
         </is>
       </c>
       <c r="N23" s="10" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M104" s="10" t="inlineStr">
         <is>
-          <t>(views for cancellation rate, ALOS and outstanding balances still to add)</t>
+          <t>Reports screen (src/routes/_authenticated/_app/reports.tsx) on report_* functions in the database: v_kpi_daily (occupancy, average rate, revenue per room), report_revenue_by_charge_code, report_outstanding_balances, report_payments, report_cancellation_rate (cancellations and no-shows), report_length_of_stay, report_balances_by_guest; finance reports need rpt.finance.view, operations reports rpt.operations.view</t>
         </is>
       </c>
       <c r="N104" s="10" t="inlineStr">

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -2735,7 +2735,7 @@
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>29_untagged_rows (10); 30_retire_room_guard (8)</t>
+          <t>29_untagged_rows (10); 30_retire_room_guard (8); 31_retire_room_future_guard (9)</t>
         </is>
       </c>
       <c r="O26" s="10" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="P26" s="10" t="inlineStr">
         <is>
-          <t>A room with a guest in it right now cannot be retired; check the guest out first ([E_ROOM_OCCUPIED], decision of 6 Oct 2026). Retiring a room that is already retired is safe to repeat. Future bookings assigned to a retired room are not checked yet (open question).</t>
+          <t>A room cannot be retired while a guest is in it ([E_ROOM_OCCUPIED], checked first) or while upcoming bookings are assigned to it ([E_ROOM_BOOKED], names up to 5 booking numbers): confirmed, or tentative with an unexpired hold, from the business date forward (decisions of 6 Oct 2026). Retiring a room that is already retired is safe to repeat; renaming and floor changes still work.</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'R1 Requirements'!$A$1:$O$108</definedName>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Subscription billing through a payment provider (Paystack or Flutterwave).</t>
+          <t>Subscription billing through a payment provider (Paystack first). A hotel picks a plan and pays online; the price comes from the database; the provider result activates the plan once, only when the amount and currency match; failed payments show to platform operators.</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
@@ -1669,55 +1669,59 @@
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>R1b</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>org.billing.paymentmethod</t>
+          <t>adm.subscription.manage; platform operator</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>A13</t>
+          <t>A13, A16</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>a hotel wants to pay online</t>
+          <t>a hotel administrator on a plan with a price</t>
         </is>
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>they choose a plan and pay</t>
+          <t>they start a payment and the provider confirms it</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>the subscription activates automatically</t>
+          <t>"the plan becomes active for a month or a year, a resent event changes nothing, a wrong amount activates nothing"</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>(pilots are invoiced by hand until then)</t>
+          <t>start_subscription_payment, billing_apply_event, platform_set_plan_price, platform_failed_payments</t>
         </is>
       </c>
       <c r="N13" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32_subscription_billing (62)</t>
         </is>
       </c>
       <c r="O13" s="10" t="inlineStr">
         <is>
-          <t>R1b</t>
-        </is>
-      </c>
-      <c r="P13" s="10" t="inlineStr"/>
+          <t>Built+tested (database only)</t>
+        </is>
+      </c>
+      <c r="P13" s="10" t="inlineStr">
+        <is>
+          <t>Checkout, webhook route and Subscription screen come next. Prices are empty until A16 is decided.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Subscription billing through a payment provider (Paystack first). A hotel picks a plan and pays online; the price comes from the database; the provider result activates the plan once, only when the amount and currency match; failed payments show to platform operators.</t>
+          <t>Subscription billing through a payment provider (Paystack first). A hotel picks a plan and pays online; the price comes from the database; the provider result activates the plan once, only when the amount and currency match; failed payments show to platform operators. Hotels pay from the Subscription tab; Paystack calls a signed webhook.</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
@@ -1704,22 +1704,22 @@
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>start_subscription_payment, billing_apply_event, platform_set_plan_price, platform_failed_payments</t>
+          <t>start_subscription_payment, billing_apply_event, platform_set_plan_price, platform_failed_payments, billing_options, paystack webhook gate</t>
         </is>
       </c>
       <c r="N13" s="10" t="inlineStr">
         <is>
-          <t>32_subscription_billing (62)</t>
+          <t>32_subscription_billing (62); 33_billing_options (13); paystack-webhook-unit (7)</t>
         </is>
       </c>
       <c r="O13" s="10" t="inlineStr">
         <is>
-          <t>Built+tested (database only)</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P13" s="10" t="inlineStr">
         <is>
-          <t>Checkout, webhook route and Subscription screen come next. Prices are empty until A16 is decided.</t>
+          <t>Needs PAYSTACK_SECRET_KEY and the webhook address set in Paystack. Prices are empty until A16 is decided.</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'R1 Requirements'!$A$1:$O$108</definedName>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Cashier shifts and reconciliation by cashier, shift and method.</t>
+          <t>Cashier shifts: a cashier opens a shift with a float, takes payments, counts each payment method at the end; the database works out expected and difference; a manager reconciles (never the closer). A hotel can require an open shift before payments.</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
@@ -8019,55 +8019,59 @@
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>fin.shift.manage, fin.shift.reconcile</t>
+          <t>fin.shift.close, fin.shift.reconcile</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>A2; decision of 7 Oct 2026</t>
         </is>
       </c>
       <c r="J94" s="10" t="inlineStr">
         <is>
-          <t>a cashier shift</t>
+          <t>a cashier with an open shift who took cash and card payments</t>
         </is>
       </c>
       <c r="K94" s="10" t="inlineStr">
         <is>
-          <t>the shift is closed</t>
+          <t>they close the shift with their counts</t>
         </is>
       </c>
       <c r="L94" s="10" t="inlineStr">
         <is>
-          <t>payments reconcile by method</t>
+          <t>the difference per method is worked out, a note is needed for a difference, and a manager reconciles it</t>
         </is>
       </c>
       <c r="M94" s="10" t="inlineStr">
         <is>
-          <t>(not in R1)</t>
+          <t>open_cashier_shift, close_cashier_shift, reconcile_cashier_shift, cashier_shift_summary, list_cashier_shifts, set_cashier_shift_required, stamp_cashier_shift</t>
         </is>
       </c>
       <c r="N94" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>34_cashier_shifts (45)</t>
         </is>
       </c>
       <c r="O94" s="10" t="inlineStr">
         <is>
-          <t>R1b</t>
-        </is>
-      </c>
-      <c r="P94" s="10" t="inlineStr"/>
+          <t>Built+tested (database only)</t>
+        </is>
+      </c>
+      <c r="P94" s="10" t="inlineStr">
+        <is>
+          <t>Shift screens come next. New permission fin.shift.reconcile goes to built-in roles only.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
@@ -8399,7 +8403,7 @@
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>Night audit gates the roll from R2.</t>
+          <t>Night audit flags list what is still open before the day closes: open cashier shifts (blocking), unreconciled differences, guests past departure, arrivals not checked in. The flags do not stop the date rolling yet.</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
@@ -8414,24 +8418,24 @@
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>fin.nightaudit.run</t>
+        </is>
+      </c>
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J99" s="10" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="H99" s="10" t="inlineStr">
-        <is>
-          <t>audit.night.run</t>
-        </is>
-      </c>
-      <c r="I99" s="10" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="J99" s="10" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
       <c r="K99" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -8444,20 +8448,24 @@
       </c>
       <c r="M99" s="10" t="inlineStr">
         <is>
-          <t>(not in R1)</t>
+          <t>night_audit_flags</t>
         </is>
       </c>
       <c r="N99" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>34_cashier_shifts (7)</t>
         </is>
       </c>
       <c r="O99" s="10" t="inlineStr">
         <is>
-          <t>R1b</t>
-        </is>
-      </c>
-      <c r="P99" s="10" t="inlineStr"/>
+          <t>Partly built, no tagged test</t>
+        </is>
+      </c>
+      <c r="P99" s="10" t="inlineStr">
+        <is>
+          <t>Flags built and tested. The gate that stops the roll while a blocking flag is open is not built.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -641,20 +641,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Partly built, no tagged test</t>
+          <t>Partly built (flags only)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Partly built, no tagged test</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>R1b</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8458,7 +8468,7 @@
       </c>
       <c r="O99" s="10" t="inlineStr">
         <is>
-          <t>Partly built, no tagged test</t>
+          <t>Partly built (flags only)</t>
         </is>
       </c>
       <c r="P99" s="10" t="inlineStr">

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -8014,7 +8014,7 @@
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>FIN-02</t>
+          <t>/cashier</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="P94" s="10" t="inlineStr">
         <is>
-          <t>Shift screens come next. New permission fin.shift.reconcile goes to built-in roles only.</t>
+          <t>Cashier shift page built (open, close with counts, review, reconcile). Not covered by a browser test yet. New permission fin.shift.reconcile goes to built-in roles only.</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>FIN-03</t>
+          <t>/admin (Business date)</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="P99" s="10" t="inlineStr">
         <is>
-          <t>Flags built and tested. The gate that stops the roll while a blocking flag is open is not built.</t>
+          <t>Flags shown in Admin, Business date. The gate that stops the roll while a blocking flag is open is not built.</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'R1 Requirements'!$A$1:$O$108</definedName>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13">
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P117"/>
+  <dimension ref="A1:P121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9870,6 +9870,318 @@
         </is>
       </c>
       <c r="P117" s="10" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>GRP-001</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>All branches</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>A built-in Group Manager role and the permission rpt.group.view exist; only System Administrator, General Manager and Group Manager hold the permission.</t>
+        </is>
+      </c>
+      <c r="E118" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G118" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H118" s="10" t="inlineStr">
+        <is>
+          <t>rpt.group.view</t>
+        </is>
+      </c>
+      <c r="I118" s="10" t="inlineStr"/>
+      <c r="J118" s="10" t="inlineStr">
+        <is>
+          <t>a hotel group with several branches</t>
+        </is>
+      </c>
+      <c r="K118" s="10" t="inlineStr">
+        <is>
+          <t>an owner wants a view-only manager for the whole group</t>
+        </is>
+      </c>
+      <c r="L118" s="10" t="inlineStr">
+        <is>
+          <t>they assign the Group Manager role branch by branch, and that person can look but not post or change anything</t>
+        </is>
+      </c>
+      <c r="M118" s="10" t="inlineStr">
+        <is>
+          <t>20261013120000_group_view.sql</t>
+        </is>
+      </c>
+      <c r="N118" s="10" t="inlineStr">
+        <is>
+          <t>35_group_view (5)</t>
+        </is>
+      </c>
+      <c r="O118" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P118" s="10" t="inlineStr">
+        <is>
+          <t>Custom roles copied earlier do not get the new permission; say so when releasing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>GRP-002</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>All branches</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>One call shows every branch the person may see: occupancy, in house, arrivals and departures to come, approvals, repairs and last night revenue, with group totals. Revenue is totalled per currency.</t>
+        </is>
+      </c>
+      <c r="E119" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F119" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G119" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H119" s="10" t="inlineStr">
+        <is>
+          <t>rpt.group.view</t>
+        </is>
+      </c>
+      <c r="I119" s="10" t="inlineStr"/>
+      <c r="J119" s="10" t="inlineStr">
+        <is>
+          <t>a group with a Lagos and an Abuja branch</t>
+        </is>
+      </c>
+      <c r="K119" s="10" t="inlineStr">
+        <is>
+          <t>a group manager opens All branches</t>
+        </is>
+      </c>
+      <c r="L119" s="10" t="inlineStr">
+        <is>
+          <t>they see both branches with figures from the database, never another hotel group, and staff without the permission are refused</t>
+        </is>
+      </c>
+      <c r="M119" s="10" t="inlineStr">
+        <is>
+          <t>group_overview; /group screen</t>
+        </is>
+      </c>
+      <c r="N119" s="10" t="inlineStr">
+        <is>
+          <t>35_group_view (10)</t>
+        </is>
+      </c>
+      <c r="O119" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P119" s="10" t="inlineStr">
+        <is>
+          <t>Figures are read from each branch own business date. No arithmetic in the browser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>GRP-003</t>
+        </is>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>All branches</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>A Group Manager sees only the branches they are assigned to, and cannot post charges or check guests in.</t>
+        </is>
+      </c>
+      <c r="E120" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F120" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G120" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H120" s="10" t="inlineStr">
+        <is>
+          <t>rpt.group.view</t>
+        </is>
+      </c>
+      <c r="I120" s="10" t="inlineStr"/>
+      <c r="J120" s="10" t="inlineStr">
+        <is>
+          <t>a Group Manager assigned to one branch</t>
+        </is>
+      </c>
+      <c r="K120" s="10" t="inlineStr">
+        <is>
+          <t>a second branch is assigned</t>
+        </is>
+      </c>
+      <c r="L120" s="10" t="inlineStr">
+        <is>
+          <t>the second branch appears; the role never gets write permissions</t>
+        </is>
+      </c>
+      <c r="M120" s="10" t="inlineStr">
+        <is>
+          <t>assign_role (existing); group_overview</t>
+        </is>
+      </c>
+      <c r="N120" s="10" t="inlineStr">
+        <is>
+          <t>35_group_view (3)</t>
+        </is>
+      </c>
+      <c r="O120" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P120" s="10" t="inlineStr">
+        <is>
+          <t>Access is per branch, using the existing role assignment screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>GRP-004</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>All branches (Copy setup)</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>A new branch can copy room types, rate plans and prices from an existing branch, once, into an empty branch.</t>
+        </is>
+      </c>
+      <c r="E121" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G121" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H121" s="10" t="inlineStr">
+        <is>
+          <t>setup.room.manage, setup.rate.manage</t>
+        </is>
+      </c>
+      <c r="I121" s="10" t="inlineStr"/>
+      <c r="J121" s="10" t="inlineStr">
+        <is>
+          <t>a new empty branch</t>
+        </is>
+      </c>
+      <c r="K121" s="10" t="inlineStr">
+        <is>
+          <t>the owner copies setup from the first branch</t>
+        </is>
+      </c>
+      <c r="L121" s="10" t="inlineStr">
+        <is>
+          <t>room types, rate plans and prices appear on the new branch and point at its own room types; rooms are not copied; a second copy is refused; the copy is audited</t>
+        </is>
+      </c>
+      <c r="M121" s="10" t="inlineStr">
+        <is>
+          <t>copy_property_setup</t>
+        </is>
+      </c>
+      <c r="N121" s="10" t="inlineStr">
+        <is>
+          <t>35_group_view (13)</t>
+        </is>
+      </c>
+      <c r="O121" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P121" s="10" t="inlineStr">
+        <is>
+          <t>Taxes, charge codes and payment methods already arrive with every new branch.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'R1 Requirements'!$A$1:$O$108</definedName>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13">
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P117"/>
+  <dimension ref="A1:P119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9870,6 +9870,162 @@
         </is>
       </c>
       <c r="P117" s="10" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>RPT-005</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>Revenue by booking source: bookings, cancellations, no-shows, room nights, room revenue and average rate for each source in a date range.</t>
+        </is>
+      </c>
+      <c r="E118" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G118" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H118" s="10" t="inlineStr">
+        <is>
+          <t>rpt.finance.view</t>
+        </is>
+      </c>
+      <c r="I118" s="10" t="inlineStr"/>
+      <c r="J118" s="10" t="inlineStr">
+        <is>
+          <t>bookings from direct, phone and company sources</t>
+        </is>
+      </c>
+      <c r="K118" s="10" t="inlineStr">
+        <is>
+          <t>the accountant picks a date range</t>
+        </is>
+      </c>
+      <c r="L118" s="10" t="inlineStr">
+        <is>
+          <t>each source shows its own counts and room revenue (room charges only, before tax); cancelled bookings add no nights</t>
+        </is>
+      </c>
+      <c r="M118" s="10" t="inlineStr">
+        <is>
+          <t>20261013130000_source_ageing_reports.sql: report_revenue_by_source; Reports, By booking source tab</t>
+        </is>
+      </c>
+      <c r="N118" s="10" t="inlineStr">
+        <is>
+          <t>36_source_ageing (13)</t>
+        </is>
+      </c>
+      <c r="O118" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P118" s="10" t="inlineStr">
+        <is>
+          <t>Bookings counted by arrival date; revenue by posting date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>RPT-006</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>Ageing of unpaid balances by booking source: current, 1 to 7, 8 to 30, 31 to 60 and over 60 days since the due departure, plus credit held.</t>
+        </is>
+      </c>
+      <c r="E119" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F119" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G119" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H119" s="10" t="inlineStr">
+        <is>
+          <t>rpt.finance.view</t>
+        </is>
+      </c>
+      <c r="I119" s="10" t="inlineStr"/>
+      <c r="J119" s="10" t="inlineStr">
+        <is>
+          <t>guests and companies who left owing money</t>
+        </is>
+      </c>
+      <c r="K119" s="10" t="inlineStr">
+        <is>
+          <t>the accountant opens the Ageing tab</t>
+        </is>
+      </c>
+      <c r="L119" s="10" t="inlineStr">
+        <is>
+          <t>each source shows what is owed in each age column; paid bills drop out; overpayments show as credit held; the total matches Outstanding balances</t>
+        </is>
+      </c>
+      <c r="M119" s="10" t="inlineStr">
+        <is>
+          <t>report_balance_ageing; Reports, Ageing tab</t>
+        </is>
+      </c>
+      <c r="N119" s="10" t="inlineStr">
+        <is>
+          <t>36_source_ageing (11)</t>
+        </is>
+      </c>
+      <c r="O119" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P119" s="10" t="inlineStr">
+        <is>
+          <t>Guests still staying count as current.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'R1 Requirements'!$A$1:$O$108</definedName>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13">
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P117"/>
+  <dimension ref="A1:P122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9870,6 +9870,388 @@
         </is>
       </c>
       <c r="P117" s="10" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>AI-001</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>AI helpers</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>Dashboard, Admin</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>AI helpers are off for every hotel until a System Administrator or General Manager switches them on, with a monthly limit; the switch is audited.</t>
+        </is>
+      </c>
+      <c r="E118" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G118" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H118" s="10" t="inlineStr">
+        <is>
+          <t>adm.ai.manage</t>
+        </is>
+      </c>
+      <c r="I118" s="10" t="inlineStr"/>
+      <c r="J118" s="10" t="inlineStr">
+        <is>
+          <t>a new hotel</t>
+        </is>
+      </c>
+      <c r="K118" s="10" t="inlineStr">
+        <is>
+          <t>a manager opens Admin, AI helpers</t>
+        </is>
+      </c>
+      <c r="L118" s="10" t="inlineStr">
+        <is>
+          <t>nothing runs until they switch it on and the change is in the audit log</t>
+        </is>
+      </c>
+      <c r="M118" s="10" t="inlineStr">
+        <is>
+          <t>20261013140000_ai_morning_brief.sql: set_ai_settings, ai_status; Admin, AI helpers tab</t>
+        </is>
+      </c>
+      <c r="N118" s="10" t="inlineStr">
+        <is>
+          <t>37_ai_brief (11)</t>
+        </is>
+      </c>
+      <c r="O118" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P118" s="10" t="inlineStr">
+        <is>
+          <t>Custom roles copied earlier do not get adm.ai.manage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>AI-002</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>AI helpers</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>Dashboard, Admin</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>The facts sent to the AI are counts and money lines built by the database: no guest names, ID details, room numbers or card data.</t>
+        </is>
+      </c>
+      <c r="E119" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F119" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G119" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H119" s="10" t="inlineStr">
+        <is>
+          <t>rpt.finance.view, rpt.operations.view</t>
+        </is>
+      </c>
+      <c r="I119" s="10" t="inlineStr"/>
+      <c r="J119" s="10" t="inlineStr">
+        <is>
+          <t>a hotel with guests, approvals and overdue bills</t>
+        </is>
+      </c>
+      <c r="K119" s="10" t="inlineStr">
+        <is>
+          <t>a brief is started</t>
+        </is>
+      </c>
+      <c r="L119" s="10" t="inlineStr">
+        <is>
+          <t>the facts hold only business date, last night, today, attention figures and plain lines, and overdue money matches the ledger</t>
+        </is>
+      </c>
+      <c r="M119" s="10" t="inlineStr">
+        <is>
+          <t>20261013140000_ai_morning_brief.sql: ai_morning_brief_start, app.morning_brief_facts</t>
+        </is>
+      </c>
+      <c r="N119" s="10" t="inlineStr">
+        <is>
+          <t>37_ai_brief (11)</t>
+        </is>
+      </c>
+      <c r="O119" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P119" s="10" t="inlineStr">
+        <is>
+          <t>Overdue means unpaid more than 30 days after departure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>AI-003</t>
+        </is>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>AI helpers</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>Dashboard, Admin</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>Each hotel has a monthly limit on AI drafts; failed calls do not count; a call can be finished once, by the person who started it.</t>
+        </is>
+      </c>
+      <c r="E120" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F120" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G120" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H120" s="10" t="inlineStr">
+        <is>
+          <t>rpt.finance.view</t>
+        </is>
+      </c>
+      <c r="I120" s="10" t="inlineStr"/>
+      <c r="J120" s="10" t="inlineStr">
+        <is>
+          <t>a limit of 2</t>
+        </is>
+      </c>
+      <c r="K120" s="10" t="inlineStr">
+        <is>
+          <t>a third brief is requested</t>
+        </is>
+      </c>
+      <c r="L120" s="10" t="inlineStr">
+        <is>
+          <t>it is refused until a failed call frees a slot or the month turns</t>
+        </is>
+      </c>
+      <c r="M120" s="10" t="inlineStr">
+        <is>
+          <t>20261013140000_ai_morning_brief.sql: ai_call_finish</t>
+        </is>
+      </c>
+      <c r="N120" s="10" t="inlineStr">
+        <is>
+          <t>37_ai_brief (5)</t>
+        </is>
+      </c>
+      <c r="O120" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P120" s="10" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>AI-004</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>AI helpers</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>Dashboard, Admin</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>Only finance and operations viewers can ask for the brief; the usage log and settings cannot be written or read directly by the browser.</t>
+        </is>
+      </c>
+      <c r="E121" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G121" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H121" s="10" t="inlineStr">
+        <is>
+          <t>rpt.finance.view, rpt.operations.view</t>
+        </is>
+      </c>
+      <c r="I121" s="10" t="inlineStr"/>
+      <c r="J121" s="10" t="inlineStr">
+        <is>
+          <t>front desk, housekeeping, another hotel</t>
+        </is>
+      </c>
+      <c r="K121" s="10" t="inlineStr">
+        <is>
+          <t>they ask for the brief or touch the tables</t>
+        </is>
+      </c>
+      <c r="L121" s="10" t="inlineStr">
+        <is>
+          <t>they are refused</t>
+        </is>
+      </c>
+      <c r="M121" s="10" t="inlineStr">
+        <is>
+          <t>20261013140000_ai_morning_brief.sql</t>
+        </is>
+      </c>
+      <c r="N121" s="10" t="inlineStr">
+        <is>
+          <t>37_ai_brief (7)</t>
+        </is>
+      </c>
+      <c r="O121" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P121" s="10" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>AI-005</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>AI helpers</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>Dashboard, Admin</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>The server accepts an AI draft only when every number in it is in the database facts; otherwise it shows the plain figures. The key stays on the server and only the fact lines are sent.</t>
+        </is>
+      </c>
+      <c r="E122" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F122" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G122" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H122" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="10" t="inlineStr"/>
+      <c r="J122" s="10" t="inlineStr">
+        <is>
+          <t>a draft that rounds or invents a figure</t>
+        </is>
+      </c>
+      <c r="K122" s="10" t="inlineStr">
+        <is>
+          <t>the brief is written</t>
+        </is>
+      </c>
+      <c r="L122" s="10" t="inlineStr">
+        <is>
+          <t>the plain database lines are shown instead, with a note</t>
+        </is>
+      </c>
+      <c r="M122" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/ai-brief.ts, ai-brief.functions.ts, Dashboard morning brief card</t>
+        </is>
+      </c>
+      <c r="N122" s="10" t="inlineStr">
+        <is>
+          <t>browser unit: ai-brief-unit (8)</t>
+        </is>
+      </c>
+      <c r="O122" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P122" s="10" t="inlineStr">
+        <is>
+          <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13">
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P122"/>
+  <dimension ref="A1:P125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10250,6 +10250,236 @@
       <c r="P122" s="10" t="inlineStr">
         <is>
           <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>SET-010</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>Setup, Rooms</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>A hotel can add room types and rooms from one checked list: preview first, then all or nothing. Existing codes and room names are skipped, so repeating adds nothing.</t>
+        </is>
+      </c>
+      <c r="E123" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F123" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G123" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H123" s="10" t="inlineStr">
+        <is>
+          <t>setup.room.manage</t>
+        </is>
+      </c>
+      <c r="I123" s="10" t="inlineStr"/>
+      <c r="J123" s="10" t="inlineStr">
+        <is>
+          <t>a list of room types and rooms</t>
+        </is>
+      </c>
+      <c r="K123" s="10" t="inlineStr">
+        <is>
+          <t>the manager previews and then applies it</t>
+        </is>
+      </c>
+      <c r="L123" s="10" t="inlineStr">
+        <is>
+          <t>the preview writes nothing; apply adds every valid item or none (bad name, unknown type, over 500 rooms, over the plan limit); a repeat adds nothing; the import is audited</t>
+        </is>
+      </c>
+      <c r="M123" s="10" t="inlineStr">
+        <is>
+          <t>20261013150000_setup_import.sql: apply_setup_import</t>
+        </is>
+      </c>
+      <c r="N123" s="10" t="inlineStr">
+        <is>
+          <t>38_setup_import (29)</t>
+        </is>
+      </c>
+      <c r="O123" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P123" s="10" t="inlineStr">
+        <is>
+          <t>The AI only drafts the list. This function is the check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>AI-006</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>AI helpers</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>Setup, Rooms</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>The setup import assistant starts only when AI is on and under the monthly limit, and the AI sees only existing room type codes and a room count.</t>
+        </is>
+      </c>
+      <c r="E124" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F124" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G124" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H124" s="10" t="inlineStr">
+        <is>
+          <t>setup.room.manage</t>
+        </is>
+      </c>
+      <c r="I124" s="10" t="inlineStr"/>
+      <c r="J124" s="10" t="inlineStr">
+        <is>
+          <t>AI switched on with a limit of 1</t>
+        </is>
+      </c>
+      <c r="K124" s="10" t="inlineStr">
+        <is>
+          <t>an import draft is started twice</t>
+        </is>
+      </c>
+      <c r="L124" s="10" t="inlineStr">
+        <is>
+          <t>the second is refused until the first fails; front desk and other hotels are refused</t>
+        </is>
+      </c>
+      <c r="M124" s="10" t="inlineStr">
+        <is>
+          <t>20261013150000_setup_import.sql: ai_import_start, app.ai_begin</t>
+        </is>
+      </c>
+      <c r="N124" s="10" t="inlineStr">
+        <is>
+          <t>38_setup_import (8)</t>
+        </is>
+      </c>
+      <c r="O124" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P124" s="10" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>AI-007</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>AI helpers</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>Setup, Rooms</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>Pasted text with an email, phone or card number is refused before anything is sent; the draft may only contain rooms, floors, guest limits and type names that are in the pasted text.</t>
+        </is>
+      </c>
+      <c r="E125" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G125" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H125" s="10" t="inlineStr">
+        <is>
+          <t>setup.room.manage</t>
+        </is>
+      </c>
+      <c r="I125" s="10" t="inlineStr"/>
+      <c r="J125" s="10" t="inlineStr">
+        <is>
+          <t>a pasted list</t>
+        </is>
+      </c>
+      <c r="K125" s="10" t="inlineStr">
+        <is>
+          <t>the assistant drafts it</t>
+        </is>
+      </c>
+      <c r="L125" s="10" t="inlineStr">
+        <is>
+          <t>invented rooms, floors and limits are dropped with a note; a draft with no matching rooms is an error</t>
+        </is>
+      </c>
+      <c r="M125" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/setup-import.ts, setup-import.functions.ts, Import from a list on Setup, Rooms</t>
+        </is>
+      </c>
+      <c r="N125" s="10" t="inlineStr">
+        <is>
+          <t>browser unit: setup-import-unit (9)</t>
+        </is>
+      </c>
+      <c r="O125" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P125" s="10" t="inlineStr">
+        <is>
+          <t>Needs ANTHROPIC_API_KEY on the server. Not set yet.</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'R1 Requirements'!$A$1:$O$108</definedName>
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -605,23 +605,23 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Built+tested (database only)</t>
+          <t>Built+tested (known limit)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Built+tested (known limit)</t>
+          <t>Not built</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -631,7 +631,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Not built</t>
+          <t>Partly built, no tagged test</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -641,20 +641,10 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Partly built, no tagged test</t>
+          <t>R1b</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>R1b</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
         <v>3</v>
       </c>
     </row>
@@ -669,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P117"/>
+  <dimension ref="A1:T117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -770,6 +760,10 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
@@ -848,6 +842,10 @@
         </is>
       </c>
       <c r="P2" s="10" t="inlineStr"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -926,6 +924,10 @@
         </is>
       </c>
       <c r="P3" s="10" t="inlineStr"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -1004,6 +1006,10 @@
         </is>
       </c>
       <c r="P4" s="10" t="inlineStr"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -1082,6 +1088,10 @@
         </is>
       </c>
       <c r="P5" s="10" t="inlineStr"/>
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="10" t="n"/>
+      <c r="S5" s="10" t="n"/>
+      <c r="T5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -1160,6 +1170,10 @@
         </is>
       </c>
       <c r="P6" s="10" t="inlineStr"/>
+      <c r="Q6" s="10" t="n"/>
+      <c r="R6" s="10" t="n"/>
+      <c r="S6" s="10" t="n"/>
+      <c r="T6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -1238,6 +1252,10 @@
         </is>
       </c>
       <c r="P7" s="10" t="inlineStr"/>
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="10" t="n"/>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -1320,6 +1338,10 @@
           <t>Adding a property: System Administrator and General Manager (ADM-002), within plans.max_properties.</t>
         </is>
       </c>
+      <c r="Q8" s="10" t="n"/>
+      <c r="R8" s="10" t="n"/>
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -1402,6 +1424,10 @@
           <t>Platform console /platform (wave 2 item 2): extend trial, activate or extend paid period, suspend, change plan, cancel; each with a reason, logged in subscription_history with the operator.</t>
         </is>
       </c>
+      <c r="Q9" s="10" t="n"/>
+      <c r="R9" s="10" t="n"/>
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -1484,6 +1510,10 @@
           <t>Corrected 6 Oct 2026: before wave 2 item 2 there was no platform staff role at all; the earlier "Built, no tagged test" was wrong.</t>
         </is>
       </c>
+      <c r="Q10" s="10" t="n"/>
+      <c r="R10" s="10" t="n"/>
+      <c r="S10" s="10" t="n"/>
+      <c r="T10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -1562,6 +1592,10 @@
         </is>
       </c>
       <c r="P11" s="10" t="inlineStr"/>
+      <c r="Q11" s="10" t="n"/>
+      <c r="R11" s="10" t="n"/>
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -1640,6 +1674,10 @@
         </is>
       </c>
       <c r="P12" s="10" t="inlineStr"/>
+      <c r="Q12" s="10" t="n"/>
+      <c r="R12" s="10" t="n"/>
+      <c r="S12" s="10" t="n"/>
+      <c r="T12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -1718,6 +1756,10 @@
         </is>
       </c>
       <c r="P13" s="10" t="inlineStr"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="n"/>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -1796,6 +1838,10 @@
         </is>
       </c>
       <c r="P14" s="10" t="inlineStr"/>
+      <c r="Q14" s="10" t="n"/>
+      <c r="R14" s="10" t="n"/>
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -1878,6 +1924,10 @@
           <t>Invites are sent by a Vercel server function (not an Edge Function).</t>
         </is>
       </c>
+      <c r="Q15" s="10" t="n"/>
+      <c r="R15" s="10" t="n"/>
+      <c r="S15" s="10" t="n"/>
+      <c r="T15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -1956,6 +2006,10 @@
         </is>
       </c>
       <c r="P16" s="10" t="inlineStr"/>
+      <c r="Q16" s="10" t="n"/>
+      <c r="R16" s="10" t="n"/>
+      <c r="S16" s="10" t="n"/>
+      <c r="T16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -2034,6 +2088,10 @@
         </is>
       </c>
       <c r="P17" s="10" t="inlineStr"/>
+      <c r="Q17" s="10" t="n"/>
+      <c r="R17" s="10" t="n"/>
+      <c r="S17" s="10" t="n"/>
+      <c r="T17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -2112,6 +2170,10 @@
         </is>
       </c>
       <c r="P18" s="10" t="inlineStr"/>
+      <c r="Q18" s="10" t="n"/>
+      <c r="R18" s="10" t="n"/>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -2190,6 +2252,10 @@
         </is>
       </c>
       <c r="P19" s="10" t="inlineStr"/>
+      <c r="Q19" s="10" t="n"/>
+      <c r="R19" s="10" t="n"/>
+      <c r="S19" s="10" t="n"/>
+      <c r="T19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
@@ -2268,6 +2334,10 @@
         </is>
       </c>
       <c r="P20" s="10" t="inlineStr"/>
+      <c r="Q20" s="10" t="n"/>
+      <c r="R20" s="10" t="n"/>
+      <c r="S20" s="10" t="n"/>
+      <c r="T20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -2346,6 +2416,10 @@
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr"/>
+      <c r="Q21" s="10" t="n"/>
+      <c r="R21" s="10" t="n"/>
+      <c r="S21" s="10" t="n"/>
+      <c r="T21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -2424,6 +2498,10 @@
         </is>
       </c>
       <c r="P22" s="10" t="inlineStr"/>
+      <c r="Q22" s="10" t="n"/>
+      <c r="R22" s="10" t="n"/>
+      <c r="S22" s="10" t="n"/>
+      <c r="T22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -2506,6 +2584,10 @@
           <t>export_data (audited), Reports &gt; Export.</t>
         </is>
       </c>
+      <c r="Q23" s="10" t="n"/>
+      <c r="R23" s="10" t="n"/>
+      <c r="S23" s="10" t="n"/>
+      <c r="T23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -2584,6 +2666,10 @@
         </is>
       </c>
       <c r="P24" s="10" t="inlineStr"/>
+      <c r="Q24" s="10" t="n"/>
+      <c r="R24" s="10" t="n"/>
+      <c r="S24" s="10" t="n"/>
+      <c r="T24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -2666,6 +2752,10 @@
           <t>Corrected 6 Oct 2026: room types and occupancy limits (save_room_type, max adults and children; Setup, Room types) exist; the overbooking allowance does not exist anywhere in the app.</t>
         </is>
       </c>
+      <c r="Q25" s="10" t="n"/>
+      <c r="R25" s="10" t="n"/>
+      <c r="S25" s="10" t="n"/>
+      <c r="T25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
@@ -2748,6 +2838,10 @@
           <t>A room cannot be retired while a guest is in it ([E_ROOM_OCCUPIED], checked first) or while upcoming bookings are assigned to it ([E_ROOM_BOOKED], names up to 5 booking numbers): confirmed, or tentative with an unexpired hold, from the business date forward (decisions of 6 Oct 2026). Retiring a room that is already retired is safe to repeat; renaming and floor changes still work.</t>
         </is>
       </c>
+      <c r="Q26" s="10" t="n"/>
+      <c r="R26" s="10" t="n"/>
+      <c r="S26" s="10" t="n"/>
+      <c r="T26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
@@ -2826,6 +2920,10 @@
         </is>
       </c>
       <c r="P27" s="10" t="inlineStr"/>
+      <c r="Q27" s="10" t="n"/>
+      <c r="R27" s="10" t="n"/>
+      <c r="S27" s="10" t="n"/>
+      <c r="T27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -2904,6 +3002,10 @@
         </is>
       </c>
       <c r="P28" s="10" t="inlineStr"/>
+      <c r="Q28" s="10" t="n"/>
+      <c r="R28" s="10" t="n"/>
+      <c r="S28" s="10" t="n"/>
+      <c r="T28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -2982,6 +3084,10 @@
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr"/>
+      <c r="Q29" s="10" t="n"/>
+      <c r="R29" s="10" t="n"/>
+      <c r="S29" s="10" t="n"/>
+      <c r="T29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
@@ -3060,6 +3166,10 @@
         </is>
       </c>
       <c r="P30" s="10" t="inlineStr"/>
+      <c r="Q30" s="10" t="n"/>
+      <c r="R30" s="10" t="n"/>
+      <c r="S30" s="10" t="n"/>
+      <c r="T30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
@@ -3138,6 +3248,10 @@
         </is>
       </c>
       <c r="P31" s="10" t="inlineStr"/>
+      <c r="Q31" s="10" t="n"/>
+      <c r="R31" s="10" t="n"/>
+      <c r="S31" s="10" t="n"/>
+      <c r="T31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
@@ -3216,6 +3330,10 @@
         </is>
       </c>
       <c r="P32" s="10" t="inlineStr"/>
+      <c r="Q32" s="10" t="n"/>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="10" t="n"/>
+      <c r="T32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
@@ -3294,6 +3412,10 @@
         </is>
       </c>
       <c r="P33" s="10" t="inlineStr"/>
+      <c r="Q33" s="10" t="n"/>
+      <c r="R33" s="10" t="n"/>
+      <c r="S33" s="10" t="n"/>
+      <c r="T33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
@@ -3372,6 +3494,10 @@
         </is>
       </c>
       <c r="P34" s="10" t="inlineStr"/>
+      <c r="Q34" s="10" t="n"/>
+      <c r="R34" s="10" t="n"/>
+      <c r="S34" s="10" t="n"/>
+      <c r="T34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
@@ -3450,6 +3576,10 @@
         </is>
       </c>
       <c r="P35" s="10" t="inlineStr"/>
+      <c r="Q35" s="10" t="n"/>
+      <c r="R35" s="10" t="n"/>
+      <c r="S35" s="10" t="n"/>
+      <c r="T35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
@@ -3528,6 +3658,10 @@
         </is>
       </c>
       <c r="P36" s="10" t="inlineStr"/>
+      <c r="Q36" s="10" t="n"/>
+      <c r="R36" s="10" t="n"/>
+      <c r="S36" s="10" t="n"/>
+      <c r="T36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
@@ -3606,6 +3740,10 @@
         </is>
       </c>
       <c r="P37" s="10" t="inlineStr"/>
+      <c r="Q37" s="10" t="n"/>
+      <c r="R37" s="10" t="n"/>
+      <c r="S37" s="10" t="n"/>
+      <c r="T37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
@@ -3684,6 +3822,10 @@
         </is>
       </c>
       <c r="P38" s="10" t="inlineStr"/>
+      <c r="Q38" s="10" t="n"/>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="10" t="n"/>
+      <c r="T38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -3762,6 +3904,10 @@
         </is>
       </c>
       <c r="P39" s="10" t="inlineStr"/>
+      <c r="Q39" s="10" t="n"/>
+      <c r="R39" s="10" t="n"/>
+      <c r="S39" s="10" t="n"/>
+      <c r="T39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
@@ -3840,6 +3986,10 @@
         </is>
       </c>
       <c r="P40" s="10" t="inlineStr"/>
+      <c r="Q40" s="10" t="n"/>
+      <c r="R40" s="10" t="n"/>
+      <c r="S40" s="10" t="n"/>
+      <c r="T40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
@@ -3918,6 +4068,10 @@
         </is>
       </c>
       <c r="P41" s="10" t="inlineStr"/>
+      <c r="Q41" s="10" t="n"/>
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="10" t="n"/>
+      <c r="T41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
@@ -3996,6 +4150,10 @@
         </is>
       </c>
       <c r="P42" s="10" t="inlineStr"/>
+      <c r="Q42" s="10" t="n"/>
+      <c r="R42" s="10" t="n"/>
+      <c r="S42" s="10" t="n"/>
+      <c r="T42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
@@ -4065,17 +4223,37 @@
       </c>
       <c r="N43" s="10" t="inlineStr">
         <is>
-          <t>29_untagged_rows (7)</t>
+          <t>29_untagged_rows (7); 39_group_booking</t>
         </is>
       </c>
       <c r="O43" s="10" t="inlineStr">
         <is>
-          <t>Built+tested (database only)</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P43" s="10" t="inlineStr">
         <is>
-          <t>save_group_booking exists and the booking form picks a group; there is no screen to create a group.</t>
+          <t>Groups list and group page (rooms</t>
+        </is>
+      </c>
+      <c r="Q43" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> totals</t>
+        </is>
+      </c>
+      <c r="R43" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> cancel</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> reactivate</t>
+        </is>
+      </c>
+      <c r="T43" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> add a room) at /reservations/groups. Groups are still created from the booking form.</t>
         </is>
       </c>
     </row>
@@ -4147,19 +4325,23 @@
       </c>
       <c r="N44" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (2); 26_small_fixes (4); 29_untagged_rows (6)</t>
+          <t>17_more_features (2); 26_small_fixes (4); 29_untagged_rows (6); 39_group_booking</t>
         </is>
       </c>
       <c r="O44" s="10" t="inlineStr">
         <is>
-          <t>Built+tested (database only)</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P44" s="10" t="inlineStr">
         <is>
-          <t>set_arrival_ready exists; no screen shows the flag yet (skipped 6 Oct 2026).</t>
-        </is>
-      </c>
+          <t>Mark ready button and badge on the booking page; badge on the Front Desk arrivals list (v_arrivals.arrival_ready).</t>
+        </is>
+      </c>
+      <c r="Q44" s="10" t="n"/>
+      <c r="R44" s="10" t="n"/>
+      <c r="S44" s="10" t="n"/>
+      <c r="T44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
@@ -4238,6 +4420,10 @@
         </is>
       </c>
       <c r="P45" s="10" t="inlineStr"/>
+      <c r="Q45" s="10" t="n"/>
+      <c r="R45" s="10" t="n"/>
+      <c r="S45" s="10" t="n"/>
+      <c r="T45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
@@ -4316,6 +4502,10 @@
         </is>
       </c>
       <c r="P46" s="10" t="inlineStr"/>
+      <c r="Q46" s="10" t="n"/>
+      <c r="R46" s="10" t="n"/>
+      <c r="S46" s="10" t="n"/>
+      <c r="T46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
@@ -4398,6 +4588,10 @@
           <t>The check-in and walk-in screens force the registration card tick; a direct database call that omits it is not refused (decision 6 Oct 2026). Drawn signature later.</t>
         </is>
       </c>
+      <c r="Q47" s="10" t="n"/>
+      <c r="R47" s="10" t="n"/>
+      <c r="S47" s="10" t="n"/>
+      <c r="T47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
@@ -4476,6 +4670,10 @@
         </is>
       </c>
       <c r="P48" s="10" t="inlineStr"/>
+      <c r="Q48" s="10" t="n"/>
+      <c r="R48" s="10" t="n"/>
+      <c r="S48" s="10" t="n"/>
+      <c r="T48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
@@ -4554,6 +4752,10 @@
         </is>
       </c>
       <c r="P49" s="10" t="inlineStr"/>
+      <c r="Q49" s="10" t="n"/>
+      <c r="R49" s="10" t="n"/>
+      <c r="S49" s="10" t="n"/>
+      <c r="T49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
@@ -4632,6 +4834,10 @@
         </is>
       </c>
       <c r="P50" s="10" t="inlineStr"/>
+      <c r="Q50" s="10" t="n"/>
+      <c r="R50" s="10" t="n"/>
+      <c r="S50" s="10" t="n"/>
+      <c r="T50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
@@ -4714,6 +4920,10 @@
           <t>Dearer room type: front desk charges the new rate; keeping it needs fo.upgrade.complimentary (SYSADMIN, GM, FOM), audited.</t>
         </is>
       </c>
+      <c r="Q51" s="10" t="n"/>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="10" t="n"/>
+      <c r="T51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
@@ -4792,6 +5002,10 @@
         </is>
       </c>
       <c r="P52" s="10" t="inlineStr"/>
+      <c r="Q52" s="10" t="n"/>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="10" t="n"/>
+      <c r="T52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
@@ -4870,6 +5084,10 @@
         </is>
       </c>
       <c r="P53" s="10" t="inlineStr"/>
+      <c r="Q53" s="10" t="n"/>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="10" t="n"/>
+      <c r="T53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
@@ -4948,6 +5166,10 @@
         </is>
       </c>
       <c r="P54" s="10" t="inlineStr"/>
+      <c r="Q54" s="10" t="n"/>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
@@ -5026,6 +5248,10 @@
         </is>
       </c>
       <c r="P55" s="10" t="inlineStr"/>
+      <c r="Q55" s="10" t="n"/>
+      <c r="R55" s="10" t="n"/>
+      <c r="S55" s="10" t="n"/>
+      <c r="T55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
@@ -5104,6 +5330,10 @@
         </is>
       </c>
       <c r="P56" s="10" t="inlineStr"/>
+      <c r="Q56" s="10" t="n"/>
+      <c r="R56" s="10" t="n"/>
+      <c r="S56" s="10" t="n"/>
+      <c r="T56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
@@ -5182,6 +5412,10 @@
         </is>
       </c>
       <c r="P57" s="10" t="inlineStr"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
@@ -5260,6 +5494,10 @@
         </is>
       </c>
       <c r="P58" s="10" t="inlineStr"/>
+      <c r="Q58" s="10" t="n"/>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
@@ -5338,6 +5576,10 @@
         </is>
       </c>
       <c r="P59" s="10" t="inlineStr"/>
+      <c r="Q59" s="10" t="n"/>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="10" t="n"/>
+      <c r="T59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
@@ -5416,6 +5658,10 @@
         </is>
       </c>
       <c r="P60" s="10" t="inlineStr"/>
+      <c r="Q60" s="10" t="n"/>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
@@ -5494,6 +5740,10 @@
         </is>
       </c>
       <c r="P61" s="10" t="inlineStr"/>
+      <c r="Q61" s="10" t="n"/>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
@@ -5572,6 +5822,10 @@
         </is>
       </c>
       <c r="P62" s="10" t="inlineStr"/>
+      <c r="Q62" s="10" t="n"/>
+      <c r="R62" s="10" t="n"/>
+      <c r="S62" s="10" t="n"/>
+      <c r="T62" s="10" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
@@ -5650,6 +5904,10 @@
         </is>
       </c>
       <c r="P63" s="10" t="inlineStr"/>
+      <c r="Q63" s="10" t="n"/>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
+      <c r="T63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
@@ -5728,6 +5986,10 @@
         </is>
       </c>
       <c r="P64" s="10" t="inlineStr"/>
+      <c r="Q64" s="10" t="n"/>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="10" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
@@ -5806,6 +6068,10 @@
         </is>
       </c>
       <c r="P65" s="10" t="inlineStr"/>
+      <c r="Q65" s="10" t="n"/>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
@@ -5884,6 +6150,10 @@
         </is>
       </c>
       <c r="P66" s="10" t="inlineStr"/>
+      <c r="Q66" s="10" t="n"/>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
@@ -5962,6 +6232,10 @@
         </is>
       </c>
       <c r="P67" s="10" t="inlineStr"/>
+      <c r="Q67" s="10" t="n"/>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
+      <c r="T67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
@@ -6040,6 +6314,10 @@
         </is>
       </c>
       <c r="P68" s="10" t="inlineStr"/>
+      <c r="Q68" s="10" t="n"/>
+      <c r="R68" s="10" t="n"/>
+      <c r="S68" s="10" t="n"/>
+      <c r="T68" s="10" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
@@ -6118,6 +6396,10 @@
         </is>
       </c>
       <c r="P69" s="10" t="inlineStr"/>
+      <c r="Q69" s="10" t="n"/>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
@@ -6196,6 +6478,10 @@
         </is>
       </c>
       <c r="P70" s="10" t="inlineStr"/>
+      <c r="Q70" s="10" t="n"/>
+      <c r="R70" s="10" t="n"/>
+      <c r="S70" s="10" t="n"/>
+      <c r="T70" s="10" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
@@ -6274,6 +6560,10 @@
         </is>
       </c>
       <c r="P71" s="10" t="inlineStr"/>
+      <c r="Q71" s="10" t="n"/>
+      <c r="R71" s="10" t="n"/>
+      <c r="S71" s="10" t="n"/>
+      <c r="T71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
@@ -6352,6 +6642,10 @@
         </is>
       </c>
       <c r="P72" s="10" t="inlineStr"/>
+      <c r="Q72" s="10" t="n"/>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
@@ -6430,6 +6724,10 @@
         </is>
       </c>
       <c r="P73" s="10" t="inlineStr"/>
+      <c r="Q73" s="10" t="n"/>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
+      <c r="T73" s="10" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
@@ -6508,6 +6806,10 @@
         </is>
       </c>
       <c r="P74" s="10" t="inlineStr"/>
+      <c r="Q74" s="10" t="n"/>
+      <c r="R74" s="10" t="n"/>
+      <c r="S74" s="10" t="n"/>
+      <c r="T74" s="10" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
@@ -6586,6 +6888,10 @@
         </is>
       </c>
       <c r="P75" s="10" t="inlineStr"/>
+      <c r="Q75" s="10" t="n"/>
+      <c r="R75" s="10" t="n"/>
+      <c r="S75" s="10" t="n"/>
+      <c r="T75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
@@ -6664,6 +6970,10 @@
         </is>
       </c>
       <c r="P76" s="10" t="inlineStr"/>
+      <c r="Q76" s="10" t="n"/>
+      <c r="R76" s="10" t="n"/>
+      <c r="S76" s="10" t="n"/>
+      <c r="T76" s="10" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
@@ -6742,6 +7052,10 @@
         </is>
       </c>
       <c r="P77" s="10" t="inlineStr"/>
+      <c r="Q77" s="10" t="n"/>
+      <c r="R77" s="10" t="n"/>
+      <c r="S77" s="10" t="n"/>
+      <c r="T77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
@@ -6820,6 +7134,10 @@
         </is>
       </c>
       <c r="P78" s="10" t="inlineStr"/>
+      <c r="Q78" s="10" t="n"/>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="10" t="n"/>
+      <c r="T78" s="10" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
@@ -6898,6 +7216,10 @@
         </is>
       </c>
       <c r="P79" s="10" t="inlineStr"/>
+      <c r="Q79" s="10" t="n"/>
+      <c r="R79" s="10" t="n"/>
+      <c r="S79" s="10" t="n"/>
+      <c r="T79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
@@ -6976,6 +7298,10 @@
         </is>
       </c>
       <c r="P80" s="10" t="inlineStr"/>
+      <c r="Q80" s="10" t="n"/>
+      <c r="R80" s="10" t="n"/>
+      <c r="S80" s="10" t="n"/>
+      <c r="T80" s="10" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
@@ -7054,6 +7380,10 @@
         </is>
       </c>
       <c r="P81" s="10" t="inlineStr"/>
+      <c r="Q81" s="10" t="n"/>
+      <c r="R81" s="10" t="n"/>
+      <c r="S81" s="10" t="n"/>
+      <c r="T81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
@@ -7132,6 +7462,10 @@
         </is>
       </c>
       <c r="P82" s="10" t="inlineStr"/>
+      <c r="Q82" s="10" t="n"/>
+      <c r="R82" s="10" t="n"/>
+      <c r="S82" s="10" t="n"/>
+      <c r="T82" s="10" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
@@ -7210,6 +7544,10 @@
         </is>
       </c>
       <c r="P83" s="10" t="inlineStr"/>
+      <c r="Q83" s="10" t="n"/>
+      <c r="R83" s="10" t="n"/>
+      <c r="S83" s="10" t="n"/>
+      <c r="T83" s="10" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
@@ -7288,6 +7626,10 @@
         </is>
       </c>
       <c r="P84" s="10" t="inlineStr"/>
+      <c r="Q84" s="10" t="n"/>
+      <c r="R84" s="10" t="n"/>
+      <c r="S84" s="10" t="n"/>
+      <c r="T84" s="10" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
@@ -7366,6 +7708,10 @@
         </is>
       </c>
       <c r="P85" s="10" t="inlineStr"/>
+      <c r="Q85" s="10" t="n"/>
+      <c r="R85" s="10" t="n"/>
+      <c r="S85" s="10" t="n"/>
+      <c r="T85" s="10" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
@@ -7444,6 +7790,10 @@
         </is>
       </c>
       <c r="P86" s="10" t="inlineStr"/>
+      <c r="Q86" s="10" t="n"/>
+      <c r="R86" s="10" t="n"/>
+      <c r="S86" s="10" t="n"/>
+      <c r="T86" s="10" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
@@ -7522,6 +7872,10 @@
         </is>
       </c>
       <c r="P87" s="10" t="inlineStr"/>
+      <c r="Q87" s="10" t="n"/>
+      <c r="R87" s="10" t="n"/>
+      <c r="S87" s="10" t="n"/>
+      <c r="T87" s="10" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
@@ -7600,6 +7954,10 @@
         </is>
       </c>
       <c r="P88" s="10" t="inlineStr"/>
+      <c r="Q88" s="10" t="n"/>
+      <c r="R88" s="10" t="n"/>
+      <c r="S88" s="10" t="n"/>
+      <c r="T88" s="10" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
@@ -7678,6 +8036,10 @@
         </is>
       </c>
       <c r="P89" s="10" t="inlineStr"/>
+      <c r="Q89" s="10" t="n"/>
+      <c r="R89" s="10" t="n"/>
+      <c r="S89" s="10" t="n"/>
+      <c r="T89" s="10" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
@@ -7756,6 +8118,10 @@
         </is>
       </c>
       <c r="P90" s="10" t="inlineStr"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="10" t="n"/>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="10" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
@@ -7834,6 +8200,10 @@
         </is>
       </c>
       <c r="P91" s="10" t="inlineStr"/>
+      <c r="Q91" s="10" t="n"/>
+      <c r="R91" s="10" t="n"/>
+      <c r="S91" s="10" t="n"/>
+      <c r="T91" s="10" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
@@ -7912,6 +8282,10 @@
         </is>
       </c>
       <c r="P92" s="10" t="inlineStr"/>
+      <c r="Q92" s="10" t="n"/>
+      <c r="R92" s="10" t="n"/>
+      <c r="S92" s="10" t="n"/>
+      <c r="T92" s="10" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
@@ -7990,6 +8364,10 @@
         </is>
       </c>
       <c r="P93" s="10" t="inlineStr"/>
+      <c r="Q93" s="10" t="n"/>
+      <c r="R93" s="10" t="n"/>
+      <c r="S93" s="10" t="n"/>
+      <c r="T93" s="10" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
@@ -8068,6 +8446,10 @@
         </is>
       </c>
       <c r="P94" s="10" t="inlineStr"/>
+      <c r="Q94" s="10" t="n"/>
+      <c r="R94" s="10" t="n"/>
+      <c r="S94" s="10" t="n"/>
+      <c r="T94" s="10" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
@@ -8146,6 +8528,10 @@
         </is>
       </c>
       <c r="P95" s="10" t="inlineStr"/>
+      <c r="Q95" s="10" t="n"/>
+      <c r="R95" s="10" t="n"/>
+      <c r="S95" s="10" t="n"/>
+      <c r="T95" s="10" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
@@ -8224,6 +8610,10 @@
         </is>
       </c>
       <c r="P96" s="10" t="inlineStr"/>
+      <c r="Q96" s="10" t="n"/>
+      <c r="R96" s="10" t="n"/>
+      <c r="S96" s="10" t="n"/>
+      <c r="T96" s="10" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
@@ -8302,6 +8692,10 @@
         </is>
       </c>
       <c r="P97" s="10" t="inlineStr"/>
+      <c r="Q97" s="10" t="n"/>
+      <c r="R97" s="10" t="n"/>
+      <c r="S97" s="10" t="n"/>
+      <c r="T97" s="10" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
@@ -8380,6 +8774,10 @@
         </is>
       </c>
       <c r="P98" s="10" t="inlineStr"/>
+      <c r="Q98" s="10" t="n"/>
+      <c r="R98" s="10" t="n"/>
+      <c r="S98" s="10" t="n"/>
+      <c r="T98" s="10" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
@@ -8458,6 +8856,10 @@
         </is>
       </c>
       <c r="P99" s="10" t="inlineStr"/>
+      <c r="Q99" s="10" t="n"/>
+      <c r="R99" s="10" t="n"/>
+      <c r="S99" s="10" t="n"/>
+      <c r="T99" s="10" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
@@ -8540,6 +8942,10 @@
           <t>Decided by Peter on 30 Sep 2026 (answer 5) and confirmed on 1 Oct 2026: same-day stays are charged one night; a manager can waive it with a reason.</t>
         </is>
       </c>
+      <c r="Q100" s="10" t="n"/>
+      <c r="R100" s="10" t="n"/>
+      <c r="S100" s="10" t="n"/>
+      <c r="T100" s="10" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
@@ -8618,6 +9024,10 @@
         </is>
       </c>
       <c r="P101" s="10" t="inlineStr"/>
+      <c r="Q101" s="10" t="n"/>
+      <c r="R101" s="10" t="n"/>
+      <c r="S101" s="10" t="n"/>
+      <c r="T101" s="10" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
@@ -8696,6 +9106,10 @@
         </is>
       </c>
       <c r="P102" s="10" t="inlineStr"/>
+      <c r="Q102" s="10" t="n"/>
+      <c r="R102" s="10" t="n"/>
+      <c r="S102" s="10" t="n"/>
+      <c r="T102" s="10" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
@@ -8774,6 +9188,10 @@
         </is>
       </c>
       <c r="P103" s="10" t="inlineStr"/>
+      <c r="Q103" s="10" t="n"/>
+      <c r="R103" s="10" t="n"/>
+      <c r="S103" s="10" t="n"/>
+      <c r="T103" s="10" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
@@ -8856,6 +9274,10 @@
           <t>Reports screen: KPIs, revenue by charge code, outstanding balances, payments, cancellations and stay length, balances by guest, export.</t>
         </is>
       </c>
+      <c r="Q104" s="10" t="n"/>
+      <c r="R104" s="10" t="n"/>
+      <c r="S104" s="10" t="n"/>
+      <c r="T104" s="10" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
@@ -8934,6 +9356,10 @@
         </is>
       </c>
       <c r="P105" s="10" t="inlineStr"/>
+      <c r="Q105" s="10" t="n"/>
+      <c r="R105" s="10" t="n"/>
+      <c r="S105" s="10" t="n"/>
+      <c r="T105" s="10" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
@@ -9012,6 +9438,10 @@
         </is>
       </c>
       <c r="P106" s="10" t="inlineStr"/>
+      <c r="Q106" s="10" t="n"/>
+      <c r="R106" s="10" t="n"/>
+      <c r="S106" s="10" t="n"/>
+      <c r="T106" s="10" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
@@ -9090,6 +9520,10 @@
         </is>
       </c>
       <c r="P107" s="10" t="inlineStr"/>
+      <c r="Q107" s="10" t="n"/>
+      <c r="R107" s="10" t="n"/>
+      <c r="S107" s="10" t="n"/>
+      <c r="T107" s="10" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
@@ -9168,6 +9602,10 @@
         </is>
       </c>
       <c r="P108" s="10" t="inlineStr"/>
+      <c r="Q108" s="10" t="n"/>
+      <c r="R108" s="10" t="n"/>
+      <c r="S108" s="10" t="n"/>
+      <c r="T108" s="10" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
@@ -9246,6 +9684,10 @@
         </is>
       </c>
       <c r="P109" s="10" t="inlineStr"/>
+      <c r="Q109" s="10" t="n"/>
+      <c r="R109" s="10" t="n"/>
+      <c r="S109" s="10" t="n"/>
+      <c r="T109" s="10" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
@@ -9324,6 +9766,10 @@
         </is>
       </c>
       <c r="P110" s="10" t="inlineStr"/>
+      <c r="Q110" s="10" t="n"/>
+      <c r="R110" s="10" t="n"/>
+      <c r="S110" s="10" t="n"/>
+      <c r="T110" s="10" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
@@ -9402,6 +9848,10 @@
         </is>
       </c>
       <c r="P111" s="10" t="inlineStr"/>
+      <c r="Q111" s="10" t="n"/>
+      <c r="R111" s="10" t="n"/>
+      <c r="S111" s="10" t="n"/>
+      <c r="T111" s="10" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
@@ -9480,6 +9930,10 @@
         </is>
       </c>
       <c r="P112" s="10" t="inlineStr"/>
+      <c r="Q112" s="10" t="n"/>
+      <c r="R112" s="10" t="n"/>
+      <c r="S112" s="10" t="n"/>
+      <c r="T112" s="10" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
@@ -9558,6 +10012,10 @@
         </is>
       </c>
       <c r="P113" s="10" t="inlineStr"/>
+      <c r="Q113" s="10" t="n"/>
+      <c r="R113" s="10" t="n"/>
+      <c r="S113" s="10" t="n"/>
+      <c r="T113" s="10" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
@@ -9636,6 +10094,10 @@
         </is>
       </c>
       <c r="P114" s="10" t="inlineStr"/>
+      <c r="Q114" s="10" t="n"/>
+      <c r="R114" s="10" t="n"/>
+      <c r="S114" s="10" t="n"/>
+      <c r="T114" s="10" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
@@ -9714,6 +10176,10 @@
         </is>
       </c>
       <c r="P115" s="10" t="inlineStr"/>
+      <c r="Q115" s="10" t="n"/>
+      <c r="R115" s="10" t="n"/>
+      <c r="S115" s="10" t="n"/>
+      <c r="T115" s="10" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
@@ -9792,6 +10258,10 @@
         </is>
       </c>
       <c r="P116" s="10" t="inlineStr"/>
+      <c r="Q116" s="10" t="n"/>
+      <c r="R116" s="10" t="n"/>
+      <c r="S116" s="10" t="n"/>
+      <c r="T116" s="10" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
@@ -9870,6 +10340,10 @@
         </is>
       </c>
       <c r="P117" s="10" t="inlineStr"/>
+      <c r="Q117" s="10" t="n"/>
+      <c r="R117" s="10" t="n"/>
+      <c r="S117" s="10" t="n"/>
+      <c r="T117" s="10" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'R1 Requirements'!$A$1:$O$108</definedName>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13">
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P117"/>
+  <dimension ref="A1:P118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9870,6 +9870,88 @@
         </is>
       </c>
       <c r="P117" s="10" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>SET-011</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>/setup; /dashboard</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>A new hotel sees a checklist of what is left to set up: property details, room types, rooms, rates, taxes, payment methods and staff. Each step says what is missing and links to the right screen. The list comes from the hotel's own data, so it is always current.</t>
+        </is>
+      </c>
+      <c r="E118" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G118" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H118" s="10" t="inlineStr">
+        <is>
+          <t>any setup permission</t>
+        </is>
+      </c>
+      <c r="I118" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J118" s="10" t="inlineStr">
+        <is>
+          <t>a hotel that is part way through setup</t>
+        </is>
+      </c>
+      <c r="K118" s="10" t="inlineStr">
+        <is>
+          <t>a manager opens Setup or the Dashboard</t>
+        </is>
+      </c>
+      <c r="L118" s="10" t="inlineStr">
+        <is>
+          <t>the steps already done are ticked and the next one is linked; once all seven are done the checklist goes away</t>
+        </is>
+      </c>
+      <c r="M118" s="10" t="inlineStr">
+        <is>
+          <t>setup_progress</t>
+        </is>
+      </c>
+      <c r="N118" s="10" t="inlineStr">
+        <is>
+          <t>40_guided_setup (30)</t>
+        </is>
+      </c>
+      <c r="O118" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P118" s="10" t="inlineStr">
+        <is>
+          <t>Read-only function, no stored progress. Staff step counts people with a role at the property (two or more).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P117"/>
+  <dimension ref="A1:P131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9882,6 +9882,1086 @@
         </is>
       </c>
       <c r="P117" s="10" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>GRP-001</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>All branches</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>A built-in Group Manager role and the permission rpt.group.view exist; only System Administrator, General Manager and Group Manager hold the permission.</t>
+        </is>
+      </c>
+      <c r="E118" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G118" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H118" s="10" t="inlineStr">
+        <is>
+          <t>rpt.group.view</t>
+        </is>
+      </c>
+      <c r="I118" s="10" t="inlineStr"/>
+      <c r="J118" s="10" t="inlineStr">
+        <is>
+          <t>a hotel group with several branches</t>
+        </is>
+      </c>
+      <c r="K118" s="10" t="inlineStr">
+        <is>
+          <t>an owner wants a view-only manager for the whole group</t>
+        </is>
+      </c>
+      <c r="L118" s="10" t="inlineStr">
+        <is>
+          <t>they assign the Group Manager role branch by branch, and that person can look but not post or change anything</t>
+        </is>
+      </c>
+      <c r="M118" s="10" t="inlineStr">
+        <is>
+          <t>20261013120000_group_view.sql</t>
+        </is>
+      </c>
+      <c r="N118" s="10" t="inlineStr">
+        <is>
+          <t>35_group_view (5)</t>
+        </is>
+      </c>
+      <c r="O118" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P118" s="10" t="inlineStr">
+        <is>
+          <t>Custom roles copied earlier do not get the new permission; say so when releasing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>GRP-002</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>All branches</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>One call shows every branch the person may see: occupancy, in house, arrivals and departures to come, approvals, repairs and last night revenue, with group totals. Revenue is totalled per currency.</t>
+        </is>
+      </c>
+      <c r="E119" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F119" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G119" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H119" s="10" t="inlineStr">
+        <is>
+          <t>rpt.group.view</t>
+        </is>
+      </c>
+      <c r="I119" s="10" t="inlineStr"/>
+      <c r="J119" s="10" t="inlineStr">
+        <is>
+          <t>a group with a Lagos and an Abuja branch</t>
+        </is>
+      </c>
+      <c r="K119" s="10" t="inlineStr">
+        <is>
+          <t>a group manager opens All branches</t>
+        </is>
+      </c>
+      <c r="L119" s="10" t="inlineStr">
+        <is>
+          <t>they see both branches with figures from the database, never another hotel group, and staff without the permission are refused</t>
+        </is>
+      </c>
+      <c r="M119" s="10" t="inlineStr">
+        <is>
+          <t>group_overview; /group screen</t>
+        </is>
+      </c>
+      <c r="N119" s="10" t="inlineStr">
+        <is>
+          <t>35_group_view (10)</t>
+        </is>
+      </c>
+      <c r="O119" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P119" s="10" t="inlineStr">
+        <is>
+          <t>Figures are read from each branch own business date. No arithmetic in the browser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>GRP-003</t>
+        </is>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>All branches</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>A Group Manager sees only the branches they are assigned to, and cannot post charges or check guests in.</t>
+        </is>
+      </c>
+      <c r="E120" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F120" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G120" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H120" s="10" t="inlineStr">
+        <is>
+          <t>rpt.group.view</t>
+        </is>
+      </c>
+      <c r="I120" s="10" t="inlineStr"/>
+      <c r="J120" s="10" t="inlineStr">
+        <is>
+          <t>a Group Manager assigned to one branch</t>
+        </is>
+      </c>
+      <c r="K120" s="10" t="inlineStr">
+        <is>
+          <t>a second branch is assigned</t>
+        </is>
+      </c>
+      <c r="L120" s="10" t="inlineStr">
+        <is>
+          <t>the second branch appears; the role never gets write permissions</t>
+        </is>
+      </c>
+      <c r="M120" s="10" t="inlineStr">
+        <is>
+          <t>assign_role (existing); group_overview</t>
+        </is>
+      </c>
+      <c r="N120" s="10" t="inlineStr">
+        <is>
+          <t>35_group_view (3)</t>
+        </is>
+      </c>
+      <c r="O120" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P120" s="10" t="inlineStr">
+        <is>
+          <t>Access is per branch, using the existing role assignment screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>GRP-004</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>All branches (Copy setup)</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>A new branch can copy room types, rate plans and prices from an existing branch, once, into an empty branch.</t>
+        </is>
+      </c>
+      <c r="E121" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G121" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H121" s="10" t="inlineStr">
+        <is>
+          <t>setup.room.manage, setup.rate.manage</t>
+        </is>
+      </c>
+      <c r="I121" s="10" t="inlineStr"/>
+      <c r="J121" s="10" t="inlineStr">
+        <is>
+          <t>a new empty branch</t>
+        </is>
+      </c>
+      <c r="K121" s="10" t="inlineStr">
+        <is>
+          <t>the owner copies setup from the first branch</t>
+        </is>
+      </c>
+      <c r="L121" s="10" t="inlineStr">
+        <is>
+          <t>room types, rate plans and prices appear on the new branch and point at its own room types; rooms are not copied; a second copy is refused; the copy is audited</t>
+        </is>
+      </c>
+      <c r="M121" s="10" t="inlineStr">
+        <is>
+          <t>copy_property_setup</t>
+        </is>
+      </c>
+      <c r="N121" s="10" t="inlineStr">
+        <is>
+          <t>35_group_view (13)</t>
+        </is>
+      </c>
+      <c r="O121" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P121" s="10" t="inlineStr">
+        <is>
+          <t>Taxes, charge codes and payment methods already arrive with every new branch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>RPT-005</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>Revenue by booking source: bookings, cancellations, no-shows, room nights, room revenue and average rate for each source in a date range.</t>
+        </is>
+      </c>
+      <c r="E122" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F122" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G122" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H122" s="10" t="inlineStr">
+        <is>
+          <t>rpt.finance.view</t>
+        </is>
+      </c>
+      <c r="I122" s="10" t="inlineStr"/>
+      <c r="J122" s="10" t="inlineStr">
+        <is>
+          <t>bookings from direct, phone and company sources</t>
+        </is>
+      </c>
+      <c r="K122" s="10" t="inlineStr">
+        <is>
+          <t>the accountant picks a date range</t>
+        </is>
+      </c>
+      <c r="L122" s="10" t="inlineStr">
+        <is>
+          <t>each source shows its own counts and room revenue (room charges only, before tax); cancelled bookings add no nights</t>
+        </is>
+      </c>
+      <c r="M122" s="10" t="inlineStr">
+        <is>
+          <t>20261013130000_source_ageing_reports.sql: report_revenue_by_source; Reports, By booking source tab</t>
+        </is>
+      </c>
+      <c r="N122" s="10" t="inlineStr">
+        <is>
+          <t>36_source_ageing (13)</t>
+        </is>
+      </c>
+      <c r="O122" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P122" s="10" t="inlineStr">
+        <is>
+          <t>Bookings counted by arrival date; revenue by posting date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>RPT-006</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>Ageing of unpaid balances by booking source: current, 1 to 7, 8 to 30, 31 to 60 and over 60 days since the due departure, plus credit held.</t>
+        </is>
+      </c>
+      <c r="E123" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F123" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G123" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H123" s="10" t="inlineStr">
+        <is>
+          <t>rpt.finance.view</t>
+        </is>
+      </c>
+      <c r="I123" s="10" t="inlineStr"/>
+      <c r="J123" s="10" t="inlineStr">
+        <is>
+          <t>guests and companies who left owing money</t>
+        </is>
+      </c>
+      <c r="K123" s="10" t="inlineStr">
+        <is>
+          <t>the accountant opens the Ageing tab</t>
+        </is>
+      </c>
+      <c r="L123" s="10" t="inlineStr">
+        <is>
+          <t>each source shows what is owed in each age column; paid bills drop out; overpayments show as credit held; the total matches Outstanding balances</t>
+        </is>
+      </c>
+      <c r="M123" s="10" t="inlineStr">
+        <is>
+          <t>report_balance_ageing; Reports, Ageing tab</t>
+        </is>
+      </c>
+      <c r="N123" s="10" t="inlineStr">
+        <is>
+          <t>36_source_ageing (11)</t>
+        </is>
+      </c>
+      <c r="O123" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P123" s="10" t="inlineStr">
+        <is>
+          <t>Guests still staying count as current.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>AI-001</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>AI helpers</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>Dashboard, Admin</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>AI helpers are off for every hotel until a System Administrator or General Manager switches them on, with a monthly limit; the switch is audited.</t>
+        </is>
+      </c>
+      <c r="E124" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F124" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G124" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H124" s="10" t="inlineStr">
+        <is>
+          <t>adm.ai.manage</t>
+        </is>
+      </c>
+      <c r="I124" s="10" t="inlineStr"/>
+      <c r="J124" s="10" t="inlineStr">
+        <is>
+          <t>a new hotel</t>
+        </is>
+      </c>
+      <c r="K124" s="10" t="inlineStr">
+        <is>
+          <t>a manager opens Admin, AI helpers</t>
+        </is>
+      </c>
+      <c r="L124" s="10" t="inlineStr">
+        <is>
+          <t>nothing runs until they switch it on and the change is in the audit log</t>
+        </is>
+      </c>
+      <c r="M124" s="10" t="inlineStr">
+        <is>
+          <t>20261013140000_ai_morning_brief.sql: set_ai_settings, ai_status; Admin, AI helpers tab</t>
+        </is>
+      </c>
+      <c r="N124" s="10" t="inlineStr">
+        <is>
+          <t>37_ai_brief (11)</t>
+        </is>
+      </c>
+      <c r="O124" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P124" s="10" t="inlineStr">
+        <is>
+          <t>Custom roles copied earlier do not get adm.ai.manage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>AI-002</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>AI helpers</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>Dashboard, Admin</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>The facts sent to the AI are counts and money lines built by the database: no guest names, ID details, room numbers or card data.</t>
+        </is>
+      </c>
+      <c r="E125" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G125" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H125" s="10" t="inlineStr">
+        <is>
+          <t>rpt.finance.view, rpt.operations.view</t>
+        </is>
+      </c>
+      <c r="I125" s="10" t="inlineStr"/>
+      <c r="J125" s="10" t="inlineStr">
+        <is>
+          <t>a hotel with guests, approvals and overdue bills</t>
+        </is>
+      </c>
+      <c r="K125" s="10" t="inlineStr">
+        <is>
+          <t>a brief is started</t>
+        </is>
+      </c>
+      <c r="L125" s="10" t="inlineStr">
+        <is>
+          <t>the facts hold only business date, last night, today, attention figures and plain lines, and overdue money matches the ledger</t>
+        </is>
+      </c>
+      <c r="M125" s="10" t="inlineStr">
+        <is>
+          <t>20261013140000_ai_morning_brief.sql: ai_morning_brief_start, app.morning_brief_facts</t>
+        </is>
+      </c>
+      <c r="N125" s="10" t="inlineStr">
+        <is>
+          <t>37_ai_brief (11)</t>
+        </is>
+      </c>
+      <c r="O125" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P125" s="10" t="inlineStr">
+        <is>
+          <t>Overdue means unpaid more than 30 days after departure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>AI-003</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>AI helpers</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>Dashboard, Admin</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t>Each hotel has a monthly limit on AI drafts; failed calls do not count; a call can be finished once, by the person who started it.</t>
+        </is>
+      </c>
+      <c r="E126" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F126" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G126" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H126" s="10" t="inlineStr">
+        <is>
+          <t>rpt.finance.view</t>
+        </is>
+      </c>
+      <c r="I126" s="10" t="inlineStr"/>
+      <c r="J126" s="10" t="inlineStr">
+        <is>
+          <t>a limit of 2</t>
+        </is>
+      </c>
+      <c r="K126" s="10" t="inlineStr">
+        <is>
+          <t>a third brief is requested</t>
+        </is>
+      </c>
+      <c r="L126" s="10" t="inlineStr">
+        <is>
+          <t>it is refused until a failed call frees a slot or the month turns</t>
+        </is>
+      </c>
+      <c r="M126" s="10" t="inlineStr">
+        <is>
+          <t>20261013140000_ai_morning_brief.sql: ai_call_finish</t>
+        </is>
+      </c>
+      <c r="N126" s="10" t="inlineStr">
+        <is>
+          <t>37_ai_brief (5)</t>
+        </is>
+      </c>
+      <c r="O126" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P126" s="10" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>AI-004</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>AI helpers</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>Dashboard, Admin</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t>Only finance and operations viewers can ask for the brief; the usage log and settings cannot be written or read directly by the browser.</t>
+        </is>
+      </c>
+      <c r="E127" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F127" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G127" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H127" s="10" t="inlineStr">
+        <is>
+          <t>rpt.finance.view, rpt.operations.view</t>
+        </is>
+      </c>
+      <c r="I127" s="10" t="inlineStr"/>
+      <c r="J127" s="10" t="inlineStr">
+        <is>
+          <t>front desk, housekeeping, another hotel</t>
+        </is>
+      </c>
+      <c r="K127" s="10" t="inlineStr">
+        <is>
+          <t>they ask for the brief or touch the tables</t>
+        </is>
+      </c>
+      <c r="L127" s="10" t="inlineStr">
+        <is>
+          <t>they are refused</t>
+        </is>
+      </c>
+      <c r="M127" s="10" t="inlineStr">
+        <is>
+          <t>20261013140000_ai_morning_brief.sql</t>
+        </is>
+      </c>
+      <c r="N127" s="10" t="inlineStr">
+        <is>
+          <t>37_ai_brief (7)</t>
+        </is>
+      </c>
+      <c r="O127" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P127" s="10" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>AI-005</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>AI helpers</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>Dashboard, Admin</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>The server accepts an AI draft only when every number in it is in the database facts; otherwise it shows the plain figures. The key stays on the server and only the fact lines are sent.</t>
+        </is>
+      </c>
+      <c r="E128" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F128" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G128" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H128" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="10" t="inlineStr"/>
+      <c r="J128" s="10" t="inlineStr">
+        <is>
+          <t>a draft that rounds or invents a figure</t>
+        </is>
+      </c>
+      <c r="K128" s="10" t="inlineStr">
+        <is>
+          <t>the brief is written</t>
+        </is>
+      </c>
+      <c r="L128" s="10" t="inlineStr">
+        <is>
+          <t>the plain database lines are shown instead, with a note</t>
+        </is>
+      </c>
+      <c r="M128" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/ai-brief.ts, ai-brief.functions.ts, Dashboard morning brief card</t>
+        </is>
+      </c>
+      <c r="N128" s="10" t="inlineStr">
+        <is>
+          <t>browser unit: ai-brief-unit (8)</t>
+        </is>
+      </c>
+      <c r="O128" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P128" s="10" t="inlineStr">
+        <is>
+          <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>SET-010</t>
+        </is>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>Setup, Rooms</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="inlineStr">
+        <is>
+          <t>A hotel can add room types and rooms from one checked list: preview first, then all or nothing. Existing codes and room names are skipped, so repeating adds nothing.</t>
+        </is>
+      </c>
+      <c r="E129" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F129" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G129" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H129" s="10" t="inlineStr">
+        <is>
+          <t>setup.room.manage</t>
+        </is>
+      </c>
+      <c r="I129" s="10" t="inlineStr"/>
+      <c r="J129" s="10" t="inlineStr">
+        <is>
+          <t>a list of room types and rooms</t>
+        </is>
+      </c>
+      <c r="K129" s="10" t="inlineStr">
+        <is>
+          <t>the manager previews and then applies it</t>
+        </is>
+      </c>
+      <c r="L129" s="10" t="inlineStr">
+        <is>
+          <t>the preview writes nothing; apply adds every valid item or none (bad name, unknown type, over 500 rooms, over the plan limit); a repeat adds nothing; the import is audited</t>
+        </is>
+      </c>
+      <c r="M129" s="10" t="inlineStr">
+        <is>
+          <t>20261013150000_setup_import.sql: apply_setup_import</t>
+        </is>
+      </c>
+      <c r="N129" s="10" t="inlineStr">
+        <is>
+          <t>38_setup_import (29)</t>
+        </is>
+      </c>
+      <c r="O129" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P129" s="10" t="inlineStr">
+        <is>
+          <t>The AI only drafts the list. This function is the check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>AI-006</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>AI helpers</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>Setup, Rooms</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="inlineStr">
+        <is>
+          <t>The setup import assistant starts only when AI is on and under the monthly limit, and the AI sees only existing room type codes and a room count.</t>
+        </is>
+      </c>
+      <c r="E130" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F130" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G130" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H130" s="10" t="inlineStr">
+        <is>
+          <t>setup.room.manage</t>
+        </is>
+      </c>
+      <c r="I130" s="10" t="inlineStr"/>
+      <c r="J130" s="10" t="inlineStr">
+        <is>
+          <t>AI switched on with a limit of 1</t>
+        </is>
+      </c>
+      <c r="K130" s="10" t="inlineStr">
+        <is>
+          <t>an import draft is started twice</t>
+        </is>
+      </c>
+      <c r="L130" s="10" t="inlineStr">
+        <is>
+          <t>the second is refused until the first fails; front desk and other hotels are refused</t>
+        </is>
+      </c>
+      <c r="M130" s="10" t="inlineStr">
+        <is>
+          <t>20261013150000_setup_import.sql: ai_import_start, app.ai_begin</t>
+        </is>
+      </c>
+      <c r="N130" s="10" t="inlineStr">
+        <is>
+          <t>38_setup_import (8)</t>
+        </is>
+      </c>
+      <c r="O130" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P130" s="10" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>AI-007</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>AI helpers</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>Setup, Rooms</t>
+        </is>
+      </c>
+      <c r="D131" s="10" t="inlineStr">
+        <is>
+          <t>Pasted text with an email, phone or card number is refused before anything is sent; the draft may only contain rooms, floors, guest limits and type names that are in the pasted text.</t>
+        </is>
+      </c>
+      <c r="E131" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F131" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G131" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H131" s="10" t="inlineStr">
+        <is>
+          <t>setup.room.manage</t>
+        </is>
+      </c>
+      <c r="I131" s="10" t="inlineStr"/>
+      <c r="J131" s="10" t="inlineStr">
+        <is>
+          <t>a pasted list</t>
+        </is>
+      </c>
+      <c r="K131" s="10" t="inlineStr">
+        <is>
+          <t>the assistant drafts it</t>
+        </is>
+      </c>
+      <c r="L131" s="10" t="inlineStr">
+        <is>
+          <t>invented rooms, floors and limits are dropped with a note; a draft with no matching rooms is an error</t>
+        </is>
+      </c>
+      <c r="M131" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/setup-import.ts, setup-import.functions.ts, Import from a list on Setup, Rooms</t>
+        </is>
+      </c>
+      <c r="N131" s="10" t="inlineStr">
+        <is>
+          <t>browser unit: setup-import-unit (9)</t>
+        </is>
+      </c>
+      <c r="O131" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P131" s="10" t="inlineStr">
+        <is>
+          <t>Needs ANTHROPIC_API_KEY on the server. Not set yet.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P132"/>
+  <dimension ref="A1:P133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11042,6 +11042,88 @@
       <c r="P132" s="10" t="inlineStr">
         <is>
           <t>Read-only function, no stored progress. Staff step counts people with a role at the property (two or more).</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>NFR-006</t>
+        </is>
+      </c>
+      <c r="B133" s="10" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>(all)</t>
+        </is>
+      </c>
+      <c r="D133" s="10" t="inlineStr">
+        <is>
+          <t>The last room of a type is sold once, however many desks book at the same moment, and a repeated booking never doubles.</t>
+        </is>
+      </c>
+      <c r="E133" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F133" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G133" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H133" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="10" t="inlineStr">
+        <is>
+          <t>Rule: Safe last-room booking</t>
+        </is>
+      </c>
+      <c r="J133" s="10" t="inlineStr">
+        <is>
+          <t>one room of a type is left and several desks book it together</t>
+        </is>
+      </c>
+      <c r="K133" s="10" t="inlineStr">
+        <is>
+          <t>all of them submit at the same moment</t>
+        </is>
+      </c>
+      <c r="L133" s="10" t="inlineStr">
+        <is>
+          <t>exactly one booking succeeds, the rest get E_NO_AVAILABILITY, and nothing is oversold</t>
+        </is>
+      </c>
+      <c r="M133" s="10" t="inlineStr">
+        <is>
+          <t>create_reservation, assert_available</t>
+        </is>
+      </c>
+      <c r="N133" s="10" t="inlineStr">
+        <is>
+          <t>concurrency/last_room.sh (6)</t>
+        </is>
+      </c>
+      <c r="O133" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P133" s="10" t="inlineStr">
+        <is>
+          <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -631,7 +631,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Not built</t>
+          <t>Partly built (flags only)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -641,20 +641,10 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Partly built (flags only)</t>
+          <t>Partly built, no tagged test</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Partly built, no tagged test</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1503,7 +1493,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Time-boxed break-glass support access, with reason, tenant notice and audit entry.</t>
+          <t>Time-boxed support access with the hotel's consent: the operator asks with a reason, the hotel's administrator says yes for 1 to 72 hours or no, can stop it at any time, and every step is in the hotel audit log. The support view is read-only and holds no guest, booking, money or contact data.</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -1523,7 +1513,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>platform.support.access</t>
+          <t>platform operator; adm.support.manage</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
@@ -1533,35 +1523,39 @@
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>a platform user needs to help a hotel</t>
+          <t>a platform operator needs to help a hotel</t>
         </is>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>they request support access with a reason</t>
+          <t>they ask for support access with a reason and the hotel says yes</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>access is limited in time, written to the hotel's audit log and the hotel is told</t>
+          <t>they can open a read-only support view until the time ends or the hotel stops it; the hotel is told and every step is audited</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>(not written)</t>
+          <t>platform_request_support_access, decide_support_access, revoke_support_access, platform_support_snapshot, list_support_access</t>
         </is>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>41_support_access</t>
         </is>
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
-          <t>Not built</t>
-        </is>
-      </c>
-      <c r="P11" s="10" t="inlineStr"/>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>Database done 8 Oct 2026. Screens for the hotel (Admin) and the operator (platform console) follow. New permission adm.support.manage reaches System Administrator and General Manager only.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P133"/>
+  <dimension ref="A1:P134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11118,6 +11118,84 @@
       <c r="P133" s="10" t="inlineStr">
         <is>
           <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="10" t="inlineStr">
+        <is>
+          <t>FO-014</t>
+        </is>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
+        <is>
+          <t>Front Office</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>/downtime</t>
+        </is>
+      </c>
+      <c r="D134" s="10" t="inlineStr">
+        <is>
+          <t>A printable downtime pack: arrivals due, in-house guests with balance, departures due, ten blank lines for new guests on paper, and a short paper routine. Staff print it when the internet or system is down.</t>
+        </is>
+      </c>
+      <c r="E134" s="10" t="inlineStr">
+        <is>
+          <t>BR-006</t>
+        </is>
+      </c>
+      <c r="F134" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G134" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H134" s="10" t="inlineStr">
+        <is>
+          <t>fo.view</t>
+        </is>
+      </c>
+      <c r="I134" s="10" t="inlineStr"/>
+      <c r="J134" s="10" t="inlineStr">
+        <is>
+          <t>a hotel with guests in house</t>
+        </is>
+      </c>
+      <c r="K134" s="10" t="inlineStr">
+        <is>
+          <t>a front desk user opens Downtime pack and prints</t>
+        </is>
+      </c>
+      <c r="L134" s="10" t="inlineStr">
+        <is>
+          <t>the lists show room, guest, phone, departure and the folio balance from the database, with blank lines and the paper routine</t>
+        </is>
+      </c>
+      <c r="M134" s="10" t="inlineStr">
+        <is>
+          <t>src/routes/_authenticated/_app/downtime.tsx</t>
+        </is>
+      </c>
+      <c r="N134" s="10" t="inlineStr">
+        <is>
+          <t>browser: downtime-pack.spec (1)</t>
+        </is>
+      </c>
+      <c r="O134" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P134" s="10" t="inlineStr">
+        <is>
+          <t>No database change. Reads v_arrivals, v_in_house and v_folio_balances. Added 8 Oct 2026.</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P133"/>
+  <dimension ref="A1:P134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11118,6 +11118,84 @@
       <c r="P133" s="10" t="inlineStr">
         <is>
           <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="10" t="inlineStr">
+        <is>
+          <t>SET-012</t>
+        </is>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>/setup/property</t>
+        </is>
+      </c>
+      <c r="D134" s="10" t="inlineStr">
+        <is>
+          <t>A manager sets the longest stay (1 to 365 nights) and how long a tentative booking holds its room (1 to 720 hours) for each property.</t>
+        </is>
+      </c>
+      <c r="E134" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F134" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G134" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H134" s="10" t="inlineStr">
+        <is>
+          <t>setup.property.edit</t>
+        </is>
+      </c>
+      <c r="I134" s="10" t="inlineStr"/>
+      <c r="J134" s="10" t="inlineStr">
+        <is>
+          <t>a property with the default rules (30 nights, 24 hours)</t>
+        </is>
+      </c>
+      <c r="K134" s="10" t="inlineStr">
+        <is>
+          <t>a manager saves new booking rules</t>
+        </is>
+      </c>
+      <c r="L134" s="10" t="inlineStr">
+        <is>
+          <t>new bookings use them, bad values are refused with E_INVALID, and the change is audited with old and new values</t>
+        </is>
+      </c>
+      <c r="M134" s="10" t="inlineStr">
+        <is>
+          <t>set_booking_rules; Booking rules on Setup, Property</t>
+        </is>
+      </c>
+      <c r="N134" s="10" t="inlineStr">
+        <is>
+          <t>42_booking_rules (9)</t>
+        </is>
+      </c>
+      <c r="O134" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P134" s="10" t="inlineStr">
+        <is>
+          <t>Added 8 Oct 2026. The columns existed since the reservations release; this adds the screen and the function.</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P135"/>
+  <dimension ref="A1:P136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11274,6 +11274,88 @@
       <c r="P135" s="10" t="inlineStr">
         <is>
           <t>No database change. Reads v_arrivals, v_in_house and v_folio_balances. Added 8 Oct 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="inlineStr">
+        <is>
+          <t>DAY-007</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>Business Date</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>Notifications bell</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>In the last hour before a property rolls its business date, if a cashier shift is still open, users who can run the night audit get one warning that night. The roll does not wait.</t>
+        </is>
+      </c>
+      <c r="E136" s="10" t="inlineStr">
+        <is>
+          <t>BR-016</t>
+        </is>
+      </c>
+      <c r="F136" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G136" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H136" s="10" t="inlineStr">
+        <is>
+          <t>fin.nightaudit.run</t>
+        </is>
+      </c>
+      <c r="I136" s="10" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J136" s="10" t="inlineStr">
+        <is>
+          <t>a cashier shift is still open</t>
+        </is>
+      </c>
+      <c r="K136" s="10" t="inlineStr">
+        <is>
+          <t>the roll time is less than 60 minutes away</t>
+        </is>
+      </c>
+      <c r="L136" s="10" t="inlineStr">
+        <is>
+          <t>each night audit user gets one rollover_warning notification for that business date; none earlier, none after the roll time, none if no shift is open, none twice</t>
+        </is>
+      </c>
+      <c r="M136" s="10" t="inlineStr">
+        <is>
+          <t>app.warn_before_rollover; cron job rollover-warning</t>
+        </is>
+      </c>
+      <c r="N136" s="10" t="inlineStr">
+        <is>
+          <t>43_rollover_warning (7)</t>
+        </is>
+      </c>
+      <c r="O136" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P136" s="10" t="inlineStr">
+        <is>
+          <t>Added 8 Oct 2026. Warning only; the hard gate stays in R2 (DAY-005).</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -11345,7 +11345,7 @@
       </c>
       <c r="N136" s="10" t="inlineStr">
         <is>
-          <t>43_rollover_warning (7)</t>
+          <t>43_rollover_warning (9)</t>
         </is>
       </c>
       <c r="O136" s="10" t="inlineStr">

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P136"/>
+  <dimension ref="A1:P137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9412,22 +9412,22 @@
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>GST-007</t>
+          <t>FIN-018</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>Guests</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>/guests/$id; check-in; walk-in</t>
+          <t>/setup/taxes</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>A photo or scan of an ID document is kept in private storage, shrunk and stripped of hidden data in the browser, and opened only through a 60-second link.</t>
+          <t>A hotel can match the tax method of its existing folio using setup alone: each tax on the room price only, food and drink untaxed. A sample bill of 45,000 room plus 12,001 bar totals 67,126.</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
@@ -9447,37 +9447,37 @@
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>guest.document.file.upload / view / delete</t>
+          <t>setup.tax.manage</t>
         </is>
       </c>
       <c r="I112" s="10" t="inlineStr">
         <is>
-          <t>SET-009 switch</t>
+          <t>Tax rates compounds_on_previous; charge code is_taxable</t>
         </is>
       </c>
       <c r="J112" s="10" t="inlineStr">
         <is>
-          <t>a hotel that allows ID photos</t>
+          <t>a property with service charge 10%, VAT 7.5% and state tax 5%, none compounding, and a non-taxable bar code</t>
         </is>
       </c>
       <c r="K112" s="10" t="inlineStr">
         <is>
-          <t>front desk adds an ID photo</t>
+          <t>a room charge of 45,000 and a bar charge of 12,001 are posted</t>
         </is>
       </c>
       <c r="L112" s="10" t="inlineStr">
         <is>
-          <t>it is stored privately and opens only through a short-lived link</t>
+          <t>the taxes are 4,500, 3,375 and 2,250, the bar has no tax and the bill is 67,126</t>
         </is>
       </c>
       <c r="M112" s="10" t="inlineStr">
         <is>
-          <t>begin_id_photo_upload, finish_id_photo_upload, open_id_photo</t>
+          <t>save_tax_rate, save_charge_code, post_charge</t>
         </is>
       </c>
       <c r="N112" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (30)</t>
+          <t>44_folio_sample_method (5)</t>
         </is>
       </c>
       <c r="O112" s="10" t="inlineStr">
@@ -9485,12 +9485,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P112" s="10" t="inlineStr"/>
+      <c r="P112" s="10" t="inlineStr">
+        <is>
+          <t>Method only; the accountant still signs off the rates (A11)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>GST-008</t>
+          <t>GST-007</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -9500,12 +9504,12 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>/guests/$id</t>
+          <t>/guests/$id; check-in; walk-in</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>Every upload, view and deletion of an ID photo is audited with ids only, no personal data.</t>
+          <t>A photo or scan of an ID document is kept in private storage, shrunk and stripped of hidden data in the browser, and opened only through a 60-second link.</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
@@ -9525,37 +9529,37 @@
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>guest.document.file.upload / view / delete</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SET-009 switch</t>
         </is>
       </c>
       <c r="J113" s="10" t="inlineStr">
         <is>
-          <t>an ID photo</t>
+          <t>a hotel that allows ID photos</t>
         </is>
       </c>
       <c r="K113" s="10" t="inlineStr">
         <is>
-          <t>it is uploaded, opened or deleted</t>
+          <t>front desk adds an ID photo</t>
         </is>
       </c>
       <c r="L113" s="10" t="inlineStr">
         <is>
-          <t>an audit row records who and which file, with no personal data</t>
+          <t>it is stored privately and opens only through a short-lived link</t>
         </is>
       </c>
       <c r="M113" s="10" t="inlineStr">
         <is>
-          <t>app.audit_id_photo</t>
+          <t>begin_id_photo_upload, finish_id_photo_upload, open_id_photo</t>
         </is>
       </c>
       <c r="N113" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (9)</t>
+          <t>24_id_photos (30)</t>
         </is>
       </c>
       <c r="O113" s="10" t="inlineStr">
@@ -9568,7 +9572,7 @@
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>GST-009</t>
+          <t>GST-008</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -9583,7 +9587,7 @@
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>ID photos are removed from storage when the guest is anonymised or the document is removed, and move with the guest when two profiles are merged.</t>
+          <t>Every upload, view and deletion of an ID photo is audited with ids only, no personal data.</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
@@ -9613,27 +9617,27 @@
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>a guest with ID photos</t>
+          <t>an ID photo</t>
         </is>
       </c>
       <c r="K114" s="10" t="inlineStr">
         <is>
-          <t>the guest is anonymised, the document removed, or the profile merged</t>
+          <t>it is uploaded, opened or deleted</t>
         </is>
       </c>
       <c r="L114" s="10" t="inlineStr">
         <is>
-          <t>the files are removed, or move to the kept profile</t>
+          <t>an audit row records who and which file, with no personal data</t>
         </is>
       </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
-          <t>anonymise_guest, merge_guests, delete_id_photo</t>
+          <t>app.audit_id_photo</t>
         </is>
       </c>
       <c r="N114" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (4)</t>
+          <t>24_id_photos (9)</t>
         </is>
       </c>
       <c r="O114" s="10" t="inlineStr">
@@ -9646,7 +9650,7 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>GST-010</t>
+          <t>GST-009</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -9656,12 +9660,12 @@
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>(daily clean-up)</t>
+          <t>/guests/$id</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>ID photos are deleted automatically a set number of months (one setting, now 12) after the guest's last check-out, unless the guest has a booking that is not over.</t>
+          <t>ID photos are removed from storage when the guest is anonymised or the document is removed, and move with the guest when two profiles are merged.</t>
         </is>
       </c>
       <c r="E115" s="10" t="inlineStr">
@@ -9686,32 +9690,32 @@
       </c>
       <c r="I115" s="10" t="inlineStr">
         <is>
-          <t>Setting id_photo_keep_months; daily cron</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>a guest whose last check-out was more than the keep period ago</t>
+          <t>a guest with ID photos</t>
         </is>
       </c>
       <c r="K115" s="10" t="inlineStr">
         <is>
-          <t>the daily clean-up runs</t>
+          <t>the guest is anonymised, the document removed, or the profile merged</t>
         </is>
       </c>
       <c r="L115" s="10" t="inlineStr">
         <is>
-          <t>their ID photos are deleted</t>
+          <t>the files are removed, or move to the kept profile</t>
         </is>
       </c>
       <c r="M115" s="10" t="inlineStr">
         <is>
-          <t>/api/cron/id-photo-cleanup</t>
+          <t>anonymise_guest, merge_guests, delete_id_photo</t>
         </is>
       </c>
       <c r="N115" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (5)</t>
+          <t>24_id_photos (4)</t>
         </is>
       </c>
       <c r="O115" s="10" t="inlineStr">
@@ -9724,22 +9728,22 @@
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>ROOM-005</t>
+          <t>GST-010</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>Rooms</t>
+          <t>Guests</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>/rooms</t>
+          <t>(daily clean-up)</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Rooms are added one at a time or several by number or by name, with a preview; labels are free text up to 30 characters, unique per hotel ignoring case and extra spaces, shown as typed and sorted in natural order.</t>
+          <t>ID photos are deleted automatically a set number of months (one setting, now 12) after the guest's last check-out, unless the guest has a booking that is not over.</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
@@ -9759,37 +9763,37 @@
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>setup.room.edit</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I116" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Setting id_photo_keep_months; daily cron</t>
         </is>
       </c>
       <c r="J116" s="10" t="inlineStr">
         <is>
-          <t>an administrator on the Rooms page</t>
+          <t>a guest whose last check-out was more than the keep period ago</t>
         </is>
       </c>
       <c r="K116" s="10" t="inlineStr">
         <is>
-          <t>they add rooms by number range or by names</t>
+          <t>the daily clean-up runs</t>
         </is>
       </c>
       <c r="L116" s="10" t="inlineStr">
         <is>
-          <t>valid new rooms are created, duplicates skipped and invalid names shown</t>
+          <t>their ID photos are deleted</t>
         </is>
       </c>
       <c r="M116" s="10" t="inlineStr">
         <is>
-          <t>add_rooms_range, add_rooms_named, save_room</t>
+          <t>/api/cron/id-photo-cleanup</t>
         </is>
       </c>
       <c r="N116" s="10" t="inlineStr">
         <is>
-          <t>23_room_labels (46); 26_small_fixes (1); browser: rooms-add</t>
+          <t>24_id_photos (5)</t>
         </is>
       </c>
       <c r="O116" s="10" t="inlineStr">
@@ -9802,22 +9806,22 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>SET-009</t>
+          <t>ROOM-005</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Rooms</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>/setup/property</t>
+          <t>/rooms</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>Per hotel: "Allow ID photos" (off by default) and "Require ID photo at check-in" (only when allowed). While Allow is off, uploading and opening ID photos are refused.</t>
+          <t>Rooms are added one at a time or several by number or by name, with a preview; labels are free text up to 30 characters, unique per hotel ignoring case and extra spaces, shown as typed and sorted in natural order.</t>
         </is>
       </c>
       <c r="E117" s="10" t="inlineStr">
@@ -9837,7 +9841,7 @@
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>setup.property.edit</t>
+          <t>setup.room.edit</t>
         </is>
       </c>
       <c r="I117" s="10" t="inlineStr">
@@ -9847,27 +9851,27 @@
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>a hotel with ID photos off</t>
+          <t>an administrator on the Rooms page</t>
         </is>
       </c>
       <c r="K117" s="10" t="inlineStr">
         <is>
-          <t>staff try to add or open an ID photo</t>
+          <t>they add rooms by number range or by names</t>
         </is>
       </c>
       <c r="L117" s="10" t="inlineStr">
         <is>
-          <t>it is refused; when Require is on, check-in waits for an ID photo</t>
+          <t>valid new rooms are created, duplicates skipped and invalid names shown</t>
         </is>
       </c>
       <c r="M117" s="10" t="inlineStr">
         <is>
-          <t>set_id_photo_settings</t>
+          <t>add_rooms_range, add_rooms_named, save_room</t>
         </is>
       </c>
       <c r="N117" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (10)</t>
+          <t>23_room_labels (46); 26_small_fixes (1); browser: rooms-add</t>
         </is>
       </c>
       <c r="O117" s="10" t="inlineStr">
@@ -9880,32 +9884,32 @@
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>GRP-001</t>
+          <t>SET-009</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>Platform &amp; Tenancy</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>All branches</t>
+          <t>/setup/property</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>A built-in Group Manager role and the permission rpt.group.view exist; only System Administrator, General Manager and Group Manager hold the permission.</t>
+          <t>Per hotel: "Allow ID photos" (off by default) and "Require ID photo at check-in" (only when allowed). While Allow is off, uploading and opening ID photos are refused.</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
@@ -9915,33 +9919,37 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>rpt.group.view</t>
-        </is>
-      </c>
-      <c r="I118" s="10" t="inlineStr"/>
+          <t>setup.property.edit</t>
+        </is>
+      </c>
+      <c r="I118" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J118" s="10" t="inlineStr">
         <is>
-          <t>a hotel group with several branches</t>
+          <t>a hotel with ID photos off</t>
         </is>
       </c>
       <c r="K118" s="10" t="inlineStr">
         <is>
-          <t>an owner wants a view-only manager for the whole group</t>
+          <t>staff try to add or open an ID photo</t>
         </is>
       </c>
       <c r="L118" s="10" t="inlineStr">
         <is>
-          <t>they assign the Group Manager role branch by branch, and that person can look but not post or change anything</t>
+          <t>it is refused; when Require is on, check-in waits for an ID photo</t>
         </is>
       </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
-          <t>20261013120000_group_view.sql</t>
+          <t>set_id_photo_settings</t>
         </is>
       </c>
       <c r="N118" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (5)</t>
+          <t>24_id_photos (10)</t>
         </is>
       </c>
       <c r="O118" s="10" t="inlineStr">
@@ -9949,16 +9957,12 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P118" s="10" t="inlineStr">
-        <is>
-          <t>Custom roles copied earlier do not get the new permission; say so when releasing.</t>
-        </is>
-      </c>
+      <c r="P118" s="10" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>GRP-002</t>
+          <t>GRP-001</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
@@ -9973,7 +9977,7 @@
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>One call shows every branch the person may see: occupancy, in house, arrivals and departures to come, approvals, repairs and last night revenue, with group totals. Revenue is totalled per currency.</t>
+          <t>A built-in Group Manager role and the permission rpt.group.view exist; only System Administrator, General Manager and Group Manager hold the permission.</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr">
@@ -9999,27 +10003,27 @@
       <c r="I119" s="10" t="inlineStr"/>
       <c r="J119" s="10" t="inlineStr">
         <is>
-          <t>a group with a Lagos and an Abuja branch</t>
+          <t>a hotel group with several branches</t>
         </is>
       </c>
       <c r="K119" s="10" t="inlineStr">
         <is>
-          <t>a group manager opens All branches</t>
+          <t>an owner wants a view-only manager for the whole group</t>
         </is>
       </c>
       <c r="L119" s="10" t="inlineStr">
         <is>
-          <t>they see both branches with figures from the database, never another hotel group, and staff without the permission are refused</t>
+          <t>they assign the Group Manager role branch by branch, and that person can look but not post or change anything</t>
         </is>
       </c>
       <c r="M119" s="10" t="inlineStr">
         <is>
-          <t>group_overview; /group screen</t>
+          <t>20261013120000_group_view.sql</t>
         </is>
       </c>
       <c r="N119" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (10)</t>
+          <t>35_group_view (5)</t>
         </is>
       </c>
       <c r="O119" s="10" t="inlineStr">
@@ -10029,14 +10033,14 @@
       </c>
       <c r="P119" s="10" t="inlineStr">
         <is>
-          <t>Figures are read from each branch own business date. No arithmetic in the browser.</t>
+          <t>Custom roles copied earlier do not get the new permission; say so when releasing.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>GRP-003</t>
+          <t>GRP-002</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -10051,7 +10055,7 @@
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>A Group Manager sees only the branches they are assigned to, and cannot post charges or check guests in.</t>
+          <t>One call shows every branch the person may see: occupancy, in house, arrivals and departures to come, approvals, repairs and last night revenue, with group totals. Revenue is totalled per currency.</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
@@ -10077,27 +10081,27 @@
       <c r="I120" s="10" t="inlineStr"/>
       <c r="J120" s="10" t="inlineStr">
         <is>
-          <t>a Group Manager assigned to one branch</t>
+          <t>a group with a Lagos and an Abuja branch</t>
         </is>
       </c>
       <c r="K120" s="10" t="inlineStr">
         <is>
-          <t>a second branch is assigned</t>
+          <t>a group manager opens All branches</t>
         </is>
       </c>
       <c r="L120" s="10" t="inlineStr">
         <is>
-          <t>the second branch appears; the role never gets write permissions</t>
+          <t>they see both branches with figures from the database, never another hotel group, and staff without the permission are refused</t>
         </is>
       </c>
       <c r="M120" s="10" t="inlineStr">
         <is>
-          <t>assign_role (existing); group_overview</t>
+          <t>group_overview; /group screen</t>
         </is>
       </c>
       <c r="N120" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (3)</t>
+          <t>35_group_view (10)</t>
         </is>
       </c>
       <c r="O120" s="10" t="inlineStr">
@@ -10107,14 +10111,14 @@
       </c>
       <c r="P120" s="10" t="inlineStr">
         <is>
-          <t>Access is per branch, using the existing role assignment screen.</t>
+          <t>Figures are read from each branch own business date. No arithmetic in the browser.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>GRP-004</t>
+          <t>GRP-003</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -10124,12 +10128,12 @@
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>All branches (Copy setup)</t>
+          <t>All branches</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>A new branch can copy room types, rate plans and prices from an existing branch, once, into an empty branch.</t>
+          <t>A Group Manager sees only the branches they are assigned to, and cannot post charges or check guests in.</t>
         </is>
       </c>
       <c r="E121" s="10" t="inlineStr">
@@ -10149,33 +10153,33 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>setup.room.manage, setup.rate.manage</t>
+          <t>rpt.group.view</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr"/>
       <c r="J121" s="10" t="inlineStr">
         <is>
-          <t>a new empty branch</t>
+          <t>a Group Manager assigned to one branch</t>
         </is>
       </c>
       <c r="K121" s="10" t="inlineStr">
         <is>
-          <t>the owner copies setup from the first branch</t>
+          <t>a second branch is assigned</t>
         </is>
       </c>
       <c r="L121" s="10" t="inlineStr">
         <is>
-          <t>room types, rate plans and prices appear on the new branch and point at its own room types; rooms are not copied; a second copy is refused; the copy is audited</t>
+          <t>the second branch appears; the role never gets write permissions</t>
         </is>
       </c>
       <c r="M121" s="10" t="inlineStr">
         <is>
-          <t>copy_property_setup</t>
+          <t>assign_role (existing); group_overview</t>
         </is>
       </c>
       <c r="N121" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (13)</t>
+          <t>35_group_view (3)</t>
         </is>
       </c>
       <c r="O121" s="10" t="inlineStr">
@@ -10185,29 +10189,29 @@
       </c>
       <c r="P121" s="10" t="inlineStr">
         <is>
-          <t>Taxes, charge codes and payment methods already arrive with every new branch.</t>
+          <t>Access is per branch, using the existing role assignment screen.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>RPT-005</t>
+          <t>GRP-004</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Platform &amp; Tenancy</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>All branches (Copy setup)</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>Revenue by booking source: bookings, cancellations, no-shows, room nights, room revenue and average rate for each source in a date range.</t>
+          <t>A new branch can copy room types, rate plans and prices from an existing branch, once, into an empty branch.</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
@@ -10227,33 +10231,33 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view</t>
+          <t>setup.room.manage, setup.rate.manage</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr"/>
       <c r="J122" s="10" t="inlineStr">
         <is>
-          <t>bookings from direct, phone and company sources</t>
+          <t>a new empty branch</t>
         </is>
       </c>
       <c r="K122" s="10" t="inlineStr">
         <is>
-          <t>the accountant picks a date range</t>
+          <t>the owner copies setup from the first branch</t>
         </is>
       </c>
       <c r="L122" s="10" t="inlineStr">
         <is>
-          <t>each source shows its own counts and room revenue (room charges only, before tax); cancelled bookings add no nights</t>
+          <t>room types, rate plans and prices appear on the new branch and point at its own room types; rooms are not copied; a second copy is refused; the copy is audited</t>
         </is>
       </c>
       <c r="M122" s="10" t="inlineStr">
         <is>
-          <t>20261013130000_source_ageing_reports.sql: report_revenue_by_source; Reports, By booking source tab</t>
+          <t>copy_property_setup</t>
         </is>
       </c>
       <c r="N122" s="10" t="inlineStr">
         <is>
-          <t>36_source_ageing (13)</t>
+          <t>35_group_view (13)</t>
         </is>
       </c>
       <c r="O122" s="10" t="inlineStr">
@@ -10263,14 +10267,14 @@
       </c>
       <c r="P122" s="10" t="inlineStr">
         <is>
-          <t>Bookings counted by arrival date; revenue by posting date.</t>
+          <t>Taxes, charge codes and payment methods already arrive with every new branch.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>RPT-006</t>
+          <t>RPT-005</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
@@ -10285,7 +10289,7 @@
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>Ageing of unpaid balances by booking source: current, 1 to 7, 8 to 30, 31 to 60 and over 60 days since the due departure, plus credit held.</t>
+          <t>Revenue by booking source: bookings, cancellations, no-shows, room nights, room revenue and average rate for each source in a date range.</t>
         </is>
       </c>
       <c r="E123" s="10" t="inlineStr">
@@ -10311,27 +10315,27 @@
       <c r="I123" s="10" t="inlineStr"/>
       <c r="J123" s="10" t="inlineStr">
         <is>
-          <t>guests and companies who left owing money</t>
+          <t>bookings from direct, phone and company sources</t>
         </is>
       </c>
       <c r="K123" s="10" t="inlineStr">
         <is>
-          <t>the accountant opens the Ageing tab</t>
+          <t>the accountant picks a date range</t>
         </is>
       </c>
       <c r="L123" s="10" t="inlineStr">
         <is>
-          <t>each source shows what is owed in each age column; paid bills drop out; overpayments show as credit held; the total matches Outstanding balances</t>
+          <t>each source shows its own counts and room revenue (room charges only, before tax); cancelled bookings add no nights</t>
         </is>
       </c>
       <c r="M123" s="10" t="inlineStr">
         <is>
-          <t>report_balance_ageing; Reports, Ageing tab</t>
+          <t>20261013130000_source_ageing_reports.sql: report_revenue_by_source; Reports, By booking source tab</t>
         </is>
       </c>
       <c r="N123" s="10" t="inlineStr">
         <is>
-          <t>36_source_ageing (11)</t>
+          <t>36_source_ageing (13)</t>
         </is>
       </c>
       <c r="O123" s="10" t="inlineStr">
@@ -10341,29 +10345,29 @@
       </c>
       <c r="P123" s="10" t="inlineStr">
         <is>
-          <t>Guests still staying count as current.</t>
+          <t>Bookings counted by arrival date; revenue by posting date.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>AI-001</t>
+          <t>RPT-006</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>AI helpers</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Dashboard, Admin</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>AI helpers are off for every hotel until a System Administrator or General Manager switches them on, with a monthly limit; the switch is audited.</t>
+          <t>Ageing of unpaid balances by booking source: current, 1 to 7, 8 to 30, 31 to 60 and over 60 days since the due departure, plus credit held.</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
@@ -10383,33 +10387,33 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>adm.ai.manage</t>
+          <t>rpt.finance.view</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr"/>
       <c r="J124" s="10" t="inlineStr">
         <is>
-          <t>a new hotel</t>
+          <t>guests and companies who left owing money</t>
         </is>
       </c>
       <c r="K124" s="10" t="inlineStr">
         <is>
-          <t>a manager opens Admin, AI helpers</t>
+          <t>the accountant opens the Ageing tab</t>
         </is>
       </c>
       <c r="L124" s="10" t="inlineStr">
         <is>
-          <t>nothing runs until they switch it on and the change is in the audit log</t>
+          <t>each source shows what is owed in each age column; paid bills drop out; overpayments show as credit held; the total matches Outstanding balances</t>
         </is>
       </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: set_ai_settings, ai_status; Admin, AI helpers tab</t>
+          <t>report_balance_ageing; Reports, Ageing tab</t>
         </is>
       </c>
       <c r="N124" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (11)</t>
+          <t>36_source_ageing (11)</t>
         </is>
       </c>
       <c r="O124" s="10" t="inlineStr">
@@ -10419,14 +10423,14 @@
       </c>
       <c r="P124" s="10" t="inlineStr">
         <is>
-          <t>Custom roles copied earlier do not get adm.ai.manage.</t>
+          <t>Guests still staying count as current.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>AI-002</t>
+          <t>AI-001</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
@@ -10441,7 +10445,7 @@
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>The facts sent to the AI are counts and money lines built by the database: no guest names, ID details, room numbers or card data.</t>
+          <t>AI helpers are off for every hotel until a System Administrator or General Manager switches them on, with a monthly limit; the switch is audited.</t>
         </is>
       </c>
       <c r="E125" s="10" t="inlineStr">
@@ -10461,28 +10465,28 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view, rpt.operations.view</t>
+          <t>adm.ai.manage</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr"/>
       <c r="J125" s="10" t="inlineStr">
         <is>
-          <t>a hotel with guests, approvals and overdue bills</t>
+          <t>a new hotel</t>
         </is>
       </c>
       <c r="K125" s="10" t="inlineStr">
         <is>
-          <t>a brief is started</t>
+          <t>a manager opens Admin, AI helpers</t>
         </is>
       </c>
       <c r="L125" s="10" t="inlineStr">
         <is>
-          <t>the facts hold only business date, last night, today, attention figures and plain lines, and overdue money matches the ledger</t>
+          <t>nothing runs until they switch it on and the change is in the audit log</t>
         </is>
       </c>
       <c r="M125" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: ai_morning_brief_start, app.morning_brief_facts</t>
+          <t>20261013140000_ai_morning_brief.sql: set_ai_settings, ai_status; Admin, AI helpers tab</t>
         </is>
       </c>
       <c r="N125" s="10" t="inlineStr">
@@ -10497,14 +10501,14 @@
       </c>
       <c r="P125" s="10" t="inlineStr">
         <is>
-          <t>Overdue means unpaid more than 30 days after departure.</t>
+          <t>Custom roles copied earlier do not get adm.ai.manage.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>AI-003</t>
+          <t>AI-002</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
@@ -10519,7 +10523,7 @@
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Each hotel has a monthly limit on AI drafts; failed calls do not count; a call can be finished once, by the person who started it.</t>
+          <t>The facts sent to the AI are counts and money lines built by the database: no guest names, ID details, room numbers or card data.</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
@@ -10539,33 +10543,33 @@
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view</t>
+          <t>rpt.finance.view, rpt.operations.view</t>
         </is>
       </c>
       <c r="I126" s="10" t="inlineStr"/>
       <c r="J126" s="10" t="inlineStr">
         <is>
-          <t>a limit of 2</t>
+          <t>a hotel with guests, approvals and overdue bills</t>
         </is>
       </c>
       <c r="K126" s="10" t="inlineStr">
         <is>
-          <t>a third brief is requested</t>
+          <t>a brief is started</t>
         </is>
       </c>
       <c r="L126" s="10" t="inlineStr">
         <is>
-          <t>it is refused until a failed call frees a slot or the month turns</t>
+          <t>the facts hold only business date, last night, today, attention figures and plain lines, and overdue money matches the ledger</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: ai_call_finish</t>
+          <t>20261013140000_ai_morning_brief.sql: ai_morning_brief_start, app.morning_brief_facts</t>
         </is>
       </c>
       <c r="N126" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (5)</t>
+          <t>37_ai_brief (11)</t>
         </is>
       </c>
       <c r="O126" s="10" t="inlineStr">
@@ -10573,12 +10577,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P126" s="10" t="inlineStr"/>
+      <c r="P126" s="10" t="inlineStr">
+        <is>
+          <t>Overdue means unpaid more than 30 days after departure.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>AI-004</t>
+          <t>AI-003</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
@@ -10593,7 +10601,7 @@
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>Only finance and operations viewers can ask for the brief; the usage log and settings cannot be written or read directly by the browser.</t>
+          <t>Each hotel has a monthly limit on AI drafts; failed calls do not count; a call can be finished once, by the person who started it.</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr">
@@ -10613,33 +10621,33 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view, rpt.operations.view</t>
+          <t>rpt.finance.view</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr"/>
       <c r="J127" s="10" t="inlineStr">
         <is>
-          <t>front desk, housekeeping, another hotel</t>
+          <t>a limit of 2</t>
         </is>
       </c>
       <c r="K127" s="10" t="inlineStr">
         <is>
-          <t>they ask for the brief or touch the tables</t>
+          <t>a third brief is requested</t>
         </is>
       </c>
       <c r="L127" s="10" t="inlineStr">
         <is>
-          <t>they are refused</t>
+          <t>it is refused until a failed call frees a slot or the month turns</t>
         </is>
       </c>
       <c r="M127" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql</t>
+          <t>20261013140000_ai_morning_brief.sql: ai_call_finish</t>
         </is>
       </c>
       <c r="N127" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (7)</t>
+          <t>37_ai_brief (5)</t>
         </is>
       </c>
       <c r="O127" s="10" t="inlineStr">
@@ -10652,7 +10660,7 @@
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>AI-005</t>
+          <t>AI-004</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -10667,7 +10675,7 @@
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>The server accepts an AI draft only when every number in it is in the database facts; otherwise it shows the plain figures. The key stays on the server and only the fact lines are sent.</t>
+          <t>Only finance and operations viewers can ask for the brief; the usage log and settings cannot be written or read directly by the browser.</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
@@ -10687,33 +10695,33 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>rpt.finance.view, rpt.operations.view</t>
         </is>
       </c>
       <c r="I128" s="10" t="inlineStr"/>
       <c r="J128" s="10" t="inlineStr">
         <is>
-          <t>a draft that rounds or invents a figure</t>
+          <t>front desk, housekeeping, another hotel</t>
         </is>
       </c>
       <c r="K128" s="10" t="inlineStr">
         <is>
-          <t>the brief is written</t>
+          <t>they ask for the brief or touch the tables</t>
         </is>
       </c>
       <c r="L128" s="10" t="inlineStr">
         <is>
-          <t>the plain database lines are shown instead, with a note</t>
+          <t>they are refused</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
-          <t>src/lib/ai-brief.ts, ai-brief.functions.ts, Dashboard morning brief card</t>
+          <t>20261013140000_ai_morning_brief.sql</t>
         </is>
       </c>
       <c r="N128" s="10" t="inlineStr">
         <is>
-          <t>browser unit: ai-brief-unit (8)</t>
+          <t>37_ai_brief (7)</t>
         </is>
       </c>
       <c r="O128" s="10" t="inlineStr">
@@ -10721,31 +10729,27 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P128" s="10" t="inlineStr">
-        <is>
-          <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
-        </is>
-      </c>
+      <c r="P128" s="10" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>SET-010</t>
+          <t>AI-005</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>AI helpers</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Setup, Rooms</t>
+          <t>Dashboard, Admin</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>A hotel can add room types and rooms from one checked list: preview first, then all or nothing. Existing codes and room names are skipped, so repeating adds nothing.</t>
+          <t>The server accepts an AI draft only when every number in it is in the database facts; otherwise it shows the plain figures. The key stays on the server and only the fact lines are sent.</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
@@ -10765,33 +10769,33 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>setup.room.manage</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr"/>
       <c r="J129" s="10" t="inlineStr">
         <is>
-          <t>a list of room types and rooms</t>
+          <t>a draft that rounds or invents a figure</t>
         </is>
       </c>
       <c r="K129" s="10" t="inlineStr">
         <is>
-          <t>the manager previews and then applies it</t>
+          <t>the brief is written</t>
         </is>
       </c>
       <c r="L129" s="10" t="inlineStr">
         <is>
-          <t>the preview writes nothing; apply adds every valid item or none (bad name, unknown type, over 500 rooms, over the plan limit); a repeat adds nothing; the import is audited</t>
+          <t>the plain database lines are shown instead, with a note</t>
         </is>
       </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
-          <t>20261013150000_setup_import.sql: apply_setup_import</t>
+          <t>src/lib/ai-brief.ts, ai-brief.functions.ts, Dashboard morning brief card</t>
         </is>
       </c>
       <c r="N129" s="10" t="inlineStr">
         <is>
-          <t>38_setup_import (29)</t>
+          <t>browser unit: ai-brief-unit (8)</t>
         </is>
       </c>
       <c r="O129" s="10" t="inlineStr">
@@ -10801,19 +10805,19 @@
       </c>
       <c r="P129" s="10" t="inlineStr">
         <is>
-          <t>The AI only drafts the list. This function is the check.</t>
+          <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>AI-006</t>
+          <t>SET-010</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>AI helpers</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
@@ -10823,7 +10827,7 @@
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>The setup import assistant starts only when AI is on and under the monthly limit, and the AI sees only existing room type codes and a room count.</t>
+          <t>A hotel can add room types and rooms from one checked list: preview first, then all or nothing. Existing codes and room names are skipped, so repeating adds nothing.</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
@@ -10849,27 +10853,27 @@
       <c r="I130" s="10" t="inlineStr"/>
       <c r="J130" s="10" t="inlineStr">
         <is>
-          <t>AI switched on with a limit of 1</t>
+          <t>a list of room types and rooms</t>
         </is>
       </c>
       <c r="K130" s="10" t="inlineStr">
         <is>
-          <t>an import draft is started twice</t>
+          <t>the manager previews and then applies it</t>
         </is>
       </c>
       <c r="L130" s="10" t="inlineStr">
         <is>
-          <t>the second is refused until the first fails; front desk and other hotels are refused</t>
+          <t>the preview writes nothing; apply adds every valid item or none (bad name, unknown type, over 500 rooms, over the plan limit); a repeat adds nothing; the import is audited</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
-          <t>20261013150000_setup_import.sql: ai_import_start, app.ai_begin</t>
+          <t>20261013150000_setup_import.sql: apply_setup_import</t>
         </is>
       </c>
       <c r="N130" s="10" t="inlineStr">
         <is>
-          <t>38_setup_import (8)</t>
+          <t>38_setup_import (29)</t>
         </is>
       </c>
       <c r="O130" s="10" t="inlineStr">
@@ -10877,12 +10881,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P130" s="10" t="inlineStr"/>
+      <c r="P130" s="10" t="inlineStr">
+        <is>
+          <t>The AI only drafts the list. This function is the check.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>AI-007</t>
+          <t>AI-006</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -10897,7 +10905,7 @@
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>Pasted text with an email, phone or card number is refused before anything is sent; the draft may only contain rooms, floors, guest limits and type names that are in the pasted text.</t>
+          <t>The setup import assistant starts only when AI is on and under the monthly limit, and the AI sees only existing room type codes and a room count.</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
@@ -10923,27 +10931,27 @@
       <c r="I131" s="10" t="inlineStr"/>
       <c r="J131" s="10" t="inlineStr">
         <is>
-          <t>a pasted list</t>
+          <t>AI switched on with a limit of 1</t>
         </is>
       </c>
       <c r="K131" s="10" t="inlineStr">
         <is>
-          <t>the assistant drafts it</t>
+          <t>an import draft is started twice</t>
         </is>
       </c>
       <c r="L131" s="10" t="inlineStr">
         <is>
-          <t>invented rooms, floors and limits are dropped with a note; a draft with no matching rooms is an error</t>
+          <t>the second is refused until the first fails; front desk and other hotels are refused</t>
         </is>
       </c>
       <c r="M131" s="10" t="inlineStr">
         <is>
-          <t>src/lib/setup-import.ts, setup-import.functions.ts, Import from a list on Setup, Rooms</t>
+          <t>20261013150000_setup_import.sql: ai_import_start, app.ai_begin</t>
         </is>
       </c>
       <c r="N131" s="10" t="inlineStr">
         <is>
-          <t>browser unit: setup-import-unit (9)</t>
+          <t>38_setup_import (8)</t>
         </is>
       </c>
       <c r="O131" s="10" t="inlineStr">
@@ -10951,36 +10959,32 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P131" s="10" t="inlineStr">
-        <is>
-          <t>Needs ANTHROPIC_API_KEY on the server. Not set yet.</t>
-        </is>
-      </c>
+      <c r="P131" s="10" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>SET-011</t>
+          <t>AI-007</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>AI helpers</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>/setup; /dashboard</t>
+          <t>Setup, Rooms</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>A new hotel sees a checklist of what is left to set up: property details, room types, rooms, rates, taxes, payment methods and staff. Each step says what is missing and links to the right screen. The list comes from the hotel's own data, so it is always current.</t>
+          <t>Pasted text with an email, phone or card number is refused before anything is sent; the draft may only contain rooms, floors, guest limits and type names that are in the pasted text.</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
@@ -10995,37 +10999,33 @@
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>any setup permission</t>
-        </is>
-      </c>
-      <c r="I132" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>setup.room.manage</t>
+        </is>
+      </c>
+      <c r="I132" s="10" t="inlineStr"/>
       <c r="J132" s="10" t="inlineStr">
         <is>
-          <t>a hotel that is part way through setup</t>
+          <t>a pasted list</t>
         </is>
       </c>
       <c r="K132" s="10" t="inlineStr">
         <is>
-          <t>a manager opens Setup or the Dashboard</t>
+          <t>the assistant drafts it</t>
         </is>
       </c>
       <c r="L132" s="10" t="inlineStr">
         <is>
-          <t>the steps already done are ticked and the next one is linked; once all seven are done the checklist goes away</t>
+          <t>invented rooms, floors and limits are dropped with a note; a draft with no matching rooms is an error</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
-          <t>setup_progress</t>
+          <t>src/lib/setup-import.ts, setup-import.functions.ts, Import from a list on Setup, Rooms</t>
         </is>
       </c>
       <c r="N132" s="10" t="inlineStr">
         <is>
-          <t>40_guided_setup (30)</t>
+          <t>browser unit: setup-import-unit (9)</t>
         </is>
       </c>
       <c r="O132" s="10" t="inlineStr">
@@ -11035,39 +11035,39 @@
       </c>
       <c r="P132" s="10" t="inlineStr">
         <is>
-          <t>Read-only function, no stored progress. Staff step counts people with a role at the property (two or more).</t>
+          <t>Needs ANTHROPIC_API_KEY on the server. Not set yet.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>NFR-006</t>
+          <t>SET-011</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>(all)</t>
+          <t>/setup; /dashboard</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>The last room of a type is sold once, however many desks book at the same moment, and a repeated booking never doubles.</t>
+          <t>A new hotel sees a checklist of what is left to set up: property details, room types, rooms, rates, taxes, payment methods and staff. Each step says what is missing and links to the right screen. The list comes from the hotel's own data, so it is always current.</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G133" s="10" t="inlineStr">
@@ -11077,37 +11077,37 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
+          <t>any setup permission</t>
+        </is>
+      </c>
+      <c r="I133" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I133" s="10" t="inlineStr">
-        <is>
-          <t>Rule: Safe last-room booking</t>
-        </is>
-      </c>
       <c r="J133" s="10" t="inlineStr">
         <is>
-          <t>one room of a type is left and several desks book it together</t>
+          <t>a hotel that is part way through setup</t>
         </is>
       </c>
       <c r="K133" s="10" t="inlineStr">
         <is>
-          <t>all of them submit at the same moment</t>
+          <t>a manager opens Setup or the Dashboard</t>
         </is>
       </c>
       <c r="L133" s="10" t="inlineStr">
         <is>
-          <t>exactly one booking succeeds, the rest get E_NO_AVAILABILITY, and nothing is oversold</t>
+          <t>the steps already done are ticked and the next one is linked; once all seven are done the checklist goes away</t>
         </is>
       </c>
       <c r="M133" s="10" t="inlineStr">
         <is>
-          <t>create_reservation, assert_available</t>
+          <t>setup_progress</t>
         </is>
       </c>
       <c r="N133" s="10" t="inlineStr">
         <is>
-          <t>concurrency/last_room.sh (6)</t>
+          <t>40_guided_setup (30)</t>
         </is>
       </c>
       <c r="O133" s="10" t="inlineStr">
@@ -11117,29 +11117,29 @@
       </c>
       <c r="P133" s="10" t="inlineStr">
         <is>
-          <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
+          <t>Read-only function, no stored progress. Staff step counts people with a role at the property (two or more).</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>SET-012</t>
+          <t>NFR-006</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Non-functional</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>/setup/property</t>
+          <t>(all)</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>A manager sets the longest stay (1 to 365 nights) and how long a tentative booking holds its room (1 to 720 hours) for each property.</t>
+          <t>The last room of a type is sold once, however many desks book at the same moment, and a repeated booking never doubles.</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G134" s="10" t="inlineStr">
@@ -11159,33 +11159,37 @@
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>setup.property.edit</t>
-        </is>
-      </c>
-      <c r="I134" s="10" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="10" t="inlineStr">
+        <is>
+          <t>Rule: Safe last-room booking</t>
+        </is>
+      </c>
       <c r="J134" s="10" t="inlineStr">
         <is>
-          <t>a property with the default rules (30 nights, 24 hours)</t>
+          <t>one room of a type is left and several desks book it together</t>
         </is>
       </c>
       <c r="K134" s="10" t="inlineStr">
         <is>
-          <t>a manager saves new booking rules</t>
+          <t>all of them submit at the same moment</t>
         </is>
       </c>
       <c r="L134" s="10" t="inlineStr">
         <is>
-          <t>new bookings use them, bad values are refused with E_INVALID, and the change is audited with old and new values</t>
+          <t>exactly one booking succeeds, the rest get E_NO_AVAILABILITY, and nothing is oversold</t>
         </is>
       </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
-          <t>set_booking_rules; Booking rules on Setup, Property</t>
+          <t>create_reservation, assert_available</t>
         </is>
       </c>
       <c r="N134" s="10" t="inlineStr">
         <is>
-          <t>42_booking_rules (9)</t>
+          <t>concurrency/last_room.sh (6)</t>
         </is>
       </c>
       <c r="O134" s="10" t="inlineStr">
@@ -11195,39 +11199,39 @@
       </c>
       <c r="P134" s="10" t="inlineStr">
         <is>
-          <t>Added 8 Oct 2026. The columns existed since the reservations release; this adds the screen and the function.</t>
+          <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>FO-014</t>
+          <t>SET-012</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>Front Office</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>/downtime</t>
+          <t>/setup/property</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>A printable downtime pack: arrivals due, in-house guests with balance, departures due, ten blank lines for new guests on paper, and a short paper routine. Staff print it when the internet or system is down.</t>
+          <t>A manager sets the longest stay (1 to 365 nights) and how long a tentative booking holds its room (1 to 720 hours) for each property.</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>BR-006</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
@@ -11237,33 +11241,33 @@
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>fo.view</t>
+          <t>setup.property.edit</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr"/>
       <c r="J135" s="10" t="inlineStr">
         <is>
-          <t>a hotel with guests in house</t>
+          <t>a property with the default rules (30 nights, 24 hours)</t>
         </is>
       </c>
       <c r="K135" s="10" t="inlineStr">
         <is>
-          <t>a front desk user opens Downtime pack and prints</t>
+          <t>a manager saves new booking rules</t>
         </is>
       </c>
       <c r="L135" s="10" t="inlineStr">
         <is>
-          <t>the lists show room, guest, phone, departure and the folio balance from the database, with blank lines and the paper routine</t>
+          <t>new bookings use them, bad values are refused with E_INVALID, and the change is audited with old and new values</t>
         </is>
       </c>
       <c r="M135" s="10" t="inlineStr">
         <is>
-          <t>src/routes/_authenticated/_app/downtime.tsx</t>
+          <t>set_booking_rules; Booking rules on Setup, Property</t>
         </is>
       </c>
       <c r="N135" s="10" t="inlineStr">
         <is>
-          <t>browser: downtime-pack.spec (1)</t>
+          <t>42_booking_rules (9)</t>
         </is>
       </c>
       <c r="O135" s="10" t="inlineStr">
@@ -11273,87 +11277,165 @@
       </c>
       <c r="P135" s="10" t="inlineStr">
         <is>
-          <t>No database change. Reads v_arrivals, v_in_house and v_folio_balances. Added 8 Oct 2026.</t>
+          <t>Added 8 Oct 2026. The columns existed since the reservations release; this adds the screen and the function.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
+          <t>FO-014</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>Front Office</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>/downtime</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>A printable downtime pack: arrivals due, in-house guests with balance, departures due, ten blank lines for new guests on paper, and a short paper routine. Staff print it when the internet or system is down.</t>
+        </is>
+      </c>
+      <c r="E136" s="10" t="inlineStr">
+        <is>
+          <t>BR-006</t>
+        </is>
+      </c>
+      <c r="F136" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G136" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H136" s="10" t="inlineStr">
+        <is>
+          <t>fo.view</t>
+        </is>
+      </c>
+      <c r="I136" s="10" t="inlineStr"/>
+      <c r="J136" s="10" t="inlineStr">
+        <is>
+          <t>a hotel with guests in house</t>
+        </is>
+      </c>
+      <c r="K136" s="10" t="inlineStr">
+        <is>
+          <t>a front desk user opens Downtime pack and prints</t>
+        </is>
+      </c>
+      <c r="L136" s="10" t="inlineStr">
+        <is>
+          <t>the lists show room, guest, phone, departure and the folio balance from the database, with blank lines and the paper routine</t>
+        </is>
+      </c>
+      <c r="M136" s="10" t="inlineStr">
+        <is>
+          <t>src/routes/_authenticated/_app/downtime.tsx</t>
+        </is>
+      </c>
+      <c r="N136" s="10" t="inlineStr">
+        <is>
+          <t>browser: downtime-pack.spec (1)</t>
+        </is>
+      </c>
+      <c r="O136" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P136" s="10" t="inlineStr">
+        <is>
+          <t>No database change. Reads v_arrivals, v_in_house and v_folio_balances. Added 8 Oct 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
           <t>DAY-007</t>
         </is>
       </c>
-      <c r="B136" s="10" t="inlineStr">
+      <c r="B137" s="10" t="inlineStr">
         <is>
           <t>Business Date</t>
         </is>
       </c>
-      <c r="C136" s="10" t="inlineStr">
+      <c r="C137" s="10" t="inlineStr">
         <is>
           <t>Notifications bell</t>
         </is>
       </c>
-      <c r="D136" s="10" t="inlineStr">
+      <c r="D137" s="10" t="inlineStr">
         <is>
           <t>In the last hour before a property rolls its business date, if a cashier shift is still open, users who can run the night audit get one warning that night. The roll does not wait.</t>
         </is>
       </c>
-      <c r="E136" s="10" t="inlineStr">
+      <c r="E137" s="10" t="inlineStr">
         <is>
           <t>BR-016</t>
         </is>
       </c>
-      <c r="F136" s="10" t="inlineStr">
+      <c r="F137" s="10" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G136" s="10" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H136" s="10" t="inlineStr">
+      <c r="G137" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H137" s="10" t="inlineStr">
         <is>
           <t>fin.nightaudit.run</t>
         </is>
       </c>
-      <c r="I136" s="10" t="inlineStr">
+      <c r="I137" s="10" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="J136" s="10" t="inlineStr">
+      <c r="J137" s="10" t="inlineStr">
         <is>
           <t>a cashier shift is still open</t>
         </is>
       </c>
-      <c r="K136" s="10" t="inlineStr">
+      <c r="K137" s="10" t="inlineStr">
         <is>
           <t>the roll time is less than 60 minutes away</t>
         </is>
       </c>
-      <c r="L136" s="10" t="inlineStr">
+      <c r="L137" s="10" t="inlineStr">
         <is>
           <t>each night audit user gets one rollover_warning notification for that business date; none earlier, none after the roll time, none if no shift is open, none twice</t>
         </is>
       </c>
-      <c r="M136" s="10" t="inlineStr">
+      <c r="M137" s="10" t="inlineStr">
         <is>
           <t>app.warn_before_rollover; cron job rollover-warning</t>
         </is>
       </c>
-      <c r="N136" s="10" t="inlineStr">
+      <c r="N137" s="10" t="inlineStr">
         <is>
           <t>43_rollover_warning (9)</t>
         </is>
       </c>
-      <c r="O136" s="10" t="inlineStr">
+      <c r="O137" s="10" t="inlineStr">
         <is>
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P136" s="10" t="inlineStr">
+      <c r="P137" s="10" t="inlineStr">
         <is>
           <t>Added 8 Oct 2026. Warning only; the hard gate stays in R2 (DAY-005).</t>
         </is>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P137"/>
+  <dimension ref="A1:P138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9494,22 +9494,22 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>GST-007</t>
+          <t>FIN-019</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>Guests</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>/guests/$id; check-in; walk-in</t>
+          <t>/invoices/$id</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>A photo or scan of an ID document is kept in private storage, shrunk and stripped of hidden data in the browser, and opened only through a 60-second link.</t>
+          <t>An invoice shows the check-in time, number of guests, number of nights, a total for each day, and the receipt reference of each charge. Invoices issued earlier stay as issued.</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
@@ -9529,37 +9529,37 @@
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>guest.document.file.upload / view / delete</t>
+          <t>fin.invoice.issue</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr">
         <is>
-          <t>SET-009 switch</t>
+          <t>Invoice snapshot is insert-only</t>
         </is>
       </c>
       <c r="J113" s="10" t="inlineStr">
         <is>
-          <t>a hotel that allows ID photos</t>
+          <t>a stay with charges, one with a receipt reference</t>
         </is>
       </c>
       <c r="K113" s="10" t="inlineStr">
         <is>
-          <t>front desk adds an ID photo</t>
+          <t>an invoice is issued</t>
         </is>
       </c>
       <c r="L113" s="10" t="inlineStr">
         <is>
-          <t>it is stored privately and opens only through a short-lived link</t>
+          <t>the invoice shows nights, guests, check-in time, a total per day and the receipt reference, all worked out in the database</t>
         </is>
       </c>
       <c r="M113" s="10" t="inlineStr">
         <is>
-          <t>begin_id_photo_upload, finish_id_photo_upload, open_id_photo</t>
+          <t>issue_invoice</t>
         </is>
       </c>
       <c r="N113" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (30)</t>
+          <t>45_invoice_layout (6)</t>
         </is>
       </c>
       <c r="O113" s="10" t="inlineStr">
@@ -9567,12 +9567,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P113" s="10" t="inlineStr"/>
+      <c r="P113" s="10" t="inlineStr">
+        <is>
+          <t>Day totals and fields are stored in the invoice header when it is issued</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>GST-008</t>
+          <t>GST-007</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -9582,12 +9586,12 @@
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>/guests/$id</t>
+          <t>/guests/$id; check-in; walk-in</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Every upload, view and deletion of an ID photo is audited with ids only, no personal data.</t>
+          <t>A photo or scan of an ID document is kept in private storage, shrunk and stripped of hidden data in the browser, and opened only through a 60-second link.</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
@@ -9607,37 +9611,37 @@
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>guest.document.file.upload / view / delete</t>
         </is>
       </c>
       <c r="I114" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SET-009 switch</t>
         </is>
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>an ID photo</t>
+          <t>a hotel that allows ID photos</t>
         </is>
       </c>
       <c r="K114" s="10" t="inlineStr">
         <is>
-          <t>it is uploaded, opened or deleted</t>
+          <t>front desk adds an ID photo</t>
         </is>
       </c>
       <c r="L114" s="10" t="inlineStr">
         <is>
-          <t>an audit row records who and which file, with no personal data</t>
+          <t>it is stored privately and opens only through a short-lived link</t>
         </is>
       </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
-          <t>app.audit_id_photo</t>
+          <t>begin_id_photo_upload, finish_id_photo_upload, open_id_photo</t>
         </is>
       </c>
       <c r="N114" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (9)</t>
+          <t>24_id_photos (30)</t>
         </is>
       </c>
       <c r="O114" s="10" t="inlineStr">
@@ -9650,7 +9654,7 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>GST-009</t>
+          <t>GST-008</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -9665,7 +9669,7 @@
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>ID photos are removed from storage when the guest is anonymised or the document is removed, and move with the guest when two profiles are merged.</t>
+          <t>Every upload, view and deletion of an ID photo is audited with ids only, no personal data.</t>
         </is>
       </c>
       <c r="E115" s="10" t="inlineStr">
@@ -9695,27 +9699,27 @@
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>a guest with ID photos</t>
+          <t>an ID photo</t>
         </is>
       </c>
       <c r="K115" s="10" t="inlineStr">
         <is>
-          <t>the guest is anonymised, the document removed, or the profile merged</t>
+          <t>it is uploaded, opened or deleted</t>
         </is>
       </c>
       <c r="L115" s="10" t="inlineStr">
         <is>
-          <t>the files are removed, or move to the kept profile</t>
+          <t>an audit row records who and which file, with no personal data</t>
         </is>
       </c>
       <c r="M115" s="10" t="inlineStr">
         <is>
-          <t>anonymise_guest, merge_guests, delete_id_photo</t>
+          <t>app.audit_id_photo</t>
         </is>
       </c>
       <c r="N115" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (4)</t>
+          <t>24_id_photos (9)</t>
         </is>
       </c>
       <c r="O115" s="10" t="inlineStr">
@@ -9728,7 +9732,7 @@
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>GST-010</t>
+          <t>GST-009</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -9738,12 +9742,12 @@
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>(daily clean-up)</t>
+          <t>/guests/$id</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>ID photos are deleted automatically a set number of months (one setting, now 12) after the guest's last check-out, unless the guest has a booking that is not over.</t>
+          <t>ID photos are removed from storage when the guest is anonymised or the document is removed, and move with the guest when two profiles are merged.</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
@@ -9768,32 +9772,32 @@
       </c>
       <c r="I116" s="10" t="inlineStr">
         <is>
-          <t>Setting id_photo_keep_months; daily cron</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J116" s="10" t="inlineStr">
         <is>
-          <t>a guest whose last check-out was more than the keep period ago</t>
+          <t>a guest with ID photos</t>
         </is>
       </c>
       <c r="K116" s="10" t="inlineStr">
         <is>
-          <t>the daily clean-up runs</t>
+          <t>the guest is anonymised, the document removed, or the profile merged</t>
         </is>
       </c>
       <c r="L116" s="10" t="inlineStr">
         <is>
-          <t>their ID photos are deleted</t>
+          <t>the files are removed, or move to the kept profile</t>
         </is>
       </c>
       <c r="M116" s="10" t="inlineStr">
         <is>
-          <t>/api/cron/id-photo-cleanup</t>
+          <t>anonymise_guest, merge_guests, delete_id_photo</t>
         </is>
       </c>
       <c r="N116" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (5)</t>
+          <t>24_id_photos (4)</t>
         </is>
       </c>
       <c r="O116" s="10" t="inlineStr">
@@ -9806,22 +9810,22 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>ROOM-005</t>
+          <t>GST-010</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>Rooms</t>
+          <t>Guests</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>/rooms</t>
+          <t>(daily clean-up)</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>Rooms are added one at a time or several by number or by name, with a preview; labels are free text up to 30 characters, unique per hotel ignoring case and extra spaces, shown as typed and sorted in natural order.</t>
+          <t>ID photos are deleted automatically a set number of months (one setting, now 12) after the guest's last check-out, unless the guest has a booking that is not over.</t>
         </is>
       </c>
       <c r="E117" s="10" t="inlineStr">
@@ -9841,37 +9845,37 @@
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>setup.room.edit</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I117" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Setting id_photo_keep_months; daily cron</t>
         </is>
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>an administrator on the Rooms page</t>
+          <t>a guest whose last check-out was more than the keep period ago</t>
         </is>
       </c>
       <c r="K117" s="10" t="inlineStr">
         <is>
-          <t>they add rooms by number range or by names</t>
+          <t>the daily clean-up runs</t>
         </is>
       </c>
       <c r="L117" s="10" t="inlineStr">
         <is>
-          <t>valid new rooms are created, duplicates skipped and invalid names shown</t>
+          <t>their ID photos are deleted</t>
         </is>
       </c>
       <c r="M117" s="10" t="inlineStr">
         <is>
-          <t>add_rooms_range, add_rooms_named, save_room</t>
+          <t>/api/cron/id-photo-cleanup</t>
         </is>
       </c>
       <c r="N117" s="10" t="inlineStr">
         <is>
-          <t>23_room_labels (46); 26_small_fixes (1); browser: rooms-add</t>
+          <t>24_id_photos (5)</t>
         </is>
       </c>
       <c r="O117" s="10" t="inlineStr">
@@ -9884,22 +9888,22 @@
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>SET-009</t>
+          <t>ROOM-005</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Rooms</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>/setup/property</t>
+          <t>/rooms</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Per hotel: "Allow ID photos" (off by default) and "Require ID photo at check-in" (only when allowed). While Allow is off, uploading and opening ID photos are refused.</t>
+          <t>Rooms are added one at a time or several by number or by name, with a preview; labels are free text up to 30 characters, unique per hotel ignoring case and extra spaces, shown as typed and sorted in natural order.</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
@@ -9919,7 +9923,7 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>setup.property.edit</t>
+          <t>setup.room.edit</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr">
@@ -9929,27 +9933,27 @@
       </c>
       <c r="J118" s="10" t="inlineStr">
         <is>
-          <t>a hotel with ID photos off</t>
+          <t>an administrator on the Rooms page</t>
         </is>
       </c>
       <c r="K118" s="10" t="inlineStr">
         <is>
-          <t>staff try to add or open an ID photo</t>
+          <t>they add rooms by number range or by names</t>
         </is>
       </c>
       <c r="L118" s="10" t="inlineStr">
         <is>
-          <t>it is refused; when Require is on, check-in waits for an ID photo</t>
+          <t>valid new rooms are created, duplicates skipped and invalid names shown</t>
         </is>
       </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
-          <t>set_id_photo_settings</t>
+          <t>add_rooms_range, add_rooms_named, save_room</t>
         </is>
       </c>
       <c r="N118" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (10)</t>
+          <t>23_room_labels (46); 26_small_fixes (1); browser: rooms-add</t>
         </is>
       </c>
       <c r="O118" s="10" t="inlineStr">
@@ -9962,32 +9966,32 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>GRP-001</t>
+          <t>SET-009</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>Platform &amp; Tenancy</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>All branches</t>
+          <t>/setup/property</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>A built-in Group Manager role and the permission rpt.group.view exist; only System Administrator, General Manager and Group Manager hold the permission.</t>
+          <t>Per hotel: "Allow ID photos" (off by default) and "Require ID photo at check-in" (only when allowed). While Allow is off, uploading and opening ID photos are refused.</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
@@ -9997,33 +10001,37 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>rpt.group.view</t>
-        </is>
-      </c>
-      <c r="I119" s="10" t="inlineStr"/>
+          <t>setup.property.edit</t>
+        </is>
+      </c>
+      <c r="I119" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
-          <t>a hotel group with several branches</t>
+          <t>a hotel with ID photos off</t>
         </is>
       </c>
       <c r="K119" s="10" t="inlineStr">
         <is>
-          <t>an owner wants a view-only manager for the whole group</t>
+          <t>staff try to add or open an ID photo</t>
         </is>
       </c>
       <c r="L119" s="10" t="inlineStr">
         <is>
-          <t>they assign the Group Manager role branch by branch, and that person can look but not post or change anything</t>
+          <t>it is refused; when Require is on, check-in waits for an ID photo</t>
         </is>
       </c>
       <c r="M119" s="10" t="inlineStr">
         <is>
-          <t>20261013120000_group_view.sql</t>
+          <t>set_id_photo_settings</t>
         </is>
       </c>
       <c r="N119" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (5)</t>
+          <t>24_id_photos (10)</t>
         </is>
       </c>
       <c r="O119" s="10" t="inlineStr">
@@ -10031,16 +10039,12 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P119" s="10" t="inlineStr">
-        <is>
-          <t>Custom roles copied earlier do not get the new permission; say so when releasing.</t>
-        </is>
-      </c>
+      <c r="P119" s="10" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>GRP-002</t>
+          <t>GRP-001</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -10055,7 +10059,7 @@
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>One call shows every branch the person may see: occupancy, in house, arrivals and departures to come, approvals, repairs and last night revenue, with group totals. Revenue is totalled per currency.</t>
+          <t>A built-in Group Manager role and the permission rpt.group.view exist; only System Administrator, General Manager and Group Manager hold the permission.</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
@@ -10081,27 +10085,27 @@
       <c r="I120" s="10" t="inlineStr"/>
       <c r="J120" s="10" t="inlineStr">
         <is>
-          <t>a group with a Lagos and an Abuja branch</t>
+          <t>a hotel group with several branches</t>
         </is>
       </c>
       <c r="K120" s="10" t="inlineStr">
         <is>
-          <t>a group manager opens All branches</t>
+          <t>an owner wants a view-only manager for the whole group</t>
         </is>
       </c>
       <c r="L120" s="10" t="inlineStr">
         <is>
-          <t>they see both branches with figures from the database, never another hotel group, and staff without the permission are refused</t>
+          <t>they assign the Group Manager role branch by branch, and that person can look but not post or change anything</t>
         </is>
       </c>
       <c r="M120" s="10" t="inlineStr">
         <is>
-          <t>group_overview; /group screen</t>
+          <t>20261013120000_group_view.sql</t>
         </is>
       </c>
       <c r="N120" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (10)</t>
+          <t>35_group_view (5)</t>
         </is>
       </c>
       <c r="O120" s="10" t="inlineStr">
@@ -10111,14 +10115,14 @@
       </c>
       <c r="P120" s="10" t="inlineStr">
         <is>
-          <t>Figures are read from each branch own business date. No arithmetic in the browser.</t>
+          <t>Custom roles copied earlier do not get the new permission; say so when releasing.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>GRP-003</t>
+          <t>GRP-002</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -10133,7 +10137,7 @@
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>A Group Manager sees only the branches they are assigned to, and cannot post charges or check guests in.</t>
+          <t>One call shows every branch the person may see: occupancy, in house, arrivals and departures to come, approvals, repairs and last night revenue, with group totals. Revenue is totalled per currency.</t>
         </is>
       </c>
       <c r="E121" s="10" t="inlineStr">
@@ -10159,27 +10163,27 @@
       <c r="I121" s="10" t="inlineStr"/>
       <c r="J121" s="10" t="inlineStr">
         <is>
-          <t>a Group Manager assigned to one branch</t>
+          <t>a group with a Lagos and an Abuja branch</t>
         </is>
       </c>
       <c r="K121" s="10" t="inlineStr">
         <is>
-          <t>a second branch is assigned</t>
+          <t>a group manager opens All branches</t>
         </is>
       </c>
       <c r="L121" s="10" t="inlineStr">
         <is>
-          <t>the second branch appears; the role never gets write permissions</t>
+          <t>they see both branches with figures from the database, never another hotel group, and staff without the permission are refused</t>
         </is>
       </c>
       <c r="M121" s="10" t="inlineStr">
         <is>
-          <t>assign_role (existing); group_overview</t>
+          <t>group_overview; /group screen</t>
         </is>
       </c>
       <c r="N121" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (3)</t>
+          <t>35_group_view (10)</t>
         </is>
       </c>
       <c r="O121" s="10" t="inlineStr">
@@ -10189,14 +10193,14 @@
       </c>
       <c r="P121" s="10" t="inlineStr">
         <is>
-          <t>Access is per branch, using the existing role assignment screen.</t>
+          <t>Figures are read from each branch own business date. No arithmetic in the browser.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>GRP-004</t>
+          <t>GRP-003</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
@@ -10206,12 +10210,12 @@
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>All branches (Copy setup)</t>
+          <t>All branches</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>A new branch can copy room types, rate plans and prices from an existing branch, once, into an empty branch.</t>
+          <t>A Group Manager sees only the branches they are assigned to, and cannot post charges or check guests in.</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
@@ -10231,33 +10235,33 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>setup.room.manage, setup.rate.manage</t>
+          <t>rpt.group.view</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr"/>
       <c r="J122" s="10" t="inlineStr">
         <is>
-          <t>a new empty branch</t>
+          <t>a Group Manager assigned to one branch</t>
         </is>
       </c>
       <c r="K122" s="10" t="inlineStr">
         <is>
-          <t>the owner copies setup from the first branch</t>
+          <t>a second branch is assigned</t>
         </is>
       </c>
       <c r="L122" s="10" t="inlineStr">
         <is>
-          <t>room types, rate plans and prices appear on the new branch and point at its own room types; rooms are not copied; a second copy is refused; the copy is audited</t>
+          <t>the second branch appears; the role never gets write permissions</t>
         </is>
       </c>
       <c r="M122" s="10" t="inlineStr">
         <is>
-          <t>copy_property_setup</t>
+          <t>assign_role (existing); group_overview</t>
         </is>
       </c>
       <c r="N122" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (13)</t>
+          <t>35_group_view (3)</t>
         </is>
       </c>
       <c r="O122" s="10" t="inlineStr">
@@ -10267,29 +10271,29 @@
       </c>
       <c r="P122" s="10" t="inlineStr">
         <is>
-          <t>Taxes, charge codes and payment methods already arrive with every new branch.</t>
+          <t>Access is per branch, using the existing role assignment screen.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>RPT-005</t>
+          <t>GRP-004</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Platform &amp; Tenancy</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>All branches (Copy setup)</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>Revenue by booking source: bookings, cancellations, no-shows, room nights, room revenue and average rate for each source in a date range.</t>
+          <t>A new branch can copy room types, rate plans and prices from an existing branch, once, into an empty branch.</t>
         </is>
       </c>
       <c r="E123" s="10" t="inlineStr">
@@ -10309,33 +10313,33 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view</t>
+          <t>setup.room.manage, setup.rate.manage</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr"/>
       <c r="J123" s="10" t="inlineStr">
         <is>
-          <t>bookings from direct, phone and company sources</t>
+          <t>a new empty branch</t>
         </is>
       </c>
       <c r="K123" s="10" t="inlineStr">
         <is>
-          <t>the accountant picks a date range</t>
+          <t>the owner copies setup from the first branch</t>
         </is>
       </c>
       <c r="L123" s="10" t="inlineStr">
         <is>
-          <t>each source shows its own counts and room revenue (room charges only, before tax); cancelled bookings add no nights</t>
+          <t>room types, rate plans and prices appear on the new branch and point at its own room types; rooms are not copied; a second copy is refused; the copy is audited</t>
         </is>
       </c>
       <c r="M123" s="10" t="inlineStr">
         <is>
-          <t>20261013130000_source_ageing_reports.sql: report_revenue_by_source; Reports, By booking source tab</t>
+          <t>copy_property_setup</t>
         </is>
       </c>
       <c r="N123" s="10" t="inlineStr">
         <is>
-          <t>36_source_ageing (13)</t>
+          <t>35_group_view (13)</t>
         </is>
       </c>
       <c r="O123" s="10" t="inlineStr">
@@ -10345,14 +10349,14 @@
       </c>
       <c r="P123" s="10" t="inlineStr">
         <is>
-          <t>Bookings counted by arrival date; revenue by posting date.</t>
+          <t>Taxes, charge codes and payment methods already arrive with every new branch.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>RPT-006</t>
+          <t>RPT-005</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -10367,7 +10371,7 @@
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>Ageing of unpaid balances by booking source: current, 1 to 7, 8 to 30, 31 to 60 and over 60 days since the due departure, plus credit held.</t>
+          <t>Revenue by booking source: bookings, cancellations, no-shows, room nights, room revenue and average rate for each source in a date range.</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
@@ -10393,27 +10397,27 @@
       <c r="I124" s="10" t="inlineStr"/>
       <c r="J124" s="10" t="inlineStr">
         <is>
-          <t>guests and companies who left owing money</t>
+          <t>bookings from direct, phone and company sources</t>
         </is>
       </c>
       <c r="K124" s="10" t="inlineStr">
         <is>
-          <t>the accountant opens the Ageing tab</t>
+          <t>the accountant picks a date range</t>
         </is>
       </c>
       <c r="L124" s="10" t="inlineStr">
         <is>
-          <t>each source shows what is owed in each age column; paid bills drop out; overpayments show as credit held; the total matches Outstanding balances</t>
+          <t>each source shows its own counts and room revenue (room charges only, before tax); cancelled bookings add no nights</t>
         </is>
       </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
-          <t>report_balance_ageing; Reports, Ageing tab</t>
+          <t>20261013130000_source_ageing_reports.sql: report_revenue_by_source; Reports, By booking source tab</t>
         </is>
       </c>
       <c r="N124" s="10" t="inlineStr">
         <is>
-          <t>36_source_ageing (11)</t>
+          <t>36_source_ageing (13)</t>
         </is>
       </c>
       <c r="O124" s="10" t="inlineStr">
@@ -10423,29 +10427,29 @@
       </c>
       <c r="P124" s="10" t="inlineStr">
         <is>
-          <t>Guests still staying count as current.</t>
+          <t>Bookings counted by arrival date; revenue by posting date.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>AI-001</t>
+          <t>RPT-006</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>AI helpers</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Dashboard, Admin</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>AI helpers are off for every hotel until a System Administrator or General Manager switches them on, with a monthly limit; the switch is audited.</t>
+          <t>Ageing of unpaid balances by booking source: current, 1 to 7, 8 to 30, 31 to 60 and over 60 days since the due departure, plus credit held.</t>
         </is>
       </c>
       <c r="E125" s="10" t="inlineStr">
@@ -10465,33 +10469,33 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>adm.ai.manage</t>
+          <t>rpt.finance.view</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr"/>
       <c r="J125" s="10" t="inlineStr">
         <is>
-          <t>a new hotel</t>
+          <t>guests and companies who left owing money</t>
         </is>
       </c>
       <c r="K125" s="10" t="inlineStr">
         <is>
-          <t>a manager opens Admin, AI helpers</t>
+          <t>the accountant opens the Ageing tab</t>
         </is>
       </c>
       <c r="L125" s="10" t="inlineStr">
         <is>
-          <t>nothing runs until they switch it on and the change is in the audit log</t>
+          <t>each source shows what is owed in each age column; paid bills drop out; overpayments show as credit held; the total matches Outstanding balances</t>
         </is>
       </c>
       <c r="M125" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: set_ai_settings, ai_status; Admin, AI helpers tab</t>
+          <t>report_balance_ageing; Reports, Ageing tab</t>
         </is>
       </c>
       <c r="N125" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (11)</t>
+          <t>36_source_ageing (11)</t>
         </is>
       </c>
       <c r="O125" s="10" t="inlineStr">
@@ -10501,14 +10505,14 @@
       </c>
       <c r="P125" s="10" t="inlineStr">
         <is>
-          <t>Custom roles copied earlier do not get adm.ai.manage.</t>
+          <t>Guests still staying count as current.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>AI-002</t>
+          <t>AI-001</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
@@ -10523,7 +10527,7 @@
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>The facts sent to the AI are counts and money lines built by the database: no guest names, ID details, room numbers or card data.</t>
+          <t>AI helpers are off for every hotel until a System Administrator or General Manager switches them on, with a monthly limit; the switch is audited.</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
@@ -10543,28 +10547,28 @@
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view, rpt.operations.view</t>
+          <t>adm.ai.manage</t>
         </is>
       </c>
       <c r="I126" s="10" t="inlineStr"/>
       <c r="J126" s="10" t="inlineStr">
         <is>
-          <t>a hotel with guests, approvals and overdue bills</t>
+          <t>a new hotel</t>
         </is>
       </c>
       <c r="K126" s="10" t="inlineStr">
         <is>
-          <t>a brief is started</t>
+          <t>a manager opens Admin, AI helpers</t>
         </is>
       </c>
       <c r="L126" s="10" t="inlineStr">
         <is>
-          <t>the facts hold only business date, last night, today, attention figures and plain lines, and overdue money matches the ledger</t>
+          <t>nothing runs until they switch it on and the change is in the audit log</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: ai_morning_brief_start, app.morning_brief_facts</t>
+          <t>20261013140000_ai_morning_brief.sql: set_ai_settings, ai_status; Admin, AI helpers tab</t>
         </is>
       </c>
       <c r="N126" s="10" t="inlineStr">
@@ -10579,14 +10583,14 @@
       </c>
       <c r="P126" s="10" t="inlineStr">
         <is>
-          <t>Overdue means unpaid more than 30 days after departure.</t>
+          <t>Custom roles copied earlier do not get adm.ai.manage.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>AI-003</t>
+          <t>AI-002</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
@@ -10601,7 +10605,7 @@
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>Each hotel has a monthly limit on AI drafts; failed calls do not count; a call can be finished once, by the person who started it.</t>
+          <t>The facts sent to the AI are counts and money lines built by the database: no guest names, ID details, room numbers or card data.</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr">
@@ -10621,33 +10625,33 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view</t>
+          <t>rpt.finance.view, rpt.operations.view</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr"/>
       <c r="J127" s="10" t="inlineStr">
         <is>
-          <t>a limit of 2</t>
+          <t>a hotel with guests, approvals and overdue bills</t>
         </is>
       </c>
       <c r="K127" s="10" t="inlineStr">
         <is>
-          <t>a third brief is requested</t>
+          <t>a brief is started</t>
         </is>
       </c>
       <c r="L127" s="10" t="inlineStr">
         <is>
-          <t>it is refused until a failed call frees a slot or the month turns</t>
+          <t>the facts hold only business date, last night, today, attention figures and plain lines, and overdue money matches the ledger</t>
         </is>
       </c>
       <c r="M127" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: ai_call_finish</t>
+          <t>20261013140000_ai_morning_brief.sql: ai_morning_brief_start, app.morning_brief_facts</t>
         </is>
       </c>
       <c r="N127" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (5)</t>
+          <t>37_ai_brief (11)</t>
         </is>
       </c>
       <c r="O127" s="10" t="inlineStr">
@@ -10655,12 +10659,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P127" s="10" t="inlineStr"/>
+      <c r="P127" s="10" t="inlineStr">
+        <is>
+          <t>Overdue means unpaid more than 30 days after departure.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>AI-004</t>
+          <t>AI-003</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -10675,7 +10683,7 @@
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>Only finance and operations viewers can ask for the brief; the usage log and settings cannot be written or read directly by the browser.</t>
+          <t>Each hotel has a monthly limit on AI drafts; failed calls do not count; a call can be finished once, by the person who started it.</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
@@ -10695,33 +10703,33 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view, rpt.operations.view</t>
+          <t>rpt.finance.view</t>
         </is>
       </c>
       <c r="I128" s="10" t="inlineStr"/>
       <c r="J128" s="10" t="inlineStr">
         <is>
-          <t>front desk, housekeeping, another hotel</t>
+          <t>a limit of 2</t>
         </is>
       </c>
       <c r="K128" s="10" t="inlineStr">
         <is>
-          <t>they ask for the brief or touch the tables</t>
+          <t>a third brief is requested</t>
         </is>
       </c>
       <c r="L128" s="10" t="inlineStr">
         <is>
-          <t>they are refused</t>
+          <t>it is refused until a failed call frees a slot or the month turns</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql</t>
+          <t>20261013140000_ai_morning_brief.sql: ai_call_finish</t>
         </is>
       </c>
       <c r="N128" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (7)</t>
+          <t>37_ai_brief (5)</t>
         </is>
       </c>
       <c r="O128" s="10" t="inlineStr">
@@ -10734,7 +10742,7 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>AI-005</t>
+          <t>AI-004</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -10749,7 +10757,7 @@
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>The server accepts an AI draft only when every number in it is in the database facts; otherwise it shows the plain figures. The key stays on the server and only the fact lines are sent.</t>
+          <t>Only finance and operations viewers can ask for the brief; the usage log and settings cannot be written or read directly by the browser.</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
@@ -10769,33 +10777,33 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>rpt.finance.view, rpt.operations.view</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr"/>
       <c r="J129" s="10" t="inlineStr">
         <is>
-          <t>a draft that rounds or invents a figure</t>
+          <t>front desk, housekeeping, another hotel</t>
         </is>
       </c>
       <c r="K129" s="10" t="inlineStr">
         <is>
-          <t>the brief is written</t>
+          <t>they ask for the brief or touch the tables</t>
         </is>
       </c>
       <c r="L129" s="10" t="inlineStr">
         <is>
-          <t>the plain database lines are shown instead, with a note</t>
+          <t>they are refused</t>
         </is>
       </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
-          <t>src/lib/ai-brief.ts, ai-brief.functions.ts, Dashboard morning brief card</t>
+          <t>20261013140000_ai_morning_brief.sql</t>
         </is>
       </c>
       <c r="N129" s="10" t="inlineStr">
         <is>
-          <t>browser unit: ai-brief-unit (8)</t>
+          <t>37_ai_brief (7)</t>
         </is>
       </c>
       <c r="O129" s="10" t="inlineStr">
@@ -10803,31 +10811,27 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P129" s="10" t="inlineStr">
-        <is>
-          <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
-        </is>
-      </c>
+      <c r="P129" s="10" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>SET-010</t>
+          <t>AI-005</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>AI helpers</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Setup, Rooms</t>
+          <t>Dashboard, Admin</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>A hotel can add room types and rooms from one checked list: preview first, then all or nothing. Existing codes and room names are skipped, so repeating adds nothing.</t>
+          <t>The server accepts an AI draft only when every number in it is in the database facts; otherwise it shows the plain figures. The key stays on the server and only the fact lines are sent.</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
@@ -10847,33 +10851,33 @@
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>setup.room.manage</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I130" s="10" t="inlineStr"/>
       <c r="J130" s="10" t="inlineStr">
         <is>
-          <t>a list of room types and rooms</t>
+          <t>a draft that rounds or invents a figure</t>
         </is>
       </c>
       <c r="K130" s="10" t="inlineStr">
         <is>
-          <t>the manager previews and then applies it</t>
+          <t>the brief is written</t>
         </is>
       </c>
       <c r="L130" s="10" t="inlineStr">
         <is>
-          <t>the preview writes nothing; apply adds every valid item or none (bad name, unknown type, over 500 rooms, over the plan limit); a repeat adds nothing; the import is audited</t>
+          <t>the plain database lines are shown instead, with a note</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
-          <t>20261013150000_setup_import.sql: apply_setup_import</t>
+          <t>src/lib/ai-brief.ts, ai-brief.functions.ts, Dashboard morning brief card</t>
         </is>
       </c>
       <c r="N130" s="10" t="inlineStr">
         <is>
-          <t>38_setup_import (29)</t>
+          <t>browser unit: ai-brief-unit (8)</t>
         </is>
       </c>
       <c r="O130" s="10" t="inlineStr">
@@ -10883,19 +10887,19 @@
       </c>
       <c r="P130" s="10" t="inlineStr">
         <is>
-          <t>The AI only drafts the list. This function is the check.</t>
+          <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>AI-006</t>
+          <t>SET-010</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>AI helpers</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
@@ -10905,7 +10909,7 @@
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>The setup import assistant starts only when AI is on and under the monthly limit, and the AI sees only existing room type codes and a room count.</t>
+          <t>A hotel can add room types and rooms from one checked list: preview first, then all or nothing. Existing codes and room names are skipped, so repeating adds nothing.</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
@@ -10931,27 +10935,27 @@
       <c r="I131" s="10" t="inlineStr"/>
       <c r="J131" s="10" t="inlineStr">
         <is>
-          <t>AI switched on with a limit of 1</t>
+          <t>a list of room types and rooms</t>
         </is>
       </c>
       <c r="K131" s="10" t="inlineStr">
         <is>
-          <t>an import draft is started twice</t>
+          <t>the manager previews and then applies it</t>
         </is>
       </c>
       <c r="L131" s="10" t="inlineStr">
         <is>
-          <t>the second is refused until the first fails; front desk and other hotels are refused</t>
+          <t>the preview writes nothing; apply adds every valid item or none (bad name, unknown type, over 500 rooms, over the plan limit); a repeat adds nothing; the import is audited</t>
         </is>
       </c>
       <c r="M131" s="10" t="inlineStr">
         <is>
-          <t>20261013150000_setup_import.sql: ai_import_start, app.ai_begin</t>
+          <t>20261013150000_setup_import.sql: apply_setup_import</t>
         </is>
       </c>
       <c r="N131" s="10" t="inlineStr">
         <is>
-          <t>38_setup_import (8)</t>
+          <t>38_setup_import (29)</t>
         </is>
       </c>
       <c r="O131" s="10" t="inlineStr">
@@ -10959,12 +10963,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P131" s="10" t="inlineStr"/>
+      <c r="P131" s="10" t="inlineStr">
+        <is>
+          <t>The AI only drafts the list. This function is the check.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>AI-007</t>
+          <t>AI-006</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -10979,7 +10987,7 @@
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Pasted text with an email, phone or card number is refused before anything is sent; the draft may only contain rooms, floors, guest limits and type names that are in the pasted text.</t>
+          <t>The setup import assistant starts only when AI is on and under the monthly limit, and the AI sees only existing room type codes and a room count.</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
@@ -11005,27 +11013,27 @@
       <c r="I132" s="10" t="inlineStr"/>
       <c r="J132" s="10" t="inlineStr">
         <is>
-          <t>a pasted list</t>
+          <t>AI switched on with a limit of 1</t>
         </is>
       </c>
       <c r="K132" s="10" t="inlineStr">
         <is>
-          <t>the assistant drafts it</t>
+          <t>an import draft is started twice</t>
         </is>
       </c>
       <c r="L132" s="10" t="inlineStr">
         <is>
-          <t>invented rooms, floors and limits are dropped with a note; a draft with no matching rooms is an error</t>
+          <t>the second is refused until the first fails; front desk and other hotels are refused</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
-          <t>src/lib/setup-import.ts, setup-import.functions.ts, Import from a list on Setup, Rooms</t>
+          <t>20261013150000_setup_import.sql: ai_import_start, app.ai_begin</t>
         </is>
       </c>
       <c r="N132" s="10" t="inlineStr">
         <is>
-          <t>browser unit: setup-import-unit (9)</t>
+          <t>38_setup_import (8)</t>
         </is>
       </c>
       <c r="O132" s="10" t="inlineStr">
@@ -11033,36 +11041,32 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P132" s="10" t="inlineStr">
-        <is>
-          <t>Needs ANTHROPIC_API_KEY on the server. Not set yet.</t>
-        </is>
-      </c>
+      <c r="P132" s="10" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>SET-011</t>
+          <t>AI-007</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>AI helpers</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>/setup; /dashboard</t>
+          <t>Setup, Rooms</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>A new hotel sees a checklist of what is left to set up: property details, room types, rooms, rates, taxes, payment methods and staff. Each step says what is missing and links to the right screen. The list comes from the hotel's own data, so it is always current.</t>
+          <t>Pasted text with an email, phone or card number is refused before anything is sent; the draft may only contain rooms, floors, guest limits and type names that are in the pasted text.</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F133" s="10" t="inlineStr">
@@ -11077,37 +11081,33 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>any setup permission</t>
-        </is>
-      </c>
-      <c r="I133" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>setup.room.manage</t>
+        </is>
+      </c>
+      <c r="I133" s="10" t="inlineStr"/>
       <c r="J133" s="10" t="inlineStr">
         <is>
-          <t>a hotel that is part way through setup</t>
+          <t>a pasted list</t>
         </is>
       </c>
       <c r="K133" s="10" t="inlineStr">
         <is>
-          <t>a manager opens Setup or the Dashboard</t>
+          <t>the assistant drafts it</t>
         </is>
       </c>
       <c r="L133" s="10" t="inlineStr">
         <is>
-          <t>the steps already done are ticked and the next one is linked; once all seven are done the checklist goes away</t>
+          <t>invented rooms, floors and limits are dropped with a note; a draft with no matching rooms is an error</t>
         </is>
       </c>
       <c r="M133" s="10" t="inlineStr">
         <is>
-          <t>setup_progress</t>
+          <t>src/lib/setup-import.ts, setup-import.functions.ts, Import from a list on Setup, Rooms</t>
         </is>
       </c>
       <c r="N133" s="10" t="inlineStr">
         <is>
-          <t>40_guided_setup (30)</t>
+          <t>browser unit: setup-import-unit (9)</t>
         </is>
       </c>
       <c r="O133" s="10" t="inlineStr">
@@ -11117,39 +11117,39 @@
       </c>
       <c r="P133" s="10" t="inlineStr">
         <is>
-          <t>Read-only function, no stored progress. Staff step counts people with a role at the property (two or more).</t>
+          <t>Needs ANTHROPIC_API_KEY on the server. Not set yet.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>NFR-006</t>
+          <t>SET-011</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>(all)</t>
+          <t>/setup; /dashboard</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>The last room of a type is sold once, however many desks book at the same moment, and a repeated booking never doubles.</t>
+          <t>A new hotel sees a checklist of what is left to set up: property details, room types, rooms, rates, taxes, payment methods and staff. Each step says what is missing and links to the right screen. The list comes from the hotel's own data, so it is always current.</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G134" s="10" t="inlineStr">
@@ -11159,37 +11159,37 @@
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
+          <t>any setup permission</t>
+        </is>
+      </c>
+      <c r="I134" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I134" s="10" t="inlineStr">
-        <is>
-          <t>Rule: Safe last-room booking</t>
-        </is>
-      </c>
       <c r="J134" s="10" t="inlineStr">
         <is>
-          <t>one room of a type is left and several desks book it together</t>
+          <t>a hotel that is part way through setup</t>
         </is>
       </c>
       <c r="K134" s="10" t="inlineStr">
         <is>
-          <t>all of them submit at the same moment</t>
+          <t>a manager opens Setup or the Dashboard</t>
         </is>
       </c>
       <c r="L134" s="10" t="inlineStr">
         <is>
-          <t>exactly one booking succeeds, the rest get E_NO_AVAILABILITY, and nothing is oversold</t>
+          <t>the steps already done are ticked and the next one is linked; once all seven are done the checklist goes away</t>
         </is>
       </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
-          <t>create_reservation, assert_available</t>
+          <t>setup_progress</t>
         </is>
       </c>
       <c r="N134" s="10" t="inlineStr">
         <is>
-          <t>concurrency/last_room.sh (6)</t>
+          <t>40_guided_setup (30)</t>
         </is>
       </c>
       <c r="O134" s="10" t="inlineStr">
@@ -11199,29 +11199,29 @@
       </c>
       <c r="P134" s="10" t="inlineStr">
         <is>
-          <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
+          <t>Read-only function, no stored progress. Staff step counts people with a role at the property (two or more).</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>SET-012</t>
+          <t>NFR-006</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Non-functional</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>/setup/property</t>
+          <t>(all)</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>A manager sets the longest stay (1 to 365 nights) and how long a tentative booking holds its room (1 to 720 hours) for each property.</t>
+          <t>The last room of a type is sold once, however many desks book at the same moment, and a repeated booking never doubles.</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
@@ -11241,33 +11241,37 @@
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>setup.property.edit</t>
-        </is>
-      </c>
-      <c r="I135" s="10" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="10" t="inlineStr">
+        <is>
+          <t>Rule: Safe last-room booking</t>
+        </is>
+      </c>
       <c r="J135" s="10" t="inlineStr">
         <is>
-          <t>a property with the default rules (30 nights, 24 hours)</t>
+          <t>one room of a type is left and several desks book it together</t>
         </is>
       </c>
       <c r="K135" s="10" t="inlineStr">
         <is>
-          <t>a manager saves new booking rules</t>
+          <t>all of them submit at the same moment</t>
         </is>
       </c>
       <c r="L135" s="10" t="inlineStr">
         <is>
-          <t>new bookings use them, bad values are refused with E_INVALID, and the change is audited with old and new values</t>
+          <t>exactly one booking succeeds, the rest get E_NO_AVAILABILITY, and nothing is oversold</t>
         </is>
       </c>
       <c r="M135" s="10" t="inlineStr">
         <is>
-          <t>set_booking_rules; Booking rules on Setup, Property</t>
+          <t>create_reservation, assert_available</t>
         </is>
       </c>
       <c r="N135" s="10" t="inlineStr">
         <is>
-          <t>42_booking_rules (9)</t>
+          <t>concurrency/last_room.sh (6)</t>
         </is>
       </c>
       <c r="O135" s="10" t="inlineStr">
@@ -11277,39 +11281,39 @@
       </c>
       <c r="P135" s="10" t="inlineStr">
         <is>
-          <t>Added 8 Oct 2026. The columns existed since the reservations release; this adds the screen and the function.</t>
+          <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>FO-014</t>
+          <t>SET-012</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>Front Office</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>/downtime</t>
+          <t>/setup/property</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>A printable downtime pack: arrivals due, in-house guests with balance, departures due, ten blank lines for new guests on paper, and a short paper routine. Staff print it when the internet or system is down.</t>
+          <t>A manager sets the longest stay (1 to 365 nights) and how long a tentative booking holds its room (1 to 720 hours) for each property.</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>BR-006</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G136" s="10" t="inlineStr">
@@ -11319,33 +11323,33 @@
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>fo.view</t>
+          <t>setup.property.edit</t>
         </is>
       </c>
       <c r="I136" s="10" t="inlineStr"/>
       <c r="J136" s="10" t="inlineStr">
         <is>
-          <t>a hotel with guests in house</t>
+          <t>a property with the default rules (30 nights, 24 hours)</t>
         </is>
       </c>
       <c r="K136" s="10" t="inlineStr">
         <is>
-          <t>a front desk user opens Downtime pack and prints</t>
+          <t>a manager saves new booking rules</t>
         </is>
       </c>
       <c r="L136" s="10" t="inlineStr">
         <is>
-          <t>the lists show room, guest, phone, departure and the folio balance from the database, with blank lines and the paper routine</t>
+          <t>new bookings use them, bad values are refused with E_INVALID, and the change is audited with old and new values</t>
         </is>
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
-          <t>src/routes/_authenticated/_app/downtime.tsx</t>
+          <t>set_booking_rules; Booking rules on Setup, Property</t>
         </is>
       </c>
       <c r="N136" s="10" t="inlineStr">
         <is>
-          <t>browser: downtime-pack.spec (1)</t>
+          <t>42_booking_rules (9)</t>
         </is>
       </c>
       <c r="O136" s="10" t="inlineStr">
@@ -11355,87 +11359,165 @@
       </c>
       <c r="P136" s="10" t="inlineStr">
         <is>
-          <t>No database change. Reads v_arrivals, v_in_house and v_folio_balances. Added 8 Oct 2026.</t>
+          <t>Added 8 Oct 2026. The columns existed since the reservations release; this adds the screen and the function.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
+          <t>FO-014</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>Front Office</t>
+        </is>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>/downtime</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t>A printable downtime pack: arrivals due, in-house guests with balance, departures due, ten blank lines for new guests on paper, and a short paper routine. Staff print it when the internet or system is down.</t>
+        </is>
+      </c>
+      <c r="E137" s="10" t="inlineStr">
+        <is>
+          <t>BR-006</t>
+        </is>
+      </c>
+      <c r="F137" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G137" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H137" s="10" t="inlineStr">
+        <is>
+          <t>fo.view</t>
+        </is>
+      </c>
+      <c r="I137" s="10" t="inlineStr"/>
+      <c r="J137" s="10" t="inlineStr">
+        <is>
+          <t>a hotel with guests in house</t>
+        </is>
+      </c>
+      <c r="K137" s="10" t="inlineStr">
+        <is>
+          <t>a front desk user opens Downtime pack and prints</t>
+        </is>
+      </c>
+      <c r="L137" s="10" t="inlineStr">
+        <is>
+          <t>the lists show room, guest, phone, departure and the folio balance from the database, with blank lines and the paper routine</t>
+        </is>
+      </c>
+      <c r="M137" s="10" t="inlineStr">
+        <is>
+          <t>src/routes/_authenticated/_app/downtime.tsx</t>
+        </is>
+      </c>
+      <c r="N137" s="10" t="inlineStr">
+        <is>
+          <t>browser: downtime-pack.spec (1)</t>
+        </is>
+      </c>
+      <c r="O137" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P137" s="10" t="inlineStr">
+        <is>
+          <t>No database change. Reads v_arrivals, v_in_house and v_folio_balances. Added 8 Oct 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
           <t>DAY-007</t>
         </is>
       </c>
-      <c r="B137" s="10" t="inlineStr">
+      <c r="B138" s="10" t="inlineStr">
         <is>
           <t>Business Date</t>
         </is>
       </c>
-      <c r="C137" s="10" t="inlineStr">
+      <c r="C138" s="10" t="inlineStr">
         <is>
           <t>Notifications bell</t>
         </is>
       </c>
-      <c r="D137" s="10" t="inlineStr">
+      <c r="D138" s="10" t="inlineStr">
         <is>
           <t>In the last hour before a property rolls its business date, if a cashier shift is still open, users who can run the night audit get one warning that night. The roll does not wait.</t>
         </is>
       </c>
-      <c r="E137" s="10" t="inlineStr">
+      <c r="E138" s="10" t="inlineStr">
         <is>
           <t>BR-016</t>
         </is>
       </c>
-      <c r="F137" s="10" t="inlineStr">
+      <c r="F138" s="10" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G137" s="10" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H137" s="10" t="inlineStr">
+      <c r="G138" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H138" s="10" t="inlineStr">
         <is>
           <t>fin.nightaudit.run</t>
         </is>
       </c>
-      <c r="I137" s="10" t="inlineStr">
+      <c r="I138" s="10" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="J137" s="10" t="inlineStr">
+      <c r="J138" s="10" t="inlineStr">
         <is>
           <t>a cashier shift is still open</t>
         </is>
       </c>
-      <c r="K137" s="10" t="inlineStr">
+      <c r="K138" s="10" t="inlineStr">
         <is>
           <t>the roll time is less than 60 minutes away</t>
         </is>
       </c>
-      <c r="L137" s="10" t="inlineStr">
+      <c r="L138" s="10" t="inlineStr">
         <is>
           <t>each night audit user gets one rollover_warning notification for that business date; none earlier, none after the roll time, none if no shift is open, none twice</t>
         </is>
       </c>
-      <c r="M137" s="10" t="inlineStr">
+      <c r="M138" s="10" t="inlineStr">
         <is>
           <t>app.warn_before_rollover; cron job rollover-warning</t>
         </is>
       </c>
-      <c r="N137" s="10" t="inlineStr">
+      <c r="N138" s="10" t="inlineStr">
         <is>
           <t>43_rollover_warning (9)</t>
         </is>
       </c>
-      <c r="O137" s="10" t="inlineStr">
+      <c r="O138" s="10" t="inlineStr">
         <is>
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P137" s="10" t="inlineStr">
+      <c r="P138" s="10" t="inlineStr">
         <is>
           <t>Added 8 Oct 2026. Warning only; the hard gate stays in R2 (DAY-005).</t>
         </is>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P138"/>
+  <dimension ref="A1:P139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9576,22 +9576,22 @@
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>GST-007</t>
+          <t>FIN-020</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>Guests</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>/guests/$id; check-in; walk-in</t>
+          <t>/invoices/$id</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>A photo or scan of an ID document is kept in private storage, shrunk and stripped of hidden data in the browser, and opened only through a 60-second link.</t>
+          <t>Invoice and interim invoice numbers carry the year and month of the hotel business date, then a count that restarts each month with no gaps (INV-202610-000001, INT-202610-000001). Invoices already issued keep their numbers.</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
@@ -9611,37 +9611,37 @@
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>guest.document.file.upload / view / delete</t>
+          <t>fin.invoice.issue</t>
         </is>
       </c>
       <c r="I114" s="10" t="inlineStr">
         <is>
-          <t>SET-009 switch</t>
+          <t>document_sequences period_key</t>
         </is>
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>a hotel that allows ID photos</t>
+          <t>a hotel with invoices issued in one month</t>
         </is>
       </c>
       <c r="K114" s="10" t="inlineStr">
         <is>
-          <t>front desk adds an ID photo</t>
+          <t>an invoice is issued in the next month</t>
         </is>
       </c>
       <c r="L114" s="10" t="inlineStr">
         <is>
-          <t>it is stored privately and opens only through a short-lived link</t>
+          <t>its number starts with the new year and month and the count restarts at 1; the INT and INV series stay separate; reservation and folio numbers are unchanged</t>
         </is>
       </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
-          <t>begin_id_photo_upload, finish_id_photo_upload, open_id_photo</t>
+          <t>next_document_number, issue_invoice</t>
         </is>
       </c>
       <c r="N114" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (30)</t>
+          <t>46_invoice_number_month (8); 17_more_features</t>
         </is>
       </c>
       <c r="O114" s="10" t="inlineStr">
@@ -9649,12 +9649,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P114" s="10" t="inlineStr"/>
+      <c r="P114" s="10" t="inlineStr">
+        <is>
+          <t>Month comes from the business date, not the clock. No hotel code in the number yet.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>GST-008</t>
+          <t>GST-007</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -9664,12 +9668,12 @@
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>/guests/$id</t>
+          <t>/guests/$id; check-in; walk-in</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>Every upload, view and deletion of an ID photo is audited with ids only, no personal data.</t>
+          <t>A photo or scan of an ID document is kept in private storage, shrunk and stripped of hidden data in the browser, and opened only through a 60-second link.</t>
         </is>
       </c>
       <c r="E115" s="10" t="inlineStr">
@@ -9689,37 +9693,37 @@
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>guest.document.file.upload / view / delete</t>
         </is>
       </c>
       <c r="I115" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SET-009 switch</t>
         </is>
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>an ID photo</t>
+          <t>a hotel that allows ID photos</t>
         </is>
       </c>
       <c r="K115" s="10" t="inlineStr">
         <is>
-          <t>it is uploaded, opened or deleted</t>
+          <t>front desk adds an ID photo</t>
         </is>
       </c>
       <c r="L115" s="10" t="inlineStr">
         <is>
-          <t>an audit row records who and which file, with no personal data</t>
+          <t>it is stored privately and opens only through a short-lived link</t>
         </is>
       </c>
       <c r="M115" s="10" t="inlineStr">
         <is>
-          <t>app.audit_id_photo</t>
+          <t>begin_id_photo_upload, finish_id_photo_upload, open_id_photo</t>
         </is>
       </c>
       <c r="N115" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (9)</t>
+          <t>24_id_photos (30)</t>
         </is>
       </c>
       <c r="O115" s="10" t="inlineStr">
@@ -9732,7 +9736,7 @@
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>GST-009</t>
+          <t>GST-008</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -9747,7 +9751,7 @@
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>ID photos are removed from storage when the guest is anonymised or the document is removed, and move with the guest when two profiles are merged.</t>
+          <t>Every upload, view and deletion of an ID photo is audited with ids only, no personal data.</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
@@ -9777,27 +9781,27 @@
       </c>
       <c r="J116" s="10" t="inlineStr">
         <is>
-          <t>a guest with ID photos</t>
+          <t>an ID photo</t>
         </is>
       </c>
       <c r="K116" s="10" t="inlineStr">
         <is>
-          <t>the guest is anonymised, the document removed, or the profile merged</t>
+          <t>it is uploaded, opened or deleted</t>
         </is>
       </c>
       <c r="L116" s="10" t="inlineStr">
         <is>
-          <t>the files are removed, or move to the kept profile</t>
+          <t>an audit row records who and which file, with no personal data</t>
         </is>
       </c>
       <c r="M116" s="10" t="inlineStr">
         <is>
-          <t>anonymise_guest, merge_guests, delete_id_photo</t>
+          <t>app.audit_id_photo</t>
         </is>
       </c>
       <c r="N116" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (4)</t>
+          <t>24_id_photos (9)</t>
         </is>
       </c>
       <c r="O116" s="10" t="inlineStr">
@@ -9810,7 +9814,7 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>GST-010</t>
+          <t>GST-009</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
@@ -9820,12 +9824,12 @@
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>(daily clean-up)</t>
+          <t>/guests/$id</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>ID photos are deleted automatically a set number of months (one setting, now 12) after the guest's last check-out, unless the guest has a booking that is not over.</t>
+          <t>ID photos are removed from storage when the guest is anonymised or the document is removed, and move with the guest when two profiles are merged.</t>
         </is>
       </c>
       <c r="E117" s="10" t="inlineStr">
@@ -9850,32 +9854,32 @@
       </c>
       <c r="I117" s="10" t="inlineStr">
         <is>
-          <t>Setting id_photo_keep_months; daily cron</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>a guest whose last check-out was more than the keep period ago</t>
+          <t>a guest with ID photos</t>
         </is>
       </c>
       <c r="K117" s="10" t="inlineStr">
         <is>
-          <t>the daily clean-up runs</t>
+          <t>the guest is anonymised, the document removed, or the profile merged</t>
         </is>
       </c>
       <c r="L117" s="10" t="inlineStr">
         <is>
-          <t>their ID photos are deleted</t>
+          <t>the files are removed, or move to the kept profile</t>
         </is>
       </c>
       <c r="M117" s="10" t="inlineStr">
         <is>
-          <t>/api/cron/id-photo-cleanup</t>
+          <t>anonymise_guest, merge_guests, delete_id_photo</t>
         </is>
       </c>
       <c r="N117" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (5)</t>
+          <t>24_id_photos (4)</t>
         </is>
       </c>
       <c r="O117" s="10" t="inlineStr">
@@ -9888,22 +9892,22 @@
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>ROOM-005</t>
+          <t>GST-010</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>Rooms</t>
+          <t>Guests</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>/rooms</t>
+          <t>(daily clean-up)</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Rooms are added one at a time or several by number or by name, with a preview; labels are free text up to 30 characters, unique per hotel ignoring case and extra spaces, shown as typed and sorted in natural order.</t>
+          <t>ID photos are deleted automatically a set number of months (one setting, now 12) after the guest's last check-out, unless the guest has a booking that is not over.</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
@@ -9923,37 +9927,37 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>setup.room.edit</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Setting id_photo_keep_months; daily cron</t>
         </is>
       </c>
       <c r="J118" s="10" t="inlineStr">
         <is>
-          <t>an administrator on the Rooms page</t>
+          <t>a guest whose last check-out was more than the keep period ago</t>
         </is>
       </c>
       <c r="K118" s="10" t="inlineStr">
         <is>
-          <t>they add rooms by number range or by names</t>
+          <t>the daily clean-up runs</t>
         </is>
       </c>
       <c r="L118" s="10" t="inlineStr">
         <is>
-          <t>valid new rooms are created, duplicates skipped and invalid names shown</t>
+          <t>their ID photos are deleted</t>
         </is>
       </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
-          <t>add_rooms_range, add_rooms_named, save_room</t>
+          <t>/api/cron/id-photo-cleanup</t>
         </is>
       </c>
       <c r="N118" s="10" t="inlineStr">
         <is>
-          <t>23_room_labels (46); 26_small_fixes (1); browser: rooms-add</t>
+          <t>24_id_photos (5)</t>
         </is>
       </c>
       <c r="O118" s="10" t="inlineStr">
@@ -9966,22 +9970,22 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>SET-009</t>
+          <t>ROOM-005</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Rooms</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>/setup/property</t>
+          <t>/rooms</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>Per hotel: "Allow ID photos" (off by default) and "Require ID photo at check-in" (only when allowed). While Allow is off, uploading and opening ID photos are refused.</t>
+          <t>Rooms are added one at a time or several by number or by name, with a preview; labels are free text up to 30 characters, unique per hotel ignoring case and extra spaces, shown as typed and sorted in natural order.</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr">
@@ -10001,7 +10005,7 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>setup.property.edit</t>
+          <t>setup.room.edit</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
@@ -10011,27 +10015,27 @@
       </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
-          <t>a hotel with ID photos off</t>
+          <t>an administrator on the Rooms page</t>
         </is>
       </c>
       <c r="K119" s="10" t="inlineStr">
         <is>
-          <t>staff try to add or open an ID photo</t>
+          <t>they add rooms by number range or by names</t>
         </is>
       </c>
       <c r="L119" s="10" t="inlineStr">
         <is>
-          <t>it is refused; when Require is on, check-in waits for an ID photo</t>
+          <t>valid new rooms are created, duplicates skipped and invalid names shown</t>
         </is>
       </c>
       <c r="M119" s="10" t="inlineStr">
         <is>
-          <t>set_id_photo_settings</t>
+          <t>add_rooms_range, add_rooms_named, save_room</t>
         </is>
       </c>
       <c r="N119" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (10)</t>
+          <t>23_room_labels (46); 26_small_fixes (1); browser: rooms-add</t>
         </is>
       </c>
       <c r="O119" s="10" t="inlineStr">
@@ -10044,32 +10048,32 @@
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>GRP-001</t>
+          <t>SET-009</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>Platform &amp; Tenancy</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>All branches</t>
+          <t>/setup/property</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>A built-in Group Manager role and the permission rpt.group.view exist; only System Administrator, General Manager and Group Manager hold the permission.</t>
+          <t>Per hotel: "Allow ID photos" (off by default) and "Require ID photo at check-in" (only when allowed). While Allow is off, uploading and opening ID photos are refused.</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
@@ -10079,33 +10083,37 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>rpt.group.view</t>
-        </is>
-      </c>
-      <c r="I120" s="10" t="inlineStr"/>
+          <t>setup.property.edit</t>
+        </is>
+      </c>
+      <c r="I120" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J120" s="10" t="inlineStr">
         <is>
-          <t>a hotel group with several branches</t>
+          <t>a hotel with ID photos off</t>
         </is>
       </c>
       <c r="K120" s="10" t="inlineStr">
         <is>
-          <t>an owner wants a view-only manager for the whole group</t>
+          <t>staff try to add or open an ID photo</t>
         </is>
       </c>
       <c r="L120" s="10" t="inlineStr">
         <is>
-          <t>they assign the Group Manager role branch by branch, and that person can look but not post or change anything</t>
+          <t>it is refused; when Require is on, check-in waits for an ID photo</t>
         </is>
       </c>
       <c r="M120" s="10" t="inlineStr">
         <is>
-          <t>20261013120000_group_view.sql</t>
+          <t>set_id_photo_settings</t>
         </is>
       </c>
       <c r="N120" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (5)</t>
+          <t>24_id_photos (10)</t>
         </is>
       </c>
       <c r="O120" s="10" t="inlineStr">
@@ -10113,16 +10121,12 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P120" s="10" t="inlineStr">
-        <is>
-          <t>Custom roles copied earlier do not get the new permission; say so when releasing.</t>
-        </is>
-      </c>
+      <c r="P120" s="10" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>GRP-002</t>
+          <t>GRP-001</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -10137,7 +10141,7 @@
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>One call shows every branch the person may see: occupancy, in house, arrivals and departures to come, approvals, repairs and last night revenue, with group totals. Revenue is totalled per currency.</t>
+          <t>A built-in Group Manager role and the permission rpt.group.view exist; only System Administrator, General Manager and Group Manager hold the permission.</t>
         </is>
       </c>
       <c r="E121" s="10" t="inlineStr">
@@ -10163,27 +10167,27 @@
       <c r="I121" s="10" t="inlineStr"/>
       <c r="J121" s="10" t="inlineStr">
         <is>
-          <t>a group with a Lagos and an Abuja branch</t>
+          <t>a hotel group with several branches</t>
         </is>
       </c>
       <c r="K121" s="10" t="inlineStr">
         <is>
-          <t>a group manager opens All branches</t>
+          <t>an owner wants a view-only manager for the whole group</t>
         </is>
       </c>
       <c r="L121" s="10" t="inlineStr">
         <is>
-          <t>they see both branches with figures from the database, never another hotel group, and staff without the permission are refused</t>
+          <t>they assign the Group Manager role branch by branch, and that person can look but not post or change anything</t>
         </is>
       </c>
       <c r="M121" s="10" t="inlineStr">
         <is>
-          <t>group_overview; /group screen</t>
+          <t>20261013120000_group_view.sql</t>
         </is>
       </c>
       <c r="N121" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (10)</t>
+          <t>35_group_view (5)</t>
         </is>
       </c>
       <c r="O121" s="10" t="inlineStr">
@@ -10193,14 +10197,14 @@
       </c>
       <c r="P121" s="10" t="inlineStr">
         <is>
-          <t>Figures are read from each branch own business date. No arithmetic in the browser.</t>
+          <t>Custom roles copied earlier do not get the new permission; say so when releasing.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>GRP-003</t>
+          <t>GRP-002</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
@@ -10215,7 +10219,7 @@
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>A Group Manager sees only the branches they are assigned to, and cannot post charges or check guests in.</t>
+          <t>One call shows every branch the person may see: occupancy, in house, arrivals and departures to come, approvals, repairs and last night revenue, with group totals. Revenue is totalled per currency.</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
@@ -10241,27 +10245,27 @@
       <c r="I122" s="10" t="inlineStr"/>
       <c r="J122" s="10" t="inlineStr">
         <is>
-          <t>a Group Manager assigned to one branch</t>
+          <t>a group with a Lagos and an Abuja branch</t>
         </is>
       </c>
       <c r="K122" s="10" t="inlineStr">
         <is>
-          <t>a second branch is assigned</t>
+          <t>a group manager opens All branches</t>
         </is>
       </c>
       <c r="L122" s="10" t="inlineStr">
         <is>
-          <t>the second branch appears; the role never gets write permissions</t>
+          <t>they see both branches with figures from the database, never another hotel group, and staff without the permission are refused</t>
         </is>
       </c>
       <c r="M122" s="10" t="inlineStr">
         <is>
-          <t>assign_role (existing); group_overview</t>
+          <t>group_overview; /group screen</t>
         </is>
       </c>
       <c r="N122" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (3)</t>
+          <t>35_group_view (10)</t>
         </is>
       </c>
       <c r="O122" s="10" t="inlineStr">
@@ -10271,14 +10275,14 @@
       </c>
       <c r="P122" s="10" t="inlineStr">
         <is>
-          <t>Access is per branch, using the existing role assignment screen.</t>
+          <t>Figures are read from each branch own business date. No arithmetic in the browser.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>GRP-004</t>
+          <t>GRP-003</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
@@ -10288,12 +10292,12 @@
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>All branches (Copy setup)</t>
+          <t>All branches</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>A new branch can copy room types, rate plans and prices from an existing branch, once, into an empty branch.</t>
+          <t>A Group Manager sees only the branches they are assigned to, and cannot post charges or check guests in.</t>
         </is>
       </c>
       <c r="E123" s="10" t="inlineStr">
@@ -10313,33 +10317,33 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>setup.room.manage, setup.rate.manage</t>
+          <t>rpt.group.view</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr"/>
       <c r="J123" s="10" t="inlineStr">
         <is>
-          <t>a new empty branch</t>
+          <t>a Group Manager assigned to one branch</t>
         </is>
       </c>
       <c r="K123" s="10" t="inlineStr">
         <is>
-          <t>the owner copies setup from the first branch</t>
+          <t>a second branch is assigned</t>
         </is>
       </c>
       <c r="L123" s="10" t="inlineStr">
         <is>
-          <t>room types, rate plans and prices appear on the new branch and point at its own room types; rooms are not copied; a second copy is refused; the copy is audited</t>
+          <t>the second branch appears; the role never gets write permissions</t>
         </is>
       </c>
       <c r="M123" s="10" t="inlineStr">
         <is>
-          <t>copy_property_setup</t>
+          <t>assign_role (existing); group_overview</t>
         </is>
       </c>
       <c r="N123" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (13)</t>
+          <t>35_group_view (3)</t>
         </is>
       </c>
       <c r="O123" s="10" t="inlineStr">
@@ -10349,29 +10353,29 @@
       </c>
       <c r="P123" s="10" t="inlineStr">
         <is>
-          <t>Taxes, charge codes and payment methods already arrive with every new branch.</t>
+          <t>Access is per branch, using the existing role assignment screen.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>RPT-005</t>
+          <t>GRP-004</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Platform &amp; Tenancy</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>All branches (Copy setup)</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>Revenue by booking source: bookings, cancellations, no-shows, room nights, room revenue and average rate for each source in a date range.</t>
+          <t>A new branch can copy room types, rate plans and prices from an existing branch, once, into an empty branch.</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
@@ -10391,33 +10395,33 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view</t>
+          <t>setup.room.manage, setup.rate.manage</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr"/>
       <c r="J124" s="10" t="inlineStr">
         <is>
-          <t>bookings from direct, phone and company sources</t>
+          <t>a new empty branch</t>
         </is>
       </c>
       <c r="K124" s="10" t="inlineStr">
         <is>
-          <t>the accountant picks a date range</t>
+          <t>the owner copies setup from the first branch</t>
         </is>
       </c>
       <c r="L124" s="10" t="inlineStr">
         <is>
-          <t>each source shows its own counts and room revenue (room charges only, before tax); cancelled bookings add no nights</t>
+          <t>room types, rate plans and prices appear on the new branch and point at its own room types; rooms are not copied; a second copy is refused; the copy is audited</t>
         </is>
       </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
-          <t>20261013130000_source_ageing_reports.sql: report_revenue_by_source; Reports, By booking source tab</t>
+          <t>copy_property_setup</t>
         </is>
       </c>
       <c r="N124" s="10" t="inlineStr">
         <is>
-          <t>36_source_ageing (13)</t>
+          <t>35_group_view (13)</t>
         </is>
       </c>
       <c r="O124" s="10" t="inlineStr">
@@ -10427,14 +10431,14 @@
       </c>
       <c r="P124" s="10" t="inlineStr">
         <is>
-          <t>Bookings counted by arrival date; revenue by posting date.</t>
+          <t>Taxes, charge codes and payment methods already arrive with every new branch.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>RPT-006</t>
+          <t>RPT-005</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
@@ -10449,7 +10453,7 @@
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>Ageing of unpaid balances by booking source: current, 1 to 7, 8 to 30, 31 to 60 and over 60 days since the due departure, plus credit held.</t>
+          <t>Revenue by booking source: bookings, cancellations, no-shows, room nights, room revenue and average rate for each source in a date range.</t>
         </is>
       </c>
       <c r="E125" s="10" t="inlineStr">
@@ -10475,27 +10479,27 @@
       <c r="I125" s="10" t="inlineStr"/>
       <c r="J125" s="10" t="inlineStr">
         <is>
-          <t>guests and companies who left owing money</t>
+          <t>bookings from direct, phone and company sources</t>
         </is>
       </c>
       <c r="K125" s="10" t="inlineStr">
         <is>
-          <t>the accountant opens the Ageing tab</t>
+          <t>the accountant picks a date range</t>
         </is>
       </c>
       <c r="L125" s="10" t="inlineStr">
         <is>
-          <t>each source shows what is owed in each age column; paid bills drop out; overpayments show as credit held; the total matches Outstanding balances</t>
+          <t>each source shows its own counts and room revenue (room charges only, before tax); cancelled bookings add no nights</t>
         </is>
       </c>
       <c r="M125" s="10" t="inlineStr">
         <is>
-          <t>report_balance_ageing; Reports, Ageing tab</t>
+          <t>20261013130000_source_ageing_reports.sql: report_revenue_by_source; Reports, By booking source tab</t>
         </is>
       </c>
       <c r="N125" s="10" t="inlineStr">
         <is>
-          <t>36_source_ageing (11)</t>
+          <t>36_source_ageing (13)</t>
         </is>
       </c>
       <c r="O125" s="10" t="inlineStr">
@@ -10505,29 +10509,29 @@
       </c>
       <c r="P125" s="10" t="inlineStr">
         <is>
-          <t>Guests still staying count as current.</t>
+          <t>Bookings counted by arrival date; revenue by posting date.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>AI-001</t>
+          <t>RPT-006</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>AI helpers</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Dashboard, Admin</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>AI helpers are off for every hotel until a System Administrator or General Manager switches them on, with a monthly limit; the switch is audited.</t>
+          <t>Ageing of unpaid balances by booking source: current, 1 to 7, 8 to 30, 31 to 60 and over 60 days since the due departure, plus credit held.</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
@@ -10547,33 +10551,33 @@
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>adm.ai.manage</t>
+          <t>rpt.finance.view</t>
         </is>
       </c>
       <c r="I126" s="10" t="inlineStr"/>
       <c r="J126" s="10" t="inlineStr">
         <is>
-          <t>a new hotel</t>
+          <t>guests and companies who left owing money</t>
         </is>
       </c>
       <c r="K126" s="10" t="inlineStr">
         <is>
-          <t>a manager opens Admin, AI helpers</t>
+          <t>the accountant opens the Ageing tab</t>
         </is>
       </c>
       <c r="L126" s="10" t="inlineStr">
         <is>
-          <t>nothing runs until they switch it on and the change is in the audit log</t>
+          <t>each source shows what is owed in each age column; paid bills drop out; overpayments show as credit held; the total matches Outstanding balances</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: set_ai_settings, ai_status; Admin, AI helpers tab</t>
+          <t>report_balance_ageing; Reports, Ageing tab</t>
         </is>
       </c>
       <c r="N126" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (11)</t>
+          <t>36_source_ageing (11)</t>
         </is>
       </c>
       <c r="O126" s="10" t="inlineStr">
@@ -10583,14 +10587,14 @@
       </c>
       <c r="P126" s="10" t="inlineStr">
         <is>
-          <t>Custom roles copied earlier do not get adm.ai.manage.</t>
+          <t>Guests still staying count as current.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>AI-002</t>
+          <t>AI-001</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
@@ -10605,7 +10609,7 @@
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>The facts sent to the AI are counts and money lines built by the database: no guest names, ID details, room numbers or card data.</t>
+          <t>AI helpers are off for every hotel until a System Administrator or General Manager switches them on, with a monthly limit; the switch is audited.</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr">
@@ -10625,28 +10629,28 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view, rpt.operations.view</t>
+          <t>adm.ai.manage</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr"/>
       <c r="J127" s="10" t="inlineStr">
         <is>
-          <t>a hotel with guests, approvals and overdue bills</t>
+          <t>a new hotel</t>
         </is>
       </c>
       <c r="K127" s="10" t="inlineStr">
         <is>
-          <t>a brief is started</t>
+          <t>a manager opens Admin, AI helpers</t>
         </is>
       </c>
       <c r="L127" s="10" t="inlineStr">
         <is>
-          <t>the facts hold only business date, last night, today, attention figures and plain lines, and overdue money matches the ledger</t>
+          <t>nothing runs until they switch it on and the change is in the audit log</t>
         </is>
       </c>
       <c r="M127" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: ai_morning_brief_start, app.morning_brief_facts</t>
+          <t>20261013140000_ai_morning_brief.sql: set_ai_settings, ai_status; Admin, AI helpers tab</t>
         </is>
       </c>
       <c r="N127" s="10" t="inlineStr">
@@ -10661,14 +10665,14 @@
       </c>
       <c r="P127" s="10" t="inlineStr">
         <is>
-          <t>Overdue means unpaid more than 30 days after departure.</t>
+          <t>Custom roles copied earlier do not get adm.ai.manage.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>AI-003</t>
+          <t>AI-002</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -10683,7 +10687,7 @@
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>Each hotel has a monthly limit on AI drafts; failed calls do not count; a call can be finished once, by the person who started it.</t>
+          <t>The facts sent to the AI are counts and money lines built by the database: no guest names, ID details, room numbers or card data.</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
@@ -10703,33 +10707,33 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view</t>
+          <t>rpt.finance.view, rpt.operations.view</t>
         </is>
       </c>
       <c r="I128" s="10" t="inlineStr"/>
       <c r="J128" s="10" t="inlineStr">
         <is>
-          <t>a limit of 2</t>
+          <t>a hotel with guests, approvals and overdue bills</t>
         </is>
       </c>
       <c r="K128" s="10" t="inlineStr">
         <is>
-          <t>a third brief is requested</t>
+          <t>a brief is started</t>
         </is>
       </c>
       <c r="L128" s="10" t="inlineStr">
         <is>
-          <t>it is refused until a failed call frees a slot or the month turns</t>
+          <t>the facts hold only business date, last night, today, attention figures and plain lines, and overdue money matches the ledger</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: ai_call_finish</t>
+          <t>20261013140000_ai_morning_brief.sql: ai_morning_brief_start, app.morning_brief_facts</t>
         </is>
       </c>
       <c r="N128" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (5)</t>
+          <t>37_ai_brief (11)</t>
         </is>
       </c>
       <c r="O128" s="10" t="inlineStr">
@@ -10737,12 +10741,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P128" s="10" t="inlineStr"/>
+      <c r="P128" s="10" t="inlineStr">
+        <is>
+          <t>Overdue means unpaid more than 30 days after departure.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>AI-004</t>
+          <t>AI-003</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -10757,7 +10765,7 @@
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>Only finance and operations viewers can ask for the brief; the usage log and settings cannot be written or read directly by the browser.</t>
+          <t>Each hotel has a monthly limit on AI drafts; failed calls do not count; a call can be finished once, by the person who started it.</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
@@ -10777,33 +10785,33 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view, rpt.operations.view</t>
+          <t>rpt.finance.view</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr"/>
       <c r="J129" s="10" t="inlineStr">
         <is>
-          <t>front desk, housekeeping, another hotel</t>
+          <t>a limit of 2</t>
         </is>
       </c>
       <c r="K129" s="10" t="inlineStr">
         <is>
-          <t>they ask for the brief or touch the tables</t>
+          <t>a third brief is requested</t>
         </is>
       </c>
       <c r="L129" s="10" t="inlineStr">
         <is>
-          <t>they are refused</t>
+          <t>it is refused until a failed call frees a slot or the month turns</t>
         </is>
       </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql</t>
+          <t>20261013140000_ai_morning_brief.sql: ai_call_finish</t>
         </is>
       </c>
       <c r="N129" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (7)</t>
+          <t>37_ai_brief (5)</t>
         </is>
       </c>
       <c r="O129" s="10" t="inlineStr">
@@ -10816,7 +10824,7 @@
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>AI-005</t>
+          <t>AI-004</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
@@ -10831,7 +10839,7 @@
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>The server accepts an AI draft only when every number in it is in the database facts; otherwise it shows the plain figures. The key stays on the server and only the fact lines are sent.</t>
+          <t>Only finance and operations viewers can ask for the brief; the usage log and settings cannot be written or read directly by the browser.</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
@@ -10851,33 +10859,33 @@
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>rpt.finance.view, rpt.operations.view</t>
         </is>
       </c>
       <c r="I130" s="10" t="inlineStr"/>
       <c r="J130" s="10" t="inlineStr">
         <is>
-          <t>a draft that rounds or invents a figure</t>
+          <t>front desk, housekeeping, another hotel</t>
         </is>
       </c>
       <c r="K130" s="10" t="inlineStr">
         <is>
-          <t>the brief is written</t>
+          <t>they ask for the brief or touch the tables</t>
         </is>
       </c>
       <c r="L130" s="10" t="inlineStr">
         <is>
-          <t>the plain database lines are shown instead, with a note</t>
+          <t>they are refused</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
-          <t>src/lib/ai-brief.ts, ai-brief.functions.ts, Dashboard morning brief card</t>
+          <t>20261013140000_ai_morning_brief.sql</t>
         </is>
       </c>
       <c r="N130" s="10" t="inlineStr">
         <is>
-          <t>browser unit: ai-brief-unit (8)</t>
+          <t>37_ai_brief (7)</t>
         </is>
       </c>
       <c r="O130" s="10" t="inlineStr">
@@ -10885,31 +10893,27 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P130" s="10" t="inlineStr">
-        <is>
-          <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
-        </is>
-      </c>
+      <c r="P130" s="10" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>SET-010</t>
+          <t>AI-005</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>AI helpers</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Setup, Rooms</t>
+          <t>Dashboard, Admin</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>A hotel can add room types and rooms from one checked list: preview first, then all or nothing. Existing codes and room names are skipped, so repeating adds nothing.</t>
+          <t>The server accepts an AI draft only when every number in it is in the database facts; otherwise it shows the plain figures. The key stays on the server and only the fact lines are sent.</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
@@ -10929,33 +10933,33 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>setup.room.manage</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr"/>
       <c r="J131" s="10" t="inlineStr">
         <is>
-          <t>a list of room types and rooms</t>
+          <t>a draft that rounds or invents a figure</t>
         </is>
       </c>
       <c r="K131" s="10" t="inlineStr">
         <is>
-          <t>the manager previews and then applies it</t>
+          <t>the brief is written</t>
         </is>
       </c>
       <c r="L131" s="10" t="inlineStr">
         <is>
-          <t>the preview writes nothing; apply adds every valid item or none (bad name, unknown type, over 500 rooms, over the plan limit); a repeat adds nothing; the import is audited</t>
+          <t>the plain database lines are shown instead, with a note</t>
         </is>
       </c>
       <c r="M131" s="10" t="inlineStr">
         <is>
-          <t>20261013150000_setup_import.sql: apply_setup_import</t>
+          <t>src/lib/ai-brief.ts, ai-brief.functions.ts, Dashboard morning brief card</t>
         </is>
       </c>
       <c r="N131" s="10" t="inlineStr">
         <is>
-          <t>38_setup_import (29)</t>
+          <t>browser unit: ai-brief-unit (8)</t>
         </is>
       </c>
       <c r="O131" s="10" t="inlineStr">
@@ -10965,19 +10969,19 @@
       </c>
       <c r="P131" s="10" t="inlineStr">
         <is>
-          <t>The AI only drafts the list. This function is the check.</t>
+          <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>AI-006</t>
+          <t>SET-010</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>AI helpers</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
@@ -10987,7 +10991,7 @@
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>The setup import assistant starts only when AI is on and under the monthly limit, and the AI sees only existing room type codes and a room count.</t>
+          <t>A hotel can add room types and rooms from one checked list: preview first, then all or nothing. Existing codes and room names are skipped, so repeating adds nothing.</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
@@ -11013,27 +11017,27 @@
       <c r="I132" s="10" t="inlineStr"/>
       <c r="J132" s="10" t="inlineStr">
         <is>
-          <t>AI switched on with a limit of 1</t>
+          <t>a list of room types and rooms</t>
         </is>
       </c>
       <c r="K132" s="10" t="inlineStr">
         <is>
-          <t>an import draft is started twice</t>
+          <t>the manager previews and then applies it</t>
         </is>
       </c>
       <c r="L132" s="10" t="inlineStr">
         <is>
-          <t>the second is refused until the first fails; front desk and other hotels are refused</t>
+          <t>the preview writes nothing; apply adds every valid item or none (bad name, unknown type, over 500 rooms, over the plan limit); a repeat adds nothing; the import is audited</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
-          <t>20261013150000_setup_import.sql: ai_import_start, app.ai_begin</t>
+          <t>20261013150000_setup_import.sql: apply_setup_import</t>
         </is>
       </c>
       <c r="N132" s="10" t="inlineStr">
         <is>
-          <t>38_setup_import (8)</t>
+          <t>38_setup_import (29)</t>
         </is>
       </c>
       <c r="O132" s="10" t="inlineStr">
@@ -11041,12 +11045,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P132" s="10" t="inlineStr"/>
+      <c r="P132" s="10" t="inlineStr">
+        <is>
+          <t>The AI only drafts the list. This function is the check.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>AI-007</t>
+          <t>AI-006</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
@@ -11061,7 +11069,7 @@
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>Pasted text with an email, phone or card number is refused before anything is sent; the draft may only contain rooms, floors, guest limits and type names that are in the pasted text.</t>
+          <t>The setup import assistant starts only when AI is on and under the monthly limit, and the AI sees only existing room type codes and a room count.</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
@@ -11087,27 +11095,27 @@
       <c r="I133" s="10" t="inlineStr"/>
       <c r="J133" s="10" t="inlineStr">
         <is>
-          <t>a pasted list</t>
+          <t>AI switched on with a limit of 1</t>
         </is>
       </c>
       <c r="K133" s="10" t="inlineStr">
         <is>
-          <t>the assistant drafts it</t>
+          <t>an import draft is started twice</t>
         </is>
       </c>
       <c r="L133" s="10" t="inlineStr">
         <is>
-          <t>invented rooms, floors and limits are dropped with a note; a draft with no matching rooms is an error</t>
+          <t>the second is refused until the first fails; front desk and other hotels are refused</t>
         </is>
       </c>
       <c r="M133" s="10" t="inlineStr">
         <is>
-          <t>src/lib/setup-import.ts, setup-import.functions.ts, Import from a list on Setup, Rooms</t>
+          <t>20261013150000_setup_import.sql: ai_import_start, app.ai_begin</t>
         </is>
       </c>
       <c r="N133" s="10" t="inlineStr">
         <is>
-          <t>browser unit: setup-import-unit (9)</t>
+          <t>38_setup_import (8)</t>
         </is>
       </c>
       <c r="O133" s="10" t="inlineStr">
@@ -11115,36 +11123,32 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P133" s="10" t="inlineStr">
-        <is>
-          <t>Needs ANTHROPIC_API_KEY on the server. Not set yet.</t>
-        </is>
-      </c>
+      <c r="P133" s="10" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>SET-011</t>
+          <t>AI-007</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>AI helpers</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>/setup; /dashboard</t>
+          <t>Setup, Rooms</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>A new hotel sees a checklist of what is left to set up: property details, room types, rooms, rates, taxes, payment methods and staff. Each step says what is missing and links to the right screen. The list comes from the hotel's own data, so it is always current.</t>
+          <t>Pasted text with an email, phone or card number is refused before anything is sent; the draft may only contain rooms, floors, guest limits and type names that are in the pasted text.</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
@@ -11159,37 +11163,33 @@
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>any setup permission</t>
-        </is>
-      </c>
-      <c r="I134" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>setup.room.manage</t>
+        </is>
+      </c>
+      <c r="I134" s="10" t="inlineStr"/>
       <c r="J134" s="10" t="inlineStr">
         <is>
-          <t>a hotel that is part way through setup</t>
+          <t>a pasted list</t>
         </is>
       </c>
       <c r="K134" s="10" t="inlineStr">
         <is>
-          <t>a manager opens Setup or the Dashboard</t>
+          <t>the assistant drafts it</t>
         </is>
       </c>
       <c r="L134" s="10" t="inlineStr">
         <is>
-          <t>the steps already done are ticked and the next one is linked; once all seven are done the checklist goes away</t>
+          <t>invented rooms, floors and limits are dropped with a note; a draft with no matching rooms is an error</t>
         </is>
       </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
-          <t>setup_progress</t>
+          <t>src/lib/setup-import.ts, setup-import.functions.ts, Import from a list on Setup, Rooms</t>
         </is>
       </c>
       <c r="N134" s="10" t="inlineStr">
         <is>
-          <t>40_guided_setup (30)</t>
+          <t>browser unit: setup-import-unit (9)</t>
         </is>
       </c>
       <c r="O134" s="10" t="inlineStr">
@@ -11199,39 +11199,39 @@
       </c>
       <c r="P134" s="10" t="inlineStr">
         <is>
-          <t>Read-only function, no stored progress. Staff step counts people with a role at the property (two or more).</t>
+          <t>Needs ANTHROPIC_API_KEY on the server. Not set yet.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>NFR-006</t>
+          <t>SET-011</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>(all)</t>
+          <t>/setup; /dashboard</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>The last room of a type is sold once, however many desks book at the same moment, and a repeated booking never doubles.</t>
+          <t>A new hotel sees a checklist of what is left to set up: property details, room types, rooms, rates, taxes, payment methods and staff. Each step says what is missing and links to the right screen. The list comes from the hotel's own data, so it is always current.</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G135" s="10" t="inlineStr">
@@ -11241,37 +11241,37 @@
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
+          <t>any setup permission</t>
+        </is>
+      </c>
+      <c r="I135" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="10" t="inlineStr">
-        <is>
-          <t>Rule: Safe last-room booking</t>
-        </is>
-      </c>
       <c r="J135" s="10" t="inlineStr">
         <is>
-          <t>one room of a type is left and several desks book it together</t>
+          <t>a hotel that is part way through setup</t>
         </is>
       </c>
       <c r="K135" s="10" t="inlineStr">
         <is>
-          <t>all of them submit at the same moment</t>
+          <t>a manager opens Setup or the Dashboard</t>
         </is>
       </c>
       <c r="L135" s="10" t="inlineStr">
         <is>
-          <t>exactly one booking succeeds, the rest get E_NO_AVAILABILITY, and nothing is oversold</t>
+          <t>the steps already done are ticked and the next one is linked; once all seven are done the checklist goes away</t>
         </is>
       </c>
       <c r="M135" s="10" t="inlineStr">
         <is>
-          <t>create_reservation, assert_available</t>
+          <t>setup_progress</t>
         </is>
       </c>
       <c r="N135" s="10" t="inlineStr">
         <is>
-          <t>concurrency/last_room.sh (6)</t>
+          <t>40_guided_setup (30)</t>
         </is>
       </c>
       <c r="O135" s="10" t="inlineStr">
@@ -11281,29 +11281,29 @@
       </c>
       <c r="P135" s="10" t="inlineStr">
         <is>
-          <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
+          <t>Read-only function, no stored progress. Staff step counts people with a role at the property (two or more).</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>SET-012</t>
+          <t>NFR-006</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Non-functional</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>/setup/property</t>
+          <t>(all)</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>A manager sets the longest stay (1 to 365 nights) and how long a tentative booking holds its room (1 to 720 hours) for each property.</t>
+          <t>The last room of a type is sold once, however many desks book at the same moment, and a repeated booking never doubles.</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G136" s="10" t="inlineStr">
@@ -11323,33 +11323,37 @@
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>setup.property.edit</t>
-        </is>
-      </c>
-      <c r="I136" s="10" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="10" t="inlineStr">
+        <is>
+          <t>Rule: Safe last-room booking</t>
+        </is>
+      </c>
       <c r="J136" s="10" t="inlineStr">
         <is>
-          <t>a property with the default rules (30 nights, 24 hours)</t>
+          <t>one room of a type is left and several desks book it together</t>
         </is>
       </c>
       <c r="K136" s="10" t="inlineStr">
         <is>
-          <t>a manager saves new booking rules</t>
+          <t>all of them submit at the same moment</t>
         </is>
       </c>
       <c r="L136" s="10" t="inlineStr">
         <is>
-          <t>new bookings use them, bad values are refused with E_INVALID, and the change is audited with old and new values</t>
+          <t>exactly one booking succeeds, the rest get E_NO_AVAILABILITY, and nothing is oversold</t>
         </is>
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
-          <t>set_booking_rules; Booking rules on Setup, Property</t>
+          <t>create_reservation, assert_available</t>
         </is>
       </c>
       <c r="N136" s="10" t="inlineStr">
         <is>
-          <t>42_booking_rules (9)</t>
+          <t>concurrency/last_room.sh (6)</t>
         </is>
       </c>
       <c r="O136" s="10" t="inlineStr">
@@ -11359,39 +11363,39 @@
       </c>
       <c r="P136" s="10" t="inlineStr">
         <is>
-          <t>Added 8 Oct 2026. The columns existed since the reservations release; this adds the screen and the function.</t>
+          <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>FO-014</t>
+          <t>SET-012</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>Front Office</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>/downtime</t>
+          <t>/setup/property</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>A printable downtime pack: arrivals due, in-house guests with balance, departures due, ten blank lines for new guests on paper, and a short paper routine. Staff print it when the internet or system is down.</t>
+          <t>A manager sets the longest stay (1 to 365 nights) and how long a tentative booking holds its room (1 to 720 hours) for each property.</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>BR-006</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G137" s="10" t="inlineStr">
@@ -11401,33 +11405,33 @@
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>fo.view</t>
+          <t>setup.property.edit</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr"/>
       <c r="J137" s="10" t="inlineStr">
         <is>
-          <t>a hotel with guests in house</t>
+          <t>a property with the default rules (30 nights, 24 hours)</t>
         </is>
       </c>
       <c r="K137" s="10" t="inlineStr">
         <is>
-          <t>a front desk user opens Downtime pack and prints</t>
+          <t>a manager saves new booking rules</t>
         </is>
       </c>
       <c r="L137" s="10" t="inlineStr">
         <is>
-          <t>the lists show room, guest, phone, departure and the folio balance from the database, with blank lines and the paper routine</t>
+          <t>new bookings use them, bad values are refused with E_INVALID, and the change is audited with old and new values</t>
         </is>
       </c>
       <c r="M137" s="10" t="inlineStr">
         <is>
-          <t>src/routes/_authenticated/_app/downtime.tsx</t>
+          <t>set_booking_rules; Booking rules on Setup, Property</t>
         </is>
       </c>
       <c r="N137" s="10" t="inlineStr">
         <is>
-          <t>browser: downtime-pack.spec (1)</t>
+          <t>42_booking_rules (9)</t>
         </is>
       </c>
       <c r="O137" s="10" t="inlineStr">
@@ -11437,87 +11441,165 @@
       </c>
       <c r="P137" s="10" t="inlineStr">
         <is>
-          <t>No database change. Reads v_arrivals, v_in_house and v_folio_balances. Added 8 Oct 2026.</t>
+          <t>Added 8 Oct 2026. The columns existed since the reservations release; this adds the screen and the function.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
+          <t>FO-014</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>Front Office</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>/downtime</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>A printable downtime pack: arrivals due, in-house guests with balance, departures due, ten blank lines for new guests on paper, and a short paper routine. Staff print it when the internet or system is down.</t>
+        </is>
+      </c>
+      <c r="E138" s="10" t="inlineStr">
+        <is>
+          <t>BR-006</t>
+        </is>
+      </c>
+      <c r="F138" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G138" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H138" s="10" t="inlineStr">
+        <is>
+          <t>fo.view</t>
+        </is>
+      </c>
+      <c r="I138" s="10" t="inlineStr"/>
+      <c r="J138" s="10" t="inlineStr">
+        <is>
+          <t>a hotel with guests in house</t>
+        </is>
+      </c>
+      <c r="K138" s="10" t="inlineStr">
+        <is>
+          <t>a front desk user opens Downtime pack and prints</t>
+        </is>
+      </c>
+      <c r="L138" s="10" t="inlineStr">
+        <is>
+          <t>the lists show room, guest, phone, departure and the folio balance from the database, with blank lines and the paper routine</t>
+        </is>
+      </c>
+      <c r="M138" s="10" t="inlineStr">
+        <is>
+          <t>src/routes/_authenticated/_app/downtime.tsx</t>
+        </is>
+      </c>
+      <c r="N138" s="10" t="inlineStr">
+        <is>
+          <t>browser: downtime-pack.spec (1)</t>
+        </is>
+      </c>
+      <c r="O138" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P138" s="10" t="inlineStr">
+        <is>
+          <t>No database change. Reads v_arrivals, v_in_house and v_folio_balances. Added 8 Oct 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
           <t>DAY-007</t>
         </is>
       </c>
-      <c r="B138" s="10" t="inlineStr">
+      <c r="B139" s="10" t="inlineStr">
         <is>
           <t>Business Date</t>
         </is>
       </c>
-      <c r="C138" s="10" t="inlineStr">
+      <c r="C139" s="10" t="inlineStr">
         <is>
           <t>Notifications bell</t>
         </is>
       </c>
-      <c r="D138" s="10" t="inlineStr">
+      <c r="D139" s="10" t="inlineStr">
         <is>
           <t>In the last hour before a property rolls its business date, if a cashier shift is still open, users who can run the night audit get one warning that night. The roll does not wait.</t>
         </is>
       </c>
-      <c r="E138" s="10" t="inlineStr">
+      <c r="E139" s="10" t="inlineStr">
         <is>
           <t>BR-016</t>
         </is>
       </c>
-      <c r="F138" s="10" t="inlineStr">
+      <c r="F139" s="10" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G138" s="10" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H138" s="10" t="inlineStr">
+      <c r="G139" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H139" s="10" t="inlineStr">
         <is>
           <t>fin.nightaudit.run</t>
         </is>
       </c>
-      <c r="I138" s="10" t="inlineStr">
+      <c r="I139" s="10" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="J138" s="10" t="inlineStr">
+      <c r="J139" s="10" t="inlineStr">
         <is>
           <t>a cashier shift is still open</t>
         </is>
       </c>
-      <c r="K138" s="10" t="inlineStr">
+      <c r="K139" s="10" t="inlineStr">
         <is>
           <t>the roll time is less than 60 minutes away</t>
         </is>
       </c>
-      <c r="L138" s="10" t="inlineStr">
+      <c r="L139" s="10" t="inlineStr">
         <is>
           <t>each night audit user gets one rollover_warning notification for that business date; none earlier, none after the roll time, none if no shift is open, none twice</t>
         </is>
       </c>
-      <c r="M138" s="10" t="inlineStr">
+      <c r="M139" s="10" t="inlineStr">
         <is>
           <t>app.warn_before_rollover; cron job rollover-warning</t>
         </is>
       </c>
-      <c r="N138" s="10" t="inlineStr">
+      <c r="N139" s="10" t="inlineStr">
         <is>
           <t>43_rollover_warning (9)</t>
         </is>
       </c>
-      <c r="O138" s="10" t="inlineStr">
+      <c r="O139" s="10" t="inlineStr">
         <is>
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P138" s="10" t="inlineStr">
+      <c r="P139" s="10" t="inlineStr">
         <is>
           <t>Added 8 Oct 2026. Warning only; the hard gate stays in R2 (DAY-005).</t>
         </is>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P139"/>
+  <dimension ref="A1:P140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10594,27 +10594,27 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>AI-001</t>
+          <t>RPT-007</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>AI helpers</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Dashboard, Admin</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>AI helpers are off for every hotel until a System Administrator or General Manager switches them on, with a monthly limit; the switch is audited.</t>
+          <t>The owner summary: last night's occupancy and revenue, money collected by payment method, today's arrivals, departures and rooms, what is waiting, and old unpaid bills, as plain sentences built in the database. Works with AI off; a later daily email can send the same text.</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
@@ -10629,33 +10629,37 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>adm.ai.manage</t>
-        </is>
-      </c>
-      <c r="I127" s="10" t="inlineStr"/>
+          <t>rpt.finance.view, rpt.operations.view</t>
+        </is>
+      </c>
+      <c r="I127" s="10" t="inlineStr">
+        <is>
+          <t>Reads the morning brief facts</t>
+        </is>
+      </c>
       <c r="J127" s="10" t="inlineStr">
         <is>
-          <t>a new hotel</t>
+          <t>a hotel with a closed day and payments on it</t>
         </is>
       </c>
       <c r="K127" s="10" t="inlineStr">
         <is>
-          <t>a manager opens Admin, AI helpers</t>
+          <t>the owner opens the dashboard</t>
         </is>
       </c>
       <c r="L127" s="10" t="inlineStr">
         <is>
-          <t>nothing runs until they switch it on and the change is in the audit log</t>
+          <t>sees yesterday at a glance with the money collected by method; front desk without finance reports is refused</t>
         </is>
       </c>
       <c r="M127" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: set_ai_settings, ai_status; Admin, AI helpers tab</t>
+          <t>owner_summary</t>
         </is>
       </c>
       <c r="N127" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (11)</t>
+          <t>47_owner_summary (8); browser: owner-summary</t>
         </is>
       </c>
       <c r="O127" s="10" t="inlineStr">
@@ -10665,14 +10669,14 @@
       </c>
       <c r="P127" s="10" t="inlineStr">
         <is>
-          <t>Custom roles copied earlier do not get adm.ai.manage.</t>
+          <t>Email delivery waits on the sending domain and email account.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>AI-002</t>
+          <t>AI-001</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -10687,7 +10691,7 @@
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>The facts sent to the AI are counts and money lines built by the database: no guest names, ID details, room numbers or card data.</t>
+          <t>AI helpers are off for every hotel until a System Administrator or General Manager switches them on, with a monthly limit; the switch is audited.</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
@@ -10707,28 +10711,28 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view, rpt.operations.view</t>
+          <t>adm.ai.manage</t>
         </is>
       </c>
       <c r="I128" s="10" t="inlineStr"/>
       <c r="J128" s="10" t="inlineStr">
         <is>
-          <t>a hotel with guests, approvals and overdue bills</t>
+          <t>a new hotel</t>
         </is>
       </c>
       <c r="K128" s="10" t="inlineStr">
         <is>
-          <t>a brief is started</t>
+          <t>a manager opens Admin, AI helpers</t>
         </is>
       </c>
       <c r="L128" s="10" t="inlineStr">
         <is>
-          <t>the facts hold only business date, last night, today, attention figures and plain lines, and overdue money matches the ledger</t>
+          <t>nothing runs until they switch it on and the change is in the audit log</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: ai_morning_brief_start, app.morning_brief_facts</t>
+          <t>20261013140000_ai_morning_brief.sql: set_ai_settings, ai_status; Admin, AI helpers tab</t>
         </is>
       </c>
       <c r="N128" s="10" t="inlineStr">
@@ -10743,14 +10747,14 @@
       </c>
       <c r="P128" s="10" t="inlineStr">
         <is>
-          <t>Overdue means unpaid more than 30 days after departure.</t>
+          <t>Custom roles copied earlier do not get adm.ai.manage.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>AI-003</t>
+          <t>AI-002</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -10765,7 +10769,7 @@
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>Each hotel has a monthly limit on AI drafts; failed calls do not count; a call can be finished once, by the person who started it.</t>
+          <t>The facts sent to the AI are counts and money lines built by the database: no guest names, ID details, room numbers or card data.</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
@@ -10785,33 +10789,33 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view</t>
+          <t>rpt.finance.view, rpt.operations.view</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr"/>
       <c r="J129" s="10" t="inlineStr">
         <is>
-          <t>a limit of 2</t>
+          <t>a hotel with guests, approvals and overdue bills</t>
         </is>
       </c>
       <c r="K129" s="10" t="inlineStr">
         <is>
-          <t>a third brief is requested</t>
+          <t>a brief is started</t>
         </is>
       </c>
       <c r="L129" s="10" t="inlineStr">
         <is>
-          <t>it is refused until a failed call frees a slot or the month turns</t>
+          <t>the facts hold only business date, last night, today, attention figures and plain lines, and overdue money matches the ledger</t>
         </is>
       </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: ai_call_finish</t>
+          <t>20261013140000_ai_morning_brief.sql: ai_morning_brief_start, app.morning_brief_facts</t>
         </is>
       </c>
       <c r="N129" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (5)</t>
+          <t>37_ai_brief (11)</t>
         </is>
       </c>
       <c r="O129" s="10" t="inlineStr">
@@ -10819,12 +10823,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P129" s="10" t="inlineStr"/>
+      <c r="P129" s="10" t="inlineStr">
+        <is>
+          <t>Overdue means unpaid more than 30 days after departure.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>AI-004</t>
+          <t>AI-003</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
@@ -10839,7 +10847,7 @@
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>Only finance and operations viewers can ask for the brief; the usage log and settings cannot be written or read directly by the browser.</t>
+          <t>Each hotel has a monthly limit on AI drafts; failed calls do not count; a call can be finished once, by the person who started it.</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
@@ -10859,33 +10867,33 @@
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view, rpt.operations.view</t>
+          <t>rpt.finance.view</t>
         </is>
       </c>
       <c r="I130" s="10" t="inlineStr"/>
       <c r="J130" s="10" t="inlineStr">
         <is>
-          <t>front desk, housekeeping, another hotel</t>
+          <t>a limit of 2</t>
         </is>
       </c>
       <c r="K130" s="10" t="inlineStr">
         <is>
-          <t>they ask for the brief or touch the tables</t>
+          <t>a third brief is requested</t>
         </is>
       </c>
       <c r="L130" s="10" t="inlineStr">
         <is>
-          <t>they are refused</t>
+          <t>it is refused until a failed call frees a slot or the month turns</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql</t>
+          <t>20261013140000_ai_morning_brief.sql: ai_call_finish</t>
         </is>
       </c>
       <c r="N130" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (7)</t>
+          <t>37_ai_brief (5)</t>
         </is>
       </c>
       <c r="O130" s="10" t="inlineStr">
@@ -10898,7 +10906,7 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>AI-005</t>
+          <t>AI-004</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -10913,7 +10921,7 @@
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>The server accepts an AI draft only when every number in it is in the database facts; otherwise it shows the plain figures. The key stays on the server and only the fact lines are sent.</t>
+          <t>Only finance and operations viewers can ask for the brief; the usage log and settings cannot be written or read directly by the browser.</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
@@ -10933,33 +10941,33 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>rpt.finance.view, rpt.operations.view</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr"/>
       <c r="J131" s="10" t="inlineStr">
         <is>
-          <t>a draft that rounds or invents a figure</t>
+          <t>front desk, housekeeping, another hotel</t>
         </is>
       </c>
       <c r="K131" s="10" t="inlineStr">
         <is>
-          <t>the brief is written</t>
+          <t>they ask for the brief or touch the tables</t>
         </is>
       </c>
       <c r="L131" s="10" t="inlineStr">
         <is>
-          <t>the plain database lines are shown instead, with a note</t>
+          <t>they are refused</t>
         </is>
       </c>
       <c r="M131" s="10" t="inlineStr">
         <is>
-          <t>src/lib/ai-brief.ts, ai-brief.functions.ts, Dashboard morning brief card</t>
+          <t>20261013140000_ai_morning_brief.sql</t>
         </is>
       </c>
       <c r="N131" s="10" t="inlineStr">
         <is>
-          <t>browser unit: ai-brief-unit (8)</t>
+          <t>37_ai_brief (7)</t>
         </is>
       </c>
       <c r="O131" s="10" t="inlineStr">
@@ -10967,31 +10975,27 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P131" s="10" t="inlineStr">
-        <is>
-          <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
-        </is>
-      </c>
+      <c r="P131" s="10" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>SET-010</t>
+          <t>AI-005</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>AI helpers</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Setup, Rooms</t>
+          <t>Dashboard, Admin</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>A hotel can add room types and rooms from one checked list: preview first, then all or nothing. Existing codes and room names are skipped, so repeating adds nothing.</t>
+          <t>The server accepts an AI draft only when every number in it is in the database facts; otherwise it shows the plain figures. The key stays on the server and only the fact lines are sent.</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
@@ -11011,33 +11015,33 @@
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>setup.room.manage</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I132" s="10" t="inlineStr"/>
       <c r="J132" s="10" t="inlineStr">
         <is>
-          <t>a list of room types and rooms</t>
+          <t>a draft that rounds or invents a figure</t>
         </is>
       </c>
       <c r="K132" s="10" t="inlineStr">
         <is>
-          <t>the manager previews and then applies it</t>
+          <t>the brief is written</t>
         </is>
       </c>
       <c r="L132" s="10" t="inlineStr">
         <is>
-          <t>the preview writes nothing; apply adds every valid item or none (bad name, unknown type, over 500 rooms, over the plan limit); a repeat adds nothing; the import is audited</t>
+          <t>the plain database lines are shown instead, with a note</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
-          <t>20261013150000_setup_import.sql: apply_setup_import</t>
+          <t>src/lib/ai-brief.ts, ai-brief.functions.ts, Dashboard morning brief card</t>
         </is>
       </c>
       <c r="N132" s="10" t="inlineStr">
         <is>
-          <t>38_setup_import (29)</t>
+          <t>browser unit: ai-brief-unit (8)</t>
         </is>
       </c>
       <c r="O132" s="10" t="inlineStr">
@@ -11047,19 +11051,19 @@
       </c>
       <c r="P132" s="10" t="inlineStr">
         <is>
-          <t>The AI only drafts the list. This function is the check.</t>
+          <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>AI-006</t>
+          <t>SET-010</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>AI helpers</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
@@ -11069,7 +11073,7 @@
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>The setup import assistant starts only when AI is on and under the monthly limit, and the AI sees only existing room type codes and a room count.</t>
+          <t>A hotel can add room types and rooms from one checked list: preview first, then all or nothing. Existing codes and room names are skipped, so repeating adds nothing.</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
@@ -11095,27 +11099,27 @@
       <c r="I133" s="10" t="inlineStr"/>
       <c r="J133" s="10" t="inlineStr">
         <is>
-          <t>AI switched on with a limit of 1</t>
+          <t>a list of room types and rooms</t>
         </is>
       </c>
       <c r="K133" s="10" t="inlineStr">
         <is>
-          <t>an import draft is started twice</t>
+          <t>the manager previews and then applies it</t>
         </is>
       </c>
       <c r="L133" s="10" t="inlineStr">
         <is>
-          <t>the second is refused until the first fails; front desk and other hotels are refused</t>
+          <t>the preview writes nothing; apply adds every valid item or none (bad name, unknown type, over 500 rooms, over the plan limit); a repeat adds nothing; the import is audited</t>
         </is>
       </c>
       <c r="M133" s="10" t="inlineStr">
         <is>
-          <t>20261013150000_setup_import.sql: ai_import_start, app.ai_begin</t>
+          <t>20261013150000_setup_import.sql: apply_setup_import</t>
         </is>
       </c>
       <c r="N133" s="10" t="inlineStr">
         <is>
-          <t>38_setup_import (8)</t>
+          <t>38_setup_import (29)</t>
         </is>
       </c>
       <c r="O133" s="10" t="inlineStr">
@@ -11123,12 +11127,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P133" s="10" t="inlineStr"/>
+      <c r="P133" s="10" t="inlineStr">
+        <is>
+          <t>The AI only drafts the list. This function is the check.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>AI-007</t>
+          <t>AI-006</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
@@ -11143,7 +11151,7 @@
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Pasted text with an email, phone or card number is refused before anything is sent; the draft may only contain rooms, floors, guest limits and type names that are in the pasted text.</t>
+          <t>The setup import assistant starts only when AI is on and under the monthly limit, and the AI sees only existing room type codes and a room count.</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
@@ -11169,27 +11177,27 @@
       <c r="I134" s="10" t="inlineStr"/>
       <c r="J134" s="10" t="inlineStr">
         <is>
-          <t>a pasted list</t>
+          <t>AI switched on with a limit of 1</t>
         </is>
       </c>
       <c r="K134" s="10" t="inlineStr">
         <is>
-          <t>the assistant drafts it</t>
+          <t>an import draft is started twice</t>
         </is>
       </c>
       <c r="L134" s="10" t="inlineStr">
         <is>
-          <t>invented rooms, floors and limits are dropped with a note; a draft with no matching rooms is an error</t>
+          <t>the second is refused until the first fails; front desk and other hotels are refused</t>
         </is>
       </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
-          <t>src/lib/setup-import.ts, setup-import.functions.ts, Import from a list on Setup, Rooms</t>
+          <t>20261013150000_setup_import.sql: ai_import_start, app.ai_begin</t>
         </is>
       </c>
       <c r="N134" s="10" t="inlineStr">
         <is>
-          <t>browser unit: setup-import-unit (9)</t>
+          <t>38_setup_import (8)</t>
         </is>
       </c>
       <c r="O134" s="10" t="inlineStr">
@@ -11197,36 +11205,32 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P134" s="10" t="inlineStr">
-        <is>
-          <t>Needs ANTHROPIC_API_KEY on the server. Not set yet.</t>
-        </is>
-      </c>
+      <c r="P134" s="10" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>SET-011</t>
+          <t>AI-007</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>AI helpers</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>/setup; /dashboard</t>
+          <t>Setup, Rooms</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>A new hotel sees a checklist of what is left to set up: property details, room types, rooms, rates, taxes, payment methods and staff. Each step says what is missing and links to the right screen. The list comes from the hotel's own data, so it is always current.</t>
+          <t>Pasted text with an email, phone or card number is refused before anything is sent; the draft may only contain rooms, floors, guest limits and type names that are in the pasted text.</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
@@ -11241,37 +11245,33 @@
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>any setup permission</t>
-        </is>
-      </c>
-      <c r="I135" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>setup.room.manage</t>
+        </is>
+      </c>
+      <c r="I135" s="10" t="inlineStr"/>
       <c r="J135" s="10" t="inlineStr">
         <is>
-          <t>a hotel that is part way through setup</t>
+          <t>a pasted list</t>
         </is>
       </c>
       <c r="K135" s="10" t="inlineStr">
         <is>
-          <t>a manager opens Setup or the Dashboard</t>
+          <t>the assistant drafts it</t>
         </is>
       </c>
       <c r="L135" s="10" t="inlineStr">
         <is>
-          <t>the steps already done are ticked and the next one is linked; once all seven are done the checklist goes away</t>
+          <t>invented rooms, floors and limits are dropped with a note; a draft with no matching rooms is an error</t>
         </is>
       </c>
       <c r="M135" s="10" t="inlineStr">
         <is>
-          <t>setup_progress</t>
+          <t>src/lib/setup-import.ts, setup-import.functions.ts, Import from a list on Setup, Rooms</t>
         </is>
       </c>
       <c r="N135" s="10" t="inlineStr">
         <is>
-          <t>40_guided_setup (30)</t>
+          <t>browser unit: setup-import-unit (9)</t>
         </is>
       </c>
       <c r="O135" s="10" t="inlineStr">
@@ -11281,39 +11281,39 @@
       </c>
       <c r="P135" s="10" t="inlineStr">
         <is>
-          <t>Read-only function, no stored progress. Staff step counts people with a role at the property (two or more).</t>
+          <t>Needs ANTHROPIC_API_KEY on the server. Not set yet.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>NFR-006</t>
+          <t>SET-011</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>(all)</t>
+          <t>/setup; /dashboard</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>The last room of a type is sold once, however many desks book at the same moment, and a repeated booking never doubles.</t>
+          <t>A new hotel sees a checklist of what is left to set up: property details, room types, rooms, rates, taxes, payment methods and staff. Each step says what is missing and links to the right screen. The list comes from the hotel's own data, so it is always current.</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G136" s="10" t="inlineStr">
@@ -11323,37 +11323,37 @@
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
+          <t>any setup permission</t>
+        </is>
+      </c>
+      <c r="I136" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I136" s="10" t="inlineStr">
-        <is>
-          <t>Rule: Safe last-room booking</t>
-        </is>
-      </c>
       <c r="J136" s="10" t="inlineStr">
         <is>
-          <t>one room of a type is left and several desks book it together</t>
+          <t>a hotel that is part way through setup</t>
         </is>
       </c>
       <c r="K136" s="10" t="inlineStr">
         <is>
-          <t>all of them submit at the same moment</t>
+          <t>a manager opens Setup or the Dashboard</t>
         </is>
       </c>
       <c r="L136" s="10" t="inlineStr">
         <is>
-          <t>exactly one booking succeeds, the rest get E_NO_AVAILABILITY, and nothing is oversold</t>
+          <t>the steps already done are ticked and the next one is linked; once all seven are done the checklist goes away</t>
         </is>
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
-          <t>create_reservation, assert_available</t>
+          <t>setup_progress</t>
         </is>
       </c>
       <c r="N136" s="10" t="inlineStr">
         <is>
-          <t>concurrency/last_room.sh (6)</t>
+          <t>40_guided_setup (30)</t>
         </is>
       </c>
       <c r="O136" s="10" t="inlineStr">
@@ -11363,29 +11363,29 @@
       </c>
       <c r="P136" s="10" t="inlineStr">
         <is>
-          <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
+          <t>Read-only function, no stored progress. Staff step counts people with a role at the property (two or more).</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>SET-012</t>
+          <t>NFR-006</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Non-functional</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>/setup/property</t>
+          <t>(all)</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>A manager sets the longest stay (1 to 365 nights) and how long a tentative booking holds its room (1 to 720 hours) for each property.</t>
+          <t>The last room of a type is sold once, however many desks book at the same moment, and a repeated booking never doubles.</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G137" s="10" t="inlineStr">
@@ -11405,33 +11405,37 @@
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>setup.property.edit</t>
-        </is>
-      </c>
-      <c r="I137" s="10" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="10" t="inlineStr">
+        <is>
+          <t>Rule: Safe last-room booking</t>
+        </is>
+      </c>
       <c r="J137" s="10" t="inlineStr">
         <is>
-          <t>a property with the default rules (30 nights, 24 hours)</t>
+          <t>one room of a type is left and several desks book it together</t>
         </is>
       </c>
       <c r="K137" s="10" t="inlineStr">
         <is>
-          <t>a manager saves new booking rules</t>
+          <t>all of them submit at the same moment</t>
         </is>
       </c>
       <c r="L137" s="10" t="inlineStr">
         <is>
-          <t>new bookings use them, bad values are refused with E_INVALID, and the change is audited with old and new values</t>
+          <t>exactly one booking succeeds, the rest get E_NO_AVAILABILITY, and nothing is oversold</t>
         </is>
       </c>
       <c r="M137" s="10" t="inlineStr">
         <is>
-          <t>set_booking_rules; Booking rules on Setup, Property</t>
+          <t>create_reservation, assert_available</t>
         </is>
       </c>
       <c r="N137" s="10" t="inlineStr">
         <is>
-          <t>42_booking_rules (9)</t>
+          <t>concurrency/last_room.sh (6)</t>
         </is>
       </c>
       <c r="O137" s="10" t="inlineStr">
@@ -11441,39 +11445,39 @@
       </c>
       <c r="P137" s="10" t="inlineStr">
         <is>
-          <t>Added 8 Oct 2026. The columns existed since the reservations release; this adds the screen and the function.</t>
+          <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>FO-014</t>
+          <t>SET-012</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>Front Office</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>/downtime</t>
+          <t>/setup/property</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>A printable downtime pack: arrivals due, in-house guests with balance, departures due, ten blank lines for new guests on paper, and a short paper routine. Staff print it when the internet or system is down.</t>
+          <t>A manager sets the longest stay (1 to 365 nights) and how long a tentative booking holds its room (1 to 720 hours) for each property.</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>BR-006</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G138" s="10" t="inlineStr">
@@ -11483,33 +11487,33 @@
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
-          <t>fo.view</t>
+          <t>setup.property.edit</t>
         </is>
       </c>
       <c r="I138" s="10" t="inlineStr"/>
       <c r="J138" s="10" t="inlineStr">
         <is>
-          <t>a hotel with guests in house</t>
+          <t>a property with the default rules (30 nights, 24 hours)</t>
         </is>
       </c>
       <c r="K138" s="10" t="inlineStr">
         <is>
-          <t>a front desk user opens Downtime pack and prints</t>
+          <t>a manager saves new booking rules</t>
         </is>
       </c>
       <c r="L138" s="10" t="inlineStr">
         <is>
-          <t>the lists show room, guest, phone, departure and the folio balance from the database, with blank lines and the paper routine</t>
+          <t>new bookings use them, bad values are refused with E_INVALID, and the change is audited with old and new values</t>
         </is>
       </c>
       <c r="M138" s="10" t="inlineStr">
         <is>
-          <t>src/routes/_authenticated/_app/downtime.tsx</t>
+          <t>set_booking_rules; Booking rules on Setup, Property</t>
         </is>
       </c>
       <c r="N138" s="10" t="inlineStr">
         <is>
-          <t>browser: downtime-pack.spec (1)</t>
+          <t>42_booking_rules (9)</t>
         </is>
       </c>
       <c r="O138" s="10" t="inlineStr">
@@ -11519,87 +11523,165 @@
       </c>
       <c r="P138" s="10" t="inlineStr">
         <is>
-          <t>No database change. Reads v_arrivals, v_in_house and v_folio_balances. Added 8 Oct 2026.</t>
+          <t>Added 8 Oct 2026. The columns existed since the reservations release; this adds the screen and the function.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
+          <t>FO-014</t>
+        </is>
+      </c>
+      <c r="B139" s="10" t="inlineStr">
+        <is>
+          <t>Front Office</t>
+        </is>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
+        <is>
+          <t>/downtime</t>
+        </is>
+      </c>
+      <c r="D139" s="10" t="inlineStr">
+        <is>
+          <t>A printable downtime pack: arrivals due, in-house guests with balance, departures due, ten blank lines for new guests on paper, and a short paper routine. Staff print it when the internet or system is down.</t>
+        </is>
+      </c>
+      <c r="E139" s="10" t="inlineStr">
+        <is>
+          <t>BR-006</t>
+        </is>
+      </c>
+      <c r="F139" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G139" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H139" s="10" t="inlineStr">
+        <is>
+          <t>fo.view</t>
+        </is>
+      </c>
+      <c r="I139" s="10" t="inlineStr"/>
+      <c r="J139" s="10" t="inlineStr">
+        <is>
+          <t>a hotel with guests in house</t>
+        </is>
+      </c>
+      <c r="K139" s="10" t="inlineStr">
+        <is>
+          <t>a front desk user opens Downtime pack and prints</t>
+        </is>
+      </c>
+      <c r="L139" s="10" t="inlineStr">
+        <is>
+          <t>the lists show room, guest, phone, departure and the folio balance from the database, with blank lines and the paper routine</t>
+        </is>
+      </c>
+      <c r="M139" s="10" t="inlineStr">
+        <is>
+          <t>src/routes/_authenticated/_app/downtime.tsx</t>
+        </is>
+      </c>
+      <c r="N139" s="10" t="inlineStr">
+        <is>
+          <t>browser: downtime-pack.spec (1)</t>
+        </is>
+      </c>
+      <c r="O139" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P139" s="10" t="inlineStr">
+        <is>
+          <t>No database change. Reads v_arrivals, v_in_house and v_folio_balances. Added 8 Oct 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="inlineStr">
+        <is>
           <t>DAY-007</t>
         </is>
       </c>
-      <c r="B139" s="10" t="inlineStr">
+      <c r="B140" s="10" t="inlineStr">
         <is>
           <t>Business Date</t>
         </is>
       </c>
-      <c r="C139" s="10" t="inlineStr">
+      <c r="C140" s="10" t="inlineStr">
         <is>
           <t>Notifications bell</t>
         </is>
       </c>
-      <c r="D139" s="10" t="inlineStr">
+      <c r="D140" s="10" t="inlineStr">
         <is>
           <t>In the last hour before a property rolls its business date, if a cashier shift is still open, users who can run the night audit get one warning that night. The roll does not wait.</t>
         </is>
       </c>
-      <c r="E139" s="10" t="inlineStr">
+      <c r="E140" s="10" t="inlineStr">
         <is>
           <t>BR-016</t>
         </is>
       </c>
-      <c r="F139" s="10" t="inlineStr">
+      <c r="F140" s="10" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G139" s="10" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H139" s="10" t="inlineStr">
+      <c r="G140" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H140" s="10" t="inlineStr">
         <is>
           <t>fin.nightaudit.run</t>
         </is>
       </c>
-      <c r="I139" s="10" t="inlineStr">
+      <c r="I140" s="10" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="J139" s="10" t="inlineStr">
+      <c r="J140" s="10" t="inlineStr">
         <is>
           <t>a cashier shift is still open</t>
         </is>
       </c>
-      <c r="K139" s="10" t="inlineStr">
+      <c r="K140" s="10" t="inlineStr">
         <is>
           <t>the roll time is less than 60 minutes away</t>
         </is>
       </c>
-      <c r="L139" s="10" t="inlineStr">
+      <c r="L140" s="10" t="inlineStr">
         <is>
           <t>each night audit user gets one rollover_warning notification for that business date; none earlier, none after the roll time, none if no shift is open, none twice</t>
         </is>
       </c>
-      <c r="M139" s="10" t="inlineStr">
+      <c r="M140" s="10" t="inlineStr">
         <is>
           <t>app.warn_before_rollover; cron job rollover-warning</t>
         </is>
       </c>
-      <c r="N139" s="10" t="inlineStr">
+      <c r="N140" s="10" t="inlineStr">
         <is>
           <t>43_rollover_warning (9)</t>
         </is>
       </c>
-      <c r="O139" s="10" t="inlineStr">
+      <c r="O140" s="10" t="inlineStr">
         <is>
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P139" s="10" t="inlineStr">
+      <c r="P140" s="10" t="inlineStr">
         <is>
           <t>Added 8 Oct 2026. Warning only; the hard gate stays in R2 (DAY-005).</t>
         </is>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -10659,7 +10659,7 @@
       </c>
       <c r="N127" s="10" t="inlineStr">
         <is>
-          <t>47_owner_summary (8); browser: owner-summary</t>
+          <t>47_owner_summary (9); browser: owner-summary</t>
         </is>
       </c>
       <c r="O127" s="10" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="P127" s="10" t="inlineStr">
         <is>
-          <t>Email delivery waits on the sending domain and email account.</t>
+          <t>Email delivery waits on the sending domain and email account. Collected money nets payment reversals the same day (migration 20261015130000).</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P140"/>
+  <dimension ref="A1:P141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6432,32 +6432,32 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>MNT-001</t>
+          <t>HK-007</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Housekeeping</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>MNT-01, MNT-02</t>
+          <t>(housekeeping on a phone)</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Tickets move from open to assigned, in progress, waiting, resolved and closed; waiting needs a reason.</t>
+          <t>An attendant logs minibar use from the room. The database prices it from the hotel price list. Front desk confirms before the charge posts to the folio.</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>BR-012</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
@@ -6467,37 +6467,37 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>mnt.ticket.create, mnt.ticket.manage, mnt.ticket.work</t>
+          <t>hk.minibar.record, setup.minibar.manage</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>States: Maintenance Ticket</t>
+          <t>Rule: Separation of duties</t>
         </is>
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>a ticket</t>
+          <t>a guest in house and a minibar price list</t>
         </is>
       </c>
       <c r="K74" s="10" t="inlineStr">
         <is>
-          <t>it is assigned, started, paused with a reason, resumed and resolved</t>
+          <t>an attendant logs 2 water and 1 cola, then front desk confirms</t>
         </is>
       </c>
       <c r="L74" s="10" t="inlineStr">
         <is>
-          <t>each step follows the allowed path and a ticket assigned to someone else cannot be started by another person</t>
+          <t>a request for the priced total waits open, a repeat with the same key makes no second request, the attendant cannot confirm, and the confirmed charge posts once</t>
         </is>
       </c>
       <c r="M74" s="10" t="inlineStr">
         <is>
-          <t>create_ticket, assign_ticket, start_ticket, wait_ticket, resolve_ticket</t>
+          <t>save_minibar_item, record_minibar_use, list_minibar_items, complete_service_request</t>
         </is>
       </c>
       <c r="N74" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (2)</t>
+          <t>48_minibar (16)</t>
         </is>
       </c>
       <c r="O74" s="10" t="inlineStr">
@@ -6510,7 +6510,7 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>MNT-002</t>
+          <t>MNT-001</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -6520,17 +6520,17 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>MNT-02</t>
+          <t>MNT-01, MNT-02</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>The person who resolved a ticket cannot close it; closing releases its room block.</t>
+          <t>Tickets move from open to assigned, in progress, waiting, resolved and closed; waiting needs a reason.</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>BR-015, BR-012</t>
+          <t>BR-012</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -6545,37 +6545,37 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>mnt.ticket.close</t>
+          <t>mnt.ticket.create, mnt.ticket.manage, mnt.ticket.work</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>Rule: Separation of duties</t>
+          <t>States: Maintenance Ticket</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>a resolved ticket with a room block</t>
+          <t>a ticket</t>
         </is>
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
-          <t>its resolver tries to close it, then a supervisor does</t>
+          <t>it is assigned, started, paused with a reason, resumed and resolved</t>
         </is>
       </c>
       <c r="L75" s="10" t="inlineStr">
         <is>
-          <t>the first is refused with E_SOD; the second closes it and releases the block</t>
+          <t>each step follows the allowed path and a ticket assigned to someone else cannot be started by another person</t>
         </is>
       </c>
       <c r="M75" s="10" t="inlineStr">
         <is>
-          <t>close_ticket</t>
+          <t>create_ticket, assign_ticket, start_ticket, wait_ticket, resolve_ticket</t>
         </is>
       </c>
       <c r="N75" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (4)</t>
+          <t>14_lifecycle (2)</t>
         </is>
       </c>
       <c r="O75" s="10" t="inlineStr">
@@ -6588,7 +6588,7 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>MNT-003</t>
+          <t>MNT-002</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -6603,17 +6603,17 @@
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Tickets can be reopened or cancelled, each with a reason.</t>
+          <t>The person who resolved a ticket cannot close it; closing releases its room block.</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>BR-012</t>
+          <t>BR-015, BR-012</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
@@ -6623,37 +6623,37 @@
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>mnt.ticket.manage, mnt.ticket.cancel</t>
+          <t>mnt.ticket.close</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>States: Maintenance Ticket</t>
+          <t>Rule: Separation of duties</t>
         </is>
       </c>
       <c r="J76" s="10" t="inlineStr">
         <is>
-          <t>a resolved ticket</t>
+          <t>a resolved ticket with a room block</t>
         </is>
       </c>
       <c r="K76" s="10" t="inlineStr">
         <is>
-          <t>a maintenance officer reopens it or cancels it</t>
+          <t>its resolver tries to close it, then a supervisor does</t>
         </is>
       </c>
       <c r="L76" s="10" t="inlineStr">
         <is>
-          <t>the status changes and the reason is audited; housekeeping cannot cancel</t>
+          <t>the first is refused with E_SOD; the second closes it and releases the block</t>
         </is>
       </c>
       <c r="M76" s="10" t="inlineStr">
         <is>
-          <t>reopen_ticket, cancel_ticket</t>
+          <t>close_ticket</t>
         </is>
       </c>
       <c r="N76" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (4)</t>
+          <t>14_lifecycle (4)</t>
         </is>
       </c>
       <c r="O76" s="10" t="inlineStr">
@@ -6666,27 +6666,27 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>SVC-001</t>
+          <t>MNT-003</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>Guest Service</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>FO-01</t>
+          <t>MNT-02</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>Guest requests are captured, assigned, progressed and completed.</t>
+          <t>Tickets can be reopened or cancelled, each with a reason.</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>BR-006</t>
+          <t>BR-012</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
@@ -6701,37 +6701,37 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>svc.request.create, svc.request.manage</t>
+          <t>mnt.ticket.manage, mnt.ticket.cancel</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
         <is>
-          <t>Workflow WF05</t>
+          <t>States: Maintenance Ticket</t>
         </is>
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>a guest in house</t>
+          <t>a resolved ticket</t>
         </is>
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>staff log a request and it is assigned, started and completed</t>
+          <t>a maintenance officer reopens it or cancels it</t>
         </is>
       </c>
       <c r="L77" s="10" t="inlineStr">
         <is>
-          <t>it is tied to the guest's room and finishes once</t>
+          <t>the status changes and the reason is audited; housekeeping cannot cancel</t>
         </is>
       </c>
       <c r="M77" s="10" t="inlineStr">
         <is>
-          <t>create_service_request, assign_service_request, start_service_request, complete_service_request</t>
+          <t>reopen_ticket, cancel_ticket</t>
         </is>
       </c>
       <c r="N77" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (3)</t>
+          <t>17_more_features (4)</t>
         </is>
       </c>
       <c r="O77" s="10" t="inlineStr">
@@ -6744,7 +6744,7 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>SVC-002</t>
+          <t>SVC-001</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -6754,17 +6754,17 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>FO-01, FIN-01</t>
+          <t>FO-01</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>A chargeable request posts its charge, with tax, to the folio when completed.</t>
+          <t>Guest requests are captured, assigned, progressed and completed.</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-006</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>svc.request.manage, fin.charge.post</t>
+          <t>svc.request.create, svc.request.manage</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
@@ -6789,22 +6789,22 @@
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>a chargeable laundry request of 3,000</t>
+          <t>a guest in house</t>
         </is>
       </c>
       <c r="K78" s="10" t="inlineStr">
         <is>
-          <t>it is completed</t>
+          <t>staff log a request and it is assigned, started and completed</t>
         </is>
       </c>
       <c r="L78" s="10" t="inlineStr">
         <is>
-          <t>3,000 plus tax is posted once to the guest's folio</t>
+          <t>it is tied to the guest's room and finishes once</t>
         </is>
       </c>
       <c r="M78" s="10" t="inlineStr">
         <is>
-          <t>complete_service_request</t>
+          <t>create_service_request, assign_service_request, start_service_request, complete_service_request</t>
         </is>
       </c>
       <c r="N78" s="10" t="inlineStr">
@@ -6822,22 +6822,22 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>FIN-001</t>
+          <t>SVC-002</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Guest Service</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>FIN-01</t>
+          <t>FO-01, FIN-01</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>Charges post with their tax lines; prices can include or exclude tax; the remainder of a rounding goes on the last tax line.</t>
+          <t>A chargeable request posts its charge, with tax, to the folio when completed.</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
@@ -6857,37 +6857,37 @@
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>fin.charge.post</t>
+          <t>svc.request.manage, fin.charge.post</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
         <is>
-          <t>Rule: Business date</t>
+          <t>Workflow WF05</t>
         </is>
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>service charge 10% and VAT 7.5%</t>
+          <t>a chargeable laundry request of 3,000</t>
         </is>
       </c>
       <c r="K79" s="10" t="inlineStr">
         <is>
-          <t>a charge of 10,000 or an inclusive 11,825 is posted</t>
+          <t>it is completed</t>
         </is>
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
-          <t>the folio owes 11,825 with a net of 10,000 either way</t>
+          <t>3,000 plus tax is posted once to the guest's folio</t>
         </is>
       </c>
       <c r="M79" s="10" t="inlineStr">
         <is>
-          <t>post_charge, compute_taxes, insert_with_tax</t>
+          <t>complete_service_request</t>
         </is>
       </c>
       <c r="N79" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (6)</t>
+          <t>17_more_features (3)</t>
         </is>
       </c>
       <c r="O79" s="10" t="inlineStr">
@@ -6900,7 +6900,7 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>FIN-002</t>
+          <t>FIN-001</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Payments and deposits are recorded against a folio with a method; payments are taken outside the system in R1.</t>
+          <t>Charges post with their tax lines; prices can include or exclude tax; the remainder of a rounding goes on the last tax line.</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
@@ -6935,37 +6935,37 @@
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>fin.payment.post, fin.deposit.take</t>
+          <t>fin.charge.post</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
-          <t>Rule: Payments in R1</t>
+          <t>Rule: Business date</t>
         </is>
       </c>
       <c r="J80" s="10" t="inlineStr">
         <is>
-          <t>a folio with a balance</t>
+          <t>service charge 10% and VAT 7.5%</t>
         </is>
       </c>
       <c r="K80" s="10" t="inlineStr">
         <is>
-          <t>staff record a cash payment or a deposit</t>
+          <t>a charge of 10,000 or an inclusive 11,825 is posted</t>
         </is>
       </c>
       <c r="L80" s="10" t="inlineStr">
         <is>
-          <t>the balance falls; a role without the matching permission is refused</t>
+          <t>the folio owes 11,825 with a net of 10,000 either way</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr">
         <is>
-          <t>post_payment</t>
+          <t>post_charge, compute_taxes, insert_with_tax</t>
         </is>
       </c>
       <c r="N80" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>12_ledger (6)</t>
         </is>
       </c>
       <c r="O80" s="10" t="inlineStr">
@@ -6978,7 +6978,7 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>FIN-003</t>
+          <t>FIN-002</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>Foreign-currency postings store the amount, currency, exchange rate and base amount.</t>
+          <t>Payments and deposits are recorded against a folio with a method; payments are taken outside the system in R1.</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
@@ -7013,32 +7013,32 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>fin.payment.post</t>
+          <t>fin.payment.post, fin.deposit.take</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
         <is>
-          <t>Rule: Multi-currency</t>
+          <t>Rule: Payments in R1</t>
         </is>
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>USD 10 at 1,500</t>
+          <t>a folio with a balance</t>
         </is>
       </c>
       <c r="K81" s="10" t="inlineStr">
         <is>
-          <t>it is posted</t>
+          <t>staff record a cash payment or a deposit</t>
         </is>
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>the row shows the rate and 15,000 in the base currency; the amount must respect the currency's decimals</t>
+          <t>the balance falls; a role without the matching permission is refused</t>
         </is>
       </c>
       <c r="M81" s="10" t="inlineStr">
         <is>
-          <t>insert_txn, fx_rate</t>
+          <t>post_payment</t>
         </is>
       </c>
       <c r="N81" s="10" t="inlineStr">
@@ -7056,7 +7056,7 @@
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>FIN-004</t>
+          <t>FIN-003</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -7071,17 +7071,17 @@
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>A discount within the user's limit posts at once; above the limit it waits for an approver who is not the requester.</t>
+          <t>Foreign-currency postings store the amount, currency, exchange rate and base amount.</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>BR-015</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
@@ -7091,37 +7091,37 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>fin.discount.apply, fin.discount.approve</t>
+          <t>fin.payment.post</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
         <is>
-          <t>Rule: Limits; Separation of duties</t>
+          <t>Rule: Multi-currency</t>
         </is>
       </c>
       <c r="J82" s="10" t="inlineStr">
         <is>
-          <t>a front desk limit of 5,000</t>
+          <t>USD 10 at 1,500</t>
         </is>
       </c>
       <c r="K82" s="10" t="inlineStr">
         <is>
-          <t>they apply 3,000 then 8,000</t>
+          <t>it is posted</t>
         </is>
       </c>
       <c r="L82" s="10" t="inlineStr">
         <is>
-          <t>the first posts; the second is pending, does not change the balance and can be approved or rejected (with a reason) by a manager</t>
+          <t>the row shows the rate and 15,000 in the base currency; the amount must respect the currency's decimals</t>
         </is>
       </c>
       <c r="M82" s="10" t="inlineStr">
         <is>
-          <t>apply_discount, decide_approval</t>
+          <t>insert_txn, fx_rate</t>
         </is>
       </c>
       <c r="N82" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (6)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O82" s="10" t="inlineStr">
@@ -7134,7 +7134,7 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>FIN-005</t>
+          <t>FIN-004</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>Adjustments, reversals and refunds always need a second person and stay within the approver's limit.</t>
+          <t>A discount within the user's limit posts at once; above the limit it waits for an approver who is not the requester.</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
@@ -7169,37 +7169,37 @@
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>fin.adjust.post, fin.adjust.approve, fin.reverse.post, fin.refund.post, fin.refund.approve</t>
+          <t>fin.discount.apply, fin.discount.approve</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
         <is>
-          <t>Rule: Separation of duties, Limits</t>
+          <t>Rule: Limits; Separation of duties</t>
         </is>
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>an adjustment of 50,000 requested by a cashier</t>
+          <t>a front desk limit of 5,000</t>
         </is>
       </c>
       <c r="K83" s="10" t="inlineStr">
         <is>
-          <t>a manager with a 20,000 limit approves</t>
+          <t>they apply 3,000 then 8,000</t>
         </is>
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>it is refused with E_LIMIT; a senior approver can; nobody approves their own request</t>
+          <t>the first posts; the second is pending, does not change the balance and can be approved or rejected (with a reason) by a manager</t>
         </is>
       </c>
       <c r="M83" s="10" t="inlineStr">
         <is>
-          <t>request_adjustment, request_reversal, request_refund, decide_approval; check constraint approver_is_not_requester</t>
+          <t>apply_discount, decide_approval</t>
         </is>
       </c>
       <c r="N83" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>12_ledger (6)</t>
         </is>
       </c>
       <c r="O83" s="10" t="inlineStr">
@@ -7212,7 +7212,7 @@
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>FIN-006</t>
+          <t>FIN-005</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -7227,12 +7227,12 @@
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>A posted transaction is never edited or deleted; corrections are linked reversal, adjustment or refund rows.</t>
+          <t>Adjustments, reversals and refunds always need a second person and stay within the approver's limit.</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>BR-014, BR-015</t>
+          <t>BR-015</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
@@ -7247,37 +7247,37 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fin.adjust.post, fin.adjust.approve, fin.reverse.post, fin.refund.post, fin.refund.approve</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>Rule: Immutability</t>
+          <t>Rule: Separation of duties, Limits</t>
         </is>
       </c>
       <c r="J84" s="10" t="inlineStr">
         <is>
-          <t>a posted charge</t>
+          <t>an adjustment of 50,000 requested by a cashier</t>
         </is>
       </c>
       <c r="K84" s="10" t="inlineStr">
         <is>
-          <t>anyone, including the database owner, changes or deletes it</t>
+          <t>a manager with a 20,000 limit approves</t>
         </is>
       </c>
       <c r="L84" s="10" t="inlineStr">
         <is>
-          <t>the change is refused with E_IMMUTABLE; a reversal posts a linked row (with its tax lines) and a charge reverses only once</t>
+          <t>it is refused with E_LIMIT; a senior approver can; nobody approves their own request</t>
         </is>
       </c>
       <c r="M84" s="10" t="inlineStr">
         <is>
-          <t>txn_guard triggers; request_reversal</t>
+          <t>request_adjustment, request_reversal, request_refund, decide_approval; check constraint approver_is_not_requester</t>
         </is>
       </c>
       <c r="N84" s="10" t="inlineStr">
         <is>
-          <t>10_security (1); 12_ledger (13)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O84" s="10" t="inlineStr">
@@ -7290,7 +7290,7 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>FIN-007</t>
+          <t>FIN-006</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
@@ -7305,12 +7305,12 @@
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>A refund cannot exceed the credit on the folio.</t>
+          <t>A posted transaction is never edited or deleted; corrections are linked reversal, adjustment or refund rows.</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>BR-015</t>
+          <t>BR-014, BR-015</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
@@ -7325,37 +7325,37 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>fin.refund.post</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Immutability</t>
         </is>
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>a folio with a small credit</t>
+          <t>a posted charge</t>
         </is>
       </c>
       <c r="K85" s="10" t="inlineStr">
         <is>
-          <t>staff request a bigger refund</t>
+          <t>anyone, including the database owner, changes or deletes it</t>
         </is>
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>it is refused with E_REFUND_LIMIT; a refund within the credit is approved and pays out</t>
+          <t>the change is refused with E_IMMUTABLE; a reversal posts a linked row (with its tax lines) and a charge reverses only once</t>
         </is>
       </c>
       <c r="M85" s="10" t="inlineStr">
         <is>
-          <t>request_refund</t>
+          <t>txn_guard triggers; request_reversal</t>
         </is>
       </c>
       <c r="N85" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>10_security (1); 12_ledger (13)</t>
         </is>
       </c>
       <c r="O85" s="10" t="inlineStr">
@@ -7368,7 +7368,7 @@
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>FIN-008</t>
+          <t>FIN-007</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Repeating the same request cannot double post (idempotency keys).</t>
+          <t>A refund cannot exceed the credit on the folio.</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-015</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
+          <t>fin.refund.post</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I86" s="10" t="inlineStr">
-        <is>
-          <t>Rule: Offline-ready design; A12</t>
-        </is>
-      </c>
       <c r="J86" s="10" t="inlineStr">
         <is>
-          <t>a charge posted with a key</t>
+          <t>a folio with a small credit</t>
         </is>
       </c>
       <c r="K86" s="10" t="inlineStr">
         <is>
-          <t>the same request arrives again</t>
+          <t>staff request a bigger refund</t>
         </is>
       </c>
       <c r="L86" s="10" t="inlineStr">
         <is>
-          <t>the second returns the first and the balance is unchanged</t>
+          <t>it is refused with E_REFUND_LIMIT; a refund within the credit is approved and pays out</t>
         </is>
       </c>
       <c r="M86" s="10" t="inlineStr">
         <is>
-          <t>idempotency_key unique per tenant</t>
+          <t>request_refund</t>
         </is>
       </c>
       <c r="N86" s="10" t="inlineStr">
@@ -7446,7 +7446,7 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>FIN-009</t>
+          <t>FIN-008</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Move a posted charge, with its tax, to another folio of the same booking; revenue does not change.</t>
+          <t>Repeating the same request cannot double post (idempotency keys).</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
@@ -7481,37 +7481,37 @@
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>fin.folio.transfer</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Offline-ready design; A12</t>
         </is>
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>a charge on the guest folio</t>
+          <t>a charge posted with a key</t>
         </is>
       </c>
       <c r="K87" s="10" t="inlineStr">
         <is>
-          <t>a manager transfers it to a company folio</t>
+          <t>the same request arrives again</t>
         </is>
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>the target owes the charge and tax, the source is relieved, the total is unchanged and the charge moves once</t>
+          <t>the second returns the first and the balance is unchanged</t>
         </is>
       </c>
       <c r="M87" s="10" t="inlineStr">
         <is>
-          <t>transfer_transaction</t>
+          <t>idempotency_key unique per tenant</t>
         </is>
       </c>
       <c r="N87" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (6)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O87" s="10" t="inlineStr">
@@ -7524,7 +7524,7 @@
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>FIN-010</t>
+          <t>FIN-009</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Split folios per reservation.</t>
+          <t>Move a posted charge, with its tax, to another folio of the same booking; revenue does not change.</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>fin.folio.split</t>
+          <t>fin.folio.transfer</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
@@ -7569,27 +7569,27 @@
       </c>
       <c r="J88" s="10" t="inlineStr">
         <is>
-          <t>a reservation</t>
+          <t>a charge on the guest folio</t>
         </is>
       </c>
       <c r="K88" s="10" t="inlineStr">
         <is>
-          <t>staff add a Company folio</t>
+          <t>a manager transfers it to a company folio</t>
         </is>
       </c>
       <c r="L88" s="10" t="inlineStr">
         <is>
-          <t>charges can be posted to either folio and check-out settles both</t>
+          <t>the target owes the charge and tax, the source is relieved, the total is unchanged and the charge moves once</t>
         </is>
       </c>
       <c r="M88" s="10" t="inlineStr">
         <is>
-          <t>split_folio</t>
+          <t>transfer_transaction</t>
         </is>
       </c>
       <c r="N88" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (1)</t>
+          <t>12_ledger (6)</t>
         </is>
       </c>
       <c r="O88" s="10" t="inlineStr">
@@ -7602,7 +7602,7 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>FIN-011</t>
+          <t>FIN-010</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
@@ -7617,17 +7617,17 @@
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>A folio closes only at a zero balance and reopens only for the accountant with a reason; a closed folio takes no postings.</t>
+          <t>Split folios per reservation.</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>BR-013, BR-015</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
@@ -7637,37 +7637,37 @@
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>fin.invoice.issue, fin.folio.reopen</t>
+          <t>fin.folio.split</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
         <is>
-          <t>Rule: Reasons</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
-          <t>a settled folio</t>
+          <t>a reservation</t>
         </is>
       </c>
       <c r="K89" s="10" t="inlineStr">
         <is>
-          <t>it is closed and then a posting is attempted</t>
+          <t>staff add a Company folio</t>
         </is>
       </c>
       <c r="L89" s="10" t="inlineStr">
         <is>
-          <t>the posting is refused with E_FOLIO_CLOSED; reopening needs the permission and a reason and is audited</t>
+          <t>charges can be posted to either folio and check-out settles both</t>
         </is>
       </c>
       <c r="M89" s="10" t="inlineStr">
         <is>
-          <t>close_folio, reopen_folio</t>
+          <t>split_folio</t>
         </is>
       </c>
       <c r="N89" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (5)</t>
+          <t>12_ledger (1)</t>
         </is>
       </c>
       <c r="O89" s="10" t="inlineStr">
@@ -7680,7 +7680,7 @@
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>FIN-012</t>
+          <t>FIN-011</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -7690,17 +7690,17 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>FIN-01, FO-03</t>
+          <t>FIN-01</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Invoices and receipts are numbered documents built from posted rows; they cannot be changed once issued.</t>
+          <t>A folio closes only at a zero balance and reopens only for the accountant with a reason; a closed folio takes no postings.</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-013, BR-015</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>fin.invoice.issue</t>
+          <t>fin.invoice.issue, fin.folio.reopen</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Reasons</t>
         </is>
       </c>
       <c r="J90" s="10" t="inlineStr">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="K90" s="10" t="inlineStr">
         <is>
-          <t>an invoice is issued</t>
+          <t>it is closed and then a posting is attempted</t>
         </is>
       </c>
       <c r="L90" s="10" t="inlineStr">
         <is>
-          <t>the total, tax and balance match the folio and the invoice cannot be edited; interim receipts have their own number series</t>
+          <t>the posting is refused with E_FOLIO_CLOSED; reopening needs the permission and a reason and is audited</t>
         </is>
       </c>
       <c r="M90" s="10" t="inlineStr">
         <is>
-          <t>issue_invoice</t>
+          <t>close_folio, reopen_folio</t>
         </is>
       </c>
       <c r="N90" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (4); 17_more_features (4)</t>
+          <t>12_ledger (5)</t>
         </is>
       </c>
       <c r="O90" s="10" t="inlineStr">
@@ -7758,7 +7758,7 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>FIN-013</t>
+          <t>FIN-012</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>FIN-01</t>
+          <t>FIN-01, FO-03</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>Balances are calculated from posted rows and never stored; pending approvals do not change them.</t>
+          <t>Invoices and receipts are numbered documents built from posted rows; they cannot be changed once issued.</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
@@ -7793,37 +7793,37 @@
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>fin.folio.view</t>
+          <t>fin.invoice.issue</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
         <is>
-          <t>Rule: Immutability</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J91" s="10" t="inlineStr">
         <is>
-          <t>a pending discount</t>
+          <t>a settled folio</t>
         </is>
       </c>
       <c r="K91" s="10" t="inlineStr">
         <is>
-          <t>the balance is read</t>
+          <t>an invoice is issued</t>
         </is>
       </c>
       <c r="L91" s="10" t="inlineStr">
         <is>
-          <t>it is unchanged until the approval posts</t>
+          <t>the total, tax and balance match the folio and the invoice cannot be edited; interim receipts have their own number series</t>
         </is>
       </c>
       <c r="M91" s="10" t="inlineStr">
         <is>
-          <t>v_folio_balances</t>
+          <t>issue_invoice</t>
         </is>
       </c>
       <c r="N91" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>12_ledger (4); 17_more_features (4)</t>
         </is>
       </c>
       <c r="O91" s="10" t="inlineStr">
@@ -7836,7 +7836,7 @@
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>FIN-014</t>
+          <t>FIN-013</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Every posting takes the open business date, and a past date is refused.</t>
+          <t>Balances are calculated from posted rows and never stored; pending approvals do not change them.</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
@@ -7871,37 +7871,37 @@
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fin.folio.view</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr">
         <is>
-          <t>Rule: Business date</t>
+          <t>Rule: Immutability</t>
         </is>
       </c>
       <c r="J92" s="10" t="inlineStr">
         <is>
-          <t>a posting for a past date</t>
+          <t>a pending discount</t>
         </is>
       </c>
       <c r="K92" s="10" t="inlineStr">
         <is>
-          <t>it is inserted</t>
+          <t>the balance is read</t>
         </is>
       </c>
       <c r="L92" s="10" t="inlineStr">
         <is>
-          <t>it is refused with E_DATE</t>
+          <t>it is unchanged until the approval posts</t>
         </is>
       </c>
       <c r="M92" s="10" t="inlineStr">
         <is>
-          <t>txn_guard</t>
+          <t>v_folio_balances</t>
         </is>
       </c>
       <c r="N92" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2); 14_lifecycle (1); upgrade (2)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O92" s="10" t="inlineStr">
@@ -7914,7 +7914,7 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>FIN-015</t>
+          <t>FIN-014</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>Folio visibility follows the role: managers see all folios, a reservation officer sees only those of their own bookings.</t>
+          <t>Every posting takes the open business date, and a past date is refused.</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
-          <t>BR-017</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
@@ -7949,37 +7949,37 @@
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>fin.folio.view</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
         <is>
-          <t>Own-record scope</t>
+          <t>Rule: Business date</t>
         </is>
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
-          <t>a reservation officer</t>
+          <t>a posting for a past date</t>
         </is>
       </c>
       <c r="K93" s="10" t="inlineStr">
         <is>
-          <t>they read a colleague's folio</t>
+          <t>it is inserted</t>
         </is>
       </c>
       <c r="L93" s="10" t="inlineStr">
         <is>
-          <t>they see nothing; they can still take a deposit</t>
+          <t>it is refused with E_DATE</t>
         </is>
       </c>
       <c r="M93" s="10" t="inlineStr">
         <is>
-          <t>can_see_folio</t>
+          <t>txn_guard</t>
         </is>
       </c>
       <c r="N93" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (6)</t>
+          <t>12_ledger (2); 14_lifecycle (1); upgrade (2)</t>
         </is>
       </c>
       <c r="O93" s="10" t="inlineStr">
@@ -7992,7 +7992,7 @@
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>FIN-016</t>
+          <t>FIN-015</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
@@ -8002,17 +8002,17 @@
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>/cashier</t>
+          <t>FIN-01</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Cashier shifts: a cashier opens a shift with a float, takes payments, counts each payment method at the end; the database works out expected and difference; a manager reconciles (never the closer). A hotel can require an open shift before payments.</t>
+          <t>Folio visibility follows the role: managers see all folios, a reservation officer sees only those of their own bookings.</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>BR-016</t>
+          <t>BR-017</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
@@ -8027,74 +8027,70 @@
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>fin.shift.close, fin.shift.reconcile</t>
+          <t>fin.folio.view</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
         <is>
-          <t>A2; decision of 7 Oct 2026</t>
+          <t>Own-record scope</t>
         </is>
       </c>
       <c r="J94" s="10" t="inlineStr">
         <is>
-          <t>a cashier with an open shift who took cash and card payments</t>
+          <t>a reservation officer</t>
         </is>
       </c>
       <c r="K94" s="10" t="inlineStr">
         <is>
-          <t>they close the shift with their counts</t>
+          <t>they read a colleague's folio</t>
         </is>
       </c>
       <c r="L94" s="10" t="inlineStr">
         <is>
-          <t>the difference per method is worked out, a note is needed for a difference, and a manager reconciles it</t>
+          <t>they see nothing; they can still take a deposit</t>
         </is>
       </c>
       <c r="M94" s="10" t="inlineStr">
         <is>
-          <t>open_cashier_shift, close_cashier_shift, reconcile_cashier_shift, cashier_shift_summary, list_cashier_shifts, set_cashier_shift_required, stamp_cashier_shift</t>
+          <t>can_see_folio</t>
         </is>
       </c>
       <c r="N94" s="10" t="inlineStr">
         <is>
-          <t>34_cashier_shifts (45)</t>
+          <t>12_ledger (6)</t>
         </is>
       </c>
       <c r="O94" s="10" t="inlineStr">
         <is>
-          <t>Built+tested (database only)</t>
-        </is>
-      </c>
-      <c r="P94" s="10" t="inlineStr">
-        <is>
-          <t>Cashier shift page built (open, close with counts, review, reconcile). Not covered by a browser test yet. New permission fin.shift.reconcile goes to built-in roles only.</t>
-        </is>
-      </c>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P94" s="10" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>DAY-001</t>
+          <t>FIN-016</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>Business Date</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>(system)</t>
+          <t>/cashier</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>The business date rolls automatically at each property's cut-off time.</t>
+          <t>Cashier shifts: a cashier opens a shift with a float, takes payments, counts each payment method at the end; the database works out expected and difference; a manager reconciles (never the closer). A hotel can require an open shift before payments.</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
-          <t>BR-019</t>
+          <t>BR-016</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
@@ -8109,50 +8105,54 @@
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>audit.businessdate.view</t>
+          <t>fin.shift.close, fin.shift.reconcile</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr">
         <is>
-          <t>Rule: Business date; A2</t>
+          <t>A2; decision of 7 Oct 2026</t>
         </is>
       </c>
       <c r="J95" s="10" t="inlineStr">
         <is>
-          <t>a property whose cut-off has passed</t>
+          <t>a cashier with an open shift who took cash and card payments</t>
         </is>
       </c>
       <c r="K95" s="10" t="inlineStr">
         <is>
-          <t>the scheduler runs</t>
+          <t>they close the shift with their counts</t>
         </is>
       </c>
       <c r="L95" s="10" t="inlineStr">
         <is>
-          <t>the date advances one day, up to three days per run; the roll is logged</t>
+          <t>the difference per method is worked out, a note is needed for a difference, and a manager reconciles it</t>
         </is>
       </c>
       <c r="M95" s="10" t="inlineStr">
         <is>
-          <t>roll_business_date, run_due_rollovers (pg_cron)</t>
+          <t>open_cashier_shift, close_cashier_shift, reconcile_cashier_shift, cashier_shift_summary, list_cashier_shifts, set_cashier_shift_required, stamp_cashier_shift</t>
         </is>
       </c>
       <c r="N95" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (4); upgrade (5)</t>
+          <t>34_cashier_shifts (45)</t>
         </is>
       </c>
       <c r="O95" s="10" t="inlineStr">
         <is>
-          <t>Built+tested</t>
-        </is>
-      </c>
-      <c r="P95" s="10" t="inlineStr"/>
+          <t>Built+tested (database only)</t>
+        </is>
+      </c>
+      <c r="P95" s="10" t="inlineStr">
+        <is>
+          <t>Cashier shift page built (open, close with counts, review, reconcile). Not covered by a browser test yet. New permission fin.shift.reconcile goes to built-in roles only.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>DAY-002</t>
+          <t>DAY-001</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
@@ -8167,12 +8167,12 @@
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>At the roll, each guest in house is charged the night's room rate and tax exactly once.</t>
+          <t>The business date rolls automatically at each property's cut-off time.</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-019</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
@@ -8187,37 +8187,37 @@
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>(system)</t>
+          <t>audit.businessdate.view</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr">
         <is>
-          <t>Rule: Business date</t>
+          <t>Rule: Business date; A2</t>
         </is>
       </c>
       <c r="J96" s="10" t="inlineStr">
         <is>
-          <t>two guests in house</t>
+          <t>a property whose cut-off has passed</t>
         </is>
       </c>
       <c r="K96" s="10" t="inlineStr">
         <is>
-          <t>the roll runs</t>
+          <t>the scheduler runs</t>
         </is>
       </c>
       <c r="L96" s="10" t="inlineStr">
         <is>
-          <t>each folio gets one room charge for the closing date, with tax; running it again for the same night cannot repeat it</t>
+          <t>the date advances one day, up to three days per run; the roll is logged</t>
         </is>
       </c>
       <c r="M96" s="10" t="inlineStr">
         <is>
-          <t>roll_business_date; idempotency keys room:&lt;reservation&gt;:&lt;date&gt;</t>
+          <t>roll_business_date, run_due_rollovers (pg_cron)</t>
         </is>
       </c>
       <c r="N96" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (3)</t>
+          <t>14_lifecycle (4); upgrade (5)</t>
         </is>
       </c>
       <c r="O96" s="10" t="inlineStr">
@@ -8230,7 +8230,7 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>DAY-003</t>
+          <t>DAY-002</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>A guest still in house past departure is charged and extended a night if the room allows; otherwise managers are told.</t>
+          <t>At the roll, each guest in house is charged the night's room rate and tax exactly once.</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
@@ -8270,12 +8270,12 @@
       </c>
       <c r="I97" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Business date</t>
         </is>
       </c>
       <c r="J97" s="10" t="inlineStr">
         <is>
-          <t>a guest due out today who is still in house</t>
+          <t>two guests in house</t>
         </is>
       </c>
       <c r="K97" s="10" t="inlineStr">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="L97" s="10" t="inlineStr">
         <is>
-          <t>the departure moves one day and the night is charged</t>
+          <t>each folio gets one room charge for the closing date, with tax; running it again for the same night cannot repeat it</t>
         </is>
       </c>
       <c r="M97" s="10" t="inlineStr">
         <is>
-          <t>roll_business_date</t>
+          <t>roll_business_date; idempotency keys room:&lt;reservation&gt;:&lt;date&gt;</t>
         </is>
       </c>
       <c r="N97" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (12); upgrade (2)</t>
+          <t>14_lifecycle (3)</t>
         </is>
       </c>
       <c r="O97" s="10" t="inlineStr">
@@ -8308,7 +8308,7 @@
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>DAY-004</t>
+          <t>DAY-003</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>A failed roll changes nothing and notifies managers; other properties are not blocked.</t>
+          <t>A guest still in house past departure is charged and extended a night if the room allows; otherwise managers are told.</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>audit.businessdate.view</t>
+          <t>(system)</t>
         </is>
       </c>
       <c r="I98" s="10" t="inlineStr">
@@ -8353,27 +8353,27 @@
       </c>
       <c r="J98" s="10" t="inlineStr">
         <is>
-          <t>a property whose roll fails</t>
+          <t>a guest due out today who is still in house</t>
         </is>
       </c>
       <c r="K98" s="10" t="inlineStr">
         <is>
-          <t>the scheduler runs</t>
+          <t>the roll runs</t>
         </is>
       </c>
       <c r="L98" s="10" t="inlineStr">
         <is>
-          <t>its date is unchanged and managers get a notification</t>
+          <t>the departure moves one day and the night is charged</t>
         </is>
       </c>
       <c r="M98" s="10" t="inlineStr">
         <is>
-          <t>run_due_rollovers</t>
+          <t>roll_business_date</t>
         </is>
       </c>
       <c r="N98" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (2)</t>
+          <t>14_lifecycle (12); upgrade (2)</t>
         </is>
       </c>
       <c r="O98" s="10" t="inlineStr">
@@ -8386,7 +8386,7 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>DAY-005</t>
+          <t>DAY-004</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
@@ -8396,22 +8396,22 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>/admin (Business date)</t>
+          <t>(system)</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>Night audit flags list what is still open before the day closes: open cashier shifts (blocking), unreconciled differences, guests past departure, arrivals not checked in. The flags do not stop the date rolling yet.</t>
+          <t>A failed roll changes nothing and notifies managers; other properties are not blocked.</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>BR-016</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
@@ -8421,54 +8421,50 @@
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>fin.nightaudit.run</t>
+          <t>audit.businessdate.view</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J99" s="10" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>a property whose roll fails</t>
         </is>
       </c>
       <c r="K99" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>the scheduler runs</t>
         </is>
       </c>
       <c r="L99" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>its date is unchanged and managers get a notification</t>
         </is>
       </c>
       <c r="M99" s="10" t="inlineStr">
         <is>
-          <t>night_audit_flags</t>
+          <t>run_due_rollovers</t>
         </is>
       </c>
       <c r="N99" s="10" t="inlineStr">
         <is>
-          <t>34_cashier_shifts (7)</t>
+          <t>17_more_features (2)</t>
         </is>
       </c>
       <c r="O99" s="10" t="inlineStr">
         <is>
-          <t>Partly built (flags only)</t>
-        </is>
-      </c>
-      <c r="P99" s="10" t="inlineStr">
-        <is>
-          <t>Flags shown in Admin, Business date. The gate that stops the roll while a blocking flag is open is not built.</t>
-        </is>
-      </c>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>DAY-006</t>
+          <t>DAY-005</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -8478,17 +8474,17 @@
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>(system)</t>
+          <t>/admin (Business date)</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>A same-day arrival and departure: decide whether a night or day-use charge applies.</t>
+          <t>Night audit flags list what is still open before the day closes: open cashier shifts (blocking), unreconciled differences, guests past departure, arrivals not checked in. The flags do not stop the date rolling yet.</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-016</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
@@ -8503,79 +8499,79 @@
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>(decision)</t>
+          <t>fin.nightaudit.run</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr">
         <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J100" s="10" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="K100" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J100" s="10" t="inlineStr">
-        <is>
-          <t>a guest checks in and out on the same business date</t>
-        </is>
-      </c>
-      <c r="K100" s="10" t="inlineStr">
-        <is>
-          <t>they leave before the roll</t>
-        </is>
-      </c>
       <c r="L100" s="10" t="inlineStr">
         <is>
-          <t>today no room charge is made; the desk can post a manual charge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M100" s="10" t="inlineStr">
         <is>
-          <t>check_out</t>
+          <t>night_audit_flags</t>
         </is>
       </c>
       <c r="N100" s="10" t="inlineStr">
         <is>
-          <t>19_same_day (21); upgrade (2); browser: desk-journey</t>
+          <t>34_cashier_shifts (7)</t>
         </is>
       </c>
       <c r="O100" s="10" t="inlineStr">
         <is>
-          <t>Built+tested</t>
+          <t>Partly built (flags only)</t>
         </is>
       </c>
       <c r="P100" s="10" t="inlineStr">
         <is>
-          <t>Decided by Peter on 30 Sep 2026 (answer 5) and confirmed on 1 Oct 2026: same-day stays are charged one night; a manager can waive it with a reason.</t>
+          <t>Flags shown in Admin, Business date. The gate that stops the roll while a blocking flag is open is not built.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>RPT-001</t>
+          <t>DAY-006</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Business Date</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>DASH-01, REP-01</t>
+          <t>(system)</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>Occupancy, ADR and RevPAR use one definition: rooms sold over rooms available (out-of-order rooms excluded), revenue net of tax.</t>
+          <t>A same-day arrival and departure: decide whether a night or day-use charge applies.</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>BR-019</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
@@ -8585,37 +8581,37 @@
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>dash.view_exec, rep.ops.view</t>
+          <t>(decision)</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr">
         <is>
-          <t>KPI Dictionary</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J101" s="10" t="inlineStr">
         <is>
-          <t>a closed day</t>
+          <t>a guest checks in and out on the same business date</t>
         </is>
       </c>
       <c r="K101" s="10" t="inlineStr">
         <is>
-          <t>management opens the KPI view</t>
+          <t>they leave before the roll</t>
         </is>
       </c>
       <c r="L101" s="10" t="inlineStr">
         <is>
-          <t>occupancy, ADR and RevPAR equal sold, revenue and available as defined; tax is shown apart</t>
+          <t>today no room charge is made; the desk can post a manual charge</t>
         </is>
       </c>
       <c r="M101" s="10" t="inlineStr">
         <is>
-          <t>daily_stats, v_kpi_daily</t>
+          <t>check_out</t>
         </is>
       </c>
       <c r="N101" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (4)</t>
+          <t>19_same_day (21); upgrade (2); browser: desk-journey</t>
         </is>
       </c>
       <c r="O101" s="10" t="inlineStr">
@@ -8623,12 +8619,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P101" s="10" t="inlineStr"/>
+      <c r="P101" s="10" t="inlineStr">
+        <is>
+          <t>Decided by Peter on 30 Sep 2026 (answer 5) and confirmed on 1 Oct 2026: same-day stays are charged one night; a manager can waive it with a reason.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>RPT-002</t>
+          <t>RPT-001</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>DASH-02</t>
+          <t>DASH-01, REP-01</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Live operations views: arrivals, in-house, room board, housekeeping board.</t>
+          <t>Occupancy, ADR and RevPAR use one definition: rooms sold over rooms available (out-of-order rooms excluded), revenue net of tax.</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>BR-006, BR-019</t>
+          <t>BR-019</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
@@ -8663,37 +8663,37 @@
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>dash.view_ops</t>
+          <t>dash.view_exec, rep.ops.view</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KPI Dictionary</t>
         </is>
       </c>
       <c r="J102" s="10" t="inlineStr">
         <is>
-          <t>activity in the hotel</t>
+          <t>a closed day</t>
         </is>
       </c>
       <c r="K102" s="10" t="inlineStr">
         <is>
-          <t>staff open the operations dashboard</t>
+          <t>management opens the KPI view</t>
         </is>
       </c>
       <c r="L102" s="10" t="inlineStr">
         <is>
-          <t>the views return only rows the user may see</t>
+          <t>occupancy, ADR and RevPAR equal sold, revenue and available as defined; tax is shown apart</t>
         </is>
       </c>
       <c r="M102" s="10" t="inlineStr">
         <is>
-          <t>v_arrivals, v_in_house, v_room_board, v_hk_board</t>
+          <t>daily_stats, v_kpi_daily</t>
         </is>
       </c>
       <c r="N102" s="10" t="inlineStr">
         <is>
-          <t>29_untagged_rows (14)</t>
+          <t>14_lifecycle (4)</t>
         </is>
       </c>
       <c r="O102" s="10" t="inlineStr">
@@ -8706,7 +8706,7 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>RPT-003</t>
+          <t>RPT-002</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
@@ -8716,17 +8716,17 @@
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>REP-01, REP-02</t>
+          <t>DASH-02</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>Every reported figure traces to ledger rows or operational records.</t>
+          <t>Live operations views: arrivals, in-house, room board, housekeeping board.</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>BR-020</t>
+          <t>BR-006, BR-019</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>rep.ops.view, rep.fin.view</t>
+          <t>dash.view_ops</t>
         </is>
       </c>
       <c r="I103" s="10" t="inlineStr">
@@ -8751,27 +8751,27 @@
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
-          <t>a daily figure</t>
+          <t>activity in the hotel</t>
         </is>
       </c>
       <c r="K103" s="10" t="inlineStr">
         <is>
-          <t>an auditor recomputes it from folio_transactions</t>
+          <t>staff open the operations dashboard</t>
         </is>
       </c>
       <c r="L103" s="10" t="inlineStr">
         <is>
-          <t>the figures agree</t>
+          <t>the views return only rows the user may see</t>
         </is>
       </c>
       <c r="M103" s="10" t="inlineStr">
         <is>
-          <t>daily_stats computed from folio_transactions</t>
+          <t>v_arrivals, v_in_house, v_room_board, v_hk_board</t>
         </is>
       </c>
       <c r="N103" s="10" t="inlineStr">
         <is>
-          <t>29_untagged_rows (11)</t>
+          <t>29_untagged_rows (14)</t>
         </is>
       </c>
       <c r="O103" s="10" t="inlineStr">
@@ -8784,7 +8784,7 @@
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>RPT-004</t>
+          <t>RPT-003</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Report screens (occupancy trend, revenue by group, outstanding balances, cancellation and no-show rates).</t>
+          <t>Every reported figure traces to ledger rows or operational records.</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>BR-019</t>
+          <t>BR-020</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
@@ -8824,32 +8824,32 @@
       </c>
       <c r="I104" s="10" t="inlineStr">
         <is>
-          <t>KPI Dictionary</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J104" s="10" t="inlineStr">
         <is>
-          <t>a date range</t>
+          <t>a daily figure</t>
         </is>
       </c>
       <c r="K104" s="10" t="inlineStr">
         <is>
-          <t>a manager opens a report</t>
+          <t>an auditor recomputes it from folio_transactions</t>
         </is>
       </c>
       <c r="L104" s="10" t="inlineStr">
         <is>
-          <t>the numbers match the KPI definitions</t>
+          <t>the figures agree</t>
         </is>
       </c>
       <c r="M104" s="10" t="inlineStr">
         <is>
-          <t>Reports screen (src/routes/_authenticated/_app/reports.tsx) on report_* functions in the database: v_kpi_daily (occupancy, average rate, revenue per room), report_revenue_by_charge_code, report_outstanding_balances, report_payments, report_cancellation_rate (cancellations and no-shows), report_length_of_stay, report_balances_by_guest; finance reports need rpt.finance.view, operations reports rpt.operations.view</t>
+          <t>daily_stats computed from folio_transactions</t>
         </is>
       </c>
       <c r="N104" s="10" t="inlineStr">
         <is>
-          <t>29_untagged_rows (14)</t>
+          <t>29_untagged_rows (11)</t>
         </is>
       </c>
       <c r="O104" s="10" t="inlineStr">
@@ -8857,36 +8857,32 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P104" s="10" t="inlineStr">
-        <is>
-          <t>Reports screen: KPIs, revenue by charge code, outstanding balances, payments, cancellations and stay length, balances by guest, export.</t>
-        </is>
-      </c>
+      <c r="P104" s="10" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>NFR-001</t>
+          <t>RPT-004</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>(all)</t>
+          <t>REP-01, REP-02</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>Every table has row-level security and tenant_id; security definer functions pin their search path.</t>
+          <t>Report screens (occupancy trend, revenue by group, outstanding balances, cancellation and no-show rates).</t>
         </is>
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>BR-017</t>
+          <t>BR-019</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
@@ -8901,37 +8897,37 @@
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>rep.ops.view, rep.fin.view</t>
         </is>
       </c>
       <c r="I105" s="10" t="inlineStr">
         <is>
-          <t>Rule: Tenant isolation</t>
+          <t>KPI Dictionary</t>
         </is>
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
-          <t>a migration adds a table or function</t>
+          <t>a date range</t>
         </is>
       </c>
       <c r="K105" s="10" t="inlineStr">
         <is>
-          <t>the test suite runs</t>
+          <t>a manager opens a report</t>
         </is>
       </c>
       <c r="L105" s="10" t="inlineStr">
         <is>
-          <t>it fails if RLS, tenant_id or search_path is missing</t>
+          <t>the numbers match the KPI definitions</t>
         </is>
       </c>
       <c r="M105" s="10" t="inlineStr">
         <is>
-          <t>structure tests</t>
+          <t>Reports screen (src/routes/_authenticated/_app/reports.tsx) on report_* functions in the database: v_kpi_daily (occupancy, average rate, revenue per room), report_revenue_by_charge_code, report_outstanding_balances, report_payments, report_cancellation_rate (cancellations and no-shows), report_length_of_stay, report_balances_by_guest; finance reports need rpt.finance.view, operations reports rpt.operations.view</t>
         </is>
       </c>
       <c r="N105" s="10" t="inlineStr">
         <is>
-          <t>10_security (3)</t>
+          <t>29_untagged_rows (14)</t>
         </is>
       </c>
       <c r="O105" s="10" t="inlineStr">
@@ -8939,12 +8935,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P105" s="10" t="inlineStr"/>
+      <c r="P105" s="10" t="inlineStr">
+        <is>
+          <t>Reports screen: KPIs, revenue by charge code, outstanding balances, payments, cancellations and stay length, balances by guest, export.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>NFR-002</t>
+          <t>NFR-001</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>The browser can write directly only to plain configuration tables; ledger, reservations, stays, tasks and blocks change only through functions.</t>
+          <t>Every table has row-level security and tenant_id; security definer functions pin their search path.</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>BR-014, BR-017</t>
+          <t>BR-017</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
@@ -8984,32 +8984,32 @@
       </c>
       <c r="I106" s="10" t="inlineStr">
         <is>
-          <t>Rule: Immutability</t>
+          <t>Rule: Tenant isolation</t>
         </is>
       </c>
       <c r="J106" s="10" t="inlineStr">
         <is>
-          <t>any user</t>
+          <t>a migration adds a table or function</t>
         </is>
       </c>
       <c r="K106" s="10" t="inlineStr">
         <is>
-          <t>they write to a ledger or state table</t>
+          <t>the test suite runs</t>
         </is>
       </c>
       <c r="L106" s="10" t="inlineStr">
         <is>
-          <t>permission denied; the list of directly writable tables is asserted by a test</t>
+          <t>it fails if RLS, tenant_id or search_path is missing</t>
         </is>
       </c>
       <c r="M106" s="10" t="inlineStr">
         <is>
-          <t>20260928001100_grants.sql</t>
+          <t>structure tests</t>
         </is>
       </c>
       <c r="N106" s="10" t="inlineStr">
         <is>
-          <t>10_security (2)</t>
+          <t>10_security (3)</t>
         </is>
       </c>
       <c r="O106" s="10" t="inlineStr">
@@ -9022,7 +9022,7 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>NFR-003</t>
+          <t>NFR-002</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
@@ -9037,17 +9037,17 @@
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>Create actions accept client-generated ids and idempotency keys so an offline queue can be added later.</t>
+          <t>The browser can write directly only to plain configuration tables; ledger, reservations, stays, tasks and blocks change only through functions.</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>BR-014, BR-017</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G107" s="10" t="inlineStr">
@@ -9062,32 +9062,32 @@
       </c>
       <c r="I107" s="10" t="inlineStr">
         <is>
-          <t>Rule: Offline-ready design; A12</t>
+          <t>Rule: Immutability</t>
         </is>
       </c>
       <c r="J107" s="10" t="inlineStr">
         <is>
-          <t>a repeated create request</t>
+          <t>any user</t>
         </is>
       </c>
       <c r="K107" s="10" t="inlineStr">
         <is>
-          <t>it arrives twice</t>
+          <t>they write to a ledger or state table</t>
         </is>
       </c>
       <c r="L107" s="10" t="inlineStr">
         <is>
-          <t>only one record exists</t>
+          <t>permission denied; the list of directly writable tables is asserted by a test</t>
         </is>
       </c>
       <c r="M107" s="10" t="inlineStr">
         <is>
-          <t>idempotency keys; client ids allowed on insert</t>
+          <t>20260928001100_grants.sql</t>
         </is>
       </c>
       <c r="N107" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (1)</t>
+          <t>10_security (2)</t>
         </is>
       </c>
       <c r="O107" s="10" t="inlineStr">
@@ -9100,7 +9100,7 @@
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>NFR-004</t>
+          <t>NFR-003</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
@@ -9115,17 +9115,17 @@
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Money uses fixed decimals per currency (naira 2, CFA franc 0), never floating point.</t>
+          <t>Create actions accept client-generated ids and idempotency keys so an offline queue can be added later.</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
@@ -9140,32 +9140,32 @@
       </c>
       <c r="I108" s="10" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>Rule: Offline-ready design; A12</t>
         </is>
       </c>
       <c r="J108" s="10" t="inlineStr">
         <is>
-          <t>an amount with too many decimals</t>
+          <t>a repeated create request</t>
         </is>
       </c>
       <c r="K108" s="10" t="inlineStr">
         <is>
-          <t>it is posted</t>
+          <t>it arrives twice</t>
         </is>
       </c>
       <c r="L108" s="10" t="inlineStr">
         <is>
-          <t>it is refused with E_PRECISION</t>
+          <t>only one record exists</t>
         </is>
       </c>
       <c r="M108" s="10" t="inlineStr">
         <is>
-          <t>numeric(20,4), currencies.decimals</t>
+          <t>idempotency keys; client ids allowed on insert</t>
         </is>
       </c>
       <c r="N108" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>13_reservations (1)</t>
         </is>
       </c>
       <c r="O108" s="10" t="inlineStr">
@@ -9178,7 +9178,7 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>NFR-005</t>
+          <t>NFR-004</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>Business date and cut-off follow the property's timezone.</t>
+          <t>Money uses fixed decimals per currency (naira 2, CFA franc 0), never floating point.</t>
         </is>
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>BR-019</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
@@ -9218,32 +9218,32 @@
       </c>
       <c r="I109" s="10" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="J109" s="10" t="inlineStr">
         <is>
-          <t>a property in Lagos</t>
+          <t>an amount with too many decimals</t>
         </is>
       </c>
       <c r="K109" s="10" t="inlineStr">
         <is>
-          <t>it is created just before or after cut-off</t>
+          <t>it is posted</t>
         </is>
       </c>
       <c r="L109" s="10" t="inlineStr">
         <is>
-          <t>the business date is the local hotel day, not the server's day</t>
+          <t>it is refused with E_PRECISION</t>
         </is>
       </c>
       <c r="M109" s="10" t="inlineStr">
         <is>
-          <t>local_business_date</t>
+          <t>numeric(20,4), currencies.decimals</t>
         </is>
       </c>
       <c r="N109" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (1)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O109" s="10" t="inlineStr">
@@ -9256,72 +9256,72 @@
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>DAY-006b</t>
+          <t>NFR-005</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>Business Date</t>
+          <t>Non-functional</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>/checkout/$id</t>
+          <t>(all)</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>A guest leaving on the arrival day is charged one night at check-out; a manager can waive it with a reason.</t>
+          <t>Business date and cut-off follow the property's timezone.</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
+          <t>BR-019</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G110" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H110" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F110" s="10" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G110" s="10" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H110" s="10" t="inlineStr">
-        <is>
-          <t>fo.checkout; fo.sameday.waive</t>
-        </is>
-      </c>
       <c r="I110" s="10" t="inlineStr">
         <is>
-          <t>Rule: DAY-006 decision</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="J110" s="10" t="inlineStr">
         <is>
-          <t>an in-house guest whose arrival and departure are today</t>
+          <t>a property in Lagos</t>
         </is>
       </c>
       <c r="K110" s="10" t="inlineStr">
         <is>
-          <t>they are checked out</t>
+          <t>it is created just before or after cut-off</t>
         </is>
       </c>
       <c r="L110" s="10" t="inlineStr">
         <is>
-          <t>one night (with tax) is posted unless a manager waives it with a reason</t>
+          <t>the business date is the local hotel day, not the server's day</t>
         </is>
       </c>
       <c r="M110" s="10" t="inlineStr">
         <is>
-          <t>preview_check_out_charge, check_out</t>
+          <t>local_business_date</t>
         </is>
       </c>
       <c r="N110" s="10" t="inlineStr">
         <is>
-          <t>21_same_day_checkout (28); upgrade (2)</t>
+          <t>17_more_features (1)</t>
         </is>
       </c>
       <c r="O110" s="10" t="inlineStr">
@@ -9334,22 +9334,22 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>FIN-017</t>
+          <t>DAY-006b</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Business Date</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>/folios/$id</t>
+          <t>/checkout/$id</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>A payment matching one on the same bill (amount, currency, method, reference) within 10 minutes is refused unless the cashier confirms it with a reason; the refusal names the earlier payment and the confirmation is audited.</t>
+          <t>A guest leaving on the arrival day is charged one night at check-out; a manager can waive it with a reason.</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
@@ -9369,37 +9369,37 @@
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>fin.payment.post</t>
+          <t>fo.checkout; fo.sameday.waive</t>
         </is>
       </c>
       <c r="I111" s="10" t="inlineStr">
         <is>
-          <t>Setting duplicate_payment_window_minutes</t>
+          <t>Rule: DAY-006 decision</t>
         </is>
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
-          <t>a payment recorded on a bill a few minutes ago</t>
+          <t>an in-house guest whose arrival and departure are today</t>
         </is>
       </c>
       <c r="K111" s="10" t="inlineStr">
         <is>
-          <t>the same payment is recorded again with a new key</t>
+          <t>they are checked out</t>
         </is>
       </c>
       <c r="L111" s="10" t="inlineStr">
         <is>
-          <t>it is refused naming the earlier payment; with a reason it is recorded and audited as payment_duplicate_confirmed</t>
+          <t>one night (with tax) is posted unless a manager waives it with a reason</t>
         </is>
       </c>
       <c r="M111" s="10" t="inlineStr">
         <is>
-          <t>post_payment</t>
+          <t>preview_check_out_charge, check_out</t>
         </is>
       </c>
       <c r="N111" s="10" t="inlineStr">
         <is>
-          <t>25_duplicate_payments (20); browser: duplicate-payment</t>
+          <t>21_same_day_checkout (28); upgrade (2)</t>
         </is>
       </c>
       <c r="O111" s="10" t="inlineStr">
@@ -9412,7 +9412,7 @@
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>FIN-018</t>
+          <t>FIN-017</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>/setup/taxes</t>
+          <t>/folios/$id</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>A hotel can match the tax method of its existing folio using setup alone: each tax on the room price only, food and drink untaxed. A sample bill of 45,000 room plus 12,001 bar totals 67,126.</t>
+          <t>A payment matching one on the same bill (amount, currency, method, reference) within 10 minutes is refused unless the cashier confirms it with a reason; the refusal names the earlier payment and the confirmation is audited.</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
@@ -9447,37 +9447,37 @@
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>setup.tax.manage</t>
+          <t>fin.payment.post</t>
         </is>
       </c>
       <c r="I112" s="10" t="inlineStr">
         <is>
-          <t>Tax rates compounds_on_previous; charge code is_taxable</t>
+          <t>Setting duplicate_payment_window_minutes</t>
         </is>
       </c>
       <c r="J112" s="10" t="inlineStr">
         <is>
-          <t>a property with service charge 10%, VAT 7.5% and state tax 5%, none compounding, and a non-taxable bar code</t>
+          <t>a payment recorded on a bill a few minutes ago</t>
         </is>
       </c>
       <c r="K112" s="10" t="inlineStr">
         <is>
-          <t>a room charge of 45,000 and a bar charge of 12,001 are posted</t>
+          <t>the same payment is recorded again with a new key</t>
         </is>
       </c>
       <c r="L112" s="10" t="inlineStr">
         <is>
-          <t>the taxes are 4,500, 3,375 and 2,250, the bar has no tax and the bill is 67,126</t>
+          <t>it is refused naming the earlier payment; with a reason it is recorded and audited as payment_duplicate_confirmed</t>
         </is>
       </c>
       <c r="M112" s="10" t="inlineStr">
         <is>
-          <t>save_tax_rate, save_charge_code, post_charge</t>
+          <t>post_payment</t>
         </is>
       </c>
       <c r="N112" s="10" t="inlineStr">
         <is>
-          <t>44_folio_sample_method (5)</t>
+          <t>25_duplicate_payments (20); browser: duplicate-payment</t>
         </is>
       </c>
       <c r="O112" s="10" t="inlineStr">
@@ -9485,16 +9485,12 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P112" s="10" t="inlineStr">
-        <is>
-          <t>Method only; the accountant still signs off the rates (A11)</t>
-        </is>
-      </c>
+      <c r="P112" s="10" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>FIN-019</t>
+          <t>FIN-018</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -9504,12 +9500,12 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>/invoices/$id</t>
+          <t>/setup/taxes</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>An invoice shows the check-in time, number of guests, number of nights, a total for each day, and the receipt reference of each charge. Invoices issued earlier stay as issued.</t>
+          <t>A hotel can match the tax method of its existing folio using setup alone: each tax on the room price only, food and drink untaxed. A sample bill of 45,000 room plus 12,001 bar totals 67,126.</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
@@ -9519,7 +9515,7 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G113" s="10" t="inlineStr">
@@ -9529,37 +9525,37 @@
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>fin.invoice.issue</t>
+          <t>setup.tax.manage</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr">
         <is>
-          <t>Invoice snapshot is insert-only</t>
+          <t>Tax rates compounds_on_previous; charge code is_taxable</t>
         </is>
       </c>
       <c r="J113" s="10" t="inlineStr">
         <is>
-          <t>a stay with charges, one with a receipt reference</t>
+          <t>a property with service charge 10%, VAT 7.5% and state tax 5%, none compounding, and a non-taxable bar code</t>
         </is>
       </c>
       <c r="K113" s="10" t="inlineStr">
         <is>
-          <t>an invoice is issued</t>
+          <t>a room charge of 45,000 and a bar charge of 12,001 are posted</t>
         </is>
       </c>
       <c r="L113" s="10" t="inlineStr">
         <is>
-          <t>the invoice shows nights, guests, check-in time, a total per day and the receipt reference, all worked out in the database</t>
+          <t>the taxes are 4,500, 3,375 and 2,250, the bar has no tax and the bill is 67,126</t>
         </is>
       </c>
       <c r="M113" s="10" t="inlineStr">
         <is>
-          <t>issue_invoice</t>
+          <t>save_tax_rate, save_charge_code, post_charge</t>
         </is>
       </c>
       <c r="N113" s="10" t="inlineStr">
         <is>
-          <t>45_invoice_layout (6)</t>
+          <t>44_folio_sample_method (5)</t>
         </is>
       </c>
       <c r="O113" s="10" t="inlineStr">
@@ -9569,14 +9565,14 @@
       </c>
       <c r="P113" s="10" t="inlineStr">
         <is>
-          <t>Day totals and fields are stored in the invoice header when it is issued</t>
+          <t>Method only; the accountant still signs off the rates (A11)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>FIN-020</t>
+          <t>FIN-019</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -9591,7 +9587,7 @@
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Invoice and interim invoice numbers carry the year and month of the hotel business date, then a count that restarts each month with no gaps (INV-202610-000001, INT-202610-000001). Invoices already issued keep their numbers.</t>
+          <t>An invoice shows the check-in time, number of guests, number of nights, a total for each day, and the receipt reference of each charge. Invoices issued earlier stay as issued.</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
@@ -9616,32 +9612,32 @@
       </c>
       <c r="I114" s="10" t="inlineStr">
         <is>
-          <t>document_sequences period_key</t>
+          <t>Invoice snapshot is insert-only</t>
         </is>
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>a hotel with invoices issued in one month</t>
+          <t>a stay with charges, one with a receipt reference</t>
         </is>
       </c>
       <c r="K114" s="10" t="inlineStr">
         <is>
-          <t>an invoice is issued in the next month</t>
+          <t>an invoice is issued</t>
         </is>
       </c>
       <c r="L114" s="10" t="inlineStr">
         <is>
-          <t>its number starts with the new year and month and the count restarts at 1; the INT and INV series stay separate; reservation and folio numbers are unchanged</t>
+          <t>the invoice shows nights, guests, check-in time, a total per day and the receipt reference, all worked out in the database</t>
         </is>
       </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
-          <t>next_document_number, issue_invoice</t>
+          <t>issue_invoice</t>
         </is>
       </c>
       <c r="N114" s="10" t="inlineStr">
         <is>
-          <t>46_invoice_number_month (8); 17_more_features</t>
+          <t>45_invoice_layout (6)</t>
         </is>
       </c>
       <c r="O114" s="10" t="inlineStr">
@@ -9651,29 +9647,29 @@
       </c>
       <c r="P114" s="10" t="inlineStr">
         <is>
-          <t>Month comes from the business date, not the clock. No hotel code in the number yet.</t>
+          <t>Day totals and fields are stored in the invoice header when it is issued</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>GST-007</t>
+          <t>FIN-020</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>Guests</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>/guests/$id; check-in; walk-in</t>
+          <t>/invoices/$id</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>A photo or scan of an ID document is kept in private storage, shrunk and stripped of hidden data in the browser, and opened only through a 60-second link.</t>
+          <t>Invoice and interim invoice numbers carry the year and month of the hotel business date, then a count that restarts each month with no gaps (INV-202610-000001, INT-202610-000001). Invoices already issued keep their numbers.</t>
         </is>
       </c>
       <c r="E115" s="10" t="inlineStr">
@@ -9683,7 +9679,7 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G115" s="10" t="inlineStr">
@@ -9693,37 +9689,37 @@
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>guest.document.file.upload / view / delete</t>
+          <t>fin.invoice.issue</t>
         </is>
       </c>
       <c r="I115" s="10" t="inlineStr">
         <is>
-          <t>SET-009 switch</t>
+          <t>document_sequences period_key</t>
         </is>
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>a hotel that allows ID photos</t>
+          <t>a hotel with invoices issued in one month</t>
         </is>
       </c>
       <c r="K115" s="10" t="inlineStr">
         <is>
-          <t>front desk adds an ID photo</t>
+          <t>an invoice is issued in the next month</t>
         </is>
       </c>
       <c r="L115" s="10" t="inlineStr">
         <is>
-          <t>it is stored privately and opens only through a short-lived link</t>
+          <t>its number starts with the new year and month and the count restarts at 1; the INT and INV series stay separate; reservation and folio numbers are unchanged</t>
         </is>
       </c>
       <c r="M115" s="10" t="inlineStr">
         <is>
-          <t>begin_id_photo_upload, finish_id_photo_upload, open_id_photo</t>
+          <t>next_document_number, issue_invoice</t>
         </is>
       </c>
       <c r="N115" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (30)</t>
+          <t>46_invoice_number_month (8); 17_more_features</t>
         </is>
       </c>
       <c r="O115" s="10" t="inlineStr">
@@ -9731,12 +9727,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P115" s="10" t="inlineStr"/>
+      <c r="P115" s="10" t="inlineStr">
+        <is>
+          <t>Month comes from the business date, not the clock. No hotel code in the number yet.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>GST-008</t>
+          <t>GST-007</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>/guests/$id</t>
+          <t>/guests/$id; check-in; walk-in</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Every upload, view and deletion of an ID photo is audited with ids only, no personal data.</t>
+          <t>A photo or scan of an ID document is kept in private storage, shrunk and stripped of hidden data in the browser, and opened only through a 60-second link.</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
@@ -9771,37 +9771,37 @@
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>guest.document.file.upload / view / delete</t>
         </is>
       </c>
       <c r="I116" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SET-009 switch</t>
         </is>
       </c>
       <c r="J116" s="10" t="inlineStr">
         <is>
-          <t>an ID photo</t>
+          <t>a hotel that allows ID photos</t>
         </is>
       </c>
       <c r="K116" s="10" t="inlineStr">
         <is>
-          <t>it is uploaded, opened or deleted</t>
+          <t>front desk adds an ID photo</t>
         </is>
       </c>
       <c r="L116" s="10" t="inlineStr">
         <is>
-          <t>an audit row records who and which file, with no personal data</t>
+          <t>it is stored privately and opens only through a short-lived link</t>
         </is>
       </c>
       <c r="M116" s="10" t="inlineStr">
         <is>
-          <t>app.audit_id_photo</t>
+          <t>begin_id_photo_upload, finish_id_photo_upload, open_id_photo</t>
         </is>
       </c>
       <c r="N116" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (9)</t>
+          <t>24_id_photos (30)</t>
         </is>
       </c>
       <c r="O116" s="10" t="inlineStr">
@@ -9814,7 +9814,7 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>GST-009</t>
+          <t>GST-008</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>ID photos are removed from storage when the guest is anonymised or the document is removed, and move with the guest when two profiles are merged.</t>
+          <t>Every upload, view and deletion of an ID photo is audited with ids only, no personal data.</t>
         </is>
       </c>
       <c r="E117" s="10" t="inlineStr">
@@ -9859,27 +9859,27 @@
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>a guest with ID photos</t>
+          <t>an ID photo</t>
         </is>
       </c>
       <c r="K117" s="10" t="inlineStr">
         <is>
-          <t>the guest is anonymised, the document removed, or the profile merged</t>
+          <t>it is uploaded, opened or deleted</t>
         </is>
       </c>
       <c r="L117" s="10" t="inlineStr">
         <is>
-          <t>the files are removed, or move to the kept profile</t>
+          <t>an audit row records who and which file, with no personal data</t>
         </is>
       </c>
       <c r="M117" s="10" t="inlineStr">
         <is>
-          <t>anonymise_guest, merge_guests, delete_id_photo</t>
+          <t>app.audit_id_photo</t>
         </is>
       </c>
       <c r="N117" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (4)</t>
+          <t>24_id_photos (9)</t>
         </is>
       </c>
       <c r="O117" s="10" t="inlineStr">
@@ -9892,7 +9892,7 @@
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>GST-010</t>
+          <t>GST-009</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>(daily clean-up)</t>
+          <t>/guests/$id</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>ID photos are deleted automatically a set number of months (one setting, now 12) after the guest's last check-out, unless the guest has a booking that is not over.</t>
+          <t>ID photos are removed from storage when the guest is anonymised or the document is removed, and move with the guest when two profiles are merged.</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
@@ -9932,32 +9932,32 @@
       </c>
       <c r="I118" s="10" t="inlineStr">
         <is>
-          <t>Setting id_photo_keep_months; daily cron</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J118" s="10" t="inlineStr">
         <is>
-          <t>a guest whose last check-out was more than the keep period ago</t>
+          <t>a guest with ID photos</t>
         </is>
       </c>
       <c r="K118" s="10" t="inlineStr">
         <is>
-          <t>the daily clean-up runs</t>
+          <t>the guest is anonymised, the document removed, or the profile merged</t>
         </is>
       </c>
       <c r="L118" s="10" t="inlineStr">
         <is>
-          <t>their ID photos are deleted</t>
+          <t>the files are removed, or move to the kept profile</t>
         </is>
       </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
-          <t>/api/cron/id-photo-cleanup</t>
+          <t>anonymise_guest, merge_guests, delete_id_photo</t>
         </is>
       </c>
       <c r="N118" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (5)</t>
+          <t>24_id_photos (4)</t>
         </is>
       </c>
       <c r="O118" s="10" t="inlineStr">
@@ -9970,22 +9970,22 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>ROOM-005</t>
+          <t>GST-010</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>Rooms</t>
+          <t>Guests</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>/rooms</t>
+          <t>(daily clean-up)</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>Rooms are added one at a time or several by number or by name, with a preview; labels are free text up to 30 characters, unique per hotel ignoring case and extra spaces, shown as typed and sorted in natural order.</t>
+          <t>ID photos are deleted automatically a set number of months (one setting, now 12) after the guest's last check-out, unless the guest has a booking that is not over.</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr">
@@ -10005,37 +10005,37 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>setup.room.edit</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Setting id_photo_keep_months; daily cron</t>
         </is>
       </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
-          <t>an administrator on the Rooms page</t>
+          <t>a guest whose last check-out was more than the keep period ago</t>
         </is>
       </c>
       <c r="K119" s="10" t="inlineStr">
         <is>
-          <t>they add rooms by number range or by names</t>
+          <t>the daily clean-up runs</t>
         </is>
       </c>
       <c r="L119" s="10" t="inlineStr">
         <is>
-          <t>valid new rooms are created, duplicates skipped and invalid names shown</t>
+          <t>their ID photos are deleted</t>
         </is>
       </c>
       <c r="M119" s="10" t="inlineStr">
         <is>
-          <t>add_rooms_range, add_rooms_named, save_room</t>
+          <t>/api/cron/id-photo-cleanup</t>
         </is>
       </c>
       <c r="N119" s="10" t="inlineStr">
         <is>
-          <t>23_room_labels (46); 26_small_fixes (1); browser: rooms-add</t>
+          <t>24_id_photos (5)</t>
         </is>
       </c>
       <c r="O119" s="10" t="inlineStr">
@@ -10048,22 +10048,22 @@
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>SET-009</t>
+          <t>ROOM-005</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Rooms</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>/setup/property</t>
+          <t>/rooms</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>Per hotel: "Allow ID photos" (off by default) and "Require ID photo at check-in" (only when allowed). While Allow is off, uploading and opening ID photos are refused.</t>
+          <t>Rooms are added one at a time or several by number or by name, with a preview; labels are free text up to 30 characters, unique per hotel ignoring case and extra spaces, shown as typed and sorted in natural order.</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>setup.property.edit</t>
+          <t>setup.room.edit</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
@@ -10093,27 +10093,27 @@
       </c>
       <c r="J120" s="10" t="inlineStr">
         <is>
-          <t>a hotel with ID photos off</t>
+          <t>an administrator on the Rooms page</t>
         </is>
       </c>
       <c r="K120" s="10" t="inlineStr">
         <is>
-          <t>staff try to add or open an ID photo</t>
+          <t>they add rooms by number range or by names</t>
         </is>
       </c>
       <c r="L120" s="10" t="inlineStr">
         <is>
-          <t>it is refused; when Require is on, check-in waits for an ID photo</t>
+          <t>valid new rooms are created, duplicates skipped and invalid names shown</t>
         </is>
       </c>
       <c r="M120" s="10" t="inlineStr">
         <is>
-          <t>set_id_photo_settings</t>
+          <t>add_rooms_range, add_rooms_named, save_room</t>
         </is>
       </c>
       <c r="N120" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (10)</t>
+          <t>23_room_labels (46); 26_small_fixes (1); browser: rooms-add</t>
         </is>
       </c>
       <c r="O120" s="10" t="inlineStr">
@@ -10126,32 +10126,32 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>GRP-001</t>
+          <t>SET-009</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>Platform &amp; Tenancy</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>All branches</t>
+          <t>/setup/property</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>A built-in Group Manager role and the permission rpt.group.view exist; only System Administrator, General Manager and Group Manager hold the permission.</t>
+          <t>Per hotel: "Allow ID photos" (off by default) and "Require ID photo at check-in" (only when allowed). While Allow is off, uploading and opening ID photos are refused.</t>
         </is>
       </c>
       <c r="E121" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -10161,33 +10161,37 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>rpt.group.view</t>
-        </is>
-      </c>
-      <c r="I121" s="10" t="inlineStr"/>
+          <t>setup.property.edit</t>
+        </is>
+      </c>
+      <c r="I121" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J121" s="10" t="inlineStr">
         <is>
-          <t>a hotel group with several branches</t>
+          <t>a hotel with ID photos off</t>
         </is>
       </c>
       <c r="K121" s="10" t="inlineStr">
         <is>
-          <t>an owner wants a view-only manager for the whole group</t>
+          <t>staff try to add or open an ID photo</t>
         </is>
       </c>
       <c r="L121" s="10" t="inlineStr">
         <is>
-          <t>they assign the Group Manager role branch by branch, and that person can look but not post or change anything</t>
+          <t>it is refused; when Require is on, check-in waits for an ID photo</t>
         </is>
       </c>
       <c r="M121" s="10" t="inlineStr">
         <is>
-          <t>20261013120000_group_view.sql</t>
+          <t>set_id_photo_settings</t>
         </is>
       </c>
       <c r="N121" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (5)</t>
+          <t>24_id_photos (10)</t>
         </is>
       </c>
       <c r="O121" s="10" t="inlineStr">
@@ -10195,16 +10199,12 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P121" s="10" t="inlineStr">
-        <is>
-          <t>Custom roles copied earlier do not get the new permission; say so when releasing.</t>
-        </is>
-      </c>
+      <c r="P121" s="10" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>GRP-002</t>
+          <t>GRP-001</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
@@ -10219,7 +10219,7 @@
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>One call shows every branch the person may see: occupancy, in house, arrivals and departures to come, approvals, repairs and last night revenue, with group totals. Revenue is totalled per currency.</t>
+          <t>A built-in Group Manager role and the permission rpt.group.view exist; only System Administrator, General Manager and Group Manager hold the permission.</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
@@ -10245,27 +10245,27 @@
       <c r="I122" s="10" t="inlineStr"/>
       <c r="J122" s="10" t="inlineStr">
         <is>
-          <t>a group with a Lagos and an Abuja branch</t>
+          <t>a hotel group with several branches</t>
         </is>
       </c>
       <c r="K122" s="10" t="inlineStr">
         <is>
-          <t>a group manager opens All branches</t>
+          <t>an owner wants a view-only manager for the whole group</t>
         </is>
       </c>
       <c r="L122" s="10" t="inlineStr">
         <is>
-          <t>they see both branches with figures from the database, never another hotel group, and staff without the permission are refused</t>
+          <t>they assign the Group Manager role branch by branch, and that person can look but not post or change anything</t>
         </is>
       </c>
       <c r="M122" s="10" t="inlineStr">
         <is>
-          <t>group_overview; /group screen</t>
+          <t>20261013120000_group_view.sql</t>
         </is>
       </c>
       <c r="N122" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (10)</t>
+          <t>35_group_view (5)</t>
         </is>
       </c>
       <c r="O122" s="10" t="inlineStr">
@@ -10275,14 +10275,14 @@
       </c>
       <c r="P122" s="10" t="inlineStr">
         <is>
-          <t>Figures are read from each branch own business date. No arithmetic in the browser.</t>
+          <t>Custom roles copied earlier do not get the new permission; say so when releasing.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>GRP-003</t>
+          <t>GRP-002</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>A Group Manager sees only the branches they are assigned to, and cannot post charges or check guests in.</t>
+          <t>One call shows every branch the person may see: occupancy, in house, arrivals and departures to come, approvals, repairs and last night revenue, with group totals. Revenue is totalled per currency.</t>
         </is>
       </c>
       <c r="E123" s="10" t="inlineStr">
@@ -10323,27 +10323,27 @@
       <c r="I123" s="10" t="inlineStr"/>
       <c r="J123" s="10" t="inlineStr">
         <is>
-          <t>a Group Manager assigned to one branch</t>
+          <t>a group with a Lagos and an Abuja branch</t>
         </is>
       </c>
       <c r="K123" s="10" t="inlineStr">
         <is>
-          <t>a second branch is assigned</t>
+          <t>a group manager opens All branches</t>
         </is>
       </c>
       <c r="L123" s="10" t="inlineStr">
         <is>
-          <t>the second branch appears; the role never gets write permissions</t>
+          <t>they see both branches with figures from the database, never another hotel group, and staff without the permission are refused</t>
         </is>
       </c>
       <c r="M123" s="10" t="inlineStr">
         <is>
-          <t>assign_role (existing); group_overview</t>
+          <t>group_overview; /group screen</t>
         </is>
       </c>
       <c r="N123" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (3)</t>
+          <t>35_group_view (10)</t>
         </is>
       </c>
       <c r="O123" s="10" t="inlineStr">
@@ -10353,14 +10353,14 @@
       </c>
       <c r="P123" s="10" t="inlineStr">
         <is>
-          <t>Access is per branch, using the existing role assignment screen.</t>
+          <t>Figures are read from each branch own business date. No arithmetic in the browser.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>GRP-004</t>
+          <t>GRP-003</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>All branches (Copy setup)</t>
+          <t>All branches</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>A new branch can copy room types, rate plans and prices from an existing branch, once, into an empty branch.</t>
+          <t>A Group Manager sees only the branches they are assigned to, and cannot post charges or check guests in.</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
@@ -10395,33 +10395,33 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>setup.room.manage, setup.rate.manage</t>
+          <t>rpt.group.view</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr"/>
       <c r="J124" s="10" t="inlineStr">
         <is>
-          <t>a new empty branch</t>
+          <t>a Group Manager assigned to one branch</t>
         </is>
       </c>
       <c r="K124" s="10" t="inlineStr">
         <is>
-          <t>the owner copies setup from the first branch</t>
+          <t>a second branch is assigned</t>
         </is>
       </c>
       <c r="L124" s="10" t="inlineStr">
         <is>
-          <t>room types, rate plans and prices appear on the new branch and point at its own room types; rooms are not copied; a second copy is refused; the copy is audited</t>
+          <t>the second branch appears; the role never gets write permissions</t>
         </is>
       </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
-          <t>copy_property_setup</t>
+          <t>assign_role (existing); group_overview</t>
         </is>
       </c>
       <c r="N124" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (13)</t>
+          <t>35_group_view (3)</t>
         </is>
       </c>
       <c r="O124" s="10" t="inlineStr">
@@ -10431,29 +10431,29 @@
       </c>
       <c r="P124" s="10" t="inlineStr">
         <is>
-          <t>Taxes, charge codes and payment methods already arrive with every new branch.</t>
+          <t>Access is per branch, using the existing role assignment screen.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>RPT-005</t>
+          <t>GRP-004</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Platform &amp; Tenancy</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>All branches (Copy setup)</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>Revenue by booking source: bookings, cancellations, no-shows, room nights, room revenue and average rate for each source in a date range.</t>
+          <t>A new branch can copy room types, rate plans and prices from an existing branch, once, into an empty branch.</t>
         </is>
       </c>
       <c r="E125" s="10" t="inlineStr">
@@ -10473,33 +10473,33 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view</t>
+          <t>setup.room.manage, setup.rate.manage</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr"/>
       <c r="J125" s="10" t="inlineStr">
         <is>
-          <t>bookings from direct, phone and company sources</t>
+          <t>a new empty branch</t>
         </is>
       </c>
       <c r="K125" s="10" t="inlineStr">
         <is>
-          <t>the accountant picks a date range</t>
+          <t>the owner copies setup from the first branch</t>
         </is>
       </c>
       <c r="L125" s="10" t="inlineStr">
         <is>
-          <t>each source shows its own counts and room revenue (room charges only, before tax); cancelled bookings add no nights</t>
+          <t>room types, rate plans and prices appear on the new branch and point at its own room types; rooms are not copied; a second copy is refused; the copy is audited</t>
         </is>
       </c>
       <c r="M125" s="10" t="inlineStr">
         <is>
-          <t>20261013130000_source_ageing_reports.sql: report_revenue_by_source; Reports, By booking source tab</t>
+          <t>copy_property_setup</t>
         </is>
       </c>
       <c r="N125" s="10" t="inlineStr">
         <is>
-          <t>36_source_ageing (13)</t>
+          <t>35_group_view (13)</t>
         </is>
       </c>
       <c r="O125" s="10" t="inlineStr">
@@ -10509,14 +10509,14 @@
       </c>
       <c r="P125" s="10" t="inlineStr">
         <is>
-          <t>Bookings counted by arrival date; revenue by posting date.</t>
+          <t>Taxes, charge codes and payment methods already arrive with every new branch.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>RPT-006</t>
+          <t>RPT-005</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Ageing of unpaid balances by booking source: current, 1 to 7, 8 to 30, 31 to 60 and over 60 days since the due departure, plus credit held.</t>
+          <t>Revenue by booking source: bookings, cancellations, no-shows, room nights, room revenue and average rate for each source in a date range.</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
@@ -10557,27 +10557,27 @@
       <c r="I126" s="10" t="inlineStr"/>
       <c r="J126" s="10" t="inlineStr">
         <is>
-          <t>guests and companies who left owing money</t>
+          <t>bookings from direct, phone and company sources</t>
         </is>
       </c>
       <c r="K126" s="10" t="inlineStr">
         <is>
-          <t>the accountant opens the Ageing tab</t>
+          <t>the accountant picks a date range</t>
         </is>
       </c>
       <c r="L126" s="10" t="inlineStr">
         <is>
-          <t>each source shows what is owed in each age column; paid bills drop out; overpayments show as credit held; the total matches Outstanding balances</t>
+          <t>each source shows its own counts and room revenue (room charges only, before tax); cancelled bookings add no nights</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
-          <t>report_balance_ageing; Reports, Ageing tab</t>
+          <t>20261013130000_source_ageing_reports.sql: report_revenue_by_source; Reports, By booking source tab</t>
         </is>
       </c>
       <c r="N126" s="10" t="inlineStr">
         <is>
-          <t>36_source_ageing (11)</t>
+          <t>36_source_ageing (13)</t>
         </is>
       </c>
       <c r="O126" s="10" t="inlineStr">
@@ -10587,14 +10587,14 @@
       </c>
       <c r="P126" s="10" t="inlineStr">
         <is>
-          <t>Guests still staying count as current.</t>
+          <t>Bookings counted by arrival date; revenue by posting date.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>RPT-007</t>
+          <t>RPT-006</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
@@ -10604,17 +10604,17 @@
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>The owner summary: last night's occupancy and revenue, money collected by payment method, today's arrivals, departures and rooms, what is waiting, and old unpaid bills, as plain sentences built in the database. Works with AI off; a later daily email can send the same text.</t>
+          <t>Ageing of unpaid balances by booking source: current, 1 to 7, 8 to 30, 31 to 60 and over 60 days since the due departure, plus credit held.</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
@@ -10629,37 +10629,33 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view, rpt.operations.view</t>
-        </is>
-      </c>
-      <c r="I127" s="10" t="inlineStr">
-        <is>
-          <t>Reads the morning brief facts</t>
-        </is>
-      </c>
+          <t>rpt.finance.view</t>
+        </is>
+      </c>
+      <c r="I127" s="10" t="inlineStr"/>
       <c r="J127" s="10" t="inlineStr">
         <is>
-          <t>a hotel with a closed day and payments on it</t>
+          <t>guests and companies who left owing money</t>
         </is>
       </c>
       <c r="K127" s="10" t="inlineStr">
         <is>
-          <t>the owner opens the dashboard</t>
+          <t>the accountant opens the Ageing tab</t>
         </is>
       </c>
       <c r="L127" s="10" t="inlineStr">
         <is>
-          <t>sees yesterday at a glance with the money collected by method; front desk without finance reports is refused</t>
+          <t>each source shows what is owed in each age column; paid bills drop out; overpayments show as credit held; the total matches Outstanding balances</t>
         </is>
       </c>
       <c r="M127" s="10" t="inlineStr">
         <is>
-          <t>owner_summary</t>
+          <t>report_balance_ageing; Reports, Ageing tab</t>
         </is>
       </c>
       <c r="N127" s="10" t="inlineStr">
         <is>
-          <t>47_owner_summary (9); browser: owner-summary</t>
+          <t>36_source_ageing (11)</t>
         </is>
       </c>
       <c r="O127" s="10" t="inlineStr">
@@ -10669,34 +10665,34 @@
       </c>
       <c r="P127" s="10" t="inlineStr">
         <is>
-          <t>Email delivery waits on the sending domain and email account. Collected money nets payment reversals the same day (migration 20261015130000).</t>
+          <t>Guests still staying count as current.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>AI-001</t>
+          <t>RPT-007</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>AI helpers</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Dashboard, Admin</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>AI helpers are off for every hotel until a System Administrator or General Manager switches them on, with a monthly limit; the switch is audited.</t>
+          <t>The owner summary: last night's occupancy and revenue, money collected by payment method, today's arrivals, departures and rooms, what is waiting, and old unpaid bills, as plain sentences built in the database. Works with AI off; a later daily email can send the same text.</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
@@ -10711,33 +10707,37 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>adm.ai.manage</t>
-        </is>
-      </c>
-      <c r="I128" s="10" t="inlineStr"/>
+          <t>rpt.finance.view, rpt.operations.view</t>
+        </is>
+      </c>
+      <c r="I128" s="10" t="inlineStr">
+        <is>
+          <t>Reads the morning brief facts</t>
+        </is>
+      </c>
       <c r="J128" s="10" t="inlineStr">
         <is>
-          <t>a new hotel</t>
+          <t>a hotel with a closed day and payments on it</t>
         </is>
       </c>
       <c r="K128" s="10" t="inlineStr">
         <is>
-          <t>a manager opens Admin, AI helpers</t>
+          <t>the owner opens the dashboard</t>
         </is>
       </c>
       <c r="L128" s="10" t="inlineStr">
         <is>
-          <t>nothing runs until they switch it on and the change is in the audit log</t>
+          <t>sees yesterday at a glance with the money collected by method; front desk without finance reports is refused</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: set_ai_settings, ai_status; Admin, AI helpers tab</t>
+          <t>owner_summary</t>
         </is>
       </c>
       <c r="N128" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (11)</t>
+          <t>47_owner_summary (9); browser: owner-summary</t>
         </is>
       </c>
       <c r="O128" s="10" t="inlineStr">
@@ -10747,14 +10747,14 @@
       </c>
       <c r="P128" s="10" t="inlineStr">
         <is>
-          <t>Custom roles copied earlier do not get adm.ai.manage.</t>
+          <t>Email delivery waits on the sending domain and email account. Collected money nets payment reversals the same day (migration 20261015130000).</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>AI-002</t>
+          <t>AI-001</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>The facts sent to the AI are counts and money lines built by the database: no guest names, ID details, room numbers or card data.</t>
+          <t>AI helpers are off for every hotel until a System Administrator or General Manager switches them on, with a monthly limit; the switch is audited.</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
@@ -10789,28 +10789,28 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view, rpt.operations.view</t>
+          <t>adm.ai.manage</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr"/>
       <c r="J129" s="10" t="inlineStr">
         <is>
-          <t>a hotel with guests, approvals and overdue bills</t>
+          <t>a new hotel</t>
         </is>
       </c>
       <c r="K129" s="10" t="inlineStr">
         <is>
-          <t>a brief is started</t>
+          <t>a manager opens Admin, AI helpers</t>
         </is>
       </c>
       <c r="L129" s="10" t="inlineStr">
         <is>
-          <t>the facts hold only business date, last night, today, attention figures and plain lines, and overdue money matches the ledger</t>
+          <t>nothing runs until they switch it on and the change is in the audit log</t>
         </is>
       </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: ai_morning_brief_start, app.morning_brief_facts</t>
+          <t>20261013140000_ai_morning_brief.sql: set_ai_settings, ai_status; Admin, AI helpers tab</t>
         </is>
       </c>
       <c r="N129" s="10" t="inlineStr">
@@ -10825,14 +10825,14 @@
       </c>
       <c r="P129" s="10" t="inlineStr">
         <is>
-          <t>Overdue means unpaid more than 30 days after departure.</t>
+          <t>Custom roles copied earlier do not get adm.ai.manage.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>AI-003</t>
+          <t>AI-002</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
@@ -10847,7 +10847,7 @@
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>Each hotel has a monthly limit on AI drafts; failed calls do not count; a call can be finished once, by the person who started it.</t>
+          <t>The facts sent to the AI are counts and money lines built by the database: no guest names, ID details, room numbers or card data.</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
@@ -10867,33 +10867,33 @@
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view</t>
+          <t>rpt.finance.view, rpt.operations.view</t>
         </is>
       </c>
       <c r="I130" s="10" t="inlineStr"/>
       <c r="J130" s="10" t="inlineStr">
         <is>
-          <t>a limit of 2</t>
+          <t>a hotel with guests, approvals and overdue bills</t>
         </is>
       </c>
       <c r="K130" s="10" t="inlineStr">
         <is>
-          <t>a third brief is requested</t>
+          <t>a brief is started</t>
         </is>
       </c>
       <c r="L130" s="10" t="inlineStr">
         <is>
-          <t>it is refused until a failed call frees a slot or the month turns</t>
+          <t>the facts hold only business date, last night, today, attention figures and plain lines, and overdue money matches the ledger</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: ai_call_finish</t>
+          <t>20261013140000_ai_morning_brief.sql: ai_morning_brief_start, app.morning_brief_facts</t>
         </is>
       </c>
       <c r="N130" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (5)</t>
+          <t>37_ai_brief (11)</t>
         </is>
       </c>
       <c r="O130" s="10" t="inlineStr">
@@ -10901,12 +10901,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P130" s="10" t="inlineStr"/>
+      <c r="P130" s="10" t="inlineStr">
+        <is>
+          <t>Overdue means unpaid more than 30 days after departure.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>AI-004</t>
+          <t>AI-003</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -10921,7 +10925,7 @@
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>Only finance and operations viewers can ask for the brief; the usage log and settings cannot be written or read directly by the browser.</t>
+          <t>Each hotel has a monthly limit on AI drafts; failed calls do not count; a call can be finished once, by the person who started it.</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
@@ -10941,33 +10945,33 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view, rpt.operations.view</t>
+          <t>rpt.finance.view</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr"/>
       <c r="J131" s="10" t="inlineStr">
         <is>
-          <t>front desk, housekeeping, another hotel</t>
+          <t>a limit of 2</t>
         </is>
       </c>
       <c r="K131" s="10" t="inlineStr">
         <is>
-          <t>they ask for the brief or touch the tables</t>
+          <t>a third brief is requested</t>
         </is>
       </c>
       <c r="L131" s="10" t="inlineStr">
         <is>
-          <t>they are refused</t>
+          <t>it is refused until a failed call frees a slot or the month turns</t>
         </is>
       </c>
       <c r="M131" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql</t>
+          <t>20261013140000_ai_morning_brief.sql: ai_call_finish</t>
         </is>
       </c>
       <c r="N131" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (7)</t>
+          <t>37_ai_brief (5)</t>
         </is>
       </c>
       <c r="O131" s="10" t="inlineStr">
@@ -10980,7 +10984,7 @@
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>AI-005</t>
+          <t>AI-004</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -10995,7 +10999,7 @@
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>The server accepts an AI draft only when every number in it is in the database facts; otherwise it shows the plain figures. The key stays on the server and only the fact lines are sent.</t>
+          <t>Only finance and operations viewers can ask for the brief; the usage log and settings cannot be written or read directly by the browser.</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
@@ -11015,33 +11019,33 @@
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>rpt.finance.view, rpt.operations.view</t>
         </is>
       </c>
       <c r="I132" s="10" t="inlineStr"/>
       <c r="J132" s="10" t="inlineStr">
         <is>
-          <t>a draft that rounds or invents a figure</t>
+          <t>front desk, housekeeping, another hotel</t>
         </is>
       </c>
       <c r="K132" s="10" t="inlineStr">
         <is>
-          <t>the brief is written</t>
+          <t>they ask for the brief or touch the tables</t>
         </is>
       </c>
       <c r="L132" s="10" t="inlineStr">
         <is>
-          <t>the plain database lines are shown instead, with a note</t>
+          <t>they are refused</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
-          <t>src/lib/ai-brief.ts, ai-brief.functions.ts, Dashboard morning brief card</t>
+          <t>20261013140000_ai_morning_brief.sql</t>
         </is>
       </c>
       <c r="N132" s="10" t="inlineStr">
         <is>
-          <t>browser unit: ai-brief-unit (8)</t>
+          <t>37_ai_brief (7)</t>
         </is>
       </c>
       <c r="O132" s="10" t="inlineStr">
@@ -11049,31 +11053,27 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P132" s="10" t="inlineStr">
-        <is>
-          <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
-        </is>
-      </c>
+      <c r="P132" s="10" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>SET-010</t>
+          <t>AI-005</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>AI helpers</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Setup, Rooms</t>
+          <t>Dashboard, Admin</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>A hotel can add room types and rooms from one checked list: preview first, then all or nothing. Existing codes and room names are skipped, so repeating adds nothing.</t>
+          <t>The server accepts an AI draft only when every number in it is in the database facts; otherwise it shows the plain figures. The key stays on the server and only the fact lines are sent.</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
@@ -11093,33 +11093,33 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>setup.room.manage</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr"/>
       <c r="J133" s="10" t="inlineStr">
         <is>
-          <t>a list of room types and rooms</t>
+          <t>a draft that rounds or invents a figure</t>
         </is>
       </c>
       <c r="K133" s="10" t="inlineStr">
         <is>
-          <t>the manager previews and then applies it</t>
+          <t>the brief is written</t>
         </is>
       </c>
       <c r="L133" s="10" t="inlineStr">
         <is>
-          <t>the preview writes nothing; apply adds every valid item or none (bad name, unknown type, over 500 rooms, over the plan limit); a repeat adds nothing; the import is audited</t>
+          <t>the plain database lines are shown instead, with a note</t>
         </is>
       </c>
       <c r="M133" s="10" t="inlineStr">
         <is>
-          <t>20261013150000_setup_import.sql: apply_setup_import</t>
+          <t>src/lib/ai-brief.ts, ai-brief.functions.ts, Dashboard morning brief card</t>
         </is>
       </c>
       <c r="N133" s="10" t="inlineStr">
         <is>
-          <t>38_setup_import (29)</t>
+          <t>browser unit: ai-brief-unit (8)</t>
         </is>
       </c>
       <c r="O133" s="10" t="inlineStr">
@@ -11129,19 +11129,19 @@
       </c>
       <c r="P133" s="10" t="inlineStr">
         <is>
-          <t>The AI only drafts the list. This function is the check.</t>
+          <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>AI-006</t>
+          <t>SET-010</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>AI helpers</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>The setup import assistant starts only when AI is on and under the monthly limit, and the AI sees only existing room type codes and a room count.</t>
+          <t>A hotel can add room types and rooms from one checked list: preview first, then all or nothing. Existing codes and room names are skipped, so repeating adds nothing.</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
@@ -11177,27 +11177,27 @@
       <c r="I134" s="10" t="inlineStr"/>
       <c r="J134" s="10" t="inlineStr">
         <is>
-          <t>AI switched on with a limit of 1</t>
+          <t>a list of room types and rooms</t>
         </is>
       </c>
       <c r="K134" s="10" t="inlineStr">
         <is>
-          <t>an import draft is started twice</t>
+          <t>the manager previews and then applies it</t>
         </is>
       </c>
       <c r="L134" s="10" t="inlineStr">
         <is>
-          <t>the second is refused until the first fails; front desk and other hotels are refused</t>
+          <t>the preview writes nothing; apply adds every valid item or none (bad name, unknown type, over 500 rooms, over the plan limit); a repeat adds nothing; the import is audited</t>
         </is>
       </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
-          <t>20261013150000_setup_import.sql: ai_import_start, app.ai_begin</t>
+          <t>20261013150000_setup_import.sql: apply_setup_import</t>
         </is>
       </c>
       <c r="N134" s="10" t="inlineStr">
         <is>
-          <t>38_setup_import (8)</t>
+          <t>38_setup_import (29)</t>
         </is>
       </c>
       <c r="O134" s="10" t="inlineStr">
@@ -11205,12 +11205,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P134" s="10" t="inlineStr"/>
+      <c r="P134" s="10" t="inlineStr">
+        <is>
+          <t>The AI only drafts the list. This function is the check.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>AI-007</t>
+          <t>AI-006</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
@@ -11225,7 +11229,7 @@
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>Pasted text with an email, phone or card number is refused before anything is sent; the draft may only contain rooms, floors, guest limits and type names that are in the pasted text.</t>
+          <t>The setup import assistant starts only when AI is on and under the monthly limit, and the AI sees only existing room type codes and a room count.</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
@@ -11251,27 +11255,27 @@
       <c r="I135" s="10" t="inlineStr"/>
       <c r="J135" s="10" t="inlineStr">
         <is>
-          <t>a pasted list</t>
+          <t>AI switched on with a limit of 1</t>
         </is>
       </c>
       <c r="K135" s="10" t="inlineStr">
         <is>
-          <t>the assistant drafts it</t>
+          <t>an import draft is started twice</t>
         </is>
       </c>
       <c r="L135" s="10" t="inlineStr">
         <is>
-          <t>invented rooms, floors and limits are dropped with a note; a draft with no matching rooms is an error</t>
+          <t>the second is refused until the first fails; front desk and other hotels are refused</t>
         </is>
       </c>
       <c r="M135" s="10" t="inlineStr">
         <is>
-          <t>src/lib/setup-import.ts, setup-import.functions.ts, Import from a list on Setup, Rooms</t>
+          <t>20261013150000_setup_import.sql: ai_import_start, app.ai_begin</t>
         </is>
       </c>
       <c r="N135" s="10" t="inlineStr">
         <is>
-          <t>browser unit: setup-import-unit (9)</t>
+          <t>38_setup_import (8)</t>
         </is>
       </c>
       <c r="O135" s="10" t="inlineStr">
@@ -11279,36 +11283,32 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P135" s="10" t="inlineStr">
-        <is>
-          <t>Needs ANTHROPIC_API_KEY on the server. Not set yet.</t>
-        </is>
-      </c>
+      <c r="P135" s="10" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>SET-011</t>
+          <t>AI-007</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>AI helpers</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>/setup; /dashboard</t>
+          <t>Setup, Rooms</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>A new hotel sees a checklist of what is left to set up: property details, room types, rooms, rates, taxes, payment methods and staff. Each step says what is missing and links to the right screen. The list comes from the hotel's own data, so it is always current.</t>
+          <t>Pasted text with an email, phone or card number is refused before anything is sent; the draft may only contain rooms, floors, guest limits and type names that are in the pasted text.</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
@@ -11323,37 +11323,33 @@
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>any setup permission</t>
-        </is>
-      </c>
-      <c r="I136" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>setup.room.manage</t>
+        </is>
+      </c>
+      <c r="I136" s="10" t="inlineStr"/>
       <c r="J136" s="10" t="inlineStr">
         <is>
-          <t>a hotel that is part way through setup</t>
+          <t>a pasted list</t>
         </is>
       </c>
       <c r="K136" s="10" t="inlineStr">
         <is>
-          <t>a manager opens Setup or the Dashboard</t>
+          <t>the assistant drafts it</t>
         </is>
       </c>
       <c r="L136" s="10" t="inlineStr">
         <is>
-          <t>the steps already done are ticked and the next one is linked; once all seven are done the checklist goes away</t>
+          <t>invented rooms, floors and limits are dropped with a note; a draft with no matching rooms is an error</t>
         </is>
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
-          <t>setup_progress</t>
+          <t>src/lib/setup-import.ts, setup-import.functions.ts, Import from a list on Setup, Rooms</t>
         </is>
       </c>
       <c r="N136" s="10" t="inlineStr">
         <is>
-          <t>40_guided_setup (30)</t>
+          <t>browser unit: setup-import-unit (9)</t>
         </is>
       </c>
       <c r="O136" s="10" t="inlineStr">
@@ -11363,39 +11359,39 @@
       </c>
       <c r="P136" s="10" t="inlineStr">
         <is>
-          <t>Read-only function, no stored progress. Staff step counts people with a role at the property (two or more).</t>
+          <t>Needs ANTHROPIC_API_KEY on the server. Not set yet.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>NFR-006</t>
+          <t>SET-011</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>(all)</t>
+          <t>/setup; /dashboard</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>The last room of a type is sold once, however many desks book at the same moment, and a repeated booking never doubles.</t>
+          <t>A new hotel sees a checklist of what is left to set up: property details, room types, rooms, rates, taxes, payment methods and staff. Each step says what is missing and links to the right screen. The list comes from the hotel's own data, so it is always current.</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G137" s="10" t="inlineStr">
@@ -11405,37 +11401,37 @@
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
+          <t>any setup permission</t>
+        </is>
+      </c>
+      <c r="I137" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="10" t="inlineStr">
-        <is>
-          <t>Rule: Safe last-room booking</t>
-        </is>
-      </c>
       <c r="J137" s="10" t="inlineStr">
         <is>
-          <t>one room of a type is left and several desks book it together</t>
+          <t>a hotel that is part way through setup</t>
         </is>
       </c>
       <c r="K137" s="10" t="inlineStr">
         <is>
-          <t>all of them submit at the same moment</t>
+          <t>a manager opens Setup or the Dashboard</t>
         </is>
       </c>
       <c r="L137" s="10" t="inlineStr">
         <is>
-          <t>exactly one booking succeeds, the rest get E_NO_AVAILABILITY, and nothing is oversold</t>
+          <t>the steps already done are ticked and the next one is linked; once all seven are done the checklist goes away</t>
         </is>
       </c>
       <c r="M137" s="10" t="inlineStr">
         <is>
-          <t>create_reservation, assert_available</t>
+          <t>setup_progress</t>
         </is>
       </c>
       <c r="N137" s="10" t="inlineStr">
         <is>
-          <t>concurrency/last_room.sh (6)</t>
+          <t>40_guided_setup (30)</t>
         </is>
       </c>
       <c r="O137" s="10" t="inlineStr">
@@ -11445,29 +11441,29 @@
       </c>
       <c r="P137" s="10" t="inlineStr">
         <is>
-          <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
+          <t>Read-only function, no stored progress. Staff step counts people with a role at the property (two or more).</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>SET-012</t>
+          <t>NFR-006</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Non-functional</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>/setup/property</t>
+          <t>(all)</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>A manager sets the longest stay (1 to 365 nights) and how long a tentative booking holds its room (1 to 720 hours) for each property.</t>
+          <t>The last room of a type is sold once, however many desks book at the same moment, and a repeated booking never doubles.</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
@@ -11477,7 +11473,7 @@
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G138" s="10" t="inlineStr">
@@ -11487,33 +11483,37 @@
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
-          <t>setup.property.edit</t>
-        </is>
-      </c>
-      <c r="I138" s="10" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" s="10" t="inlineStr">
+        <is>
+          <t>Rule: Safe last-room booking</t>
+        </is>
+      </c>
       <c r="J138" s="10" t="inlineStr">
         <is>
-          <t>a property with the default rules (30 nights, 24 hours)</t>
+          <t>one room of a type is left and several desks book it together</t>
         </is>
       </c>
       <c r="K138" s="10" t="inlineStr">
         <is>
-          <t>a manager saves new booking rules</t>
+          <t>all of them submit at the same moment</t>
         </is>
       </c>
       <c r="L138" s="10" t="inlineStr">
         <is>
-          <t>new bookings use them, bad values are refused with E_INVALID, and the change is audited with old and new values</t>
+          <t>exactly one booking succeeds, the rest get E_NO_AVAILABILITY, and nothing is oversold</t>
         </is>
       </c>
       <c r="M138" s="10" t="inlineStr">
         <is>
-          <t>set_booking_rules; Booking rules on Setup, Property</t>
+          <t>create_reservation, assert_available</t>
         </is>
       </c>
       <c r="N138" s="10" t="inlineStr">
         <is>
-          <t>42_booking_rules (9)</t>
+          <t>concurrency/last_room.sh (6)</t>
         </is>
       </c>
       <c r="O138" s="10" t="inlineStr">
@@ -11523,39 +11523,39 @@
       </c>
       <c r="P138" s="10" t="inlineStr">
         <is>
-          <t>Added 8 Oct 2026. The columns existed since the reservations release; this adds the screen and the function.</t>
+          <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>FO-014</t>
+          <t>SET-012</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>Front Office</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>/downtime</t>
+          <t>/setup/property</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>A printable downtime pack: arrivals due, in-house guests with balance, departures due, ten blank lines for new guests on paper, and a short paper routine. Staff print it when the internet or system is down.</t>
+          <t>A manager sets the longest stay (1 to 365 nights) and how long a tentative booking holds its room (1 to 720 hours) for each property.</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr">
         <is>
-          <t>BR-006</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G139" s="10" t="inlineStr">
@@ -11565,33 +11565,33 @@
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>fo.view</t>
+          <t>setup.property.edit</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr"/>
       <c r="J139" s="10" t="inlineStr">
         <is>
-          <t>a hotel with guests in house</t>
+          <t>a property with the default rules (30 nights, 24 hours)</t>
         </is>
       </c>
       <c r="K139" s="10" t="inlineStr">
         <is>
-          <t>a front desk user opens Downtime pack and prints</t>
+          <t>a manager saves new booking rules</t>
         </is>
       </c>
       <c r="L139" s="10" t="inlineStr">
         <is>
-          <t>the lists show room, guest, phone, departure and the folio balance from the database, with blank lines and the paper routine</t>
+          <t>new bookings use them, bad values are refused with E_INVALID, and the change is audited with old and new values</t>
         </is>
       </c>
       <c r="M139" s="10" t="inlineStr">
         <is>
-          <t>src/routes/_authenticated/_app/downtime.tsx</t>
+          <t>set_booking_rules; Booking rules on Setup, Property</t>
         </is>
       </c>
       <c r="N139" s="10" t="inlineStr">
         <is>
-          <t>browser: downtime-pack.spec (1)</t>
+          <t>42_booking_rules (9)</t>
         </is>
       </c>
       <c r="O139" s="10" t="inlineStr">
@@ -11601,87 +11601,165 @@
       </c>
       <c r="P139" s="10" t="inlineStr">
         <is>
-          <t>No database change. Reads v_arrivals, v_in_house and v_folio_balances. Added 8 Oct 2026.</t>
+          <t>Added 8 Oct 2026. The columns existed since the reservations release; this adds the screen and the function.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
+          <t>FO-014</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>Front Office</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>/downtime</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="inlineStr">
+        <is>
+          <t>A printable downtime pack: arrivals due, in-house guests with balance, departures due, ten blank lines for new guests on paper, and a short paper routine. Staff print it when the internet or system is down.</t>
+        </is>
+      </c>
+      <c r="E140" s="10" t="inlineStr">
+        <is>
+          <t>BR-006</t>
+        </is>
+      </c>
+      <c r="F140" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G140" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H140" s="10" t="inlineStr">
+        <is>
+          <t>fo.view</t>
+        </is>
+      </c>
+      <c r="I140" s="10" t="inlineStr"/>
+      <c r="J140" s="10" t="inlineStr">
+        <is>
+          <t>a hotel with guests in house</t>
+        </is>
+      </c>
+      <c r="K140" s="10" t="inlineStr">
+        <is>
+          <t>a front desk user opens Downtime pack and prints</t>
+        </is>
+      </c>
+      <c r="L140" s="10" t="inlineStr">
+        <is>
+          <t>the lists show room, guest, phone, departure and the folio balance from the database, with blank lines and the paper routine</t>
+        </is>
+      </c>
+      <c r="M140" s="10" t="inlineStr">
+        <is>
+          <t>src/routes/_authenticated/_app/downtime.tsx</t>
+        </is>
+      </c>
+      <c r="N140" s="10" t="inlineStr">
+        <is>
+          <t>browser: downtime-pack.spec (1)</t>
+        </is>
+      </c>
+      <c r="O140" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P140" s="10" t="inlineStr">
+        <is>
+          <t>No database change. Reads v_arrivals, v_in_house and v_folio_balances. Added 8 Oct 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
           <t>DAY-007</t>
         </is>
       </c>
-      <c r="B140" s="10" t="inlineStr">
+      <c r="B141" s="10" t="inlineStr">
         <is>
           <t>Business Date</t>
         </is>
       </c>
-      <c r="C140" s="10" t="inlineStr">
+      <c r="C141" s="10" t="inlineStr">
         <is>
           <t>Notifications bell</t>
         </is>
       </c>
-      <c r="D140" s="10" t="inlineStr">
+      <c r="D141" s="10" t="inlineStr">
         <is>
           <t>In the last hour before a property rolls its business date, if a cashier shift is still open, users who can run the night audit get one warning that night. The roll does not wait.</t>
         </is>
       </c>
-      <c r="E140" s="10" t="inlineStr">
+      <c r="E141" s="10" t="inlineStr">
         <is>
           <t>BR-016</t>
         </is>
       </c>
-      <c r="F140" s="10" t="inlineStr">
+      <c r="F141" s="10" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G140" s="10" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H140" s="10" t="inlineStr">
+      <c r="G141" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H141" s="10" t="inlineStr">
         <is>
           <t>fin.nightaudit.run</t>
         </is>
       </c>
-      <c r="I140" s="10" t="inlineStr">
+      <c r="I141" s="10" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="J140" s="10" t="inlineStr">
+      <c r="J141" s="10" t="inlineStr">
         <is>
           <t>a cashier shift is still open</t>
         </is>
       </c>
-      <c r="K140" s="10" t="inlineStr">
+      <c r="K141" s="10" t="inlineStr">
         <is>
           <t>the roll time is less than 60 minutes away</t>
         </is>
       </c>
-      <c r="L140" s="10" t="inlineStr">
+      <c r="L141" s="10" t="inlineStr">
         <is>
           <t>each night audit user gets one rollover_warning notification for that business date; none earlier, none after the roll time, none if no shift is open, none twice</t>
         </is>
       </c>
-      <c r="M140" s="10" t="inlineStr">
+      <c r="M141" s="10" t="inlineStr">
         <is>
           <t>app.warn_before_rollover; cron job rollover-warning</t>
         </is>
       </c>
-      <c r="N140" s="10" t="inlineStr">
+      <c r="N141" s="10" t="inlineStr">
         <is>
           <t>43_rollover_warning (9)</t>
         </is>
       </c>
-      <c r="O140" s="10" t="inlineStr">
+      <c r="O141" s="10" t="inlineStr">
         <is>
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P140" s="10" t="inlineStr">
+      <c r="P141" s="10" t="inlineStr">
         <is>
           <t>Added 8 Oct 2026. Warning only; the hard gate stays in R2 (DAY-005).</t>
         </is>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P141"/>
+  <dimension ref="A1:P142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6744,27 +6744,27 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>SVC-001</t>
+          <t>MNT-004</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>Guest Service</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>FO-01</t>
+          <t>MNT-02</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Guest requests are captured, assigned, progressed and completed.</t>
+          <t>Staff add up to 5 photos to a maintenance ticket from the phone. Photos are private, and uploads and views are audited by ids only.</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>BR-006</t>
+          <t>BR-012</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
@@ -6779,37 +6779,37 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>svc.request.create, svc.request.manage</t>
+          <t>mnt.ticket.create, mnt.ticket.work, mnt.view, mnt.ticket.assign</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
         <is>
-          <t>Workflow WF05</t>
+          <t>Rule: Private storage</t>
         </is>
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>a guest in house</t>
+          <t>an open ticket</t>
         </is>
       </c>
       <c r="K78" s="10" t="inlineStr">
         <is>
-          <t>staff log a request and it is assigned, started and completed</t>
+          <t>an attendant adds a photo, others view it, a supervisor removes it</t>
         </is>
       </c>
       <c r="L78" s="10" t="inlineStr">
         <is>
-          <t>it is tied to the guest's room and finishes once</t>
+          <t>only people tied to the ticket can add or view, the limit is 5, a removed photo is cleaned from storage, and a finished ticket takes no new photos</t>
         </is>
       </c>
       <c r="M78" s="10" t="inlineStr">
         <is>
-          <t>create_service_request, assign_service_request, start_service_request, complete_service_request</t>
+          <t>begin_ticket_photo_upload, finish_ticket_photo_upload, list_ticket_photos, open_ticket_photo, delete_ticket_photo</t>
         </is>
       </c>
       <c r="N78" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (3)</t>
+          <t>49_ticket_photos (17)</t>
         </is>
       </c>
       <c r="O78" s="10" t="inlineStr">
@@ -6822,7 +6822,7 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>SVC-002</t>
+          <t>SVC-001</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
@@ -6832,17 +6832,17 @@
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>FO-01, FIN-01</t>
+          <t>FO-01</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>A chargeable request posts its charge, with tax, to the folio when completed.</t>
+          <t>Guest requests are captured, assigned, progressed and completed.</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-006</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>svc.request.manage, fin.charge.post</t>
+          <t>svc.request.create, svc.request.manage</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
@@ -6867,22 +6867,22 @@
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>a chargeable laundry request of 3,000</t>
+          <t>a guest in house</t>
         </is>
       </c>
       <c r="K79" s="10" t="inlineStr">
         <is>
-          <t>it is completed</t>
+          <t>staff log a request and it is assigned, started and completed</t>
         </is>
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
-          <t>3,000 plus tax is posted once to the guest's folio</t>
+          <t>it is tied to the guest's room and finishes once</t>
         </is>
       </c>
       <c r="M79" s="10" t="inlineStr">
         <is>
-          <t>complete_service_request</t>
+          <t>create_service_request, assign_service_request, start_service_request, complete_service_request</t>
         </is>
       </c>
       <c r="N79" s="10" t="inlineStr">
@@ -6900,22 +6900,22 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>FIN-001</t>
+          <t>SVC-002</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Guest Service</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>FIN-01</t>
+          <t>FO-01, FIN-01</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Charges post with their tax lines; prices can include or exclude tax; the remainder of a rounding goes on the last tax line.</t>
+          <t>A chargeable request posts its charge, with tax, to the folio when completed.</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
@@ -6935,37 +6935,37 @@
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>fin.charge.post</t>
+          <t>svc.request.manage, fin.charge.post</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
-          <t>Rule: Business date</t>
+          <t>Workflow WF05</t>
         </is>
       </c>
       <c r="J80" s="10" t="inlineStr">
         <is>
-          <t>service charge 10% and VAT 7.5%</t>
+          <t>a chargeable laundry request of 3,000</t>
         </is>
       </c>
       <c r="K80" s="10" t="inlineStr">
         <is>
-          <t>a charge of 10,000 or an inclusive 11,825 is posted</t>
+          <t>it is completed</t>
         </is>
       </c>
       <c r="L80" s="10" t="inlineStr">
         <is>
-          <t>the folio owes 11,825 with a net of 10,000 either way</t>
+          <t>3,000 plus tax is posted once to the guest's folio</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr">
         <is>
-          <t>post_charge, compute_taxes, insert_with_tax</t>
+          <t>complete_service_request</t>
         </is>
       </c>
       <c r="N80" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (6)</t>
+          <t>17_more_features (3)</t>
         </is>
       </c>
       <c r="O80" s="10" t="inlineStr">
@@ -6978,7 +6978,7 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>FIN-002</t>
+          <t>FIN-001</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>Payments and deposits are recorded against a folio with a method; payments are taken outside the system in R1.</t>
+          <t>Charges post with their tax lines; prices can include or exclude tax; the remainder of a rounding goes on the last tax line.</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
@@ -7013,37 +7013,37 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>fin.payment.post, fin.deposit.take</t>
+          <t>fin.charge.post</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
         <is>
-          <t>Rule: Payments in R1</t>
+          <t>Rule: Business date</t>
         </is>
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>a folio with a balance</t>
+          <t>service charge 10% and VAT 7.5%</t>
         </is>
       </c>
       <c r="K81" s="10" t="inlineStr">
         <is>
-          <t>staff record a cash payment or a deposit</t>
+          <t>a charge of 10,000 or an inclusive 11,825 is posted</t>
         </is>
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>the balance falls; a role without the matching permission is refused</t>
+          <t>the folio owes 11,825 with a net of 10,000 either way</t>
         </is>
       </c>
       <c r="M81" s="10" t="inlineStr">
         <is>
-          <t>post_payment</t>
+          <t>post_charge, compute_taxes, insert_with_tax</t>
         </is>
       </c>
       <c r="N81" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>12_ledger (6)</t>
         </is>
       </c>
       <c r="O81" s="10" t="inlineStr">
@@ -7056,7 +7056,7 @@
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>FIN-003</t>
+          <t>FIN-002</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>Foreign-currency postings store the amount, currency, exchange rate and base amount.</t>
+          <t>Payments and deposits are recorded against a folio with a method; payments are taken outside the system in R1.</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
@@ -7091,32 +7091,32 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>fin.payment.post</t>
+          <t>fin.payment.post, fin.deposit.take</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
         <is>
-          <t>Rule: Multi-currency</t>
+          <t>Rule: Payments in R1</t>
         </is>
       </c>
       <c r="J82" s="10" t="inlineStr">
         <is>
-          <t>USD 10 at 1,500</t>
+          <t>a folio with a balance</t>
         </is>
       </c>
       <c r="K82" s="10" t="inlineStr">
         <is>
-          <t>it is posted</t>
+          <t>staff record a cash payment or a deposit</t>
         </is>
       </c>
       <c r="L82" s="10" t="inlineStr">
         <is>
-          <t>the row shows the rate and 15,000 in the base currency; the amount must respect the currency's decimals</t>
+          <t>the balance falls; a role without the matching permission is refused</t>
         </is>
       </c>
       <c r="M82" s="10" t="inlineStr">
         <is>
-          <t>insert_txn, fx_rate</t>
+          <t>post_payment</t>
         </is>
       </c>
       <c r="N82" s="10" t="inlineStr">
@@ -7134,7 +7134,7 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>FIN-004</t>
+          <t>FIN-003</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -7149,17 +7149,17 @@
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>A discount within the user's limit posts at once; above the limit it waits for an approver who is not the requester.</t>
+          <t>Foreign-currency postings store the amount, currency, exchange rate and base amount.</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>BR-015</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
@@ -7169,37 +7169,37 @@
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>fin.discount.apply, fin.discount.approve</t>
+          <t>fin.payment.post</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
         <is>
-          <t>Rule: Limits; Separation of duties</t>
+          <t>Rule: Multi-currency</t>
         </is>
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>a front desk limit of 5,000</t>
+          <t>USD 10 at 1,500</t>
         </is>
       </c>
       <c r="K83" s="10" t="inlineStr">
         <is>
-          <t>they apply 3,000 then 8,000</t>
+          <t>it is posted</t>
         </is>
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>the first posts; the second is pending, does not change the balance and can be approved or rejected (with a reason) by a manager</t>
+          <t>the row shows the rate and 15,000 in the base currency; the amount must respect the currency's decimals</t>
         </is>
       </c>
       <c r="M83" s="10" t="inlineStr">
         <is>
-          <t>apply_discount, decide_approval</t>
+          <t>insert_txn, fx_rate</t>
         </is>
       </c>
       <c r="N83" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (6)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O83" s="10" t="inlineStr">
@@ -7212,7 +7212,7 @@
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>FIN-005</t>
+          <t>FIN-004</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Adjustments, reversals and refunds always need a second person and stay within the approver's limit.</t>
+          <t>A discount within the user's limit posts at once; above the limit it waits for an approver who is not the requester.</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
@@ -7247,37 +7247,37 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>fin.adjust.post, fin.adjust.approve, fin.reverse.post, fin.refund.post, fin.refund.approve</t>
+          <t>fin.discount.apply, fin.discount.approve</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>Rule: Separation of duties, Limits</t>
+          <t>Rule: Limits; Separation of duties</t>
         </is>
       </c>
       <c r="J84" s="10" t="inlineStr">
         <is>
-          <t>an adjustment of 50,000 requested by a cashier</t>
+          <t>a front desk limit of 5,000</t>
         </is>
       </c>
       <c r="K84" s="10" t="inlineStr">
         <is>
-          <t>a manager with a 20,000 limit approves</t>
+          <t>they apply 3,000 then 8,000</t>
         </is>
       </c>
       <c r="L84" s="10" t="inlineStr">
         <is>
-          <t>it is refused with E_LIMIT; a senior approver can; nobody approves their own request</t>
+          <t>the first posts; the second is pending, does not change the balance and can be approved or rejected (with a reason) by a manager</t>
         </is>
       </c>
       <c r="M84" s="10" t="inlineStr">
         <is>
-          <t>request_adjustment, request_reversal, request_refund, decide_approval; check constraint approver_is_not_requester</t>
+          <t>apply_discount, decide_approval</t>
         </is>
       </c>
       <c r="N84" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>12_ledger (6)</t>
         </is>
       </c>
       <c r="O84" s="10" t="inlineStr">
@@ -7290,7 +7290,7 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>FIN-006</t>
+          <t>FIN-005</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
@@ -7305,12 +7305,12 @@
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>A posted transaction is never edited or deleted; corrections are linked reversal, adjustment or refund rows.</t>
+          <t>Adjustments, reversals and refunds always need a second person and stay within the approver's limit.</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>BR-014, BR-015</t>
+          <t>BR-015</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
@@ -7325,37 +7325,37 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fin.adjust.post, fin.adjust.approve, fin.reverse.post, fin.refund.post, fin.refund.approve</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
         <is>
-          <t>Rule: Immutability</t>
+          <t>Rule: Separation of duties, Limits</t>
         </is>
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>a posted charge</t>
+          <t>an adjustment of 50,000 requested by a cashier</t>
         </is>
       </c>
       <c r="K85" s="10" t="inlineStr">
         <is>
-          <t>anyone, including the database owner, changes or deletes it</t>
+          <t>a manager with a 20,000 limit approves</t>
         </is>
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>the change is refused with E_IMMUTABLE; a reversal posts a linked row (with its tax lines) and a charge reverses only once</t>
+          <t>it is refused with E_LIMIT; a senior approver can; nobody approves their own request</t>
         </is>
       </c>
       <c r="M85" s="10" t="inlineStr">
         <is>
-          <t>txn_guard triggers; request_reversal</t>
+          <t>request_adjustment, request_reversal, request_refund, decide_approval; check constraint approver_is_not_requester</t>
         </is>
       </c>
       <c r="N85" s="10" t="inlineStr">
         <is>
-          <t>10_security (1); 12_ledger (13)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O85" s="10" t="inlineStr">
@@ -7368,7 +7368,7 @@
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>FIN-007</t>
+          <t>FIN-006</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>A refund cannot exceed the credit on the folio.</t>
+          <t>A posted transaction is never edited or deleted; corrections are linked reversal, adjustment or refund rows.</t>
         </is>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>BR-015</t>
+          <t>BR-014, BR-015</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
@@ -7403,37 +7403,37 @@
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>fin.refund.post</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Immutability</t>
         </is>
       </c>
       <c r="J86" s="10" t="inlineStr">
         <is>
-          <t>a folio with a small credit</t>
+          <t>a posted charge</t>
         </is>
       </c>
       <c r="K86" s="10" t="inlineStr">
         <is>
-          <t>staff request a bigger refund</t>
+          <t>anyone, including the database owner, changes or deletes it</t>
         </is>
       </c>
       <c r="L86" s="10" t="inlineStr">
         <is>
-          <t>it is refused with E_REFUND_LIMIT; a refund within the credit is approved and pays out</t>
+          <t>the change is refused with E_IMMUTABLE; a reversal posts a linked row (with its tax lines) and a charge reverses only once</t>
         </is>
       </c>
       <c r="M86" s="10" t="inlineStr">
         <is>
-          <t>request_refund</t>
+          <t>txn_guard triggers; request_reversal</t>
         </is>
       </c>
       <c r="N86" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>10_security (1); 12_ledger (13)</t>
         </is>
       </c>
       <c r="O86" s="10" t="inlineStr">
@@ -7446,7 +7446,7 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>FIN-008</t>
+          <t>FIN-007</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Repeating the same request cannot double post (idempotency keys).</t>
+          <t>A refund cannot exceed the credit on the folio.</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-015</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
@@ -7481,32 +7481,32 @@
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
+          <t>fin.refund.post</t>
+        </is>
+      </c>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="10" t="inlineStr">
-        <is>
-          <t>Rule: Offline-ready design; A12</t>
-        </is>
-      </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>a charge posted with a key</t>
+          <t>a folio with a small credit</t>
         </is>
       </c>
       <c r="K87" s="10" t="inlineStr">
         <is>
-          <t>the same request arrives again</t>
+          <t>staff request a bigger refund</t>
         </is>
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>the second returns the first and the balance is unchanged</t>
+          <t>it is refused with E_REFUND_LIMIT; a refund within the credit is approved and pays out</t>
         </is>
       </c>
       <c r="M87" s="10" t="inlineStr">
         <is>
-          <t>idempotency_key unique per tenant</t>
+          <t>request_refund</t>
         </is>
       </c>
       <c r="N87" s="10" t="inlineStr">
@@ -7524,7 +7524,7 @@
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>FIN-009</t>
+          <t>FIN-008</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Move a posted charge, with its tax, to another folio of the same booking; revenue does not change.</t>
+          <t>Repeating the same request cannot double post (idempotency keys).</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
@@ -7559,37 +7559,37 @@
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>fin.folio.transfer</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Offline-ready design; A12</t>
         </is>
       </c>
       <c r="J88" s="10" t="inlineStr">
         <is>
-          <t>a charge on the guest folio</t>
+          <t>a charge posted with a key</t>
         </is>
       </c>
       <c r="K88" s="10" t="inlineStr">
         <is>
-          <t>a manager transfers it to a company folio</t>
+          <t>the same request arrives again</t>
         </is>
       </c>
       <c r="L88" s="10" t="inlineStr">
         <is>
-          <t>the target owes the charge and tax, the source is relieved, the total is unchanged and the charge moves once</t>
+          <t>the second returns the first and the balance is unchanged</t>
         </is>
       </c>
       <c r="M88" s="10" t="inlineStr">
         <is>
-          <t>transfer_transaction</t>
+          <t>idempotency_key unique per tenant</t>
         </is>
       </c>
       <c r="N88" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (6)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O88" s="10" t="inlineStr">
@@ -7602,7 +7602,7 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>FIN-010</t>
+          <t>FIN-009</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>Split folios per reservation.</t>
+          <t>Move a posted charge, with its tax, to another folio of the same booking; revenue does not change.</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>fin.folio.split</t>
+          <t>fin.folio.transfer</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
@@ -7647,27 +7647,27 @@
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
-          <t>a reservation</t>
+          <t>a charge on the guest folio</t>
         </is>
       </c>
       <c r="K89" s="10" t="inlineStr">
         <is>
-          <t>staff add a Company folio</t>
+          <t>a manager transfers it to a company folio</t>
         </is>
       </c>
       <c r="L89" s="10" t="inlineStr">
         <is>
-          <t>charges can be posted to either folio and check-out settles both</t>
+          <t>the target owes the charge and tax, the source is relieved, the total is unchanged and the charge moves once</t>
         </is>
       </c>
       <c r="M89" s="10" t="inlineStr">
         <is>
-          <t>split_folio</t>
+          <t>transfer_transaction</t>
         </is>
       </c>
       <c r="N89" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (1)</t>
+          <t>12_ledger (6)</t>
         </is>
       </c>
       <c r="O89" s="10" t="inlineStr">
@@ -7680,7 +7680,7 @@
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>FIN-011</t>
+          <t>FIN-010</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -7695,17 +7695,17 @@
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>A folio closes only at a zero balance and reopens only for the accountant with a reason; a closed folio takes no postings.</t>
+          <t>Split folios per reservation.</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>BR-013, BR-015</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
@@ -7715,37 +7715,37 @@
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>fin.invoice.issue, fin.folio.reopen</t>
+          <t>fin.folio.split</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
         <is>
-          <t>Rule: Reasons</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J90" s="10" t="inlineStr">
         <is>
-          <t>a settled folio</t>
+          <t>a reservation</t>
         </is>
       </c>
       <c r="K90" s="10" t="inlineStr">
         <is>
-          <t>it is closed and then a posting is attempted</t>
+          <t>staff add a Company folio</t>
         </is>
       </c>
       <c r="L90" s="10" t="inlineStr">
         <is>
-          <t>the posting is refused with E_FOLIO_CLOSED; reopening needs the permission and a reason and is audited</t>
+          <t>charges can be posted to either folio and check-out settles both</t>
         </is>
       </c>
       <c r="M90" s="10" t="inlineStr">
         <is>
-          <t>close_folio, reopen_folio</t>
+          <t>split_folio</t>
         </is>
       </c>
       <c r="N90" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (5)</t>
+          <t>12_ledger (1)</t>
         </is>
       </c>
       <c r="O90" s="10" t="inlineStr">
@@ -7758,7 +7758,7 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>FIN-012</t>
+          <t>FIN-011</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
@@ -7768,17 +7768,17 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>FIN-01, FO-03</t>
+          <t>FIN-01</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>Invoices and receipts are numbered documents built from posted rows; they cannot be changed once issued.</t>
+          <t>A folio closes only at a zero balance and reopens only for the accountant with a reason; a closed folio takes no postings.</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-013, BR-015</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>fin.invoice.issue</t>
+          <t>fin.invoice.issue, fin.folio.reopen</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Reasons</t>
         </is>
       </c>
       <c r="J91" s="10" t="inlineStr">
@@ -7808,22 +7808,22 @@
       </c>
       <c r="K91" s="10" t="inlineStr">
         <is>
-          <t>an invoice is issued</t>
+          <t>it is closed and then a posting is attempted</t>
         </is>
       </c>
       <c r="L91" s="10" t="inlineStr">
         <is>
-          <t>the total, tax and balance match the folio and the invoice cannot be edited; interim receipts have their own number series</t>
+          <t>the posting is refused with E_FOLIO_CLOSED; reopening needs the permission and a reason and is audited</t>
         </is>
       </c>
       <c r="M91" s="10" t="inlineStr">
         <is>
-          <t>issue_invoice</t>
+          <t>close_folio, reopen_folio</t>
         </is>
       </c>
       <c r="N91" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (4); 17_more_features (4)</t>
+          <t>12_ledger (5)</t>
         </is>
       </c>
       <c r="O91" s="10" t="inlineStr">
@@ -7836,7 +7836,7 @@
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>FIN-013</t>
+          <t>FIN-012</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>FIN-01</t>
+          <t>FIN-01, FO-03</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Balances are calculated from posted rows and never stored; pending approvals do not change them.</t>
+          <t>Invoices and receipts are numbered documents built from posted rows; they cannot be changed once issued.</t>
         </is>
       </c>
       <c r="E92" s="10" t="inlineStr">
@@ -7871,37 +7871,37 @@
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>fin.folio.view</t>
+          <t>fin.invoice.issue</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr">
         <is>
-          <t>Rule: Immutability</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J92" s="10" t="inlineStr">
         <is>
-          <t>a pending discount</t>
+          <t>a settled folio</t>
         </is>
       </c>
       <c r="K92" s="10" t="inlineStr">
         <is>
-          <t>the balance is read</t>
+          <t>an invoice is issued</t>
         </is>
       </c>
       <c r="L92" s="10" t="inlineStr">
         <is>
-          <t>it is unchanged until the approval posts</t>
+          <t>the total, tax and balance match the folio and the invoice cannot be edited; interim receipts have their own number series</t>
         </is>
       </c>
       <c r="M92" s="10" t="inlineStr">
         <is>
-          <t>v_folio_balances</t>
+          <t>issue_invoice</t>
         </is>
       </c>
       <c r="N92" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>12_ledger (4); 17_more_features (4)</t>
         </is>
       </c>
       <c r="O92" s="10" t="inlineStr">
@@ -7914,7 +7914,7 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>FIN-014</t>
+          <t>FIN-013</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>Every posting takes the open business date, and a past date is refused.</t>
+          <t>Balances are calculated from posted rows and never stored; pending approvals do not change them.</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
@@ -7949,37 +7949,37 @@
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fin.folio.view</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
         <is>
-          <t>Rule: Business date</t>
+          <t>Rule: Immutability</t>
         </is>
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
-          <t>a posting for a past date</t>
+          <t>a pending discount</t>
         </is>
       </c>
       <c r="K93" s="10" t="inlineStr">
         <is>
-          <t>it is inserted</t>
+          <t>the balance is read</t>
         </is>
       </c>
       <c r="L93" s="10" t="inlineStr">
         <is>
-          <t>it is refused with E_DATE</t>
+          <t>it is unchanged until the approval posts</t>
         </is>
       </c>
       <c r="M93" s="10" t="inlineStr">
         <is>
-          <t>txn_guard</t>
+          <t>v_folio_balances</t>
         </is>
       </c>
       <c r="N93" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2); 14_lifecycle (1); upgrade (2)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O93" s="10" t="inlineStr">
@@ -7992,7 +7992,7 @@
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>FIN-015</t>
+          <t>FIN-014</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Folio visibility follows the role: managers see all folios, a reservation officer sees only those of their own bookings.</t>
+          <t>Every posting takes the open business date, and a past date is refused.</t>
         </is>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>BR-017</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
@@ -8027,37 +8027,37 @@
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>fin.folio.view</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
         <is>
-          <t>Own-record scope</t>
+          <t>Rule: Business date</t>
         </is>
       </c>
       <c r="J94" s="10" t="inlineStr">
         <is>
-          <t>a reservation officer</t>
+          <t>a posting for a past date</t>
         </is>
       </c>
       <c r="K94" s="10" t="inlineStr">
         <is>
-          <t>they read a colleague's folio</t>
+          <t>it is inserted</t>
         </is>
       </c>
       <c r="L94" s="10" t="inlineStr">
         <is>
-          <t>they see nothing; they can still take a deposit</t>
+          <t>it is refused with E_DATE</t>
         </is>
       </c>
       <c r="M94" s="10" t="inlineStr">
         <is>
-          <t>can_see_folio</t>
+          <t>txn_guard</t>
         </is>
       </c>
       <c r="N94" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (6)</t>
+          <t>12_ledger (2); 14_lifecycle (1); upgrade (2)</t>
         </is>
       </c>
       <c r="O94" s="10" t="inlineStr">
@@ -8070,7 +8070,7 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>FIN-016</t>
+          <t>FIN-015</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
@@ -8080,17 +8080,17 @@
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>/cashier</t>
+          <t>FIN-01</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>Cashier shifts: a cashier opens a shift with a float, takes payments, counts each payment method at the end; the database works out expected and difference; a manager reconciles (never the closer). A hotel can require an open shift before payments.</t>
+          <t>Folio visibility follows the role: managers see all folios, a reservation officer sees only those of their own bookings.</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
-          <t>BR-016</t>
+          <t>BR-017</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
@@ -8105,74 +8105,70 @@
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>fin.shift.close, fin.shift.reconcile</t>
+          <t>fin.folio.view</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr">
         <is>
-          <t>A2; decision of 7 Oct 2026</t>
+          <t>Own-record scope</t>
         </is>
       </c>
       <c r="J95" s="10" t="inlineStr">
         <is>
-          <t>a cashier with an open shift who took cash and card payments</t>
+          <t>a reservation officer</t>
         </is>
       </c>
       <c r="K95" s="10" t="inlineStr">
         <is>
-          <t>they close the shift with their counts</t>
+          <t>they read a colleague's folio</t>
         </is>
       </c>
       <c r="L95" s="10" t="inlineStr">
         <is>
-          <t>the difference per method is worked out, a note is needed for a difference, and a manager reconciles it</t>
+          <t>they see nothing; they can still take a deposit</t>
         </is>
       </c>
       <c r="M95" s="10" t="inlineStr">
         <is>
-          <t>open_cashier_shift, close_cashier_shift, reconcile_cashier_shift, cashier_shift_summary, list_cashier_shifts, set_cashier_shift_required, stamp_cashier_shift</t>
+          <t>can_see_folio</t>
         </is>
       </c>
       <c r="N95" s="10" t="inlineStr">
         <is>
-          <t>34_cashier_shifts (45)</t>
+          <t>12_ledger (6)</t>
         </is>
       </c>
       <c r="O95" s="10" t="inlineStr">
         <is>
-          <t>Built+tested (database only)</t>
-        </is>
-      </c>
-      <c r="P95" s="10" t="inlineStr">
-        <is>
-          <t>Cashier shift page built (open, close with counts, review, reconcile). Not covered by a browser test yet. New permission fin.shift.reconcile goes to built-in roles only.</t>
-        </is>
-      </c>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>DAY-001</t>
+          <t>FIN-016</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Business Date</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>(system)</t>
+          <t>/cashier</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>The business date rolls automatically at each property's cut-off time.</t>
+          <t>Cashier shifts: a cashier opens a shift with a float, takes payments, counts each payment method at the end; the database works out expected and difference; a manager reconciles (never the closer). A hotel can require an open shift before payments.</t>
         </is>
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>BR-019</t>
+          <t>BR-016</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
@@ -8187,50 +8183,54 @@
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>audit.businessdate.view</t>
+          <t>fin.shift.close, fin.shift.reconcile</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr">
         <is>
-          <t>Rule: Business date; A2</t>
+          <t>A2; decision of 7 Oct 2026</t>
         </is>
       </c>
       <c r="J96" s="10" t="inlineStr">
         <is>
-          <t>a property whose cut-off has passed</t>
+          <t>a cashier with an open shift who took cash and card payments</t>
         </is>
       </c>
       <c r="K96" s="10" t="inlineStr">
         <is>
-          <t>the scheduler runs</t>
+          <t>they close the shift with their counts</t>
         </is>
       </c>
       <c r="L96" s="10" t="inlineStr">
         <is>
-          <t>the date advances one day, up to three days per run; the roll is logged</t>
+          <t>the difference per method is worked out, a note is needed for a difference, and a manager reconciles it</t>
         </is>
       </c>
       <c r="M96" s="10" t="inlineStr">
         <is>
-          <t>roll_business_date, run_due_rollovers (pg_cron)</t>
+          <t>open_cashier_shift, close_cashier_shift, reconcile_cashier_shift, cashier_shift_summary, list_cashier_shifts, set_cashier_shift_required, stamp_cashier_shift</t>
         </is>
       </c>
       <c r="N96" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (4); upgrade (5)</t>
+          <t>34_cashier_shifts (45)</t>
         </is>
       </c>
       <c r="O96" s="10" t="inlineStr">
         <is>
-          <t>Built+tested</t>
-        </is>
-      </c>
-      <c r="P96" s="10" t="inlineStr"/>
+          <t>Built+tested (database only)</t>
+        </is>
+      </c>
+      <c r="P96" s="10" t="inlineStr">
+        <is>
+          <t>Cashier shift page built (open, close with counts, review, reconcile). Not covered by a browser test yet. New permission fin.shift.reconcile goes to built-in roles only.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>DAY-002</t>
+          <t>DAY-001</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>At the roll, each guest in house is charged the night's room rate and tax exactly once.</t>
+          <t>The business date rolls automatically at each property's cut-off time.</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-019</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
@@ -8265,37 +8265,37 @@
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>(system)</t>
+          <t>audit.businessdate.view</t>
         </is>
       </c>
       <c r="I97" s="10" t="inlineStr">
         <is>
-          <t>Rule: Business date</t>
+          <t>Rule: Business date; A2</t>
         </is>
       </c>
       <c r="J97" s="10" t="inlineStr">
         <is>
-          <t>two guests in house</t>
+          <t>a property whose cut-off has passed</t>
         </is>
       </c>
       <c r="K97" s="10" t="inlineStr">
         <is>
-          <t>the roll runs</t>
+          <t>the scheduler runs</t>
         </is>
       </c>
       <c r="L97" s="10" t="inlineStr">
         <is>
-          <t>each folio gets one room charge for the closing date, with tax; running it again for the same night cannot repeat it</t>
+          <t>the date advances one day, up to three days per run; the roll is logged</t>
         </is>
       </c>
       <c r="M97" s="10" t="inlineStr">
         <is>
-          <t>roll_business_date; idempotency keys room:&lt;reservation&gt;:&lt;date&gt;</t>
+          <t>roll_business_date, run_due_rollovers (pg_cron)</t>
         </is>
       </c>
       <c r="N97" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (3)</t>
+          <t>14_lifecycle (4); upgrade (5)</t>
         </is>
       </c>
       <c r="O97" s="10" t="inlineStr">
@@ -8308,7 +8308,7 @@
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>DAY-003</t>
+          <t>DAY-002</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>A guest still in house past departure is charged and extended a night if the room allows; otherwise managers are told.</t>
+          <t>At the roll, each guest in house is charged the night's room rate and tax exactly once.</t>
         </is>
       </c>
       <c r="E98" s="10" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
@@ -8348,12 +8348,12 @@
       </c>
       <c r="I98" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rule: Business date</t>
         </is>
       </c>
       <c r="J98" s="10" t="inlineStr">
         <is>
-          <t>a guest due out today who is still in house</t>
+          <t>two guests in house</t>
         </is>
       </c>
       <c r="K98" s="10" t="inlineStr">
@@ -8363,17 +8363,17 @@
       </c>
       <c r="L98" s="10" t="inlineStr">
         <is>
-          <t>the departure moves one day and the night is charged</t>
+          <t>each folio gets one room charge for the closing date, with tax; running it again for the same night cannot repeat it</t>
         </is>
       </c>
       <c r="M98" s="10" t="inlineStr">
         <is>
-          <t>roll_business_date</t>
+          <t>roll_business_date; idempotency keys room:&lt;reservation&gt;:&lt;date&gt;</t>
         </is>
       </c>
       <c r="N98" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (12); upgrade (2)</t>
+          <t>14_lifecycle (3)</t>
         </is>
       </c>
       <c r="O98" s="10" t="inlineStr">
@@ -8386,7 +8386,7 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>DAY-004</t>
+          <t>DAY-003</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>A failed roll changes nothing and notifies managers; other properties are not blocked.</t>
+          <t>A guest still in house past departure is charged and extended a night if the room allows; otherwise managers are told.</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>audit.businessdate.view</t>
+          <t>(system)</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr">
@@ -8431,27 +8431,27 @@
       </c>
       <c r="J99" s="10" t="inlineStr">
         <is>
-          <t>a property whose roll fails</t>
+          <t>a guest due out today who is still in house</t>
         </is>
       </c>
       <c r="K99" s="10" t="inlineStr">
         <is>
-          <t>the scheduler runs</t>
+          <t>the roll runs</t>
         </is>
       </c>
       <c r="L99" s="10" t="inlineStr">
         <is>
-          <t>its date is unchanged and managers get a notification</t>
+          <t>the departure moves one day and the night is charged</t>
         </is>
       </c>
       <c r="M99" s="10" t="inlineStr">
         <is>
-          <t>run_due_rollovers</t>
+          <t>roll_business_date</t>
         </is>
       </c>
       <c r="N99" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (2)</t>
+          <t>14_lifecycle (12); upgrade (2)</t>
         </is>
       </c>
       <c r="O99" s="10" t="inlineStr">
@@ -8464,7 +8464,7 @@
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>DAY-005</t>
+          <t>DAY-004</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>/admin (Business date)</t>
+          <t>(system)</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Night audit flags list what is still open before the day closes: open cashier shifts (blocking), unreconciled differences, guests past departure, arrivals not checked in. The flags do not stop the date rolling yet.</t>
+          <t>A failed roll changes nothing and notifies managers; other properties are not blocked.</t>
         </is>
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>BR-016</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
@@ -8499,54 +8499,50 @@
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>fin.nightaudit.run</t>
+          <t>audit.businessdate.view</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J100" s="10" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>a property whose roll fails</t>
         </is>
       </c>
       <c r="K100" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>the scheduler runs</t>
         </is>
       </c>
       <c r="L100" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>its date is unchanged and managers get a notification</t>
         </is>
       </c>
       <c r="M100" s="10" t="inlineStr">
         <is>
-          <t>night_audit_flags</t>
+          <t>run_due_rollovers</t>
         </is>
       </c>
       <c r="N100" s="10" t="inlineStr">
         <is>
-          <t>34_cashier_shifts (7)</t>
+          <t>17_more_features (2)</t>
         </is>
       </c>
       <c r="O100" s="10" t="inlineStr">
         <is>
-          <t>Partly built (flags only)</t>
-        </is>
-      </c>
-      <c r="P100" s="10" t="inlineStr">
-        <is>
-          <t>Flags shown in Admin, Business date. The gate that stops the roll while a blocking flag is open is not built.</t>
-        </is>
-      </c>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P100" s="10" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>DAY-006</t>
+          <t>DAY-005</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
@@ -8556,17 +8552,17 @@
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>(system)</t>
+          <t>/admin (Business date)</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>A same-day arrival and departure: decide whether a night or day-use charge applies.</t>
+          <t>Night audit flags list what is still open before the day closes: open cashier shifts (blocking), unreconciled differences, guests past departure, arrivals not checked in. The flags do not stop the date rolling yet.</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-016</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
@@ -8581,79 +8577,79 @@
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>(decision)</t>
+          <t>fin.nightaudit.run</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr">
         <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J101" s="10" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="K101" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J101" s="10" t="inlineStr">
-        <is>
-          <t>a guest checks in and out on the same business date</t>
-        </is>
-      </c>
-      <c r="K101" s="10" t="inlineStr">
-        <is>
-          <t>they leave before the roll</t>
-        </is>
-      </c>
       <c r="L101" s="10" t="inlineStr">
         <is>
-          <t>today no room charge is made; the desk can post a manual charge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M101" s="10" t="inlineStr">
         <is>
-          <t>check_out</t>
+          <t>night_audit_flags</t>
         </is>
       </c>
       <c r="N101" s="10" t="inlineStr">
         <is>
-          <t>19_same_day (21); upgrade (2); browser: desk-journey</t>
+          <t>34_cashier_shifts (7)</t>
         </is>
       </c>
       <c r="O101" s="10" t="inlineStr">
         <is>
-          <t>Built+tested</t>
+          <t>Partly built (flags only)</t>
         </is>
       </c>
       <c r="P101" s="10" t="inlineStr">
         <is>
-          <t>Decided by Peter on 30 Sep 2026 (answer 5) and confirmed on 1 Oct 2026: same-day stays are charged one night; a manager can waive it with a reason.</t>
+          <t>Flags shown in Admin, Business date. The gate that stops the roll while a blocking flag is open is not built.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>RPT-001</t>
+          <t>DAY-006</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Business Date</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>DASH-01, REP-01</t>
+          <t>(system)</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Occupancy, ADR and RevPAR use one definition: rooms sold over rooms available (out-of-order rooms excluded), revenue net of tax.</t>
+          <t>A same-day arrival and departure: decide whether a night or day-use charge applies.</t>
         </is>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>BR-019</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
@@ -8663,37 +8659,37 @@
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>dash.view_exec, rep.ops.view</t>
+          <t>(decision)</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr">
         <is>
-          <t>KPI Dictionary</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J102" s="10" t="inlineStr">
         <is>
-          <t>a closed day</t>
+          <t>a guest checks in and out on the same business date</t>
         </is>
       </c>
       <c r="K102" s="10" t="inlineStr">
         <is>
-          <t>management opens the KPI view</t>
+          <t>they leave before the roll</t>
         </is>
       </c>
       <c r="L102" s="10" t="inlineStr">
         <is>
-          <t>occupancy, ADR and RevPAR equal sold, revenue and available as defined; tax is shown apart</t>
+          <t>today no room charge is made; the desk can post a manual charge</t>
         </is>
       </c>
       <c r="M102" s="10" t="inlineStr">
         <is>
-          <t>daily_stats, v_kpi_daily</t>
+          <t>check_out</t>
         </is>
       </c>
       <c r="N102" s="10" t="inlineStr">
         <is>
-          <t>14_lifecycle (4)</t>
+          <t>19_same_day (21); upgrade (2); browser: desk-journey</t>
         </is>
       </c>
       <c r="O102" s="10" t="inlineStr">
@@ -8701,12 +8697,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P102" s="10" t="inlineStr"/>
+      <c r="P102" s="10" t="inlineStr">
+        <is>
+          <t>Decided by Peter on 30 Sep 2026 (answer 5) and confirmed on 1 Oct 2026: same-day stays are charged one night; a manager can waive it with a reason.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>RPT-002</t>
+          <t>RPT-001</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
@@ -8716,17 +8716,17 @@
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>DASH-02</t>
+          <t>DASH-01, REP-01</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>Live operations views: arrivals, in-house, room board, housekeeping board.</t>
+          <t>Occupancy, ADR and RevPAR use one definition: rooms sold over rooms available (out-of-order rooms excluded), revenue net of tax.</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>BR-006, BR-019</t>
+          <t>BR-019</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
@@ -8741,37 +8741,37 @@
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>dash.view_ops</t>
+          <t>dash.view_exec, rep.ops.view</t>
         </is>
       </c>
       <c r="I103" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KPI Dictionary</t>
         </is>
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
-          <t>activity in the hotel</t>
+          <t>a closed day</t>
         </is>
       </c>
       <c r="K103" s="10" t="inlineStr">
         <is>
-          <t>staff open the operations dashboard</t>
+          <t>management opens the KPI view</t>
         </is>
       </c>
       <c r="L103" s="10" t="inlineStr">
         <is>
-          <t>the views return only rows the user may see</t>
+          <t>occupancy, ADR and RevPAR equal sold, revenue and available as defined; tax is shown apart</t>
         </is>
       </c>
       <c r="M103" s="10" t="inlineStr">
         <is>
-          <t>v_arrivals, v_in_house, v_room_board, v_hk_board</t>
+          <t>daily_stats, v_kpi_daily</t>
         </is>
       </c>
       <c r="N103" s="10" t="inlineStr">
         <is>
-          <t>29_untagged_rows (14)</t>
+          <t>14_lifecycle (4)</t>
         </is>
       </c>
       <c r="O103" s="10" t="inlineStr">
@@ -8784,7 +8784,7 @@
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>RPT-003</t>
+          <t>RPT-002</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -8794,17 +8794,17 @@
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>REP-01, REP-02</t>
+          <t>DASH-02</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Every reported figure traces to ledger rows or operational records.</t>
+          <t>Live operations views: arrivals, in-house, room board, housekeeping board.</t>
         </is>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>BR-020</t>
+          <t>BR-006, BR-019</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>rep.ops.view, rep.fin.view</t>
+          <t>dash.view_ops</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr">
@@ -8829,27 +8829,27 @@
       </c>
       <c r="J104" s="10" t="inlineStr">
         <is>
-          <t>a daily figure</t>
+          <t>activity in the hotel</t>
         </is>
       </c>
       <c r="K104" s="10" t="inlineStr">
         <is>
-          <t>an auditor recomputes it from folio_transactions</t>
+          <t>staff open the operations dashboard</t>
         </is>
       </c>
       <c r="L104" s="10" t="inlineStr">
         <is>
-          <t>the figures agree</t>
+          <t>the views return only rows the user may see</t>
         </is>
       </c>
       <c r="M104" s="10" t="inlineStr">
         <is>
-          <t>daily_stats computed from folio_transactions</t>
+          <t>v_arrivals, v_in_house, v_room_board, v_hk_board</t>
         </is>
       </c>
       <c r="N104" s="10" t="inlineStr">
         <is>
-          <t>29_untagged_rows (11)</t>
+          <t>29_untagged_rows (14)</t>
         </is>
       </c>
       <c r="O104" s="10" t="inlineStr">
@@ -8862,7 +8862,7 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>RPT-004</t>
+          <t>RPT-003</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>Report screens (occupancy trend, revenue by group, outstanding balances, cancellation and no-show rates).</t>
+          <t>Every reported figure traces to ledger rows or operational records.</t>
         </is>
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>BR-019</t>
+          <t>BR-020</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
@@ -8902,32 +8902,32 @@
       </c>
       <c r="I105" s="10" t="inlineStr">
         <is>
-          <t>KPI Dictionary</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
-          <t>a date range</t>
+          <t>a daily figure</t>
         </is>
       </c>
       <c r="K105" s="10" t="inlineStr">
         <is>
-          <t>a manager opens a report</t>
+          <t>an auditor recomputes it from folio_transactions</t>
         </is>
       </c>
       <c r="L105" s="10" t="inlineStr">
         <is>
-          <t>the numbers match the KPI definitions</t>
+          <t>the figures agree</t>
         </is>
       </c>
       <c r="M105" s="10" t="inlineStr">
         <is>
-          <t>Reports screen (src/routes/_authenticated/_app/reports.tsx) on report_* functions in the database: v_kpi_daily (occupancy, average rate, revenue per room), report_revenue_by_charge_code, report_outstanding_balances, report_payments, report_cancellation_rate (cancellations and no-shows), report_length_of_stay, report_balances_by_guest; finance reports need rpt.finance.view, operations reports rpt.operations.view</t>
+          <t>daily_stats computed from folio_transactions</t>
         </is>
       </c>
       <c r="N105" s="10" t="inlineStr">
         <is>
-          <t>29_untagged_rows (14)</t>
+          <t>29_untagged_rows (11)</t>
         </is>
       </c>
       <c r="O105" s="10" t="inlineStr">
@@ -8935,36 +8935,32 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P105" s="10" t="inlineStr">
-        <is>
-          <t>Reports screen: KPIs, revenue by charge code, outstanding balances, payments, cancellations and stay length, balances by guest, export.</t>
-        </is>
-      </c>
+      <c r="P105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>NFR-001</t>
+          <t>RPT-004</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>(all)</t>
+          <t>REP-01, REP-02</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Every table has row-level security and tenant_id; security definer functions pin their search path.</t>
+          <t>Report screens (occupancy trend, revenue by group, outstanding balances, cancellation and no-show rates).</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>BR-017</t>
+          <t>BR-019</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
@@ -8979,37 +8975,37 @@
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>rep.ops.view, rep.fin.view</t>
         </is>
       </c>
       <c r="I106" s="10" t="inlineStr">
         <is>
-          <t>Rule: Tenant isolation</t>
+          <t>KPI Dictionary</t>
         </is>
       </c>
       <c r="J106" s="10" t="inlineStr">
         <is>
-          <t>a migration adds a table or function</t>
+          <t>a date range</t>
         </is>
       </c>
       <c r="K106" s="10" t="inlineStr">
         <is>
-          <t>the test suite runs</t>
+          <t>a manager opens a report</t>
         </is>
       </c>
       <c r="L106" s="10" t="inlineStr">
         <is>
-          <t>it fails if RLS, tenant_id or search_path is missing</t>
+          <t>the numbers match the KPI definitions</t>
         </is>
       </c>
       <c r="M106" s="10" t="inlineStr">
         <is>
-          <t>structure tests</t>
+          <t>Reports screen (src/routes/_authenticated/_app/reports.tsx) on report_* functions in the database: v_kpi_daily (occupancy, average rate, revenue per room), report_revenue_by_charge_code, report_outstanding_balances, report_payments, report_cancellation_rate (cancellations and no-shows), report_length_of_stay, report_balances_by_guest; finance reports need rpt.finance.view, operations reports rpt.operations.view</t>
         </is>
       </c>
       <c r="N106" s="10" t="inlineStr">
         <is>
-          <t>10_security (3)</t>
+          <t>29_untagged_rows (14)</t>
         </is>
       </c>
       <c r="O106" s="10" t="inlineStr">
@@ -9017,12 +9013,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P106" s="10" t="inlineStr"/>
+      <c r="P106" s="10" t="inlineStr">
+        <is>
+          <t>Reports screen: KPIs, revenue by charge code, outstanding balances, payments, cancellations and stay length, balances by guest, export.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>NFR-002</t>
+          <t>NFR-001</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>The browser can write directly only to plain configuration tables; ledger, reservations, stays, tasks and blocks change only through functions.</t>
+          <t>Every table has row-level security and tenant_id; security definer functions pin their search path.</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>BR-014, BR-017</t>
+          <t>BR-017</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
@@ -9062,32 +9062,32 @@
       </c>
       <c r="I107" s="10" t="inlineStr">
         <is>
-          <t>Rule: Immutability</t>
+          <t>Rule: Tenant isolation</t>
         </is>
       </c>
       <c r="J107" s="10" t="inlineStr">
         <is>
-          <t>any user</t>
+          <t>a migration adds a table or function</t>
         </is>
       </c>
       <c r="K107" s="10" t="inlineStr">
         <is>
-          <t>they write to a ledger or state table</t>
+          <t>the test suite runs</t>
         </is>
       </c>
       <c r="L107" s="10" t="inlineStr">
         <is>
-          <t>permission denied; the list of directly writable tables is asserted by a test</t>
+          <t>it fails if RLS, tenant_id or search_path is missing</t>
         </is>
       </c>
       <c r="M107" s="10" t="inlineStr">
         <is>
-          <t>20260928001100_grants.sql</t>
+          <t>structure tests</t>
         </is>
       </c>
       <c r="N107" s="10" t="inlineStr">
         <is>
-          <t>10_security (2)</t>
+          <t>10_security (3)</t>
         </is>
       </c>
       <c r="O107" s="10" t="inlineStr">
@@ -9100,7 +9100,7 @@
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>NFR-003</t>
+          <t>NFR-002</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
@@ -9115,17 +9115,17 @@
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Create actions accept client-generated ids and idempotency keys so an offline queue can be added later.</t>
+          <t>The browser can write directly only to plain configuration tables; ledger, reservations, stays, tasks and blocks change only through functions.</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>BR-014, BR-017</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
@@ -9140,32 +9140,32 @@
       </c>
       <c r="I108" s="10" t="inlineStr">
         <is>
-          <t>Rule: Offline-ready design; A12</t>
+          <t>Rule: Immutability</t>
         </is>
       </c>
       <c r="J108" s="10" t="inlineStr">
         <is>
-          <t>a repeated create request</t>
+          <t>any user</t>
         </is>
       </c>
       <c r="K108" s="10" t="inlineStr">
         <is>
-          <t>it arrives twice</t>
+          <t>they write to a ledger or state table</t>
         </is>
       </c>
       <c r="L108" s="10" t="inlineStr">
         <is>
-          <t>only one record exists</t>
+          <t>permission denied; the list of directly writable tables is asserted by a test</t>
         </is>
       </c>
       <c r="M108" s="10" t="inlineStr">
         <is>
-          <t>idempotency keys; client ids allowed on insert</t>
+          <t>20260928001100_grants.sql</t>
         </is>
       </c>
       <c r="N108" s="10" t="inlineStr">
         <is>
-          <t>13_reservations (1)</t>
+          <t>10_security (2)</t>
         </is>
       </c>
       <c r="O108" s="10" t="inlineStr">
@@ -9178,7 +9178,7 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>NFR-004</t>
+          <t>NFR-003</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
@@ -9193,17 +9193,17 @@
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>Money uses fixed decimals per currency (naira 2, CFA franc 0), never floating point.</t>
+          <t>Create actions accept client-generated ids and idempotency keys so an offline queue can be added later.</t>
         </is>
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>BR-013</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
@@ -9218,32 +9218,32 @@
       </c>
       <c r="I109" s="10" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>Rule: Offline-ready design; A12</t>
         </is>
       </c>
       <c r="J109" s="10" t="inlineStr">
         <is>
-          <t>an amount with too many decimals</t>
+          <t>a repeated create request</t>
         </is>
       </c>
       <c r="K109" s="10" t="inlineStr">
         <is>
-          <t>it is posted</t>
+          <t>it arrives twice</t>
         </is>
       </c>
       <c r="L109" s="10" t="inlineStr">
         <is>
-          <t>it is refused with E_PRECISION</t>
+          <t>only one record exists</t>
         </is>
       </c>
       <c r="M109" s="10" t="inlineStr">
         <is>
-          <t>numeric(20,4), currencies.decimals</t>
+          <t>idempotency keys; client ids allowed on insert</t>
         </is>
       </c>
       <c r="N109" s="10" t="inlineStr">
         <is>
-          <t>12_ledger (2)</t>
+          <t>13_reservations (1)</t>
         </is>
       </c>
       <c r="O109" s="10" t="inlineStr">
@@ -9256,7 +9256,7 @@
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>NFR-005</t>
+          <t>NFR-004</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Business date and cut-off follow the property's timezone.</t>
+          <t>Money uses fixed decimals per currency (naira 2, CFA franc 0), never floating point.</t>
         </is>
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>BR-019</t>
+          <t>BR-013</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
@@ -9296,32 +9296,32 @@
       </c>
       <c r="I110" s="10" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="J110" s="10" t="inlineStr">
         <is>
-          <t>a property in Lagos</t>
+          <t>an amount with too many decimals</t>
         </is>
       </c>
       <c r="K110" s="10" t="inlineStr">
         <is>
-          <t>it is created just before or after cut-off</t>
+          <t>it is posted</t>
         </is>
       </c>
       <c r="L110" s="10" t="inlineStr">
         <is>
-          <t>the business date is the local hotel day, not the server's day</t>
+          <t>it is refused with E_PRECISION</t>
         </is>
       </c>
       <c r="M110" s="10" t="inlineStr">
         <is>
-          <t>local_business_date</t>
+          <t>numeric(20,4), currencies.decimals</t>
         </is>
       </c>
       <c r="N110" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (1)</t>
+          <t>12_ledger (2)</t>
         </is>
       </c>
       <c r="O110" s="10" t="inlineStr">
@@ -9334,72 +9334,72 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>DAY-006b</t>
+          <t>NFR-005</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>Business Date</t>
+          <t>Non-functional</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>/checkout/$id</t>
+          <t>(all)</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>A guest leaving on the arrival day is charged one night at check-out; a manager can waive it with a reason.</t>
+          <t>Business date and cut-off follow the property's timezone.</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
+          <t>BR-019</t>
+        </is>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G111" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H111" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F111" s="10" t="inlineStr">
-        <is>
-          <t>Must</t>
-        </is>
-      </c>
-      <c r="G111" s="10" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H111" s="10" t="inlineStr">
-        <is>
-          <t>fo.checkout; fo.sameday.waive</t>
-        </is>
-      </c>
       <c r="I111" s="10" t="inlineStr">
         <is>
-          <t>Rule: DAY-006 decision</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
-          <t>an in-house guest whose arrival and departure are today</t>
+          <t>a property in Lagos</t>
         </is>
       </c>
       <c r="K111" s="10" t="inlineStr">
         <is>
-          <t>they are checked out</t>
+          <t>it is created just before or after cut-off</t>
         </is>
       </c>
       <c r="L111" s="10" t="inlineStr">
         <is>
-          <t>one night (with tax) is posted unless a manager waives it with a reason</t>
+          <t>the business date is the local hotel day, not the server's day</t>
         </is>
       </c>
       <c r="M111" s="10" t="inlineStr">
         <is>
-          <t>preview_check_out_charge, check_out</t>
+          <t>local_business_date</t>
         </is>
       </c>
       <c r="N111" s="10" t="inlineStr">
         <is>
-          <t>21_same_day_checkout (28); upgrade (2)</t>
+          <t>17_more_features (1)</t>
         </is>
       </c>
       <c r="O111" s="10" t="inlineStr">
@@ -9412,22 +9412,22 @@
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>FIN-017</t>
+          <t>DAY-006b</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Business Date</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>/folios/$id</t>
+          <t>/checkout/$id</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>A payment matching one on the same bill (amount, currency, method, reference) within 10 minutes is refused unless the cashier confirms it with a reason; the refusal names the earlier payment and the confirmation is audited.</t>
+          <t>A guest leaving on the arrival day is charged one night at check-out; a manager can waive it with a reason.</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
@@ -9447,37 +9447,37 @@
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>fin.payment.post</t>
+          <t>fo.checkout; fo.sameday.waive</t>
         </is>
       </c>
       <c r="I112" s="10" t="inlineStr">
         <is>
-          <t>Setting duplicate_payment_window_minutes</t>
+          <t>Rule: DAY-006 decision</t>
         </is>
       </c>
       <c r="J112" s="10" t="inlineStr">
         <is>
-          <t>a payment recorded on a bill a few minutes ago</t>
+          <t>an in-house guest whose arrival and departure are today</t>
         </is>
       </c>
       <c r="K112" s="10" t="inlineStr">
         <is>
-          <t>the same payment is recorded again with a new key</t>
+          <t>they are checked out</t>
         </is>
       </c>
       <c r="L112" s="10" t="inlineStr">
         <is>
-          <t>it is refused naming the earlier payment; with a reason it is recorded and audited as payment_duplicate_confirmed</t>
+          <t>one night (with tax) is posted unless a manager waives it with a reason</t>
         </is>
       </c>
       <c r="M112" s="10" t="inlineStr">
         <is>
-          <t>post_payment</t>
+          <t>preview_check_out_charge, check_out</t>
         </is>
       </c>
       <c r="N112" s="10" t="inlineStr">
         <is>
-          <t>25_duplicate_payments (20); browser: duplicate-payment</t>
+          <t>21_same_day_checkout (28); upgrade (2)</t>
         </is>
       </c>
       <c r="O112" s="10" t="inlineStr">
@@ -9490,7 +9490,7 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>FIN-018</t>
+          <t>FIN-017</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -9500,12 +9500,12 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>/setup/taxes</t>
+          <t>/folios/$id</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>A hotel can match the tax method of its existing folio using setup alone: each tax on the room price only, food and drink untaxed. A sample bill of 45,000 room plus 12,001 bar totals 67,126.</t>
+          <t>A payment matching one on the same bill (amount, currency, method, reference) within 10 minutes is refused unless the cashier confirms it with a reason; the refusal names the earlier payment and the confirmation is audited.</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
@@ -9525,37 +9525,37 @@
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>setup.tax.manage</t>
+          <t>fin.payment.post</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr">
         <is>
-          <t>Tax rates compounds_on_previous; charge code is_taxable</t>
+          <t>Setting duplicate_payment_window_minutes</t>
         </is>
       </c>
       <c r="J113" s="10" t="inlineStr">
         <is>
-          <t>a property with service charge 10%, VAT 7.5% and state tax 5%, none compounding, and a non-taxable bar code</t>
+          <t>a payment recorded on a bill a few minutes ago</t>
         </is>
       </c>
       <c r="K113" s="10" t="inlineStr">
         <is>
-          <t>a room charge of 45,000 and a bar charge of 12,001 are posted</t>
+          <t>the same payment is recorded again with a new key</t>
         </is>
       </c>
       <c r="L113" s="10" t="inlineStr">
         <is>
-          <t>the taxes are 4,500, 3,375 and 2,250, the bar has no tax and the bill is 67,126</t>
+          <t>it is refused naming the earlier payment; with a reason it is recorded and audited as payment_duplicate_confirmed</t>
         </is>
       </c>
       <c r="M113" s="10" t="inlineStr">
         <is>
-          <t>save_tax_rate, save_charge_code, post_charge</t>
+          <t>post_payment</t>
         </is>
       </c>
       <c r="N113" s="10" t="inlineStr">
         <is>
-          <t>44_folio_sample_method (5)</t>
+          <t>25_duplicate_payments (20); browser: duplicate-payment</t>
         </is>
       </c>
       <c r="O113" s="10" t="inlineStr">
@@ -9563,16 +9563,12 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P113" s="10" t="inlineStr">
-        <is>
-          <t>Method only; the accountant still signs off the rates (A11)</t>
-        </is>
-      </c>
+      <c r="P113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>FIN-019</t>
+          <t>FIN-018</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -9582,12 +9578,12 @@
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>/invoices/$id</t>
+          <t>/setup/taxes</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>An invoice shows the check-in time, number of guests, number of nights, a total for each day, and the receipt reference of each charge. Invoices issued earlier stay as issued.</t>
+          <t>A hotel can match the tax method of its existing folio using setup alone: each tax on the room price only, food and drink untaxed. A sample bill of 45,000 room plus 12,001 bar totals 67,126.</t>
         </is>
       </c>
       <c r="E114" s="10" t="inlineStr">
@@ -9597,7 +9593,7 @@
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
@@ -9607,37 +9603,37 @@
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>fin.invoice.issue</t>
+          <t>setup.tax.manage</t>
         </is>
       </c>
       <c r="I114" s="10" t="inlineStr">
         <is>
-          <t>Invoice snapshot is insert-only</t>
+          <t>Tax rates compounds_on_previous; charge code is_taxable</t>
         </is>
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>a stay with charges, one with a receipt reference</t>
+          <t>a property with service charge 10%, VAT 7.5% and state tax 5%, none compounding, and a non-taxable bar code</t>
         </is>
       </c>
       <c r="K114" s="10" t="inlineStr">
         <is>
-          <t>an invoice is issued</t>
+          <t>a room charge of 45,000 and a bar charge of 12,001 are posted</t>
         </is>
       </c>
       <c r="L114" s="10" t="inlineStr">
         <is>
-          <t>the invoice shows nights, guests, check-in time, a total per day and the receipt reference, all worked out in the database</t>
+          <t>the taxes are 4,500, 3,375 and 2,250, the bar has no tax and the bill is 67,126</t>
         </is>
       </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
-          <t>issue_invoice</t>
+          <t>save_tax_rate, save_charge_code, post_charge</t>
         </is>
       </c>
       <c r="N114" s="10" t="inlineStr">
         <is>
-          <t>45_invoice_layout (6)</t>
+          <t>44_folio_sample_method (5)</t>
         </is>
       </c>
       <c r="O114" s="10" t="inlineStr">
@@ -9647,14 +9643,14 @@
       </c>
       <c r="P114" s="10" t="inlineStr">
         <is>
-          <t>Day totals and fields are stored in the invoice header when it is issued</t>
+          <t>Method only; the accountant still signs off the rates (A11)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>FIN-020</t>
+          <t>FIN-019</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -9669,7 +9665,7 @@
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>Invoice and interim invoice numbers carry the year and month of the hotel business date, then a count that restarts each month with no gaps (INV-202610-000001, INT-202610-000001). Invoices already issued keep their numbers.</t>
+          <t>An invoice shows the check-in time, number of guests, number of nights, a total for each day, and the receipt reference of each charge. Invoices issued earlier stay as issued.</t>
         </is>
       </c>
       <c r="E115" s="10" t="inlineStr">
@@ -9694,32 +9690,32 @@
       </c>
       <c r="I115" s="10" t="inlineStr">
         <is>
-          <t>document_sequences period_key</t>
+          <t>Invoice snapshot is insert-only</t>
         </is>
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>a hotel with invoices issued in one month</t>
+          <t>a stay with charges, one with a receipt reference</t>
         </is>
       </c>
       <c r="K115" s="10" t="inlineStr">
         <is>
-          <t>an invoice is issued in the next month</t>
+          <t>an invoice is issued</t>
         </is>
       </c>
       <c r="L115" s="10" t="inlineStr">
         <is>
-          <t>its number starts with the new year and month and the count restarts at 1; the INT and INV series stay separate; reservation and folio numbers are unchanged</t>
+          <t>the invoice shows nights, guests, check-in time, a total per day and the receipt reference, all worked out in the database</t>
         </is>
       </c>
       <c r="M115" s="10" t="inlineStr">
         <is>
-          <t>next_document_number, issue_invoice</t>
+          <t>issue_invoice</t>
         </is>
       </c>
       <c r="N115" s="10" t="inlineStr">
         <is>
-          <t>46_invoice_number_month (8); 17_more_features</t>
+          <t>45_invoice_layout (6)</t>
         </is>
       </c>
       <c r="O115" s="10" t="inlineStr">
@@ -9729,29 +9725,29 @@
       </c>
       <c r="P115" s="10" t="inlineStr">
         <is>
-          <t>Month comes from the business date, not the clock. No hotel code in the number yet.</t>
+          <t>Day totals and fields are stored in the invoice header when it is issued</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>GST-007</t>
+          <t>FIN-020</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>Guests</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>/guests/$id; check-in; walk-in</t>
+          <t>/invoices/$id</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>A photo or scan of an ID document is kept in private storage, shrunk and stripped of hidden data in the browser, and opened only through a 60-second link.</t>
+          <t>Invoice and interim invoice numbers carry the year and month of the hotel business date, then a count that restarts each month with no gaps (INV-202610-000001, INT-202610-000001). Invoices already issued keep their numbers.</t>
         </is>
       </c>
       <c r="E116" s="10" t="inlineStr">
@@ -9761,7 +9757,7 @@
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G116" s="10" t="inlineStr">
@@ -9771,37 +9767,37 @@
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>guest.document.file.upload / view / delete</t>
+          <t>fin.invoice.issue</t>
         </is>
       </c>
       <c r="I116" s="10" t="inlineStr">
         <is>
-          <t>SET-009 switch</t>
+          <t>document_sequences period_key</t>
         </is>
       </c>
       <c r="J116" s="10" t="inlineStr">
         <is>
-          <t>a hotel that allows ID photos</t>
+          <t>a hotel with invoices issued in one month</t>
         </is>
       </c>
       <c r="K116" s="10" t="inlineStr">
         <is>
-          <t>front desk adds an ID photo</t>
+          <t>an invoice is issued in the next month</t>
         </is>
       </c>
       <c r="L116" s="10" t="inlineStr">
         <is>
-          <t>it is stored privately and opens only through a short-lived link</t>
+          <t>its number starts with the new year and month and the count restarts at 1; the INT and INV series stay separate; reservation and folio numbers are unchanged</t>
         </is>
       </c>
       <c r="M116" s="10" t="inlineStr">
         <is>
-          <t>begin_id_photo_upload, finish_id_photo_upload, open_id_photo</t>
+          <t>next_document_number, issue_invoice</t>
         </is>
       </c>
       <c r="N116" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (30)</t>
+          <t>46_invoice_number_month (8); 17_more_features</t>
         </is>
       </c>
       <c r="O116" s="10" t="inlineStr">
@@ -9809,12 +9805,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P116" s="10" t="inlineStr"/>
+      <c r="P116" s="10" t="inlineStr">
+        <is>
+          <t>Month comes from the business date, not the clock. No hotel code in the number yet.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>GST-008</t>
+          <t>GST-007</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
@@ -9824,12 +9824,12 @@
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>/guests/$id</t>
+          <t>/guests/$id; check-in; walk-in</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>Every upload, view and deletion of an ID photo is audited with ids only, no personal data.</t>
+          <t>A photo or scan of an ID document is kept in private storage, shrunk and stripped of hidden data in the browser, and opened only through a 60-second link.</t>
         </is>
       </c>
       <c r="E117" s="10" t="inlineStr">
@@ -9849,37 +9849,37 @@
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>guest.document.file.upload / view / delete</t>
         </is>
       </c>
       <c r="I117" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SET-009 switch</t>
         </is>
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>an ID photo</t>
+          <t>a hotel that allows ID photos</t>
         </is>
       </c>
       <c r="K117" s="10" t="inlineStr">
         <is>
-          <t>it is uploaded, opened or deleted</t>
+          <t>front desk adds an ID photo</t>
         </is>
       </c>
       <c r="L117" s="10" t="inlineStr">
         <is>
-          <t>an audit row records who and which file, with no personal data</t>
+          <t>it is stored privately and opens only through a short-lived link</t>
         </is>
       </c>
       <c r="M117" s="10" t="inlineStr">
         <is>
-          <t>app.audit_id_photo</t>
+          <t>begin_id_photo_upload, finish_id_photo_upload, open_id_photo</t>
         </is>
       </c>
       <c r="N117" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (9)</t>
+          <t>24_id_photos (30)</t>
         </is>
       </c>
       <c r="O117" s="10" t="inlineStr">
@@ -9892,7 +9892,7 @@
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>GST-009</t>
+          <t>GST-008</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>ID photos are removed from storage when the guest is anonymised or the document is removed, and move with the guest when two profiles are merged.</t>
+          <t>Every upload, view and deletion of an ID photo is audited with ids only, no personal data.</t>
         </is>
       </c>
       <c r="E118" s="10" t="inlineStr">
@@ -9937,27 +9937,27 @@
       </c>
       <c r="J118" s="10" t="inlineStr">
         <is>
-          <t>a guest with ID photos</t>
+          <t>an ID photo</t>
         </is>
       </c>
       <c r="K118" s="10" t="inlineStr">
         <is>
-          <t>the guest is anonymised, the document removed, or the profile merged</t>
+          <t>it is uploaded, opened or deleted</t>
         </is>
       </c>
       <c r="L118" s="10" t="inlineStr">
         <is>
-          <t>the files are removed, or move to the kept profile</t>
+          <t>an audit row records who and which file, with no personal data</t>
         </is>
       </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
-          <t>anonymise_guest, merge_guests, delete_id_photo</t>
+          <t>app.audit_id_photo</t>
         </is>
       </c>
       <c r="N118" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (4)</t>
+          <t>24_id_photos (9)</t>
         </is>
       </c>
       <c r="O118" s="10" t="inlineStr">
@@ -9970,7 +9970,7 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>GST-010</t>
+          <t>GST-009</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>(daily clean-up)</t>
+          <t>/guests/$id</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>ID photos are deleted automatically a set number of months (one setting, now 12) after the guest's last check-out, unless the guest has a booking that is not over.</t>
+          <t>ID photos are removed from storage when the guest is anonymised or the document is removed, and move with the guest when two profiles are merged.</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr">
@@ -10010,32 +10010,32 @@
       </c>
       <c r="I119" s="10" t="inlineStr">
         <is>
-          <t>Setting id_photo_keep_months; daily cron</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
-          <t>a guest whose last check-out was more than the keep period ago</t>
+          <t>a guest with ID photos</t>
         </is>
       </c>
       <c r="K119" s="10" t="inlineStr">
         <is>
-          <t>the daily clean-up runs</t>
+          <t>the guest is anonymised, the document removed, or the profile merged</t>
         </is>
       </c>
       <c r="L119" s="10" t="inlineStr">
         <is>
-          <t>their ID photos are deleted</t>
+          <t>the files are removed, or move to the kept profile</t>
         </is>
       </c>
       <c r="M119" s="10" t="inlineStr">
         <is>
-          <t>/api/cron/id-photo-cleanup</t>
+          <t>anonymise_guest, merge_guests, delete_id_photo</t>
         </is>
       </c>
       <c r="N119" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (5)</t>
+          <t>24_id_photos (4)</t>
         </is>
       </c>
       <c r="O119" s="10" t="inlineStr">
@@ -10048,22 +10048,22 @@
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>ROOM-005</t>
+          <t>GST-010</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>Rooms</t>
+          <t>Guests</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>/rooms</t>
+          <t>(daily clean-up)</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>Rooms are added one at a time or several by number or by name, with a preview; labels are free text up to 30 characters, unique per hotel ignoring case and extra spaces, shown as typed and sorted in natural order.</t>
+          <t>ID photos are deleted automatically a set number of months (one setting, now 12) after the guest's last check-out, unless the guest has a booking that is not over.</t>
         </is>
       </c>
       <c r="E120" s="10" t="inlineStr">
@@ -10083,37 +10083,37 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>setup.room.edit</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Setting id_photo_keep_months; daily cron</t>
         </is>
       </c>
       <c r="J120" s="10" t="inlineStr">
         <is>
-          <t>an administrator on the Rooms page</t>
+          <t>a guest whose last check-out was more than the keep period ago</t>
         </is>
       </c>
       <c r="K120" s="10" t="inlineStr">
         <is>
-          <t>they add rooms by number range or by names</t>
+          <t>the daily clean-up runs</t>
         </is>
       </c>
       <c r="L120" s="10" t="inlineStr">
         <is>
-          <t>valid new rooms are created, duplicates skipped and invalid names shown</t>
+          <t>their ID photos are deleted</t>
         </is>
       </c>
       <c r="M120" s="10" t="inlineStr">
         <is>
-          <t>add_rooms_range, add_rooms_named, save_room</t>
+          <t>/api/cron/id-photo-cleanup</t>
         </is>
       </c>
       <c r="N120" s="10" t="inlineStr">
         <is>
-          <t>23_room_labels (46); 26_small_fixes (1); browser: rooms-add</t>
+          <t>24_id_photos (5)</t>
         </is>
       </c>
       <c r="O120" s="10" t="inlineStr">
@@ -10126,22 +10126,22 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>SET-009</t>
+          <t>ROOM-005</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Rooms</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>/setup/property</t>
+          <t>/rooms</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>Per hotel: "Allow ID photos" (off by default) and "Require ID photo at check-in" (only when allowed). While Allow is off, uploading and opening ID photos are refused.</t>
+          <t>Rooms are added one at a time or several by number or by name, with a preview; labels are free text up to 30 characters, unique per hotel ignoring case and extra spaces, shown as typed and sorted in natural order.</t>
         </is>
       </c>
       <c r="E121" s="10" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>setup.property.edit</t>
+          <t>setup.room.edit</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
@@ -10171,27 +10171,27 @@
       </c>
       <c r="J121" s="10" t="inlineStr">
         <is>
-          <t>a hotel with ID photos off</t>
+          <t>an administrator on the Rooms page</t>
         </is>
       </c>
       <c r="K121" s="10" t="inlineStr">
         <is>
-          <t>staff try to add or open an ID photo</t>
+          <t>they add rooms by number range or by names</t>
         </is>
       </c>
       <c r="L121" s="10" t="inlineStr">
         <is>
-          <t>it is refused; when Require is on, check-in waits for an ID photo</t>
+          <t>valid new rooms are created, duplicates skipped and invalid names shown</t>
         </is>
       </c>
       <c r="M121" s="10" t="inlineStr">
         <is>
-          <t>set_id_photo_settings</t>
+          <t>add_rooms_range, add_rooms_named, save_room</t>
         </is>
       </c>
       <c r="N121" s="10" t="inlineStr">
         <is>
-          <t>24_id_photos (10)</t>
+          <t>23_room_labels (46); 26_small_fixes (1); browser: rooms-add</t>
         </is>
       </c>
       <c r="O121" s="10" t="inlineStr">
@@ -10204,32 +10204,32 @@
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>GRP-001</t>
+          <t>SET-009</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>Platform &amp; Tenancy</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>All branches</t>
+          <t>/setup/property</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>A built-in Group Manager role and the permission rpt.group.view exist; only System Administrator, General Manager and Group Manager hold the permission.</t>
+          <t>Per hotel: "Allow ID photos" (off by default) and "Require ID photo at check-in" (only when allowed). While Allow is off, uploading and opening ID photos are refused.</t>
         </is>
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
@@ -10239,33 +10239,37 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>rpt.group.view</t>
-        </is>
-      </c>
-      <c r="I122" s="10" t="inlineStr"/>
+          <t>setup.property.edit</t>
+        </is>
+      </c>
+      <c r="I122" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J122" s="10" t="inlineStr">
         <is>
-          <t>a hotel group with several branches</t>
+          <t>a hotel with ID photos off</t>
         </is>
       </c>
       <c r="K122" s="10" t="inlineStr">
         <is>
-          <t>an owner wants a view-only manager for the whole group</t>
+          <t>staff try to add or open an ID photo</t>
         </is>
       </c>
       <c r="L122" s="10" t="inlineStr">
         <is>
-          <t>they assign the Group Manager role branch by branch, and that person can look but not post or change anything</t>
+          <t>it is refused; when Require is on, check-in waits for an ID photo</t>
         </is>
       </c>
       <c r="M122" s="10" t="inlineStr">
         <is>
-          <t>20261013120000_group_view.sql</t>
+          <t>set_id_photo_settings</t>
         </is>
       </c>
       <c r="N122" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (5)</t>
+          <t>24_id_photos (10)</t>
         </is>
       </c>
       <c r="O122" s="10" t="inlineStr">
@@ -10273,16 +10277,12 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P122" s="10" t="inlineStr">
-        <is>
-          <t>Custom roles copied earlier do not get the new permission; say so when releasing.</t>
-        </is>
-      </c>
+      <c r="P122" s="10" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>GRP-002</t>
+          <t>GRP-001</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>One call shows every branch the person may see: occupancy, in house, arrivals and departures to come, approvals, repairs and last night revenue, with group totals. Revenue is totalled per currency.</t>
+          <t>A built-in Group Manager role and the permission rpt.group.view exist; only System Administrator, General Manager and Group Manager hold the permission.</t>
         </is>
       </c>
       <c r="E123" s="10" t="inlineStr">
@@ -10323,27 +10323,27 @@
       <c r="I123" s="10" t="inlineStr"/>
       <c r="J123" s="10" t="inlineStr">
         <is>
-          <t>a group with a Lagos and an Abuja branch</t>
+          <t>a hotel group with several branches</t>
         </is>
       </c>
       <c r="K123" s="10" t="inlineStr">
         <is>
-          <t>a group manager opens All branches</t>
+          <t>an owner wants a view-only manager for the whole group</t>
         </is>
       </c>
       <c r="L123" s="10" t="inlineStr">
         <is>
-          <t>they see both branches with figures from the database, never another hotel group, and staff without the permission are refused</t>
+          <t>they assign the Group Manager role branch by branch, and that person can look but not post or change anything</t>
         </is>
       </c>
       <c r="M123" s="10" t="inlineStr">
         <is>
-          <t>group_overview; /group screen</t>
+          <t>20261013120000_group_view.sql</t>
         </is>
       </c>
       <c r="N123" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (10)</t>
+          <t>35_group_view (5)</t>
         </is>
       </c>
       <c r="O123" s="10" t="inlineStr">
@@ -10353,14 +10353,14 @@
       </c>
       <c r="P123" s="10" t="inlineStr">
         <is>
-          <t>Figures are read from each branch own business date. No arithmetic in the browser.</t>
+          <t>Custom roles copied earlier do not get the new permission; say so when releasing.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>GRP-003</t>
+          <t>GRP-002</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>A Group Manager sees only the branches they are assigned to, and cannot post charges or check guests in.</t>
+          <t>One call shows every branch the person may see: occupancy, in house, arrivals and departures to come, approvals, repairs and last night revenue, with group totals. Revenue is totalled per currency.</t>
         </is>
       </c>
       <c r="E124" s="10" t="inlineStr">
@@ -10401,27 +10401,27 @@
       <c r="I124" s="10" t="inlineStr"/>
       <c r="J124" s="10" t="inlineStr">
         <is>
-          <t>a Group Manager assigned to one branch</t>
+          <t>a group with a Lagos and an Abuja branch</t>
         </is>
       </c>
       <c r="K124" s="10" t="inlineStr">
         <is>
-          <t>a second branch is assigned</t>
+          <t>a group manager opens All branches</t>
         </is>
       </c>
       <c r="L124" s="10" t="inlineStr">
         <is>
-          <t>the second branch appears; the role never gets write permissions</t>
+          <t>they see both branches with figures from the database, never another hotel group, and staff without the permission are refused</t>
         </is>
       </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
-          <t>assign_role (existing); group_overview</t>
+          <t>group_overview; /group screen</t>
         </is>
       </c>
       <c r="N124" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (3)</t>
+          <t>35_group_view (10)</t>
         </is>
       </c>
       <c r="O124" s="10" t="inlineStr">
@@ -10431,14 +10431,14 @@
       </c>
       <c r="P124" s="10" t="inlineStr">
         <is>
-          <t>Access is per branch, using the existing role assignment screen.</t>
+          <t>Figures are read from each branch own business date. No arithmetic in the browser.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>GRP-004</t>
+          <t>GRP-003</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>All branches (Copy setup)</t>
+          <t>All branches</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>A new branch can copy room types, rate plans and prices from an existing branch, once, into an empty branch.</t>
+          <t>A Group Manager sees only the branches they are assigned to, and cannot post charges or check guests in.</t>
         </is>
       </c>
       <c r="E125" s="10" t="inlineStr">
@@ -10473,33 +10473,33 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>setup.room.manage, setup.rate.manage</t>
+          <t>rpt.group.view</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr"/>
       <c r="J125" s="10" t="inlineStr">
         <is>
-          <t>a new empty branch</t>
+          <t>a Group Manager assigned to one branch</t>
         </is>
       </c>
       <c r="K125" s="10" t="inlineStr">
         <is>
-          <t>the owner copies setup from the first branch</t>
+          <t>a second branch is assigned</t>
         </is>
       </c>
       <c r="L125" s="10" t="inlineStr">
         <is>
-          <t>room types, rate plans and prices appear on the new branch and point at its own room types; rooms are not copied; a second copy is refused; the copy is audited</t>
+          <t>the second branch appears; the role never gets write permissions</t>
         </is>
       </c>
       <c r="M125" s="10" t="inlineStr">
         <is>
-          <t>copy_property_setup</t>
+          <t>assign_role (existing); group_overview</t>
         </is>
       </c>
       <c r="N125" s="10" t="inlineStr">
         <is>
-          <t>35_group_view (13)</t>
+          <t>35_group_view (3)</t>
         </is>
       </c>
       <c r="O125" s="10" t="inlineStr">
@@ -10509,29 +10509,29 @@
       </c>
       <c r="P125" s="10" t="inlineStr">
         <is>
-          <t>Taxes, charge codes and payment methods already arrive with every new branch.</t>
+          <t>Access is per branch, using the existing role assignment screen.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>RPT-005</t>
+          <t>GRP-004</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Platform &amp; Tenancy</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>All branches (Copy setup)</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Revenue by booking source: bookings, cancellations, no-shows, room nights, room revenue and average rate for each source in a date range.</t>
+          <t>A new branch can copy room types, rate plans and prices from an existing branch, once, into an empty branch.</t>
         </is>
       </c>
       <c r="E126" s="10" t="inlineStr">
@@ -10551,33 +10551,33 @@
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view</t>
+          <t>setup.room.manage, setup.rate.manage</t>
         </is>
       </c>
       <c r="I126" s="10" t="inlineStr"/>
       <c r="J126" s="10" t="inlineStr">
         <is>
-          <t>bookings from direct, phone and company sources</t>
+          <t>a new empty branch</t>
         </is>
       </c>
       <c r="K126" s="10" t="inlineStr">
         <is>
-          <t>the accountant picks a date range</t>
+          <t>the owner copies setup from the first branch</t>
         </is>
       </c>
       <c r="L126" s="10" t="inlineStr">
         <is>
-          <t>each source shows its own counts and room revenue (room charges only, before tax); cancelled bookings add no nights</t>
+          <t>room types, rate plans and prices appear on the new branch and point at its own room types; rooms are not copied; a second copy is refused; the copy is audited</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
-          <t>20261013130000_source_ageing_reports.sql: report_revenue_by_source; Reports, By booking source tab</t>
+          <t>copy_property_setup</t>
         </is>
       </c>
       <c r="N126" s="10" t="inlineStr">
         <is>
-          <t>36_source_ageing (13)</t>
+          <t>35_group_view (13)</t>
         </is>
       </c>
       <c r="O126" s="10" t="inlineStr">
@@ -10587,14 +10587,14 @@
       </c>
       <c r="P126" s="10" t="inlineStr">
         <is>
-          <t>Bookings counted by arrival date; revenue by posting date.</t>
+          <t>Taxes, charge codes and payment methods already arrive with every new branch.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>RPT-006</t>
+          <t>RPT-005</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>Ageing of unpaid balances by booking source: current, 1 to 7, 8 to 30, 31 to 60 and over 60 days since the due departure, plus credit held.</t>
+          <t>Revenue by booking source: bookings, cancellations, no-shows, room nights, room revenue and average rate for each source in a date range.</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr">
@@ -10635,27 +10635,27 @@
       <c r="I127" s="10" t="inlineStr"/>
       <c r="J127" s="10" t="inlineStr">
         <is>
-          <t>guests and companies who left owing money</t>
+          <t>bookings from direct, phone and company sources</t>
         </is>
       </c>
       <c r="K127" s="10" t="inlineStr">
         <is>
-          <t>the accountant opens the Ageing tab</t>
+          <t>the accountant picks a date range</t>
         </is>
       </c>
       <c r="L127" s="10" t="inlineStr">
         <is>
-          <t>each source shows what is owed in each age column; paid bills drop out; overpayments show as credit held; the total matches Outstanding balances</t>
+          <t>each source shows its own counts and room revenue (room charges only, before tax); cancelled bookings add no nights</t>
         </is>
       </c>
       <c r="M127" s="10" t="inlineStr">
         <is>
-          <t>report_balance_ageing; Reports, Ageing tab</t>
+          <t>20261013130000_source_ageing_reports.sql: report_revenue_by_source; Reports, By booking source tab</t>
         </is>
       </c>
       <c r="N127" s="10" t="inlineStr">
         <is>
-          <t>36_source_ageing (11)</t>
+          <t>36_source_ageing (13)</t>
         </is>
       </c>
       <c r="O127" s="10" t="inlineStr">
@@ -10665,14 +10665,14 @@
       </c>
       <c r="P127" s="10" t="inlineStr">
         <is>
-          <t>Guests still staying count as current.</t>
+          <t>Bookings counted by arrival date; revenue by posting date.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>RPT-007</t>
+          <t>RPT-006</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -10682,17 +10682,17 @@
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>The owner summary: last night's occupancy and revenue, money collected by payment method, today's arrivals, departures and rooms, what is waiting, and old unpaid bills, as plain sentences built in the database. Works with AI off; a later daily email can send the same text.</t>
+          <t>Ageing of unpaid balances by booking source: current, 1 to 7, 8 to 30, 31 to 60 and over 60 days since the due departure, plus credit held.</t>
         </is>
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
@@ -10707,37 +10707,33 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view, rpt.operations.view</t>
-        </is>
-      </c>
-      <c r="I128" s="10" t="inlineStr">
-        <is>
-          <t>Reads the morning brief facts</t>
-        </is>
-      </c>
+          <t>rpt.finance.view</t>
+        </is>
+      </c>
+      <c r="I128" s="10" t="inlineStr"/>
       <c r="J128" s="10" t="inlineStr">
         <is>
-          <t>a hotel with a closed day and payments on it</t>
+          <t>guests and companies who left owing money</t>
         </is>
       </c>
       <c r="K128" s="10" t="inlineStr">
         <is>
-          <t>the owner opens the dashboard</t>
+          <t>the accountant opens the Ageing tab</t>
         </is>
       </c>
       <c r="L128" s="10" t="inlineStr">
         <is>
-          <t>sees yesterday at a glance with the money collected by method; front desk without finance reports is refused</t>
+          <t>each source shows what is owed in each age column; paid bills drop out; overpayments show as credit held; the total matches Outstanding balances</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
-          <t>owner_summary</t>
+          <t>report_balance_ageing; Reports, Ageing tab</t>
         </is>
       </c>
       <c r="N128" s="10" t="inlineStr">
         <is>
-          <t>47_owner_summary (9); browser: owner-summary</t>
+          <t>36_source_ageing (11)</t>
         </is>
       </c>
       <c r="O128" s="10" t="inlineStr">
@@ -10747,34 +10743,34 @@
       </c>
       <c r="P128" s="10" t="inlineStr">
         <is>
-          <t>Email delivery waits on the sending domain and email account. Collected money nets payment reversals the same day (migration 20261015130000).</t>
+          <t>Guests still staying count as current.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>AI-001</t>
+          <t>RPT-007</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>AI helpers</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Dashboard, Admin</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>AI helpers are off for every hotel until a System Administrator or General Manager switches them on, with a monthly limit; the switch is audited.</t>
+          <t>The owner summary: last night's occupancy and revenue, money collected by payment method, today's arrivals, departures and rooms, what is waiting, and old unpaid bills, as plain sentences built in the database. Works with AI off; a later daily email can send the same text.</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F129" s="10" t="inlineStr">
@@ -10789,33 +10785,37 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>adm.ai.manage</t>
-        </is>
-      </c>
-      <c r="I129" s="10" t="inlineStr"/>
+          <t>rpt.finance.view, rpt.operations.view</t>
+        </is>
+      </c>
+      <c r="I129" s="10" t="inlineStr">
+        <is>
+          <t>Reads the morning brief facts</t>
+        </is>
+      </c>
       <c r="J129" s="10" t="inlineStr">
         <is>
-          <t>a new hotel</t>
+          <t>a hotel with a closed day and payments on it</t>
         </is>
       </c>
       <c r="K129" s="10" t="inlineStr">
         <is>
-          <t>a manager opens Admin, AI helpers</t>
+          <t>the owner opens the dashboard</t>
         </is>
       </c>
       <c r="L129" s="10" t="inlineStr">
         <is>
-          <t>nothing runs until they switch it on and the change is in the audit log</t>
+          <t>sees yesterday at a glance with the money collected by method; front desk without finance reports is refused</t>
         </is>
       </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: set_ai_settings, ai_status; Admin, AI helpers tab</t>
+          <t>owner_summary</t>
         </is>
       </c>
       <c r="N129" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (11)</t>
+          <t>47_owner_summary (9); browser: owner-summary</t>
         </is>
       </c>
       <c r="O129" s="10" t="inlineStr">
@@ -10825,14 +10825,14 @@
       </c>
       <c r="P129" s="10" t="inlineStr">
         <is>
-          <t>Custom roles copied earlier do not get adm.ai.manage.</t>
+          <t>Email delivery waits on the sending domain and email account. Collected money nets payment reversals the same day (migration 20261015130000).</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>AI-002</t>
+          <t>AI-001</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
@@ -10847,7 +10847,7 @@
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>The facts sent to the AI are counts and money lines built by the database: no guest names, ID details, room numbers or card data.</t>
+          <t>AI helpers are off for every hotel until a System Administrator or General Manager switches them on, with a monthly limit; the switch is audited.</t>
         </is>
       </c>
       <c r="E130" s="10" t="inlineStr">
@@ -10867,28 +10867,28 @@
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view, rpt.operations.view</t>
+          <t>adm.ai.manage</t>
         </is>
       </c>
       <c r="I130" s="10" t="inlineStr"/>
       <c r="J130" s="10" t="inlineStr">
         <is>
-          <t>a hotel with guests, approvals and overdue bills</t>
+          <t>a new hotel</t>
         </is>
       </c>
       <c r="K130" s="10" t="inlineStr">
         <is>
-          <t>a brief is started</t>
+          <t>a manager opens Admin, AI helpers</t>
         </is>
       </c>
       <c r="L130" s="10" t="inlineStr">
         <is>
-          <t>the facts hold only business date, last night, today, attention figures and plain lines, and overdue money matches the ledger</t>
+          <t>nothing runs until they switch it on and the change is in the audit log</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: ai_morning_brief_start, app.morning_brief_facts</t>
+          <t>20261013140000_ai_morning_brief.sql: set_ai_settings, ai_status; Admin, AI helpers tab</t>
         </is>
       </c>
       <c r="N130" s="10" t="inlineStr">
@@ -10903,14 +10903,14 @@
       </c>
       <c r="P130" s="10" t="inlineStr">
         <is>
-          <t>Overdue means unpaid more than 30 days after departure.</t>
+          <t>Custom roles copied earlier do not get adm.ai.manage.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>AI-003</t>
+          <t>AI-002</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>Each hotel has a monthly limit on AI drafts; failed calls do not count; a call can be finished once, by the person who started it.</t>
+          <t>The facts sent to the AI are counts and money lines built by the database: no guest names, ID details, room numbers or card data.</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
@@ -10945,33 +10945,33 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view</t>
+          <t>rpt.finance.view, rpt.operations.view</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr"/>
       <c r="J131" s="10" t="inlineStr">
         <is>
-          <t>a limit of 2</t>
+          <t>a hotel with guests, approvals and overdue bills</t>
         </is>
       </c>
       <c r="K131" s="10" t="inlineStr">
         <is>
-          <t>a third brief is requested</t>
+          <t>a brief is started</t>
         </is>
       </c>
       <c r="L131" s="10" t="inlineStr">
         <is>
-          <t>it is refused until a failed call frees a slot or the month turns</t>
+          <t>the facts hold only business date, last night, today, attention figures and plain lines, and overdue money matches the ledger</t>
         </is>
       </c>
       <c r="M131" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql: ai_call_finish</t>
+          <t>20261013140000_ai_morning_brief.sql: ai_morning_brief_start, app.morning_brief_facts</t>
         </is>
       </c>
       <c r="N131" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (5)</t>
+          <t>37_ai_brief (11)</t>
         </is>
       </c>
       <c r="O131" s="10" t="inlineStr">
@@ -10979,12 +10979,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P131" s="10" t="inlineStr"/>
+      <c r="P131" s="10" t="inlineStr">
+        <is>
+          <t>Overdue means unpaid more than 30 days after departure.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>AI-004</t>
+          <t>AI-003</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -10999,7 +11003,7 @@
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Only finance and operations viewers can ask for the brief; the usage log and settings cannot be written or read directly by the browser.</t>
+          <t>Each hotel has a monthly limit on AI drafts; failed calls do not count; a call can be finished once, by the person who started it.</t>
         </is>
       </c>
       <c r="E132" s="10" t="inlineStr">
@@ -11019,33 +11023,33 @@
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>rpt.finance.view, rpt.operations.view</t>
+          <t>rpt.finance.view</t>
         </is>
       </c>
       <c r="I132" s="10" t="inlineStr"/>
       <c r="J132" s="10" t="inlineStr">
         <is>
-          <t>front desk, housekeeping, another hotel</t>
+          <t>a limit of 2</t>
         </is>
       </c>
       <c r="K132" s="10" t="inlineStr">
         <is>
-          <t>they ask for the brief or touch the tables</t>
+          <t>a third brief is requested</t>
         </is>
       </c>
       <c r="L132" s="10" t="inlineStr">
         <is>
-          <t>they are refused</t>
+          <t>it is refused until a failed call frees a slot or the month turns</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
         <is>
-          <t>20261013140000_ai_morning_brief.sql</t>
+          <t>20261013140000_ai_morning_brief.sql: ai_call_finish</t>
         </is>
       </c>
       <c r="N132" s="10" t="inlineStr">
         <is>
-          <t>37_ai_brief (7)</t>
+          <t>37_ai_brief (5)</t>
         </is>
       </c>
       <c r="O132" s="10" t="inlineStr">
@@ -11058,7 +11062,7 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>AI-005</t>
+          <t>AI-004</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
@@ -11073,7 +11077,7 @@
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>The server accepts an AI draft only when every number in it is in the database facts; otherwise it shows the plain figures. The key stays on the server and only the fact lines are sent.</t>
+          <t>Only finance and operations viewers can ask for the brief; the usage log and settings cannot be written or read directly by the browser.</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
@@ -11093,33 +11097,33 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>rpt.finance.view, rpt.operations.view</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr"/>
       <c r="J133" s="10" t="inlineStr">
         <is>
-          <t>a draft that rounds or invents a figure</t>
+          <t>front desk, housekeeping, another hotel</t>
         </is>
       </c>
       <c r="K133" s="10" t="inlineStr">
         <is>
-          <t>the brief is written</t>
+          <t>they ask for the brief or touch the tables</t>
         </is>
       </c>
       <c r="L133" s="10" t="inlineStr">
         <is>
-          <t>the plain database lines are shown instead, with a note</t>
+          <t>they are refused</t>
         </is>
       </c>
       <c r="M133" s="10" t="inlineStr">
         <is>
-          <t>src/lib/ai-brief.ts, ai-brief.functions.ts, Dashboard morning brief card</t>
+          <t>20261013140000_ai_morning_brief.sql</t>
         </is>
       </c>
       <c r="N133" s="10" t="inlineStr">
         <is>
-          <t>browser unit: ai-brief-unit (8)</t>
+          <t>37_ai_brief (7)</t>
         </is>
       </c>
       <c r="O133" s="10" t="inlineStr">
@@ -11127,31 +11131,27 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P133" s="10" t="inlineStr">
-        <is>
-          <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
-        </is>
-      </c>
+      <c r="P133" s="10" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>SET-010</t>
+          <t>AI-005</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>AI helpers</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>Setup, Rooms</t>
+          <t>Dashboard, Admin</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>A hotel can add room types and rooms from one checked list: preview first, then all or nothing. Existing codes and room names are skipped, so repeating adds nothing.</t>
+          <t>The server accepts an AI draft only when every number in it is in the database facts; otherwise it shows the plain figures. The key stays on the server and only the fact lines are sent.</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
@@ -11171,33 +11171,33 @@
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>setup.room.manage</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I134" s="10" t="inlineStr"/>
       <c r="J134" s="10" t="inlineStr">
         <is>
-          <t>a list of room types and rooms</t>
+          <t>a draft that rounds or invents a figure</t>
         </is>
       </c>
       <c r="K134" s="10" t="inlineStr">
         <is>
-          <t>the manager previews and then applies it</t>
+          <t>the brief is written</t>
         </is>
       </c>
       <c r="L134" s="10" t="inlineStr">
         <is>
-          <t>the preview writes nothing; apply adds every valid item or none (bad name, unknown type, over 500 rooms, over the plan limit); a repeat adds nothing; the import is audited</t>
+          <t>the plain database lines are shown instead, with a note</t>
         </is>
       </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
-          <t>20261013150000_setup_import.sql: apply_setup_import</t>
+          <t>src/lib/ai-brief.ts, ai-brief.functions.ts, Dashboard morning brief card</t>
         </is>
       </c>
       <c r="N134" s="10" t="inlineStr">
         <is>
-          <t>38_setup_import (29)</t>
+          <t>browser unit: ai-brief-unit (8)</t>
         </is>
       </c>
       <c r="O134" s="10" t="inlineStr">
@@ -11207,19 +11207,19 @@
       </c>
       <c r="P134" s="10" t="inlineStr">
         <is>
-          <t>The AI only drafts the list. This function is the check.</t>
+          <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>AI-006</t>
+          <t>SET-010</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>AI helpers</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>The setup import assistant starts only when AI is on and under the monthly limit, and the AI sees only existing room type codes and a room count.</t>
+          <t>A hotel can add room types and rooms from one checked list: preview first, then all or nothing. Existing codes and room names are skipped, so repeating adds nothing.</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
@@ -11255,27 +11255,27 @@
       <c r="I135" s="10" t="inlineStr"/>
       <c r="J135" s="10" t="inlineStr">
         <is>
-          <t>AI switched on with a limit of 1</t>
+          <t>a list of room types and rooms</t>
         </is>
       </c>
       <c r="K135" s="10" t="inlineStr">
         <is>
-          <t>an import draft is started twice</t>
+          <t>the manager previews and then applies it</t>
         </is>
       </c>
       <c r="L135" s="10" t="inlineStr">
         <is>
-          <t>the second is refused until the first fails; front desk and other hotels are refused</t>
+          <t>the preview writes nothing; apply adds every valid item or none (bad name, unknown type, over 500 rooms, over the plan limit); a repeat adds nothing; the import is audited</t>
         </is>
       </c>
       <c r="M135" s="10" t="inlineStr">
         <is>
-          <t>20261013150000_setup_import.sql: ai_import_start, app.ai_begin</t>
+          <t>20261013150000_setup_import.sql: apply_setup_import</t>
         </is>
       </c>
       <c r="N135" s="10" t="inlineStr">
         <is>
-          <t>38_setup_import (8)</t>
+          <t>38_setup_import (29)</t>
         </is>
       </c>
       <c r="O135" s="10" t="inlineStr">
@@ -11283,12 +11283,16 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P135" s="10" t="inlineStr"/>
+      <c r="P135" s="10" t="inlineStr">
+        <is>
+          <t>The AI only drafts the list. This function is the check.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>AI-007</t>
+          <t>AI-006</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
@@ -11303,7 +11307,7 @@
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t>Pasted text with an email, phone or card number is refused before anything is sent; the draft may only contain rooms, floors, guest limits and type names that are in the pasted text.</t>
+          <t>The setup import assistant starts only when AI is on and under the monthly limit, and the AI sees only existing room type codes and a room count.</t>
         </is>
       </c>
       <c r="E136" s="10" t="inlineStr">
@@ -11329,27 +11333,27 @@
       <c r="I136" s="10" t="inlineStr"/>
       <c r="J136" s="10" t="inlineStr">
         <is>
-          <t>a pasted list</t>
+          <t>AI switched on with a limit of 1</t>
         </is>
       </c>
       <c r="K136" s="10" t="inlineStr">
         <is>
-          <t>the assistant drafts it</t>
+          <t>an import draft is started twice</t>
         </is>
       </c>
       <c r="L136" s="10" t="inlineStr">
         <is>
-          <t>invented rooms, floors and limits are dropped with a note; a draft with no matching rooms is an error</t>
+          <t>the second is refused until the first fails; front desk and other hotels are refused</t>
         </is>
       </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
-          <t>src/lib/setup-import.ts, setup-import.functions.ts, Import from a list on Setup, Rooms</t>
+          <t>20261013150000_setup_import.sql: ai_import_start, app.ai_begin</t>
         </is>
       </c>
       <c r="N136" s="10" t="inlineStr">
         <is>
-          <t>browser unit: setup-import-unit (9)</t>
+          <t>38_setup_import (8)</t>
         </is>
       </c>
       <c r="O136" s="10" t="inlineStr">
@@ -11357,36 +11361,32 @@
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P136" s="10" t="inlineStr">
-        <is>
-          <t>Needs ANTHROPIC_API_KEY on the server. Not set yet.</t>
-        </is>
-      </c>
+      <c r="P136" s="10" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>SET-011</t>
+          <t>AI-007</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>AI helpers</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>/setup; /dashboard</t>
+          <t>Setup, Rooms</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>A new hotel sees a checklist of what is left to set up: property details, room types, rooms, rates, taxes, payment methods and staff. Each step says what is missing and links to the right screen. The list comes from the hotel's own data, so it is always current.</t>
+          <t>Pasted text with an email, phone or card number is refused before anything is sent; the draft may only contain rooms, floors, guest limits and type names that are in the pasted text.</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
@@ -11401,37 +11401,33 @@
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>any setup permission</t>
-        </is>
-      </c>
-      <c r="I137" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>setup.room.manage</t>
+        </is>
+      </c>
+      <c r="I137" s="10" t="inlineStr"/>
       <c r="J137" s="10" t="inlineStr">
         <is>
-          <t>a hotel that is part way through setup</t>
+          <t>a pasted list</t>
         </is>
       </c>
       <c r="K137" s="10" t="inlineStr">
         <is>
-          <t>a manager opens Setup or the Dashboard</t>
+          <t>the assistant drafts it</t>
         </is>
       </c>
       <c r="L137" s="10" t="inlineStr">
         <is>
-          <t>the steps already done are ticked and the next one is linked; once all seven are done the checklist goes away</t>
+          <t>invented rooms, floors and limits are dropped with a note; a draft with no matching rooms is an error</t>
         </is>
       </c>
       <c r="M137" s="10" t="inlineStr">
         <is>
-          <t>setup_progress</t>
+          <t>src/lib/setup-import.ts, setup-import.functions.ts, Import from a list on Setup, Rooms</t>
         </is>
       </c>
       <c r="N137" s="10" t="inlineStr">
         <is>
-          <t>40_guided_setup (30)</t>
+          <t>browser unit: setup-import-unit (9)</t>
         </is>
       </c>
       <c r="O137" s="10" t="inlineStr">
@@ -11441,39 +11437,39 @@
       </c>
       <c r="P137" s="10" t="inlineStr">
         <is>
-          <t>Read-only function, no stored progress. Staff step counts people with a role at the property (two or more).</t>
+          <t>Needs ANTHROPIC_API_KEY on the server. Not set yet.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>NFR-006</t>
+          <t>SET-011</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>(all)</t>
+          <t>/setup; /dashboard</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>The last room of a type is sold once, however many desks book at the same moment, and a repeated booking never doubles.</t>
+          <t>A new hotel sees a checklist of what is left to set up: property details, room types, rooms, rates, taxes, payment methods and staff. Each step says what is missing and links to the right screen. The list comes from the hotel's own data, so it is always current.</t>
         </is>
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>BR-001</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G138" s="10" t="inlineStr">
@@ -11483,37 +11479,37 @@
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
+          <t>any setup permission</t>
+        </is>
+      </c>
+      <c r="I138" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I138" s="10" t="inlineStr">
-        <is>
-          <t>Rule: Safe last-room booking</t>
-        </is>
-      </c>
       <c r="J138" s="10" t="inlineStr">
         <is>
-          <t>one room of a type is left and several desks book it together</t>
+          <t>a hotel that is part way through setup</t>
         </is>
       </c>
       <c r="K138" s="10" t="inlineStr">
         <is>
-          <t>all of them submit at the same moment</t>
+          <t>a manager opens Setup or the Dashboard</t>
         </is>
       </c>
       <c r="L138" s="10" t="inlineStr">
         <is>
-          <t>exactly one booking succeeds, the rest get E_NO_AVAILABILITY, and nothing is oversold</t>
+          <t>the steps already done are ticked and the next one is linked; once all seven are done the checklist goes away</t>
         </is>
       </c>
       <c r="M138" s="10" t="inlineStr">
         <is>
-          <t>create_reservation, assert_available</t>
+          <t>setup_progress</t>
         </is>
       </c>
       <c r="N138" s="10" t="inlineStr">
         <is>
-          <t>concurrency/last_room.sh (6)</t>
+          <t>40_guided_setup (30)</t>
         </is>
       </c>
       <c r="O138" s="10" t="inlineStr">
@@ -11523,29 +11519,29 @@
       </c>
       <c r="P138" s="10" t="inlineStr">
         <is>
-          <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
+          <t>Read-only function, no stored progress. Staff step counts people with a role at the property (two or more).</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>SET-012</t>
+          <t>NFR-006</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Non-functional</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>/setup/property</t>
+          <t>(all)</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>A manager sets the longest stay (1 to 365 nights) and how long a tentative booking holds its room (1 to 720 hours) for each property.</t>
+          <t>The last room of a type is sold once, however many desks book at the same moment, and a repeated booking never doubles.</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr">
@@ -11555,7 +11551,7 @@
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>Should</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="G139" s="10" t="inlineStr">
@@ -11565,33 +11561,37 @@
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>setup.property.edit</t>
-        </is>
-      </c>
-      <c r="I139" s="10" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="10" t="inlineStr">
+        <is>
+          <t>Rule: Safe last-room booking</t>
+        </is>
+      </c>
       <c r="J139" s="10" t="inlineStr">
         <is>
-          <t>a property with the default rules (30 nights, 24 hours)</t>
+          <t>one room of a type is left and several desks book it together</t>
         </is>
       </c>
       <c r="K139" s="10" t="inlineStr">
         <is>
-          <t>a manager saves new booking rules</t>
+          <t>all of them submit at the same moment</t>
         </is>
       </c>
       <c r="L139" s="10" t="inlineStr">
         <is>
-          <t>new bookings use them, bad values are refused with E_INVALID, and the change is audited with old and new values</t>
+          <t>exactly one booking succeeds, the rest get E_NO_AVAILABILITY, and nothing is oversold</t>
         </is>
       </c>
       <c r="M139" s="10" t="inlineStr">
         <is>
-          <t>set_booking_rules; Booking rules on Setup, Property</t>
+          <t>create_reservation, assert_available</t>
         </is>
       </c>
       <c r="N139" s="10" t="inlineStr">
         <is>
-          <t>42_booking_rules (9)</t>
+          <t>concurrency/last_room.sh (6)</t>
         </is>
       </c>
       <c r="O139" s="10" t="inlineStr">
@@ -11601,39 +11601,39 @@
       </c>
       <c r="P139" s="10" t="inlineStr">
         <is>
-          <t>Added 8 Oct 2026. The columns existed since the reservations release; this adds the screen and the function.</t>
+          <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>FO-014</t>
+          <t>SET-012</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>Front Office</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>/downtime</t>
+          <t>/setup/property</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>A printable downtime pack: arrivals due, in-house guests with balance, departures due, ten blank lines for new guests on paper, and a short paper routine. Staff print it when the internet or system is down.</t>
+          <t>A manager sets the longest stay (1 to 365 nights) and how long a tentative booking holds its room (1 to 720 hours) for each property.</t>
         </is>
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>BR-006</t>
+          <t>BR-001</t>
         </is>
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G140" s="10" t="inlineStr">
@@ -11643,33 +11643,33 @@
       </c>
       <c r="H140" s="10" t="inlineStr">
         <is>
-          <t>fo.view</t>
+          <t>setup.property.edit</t>
         </is>
       </c>
       <c r="I140" s="10" t="inlineStr"/>
       <c r="J140" s="10" t="inlineStr">
         <is>
-          <t>a hotel with guests in house</t>
+          <t>a property with the default rules (30 nights, 24 hours)</t>
         </is>
       </c>
       <c r="K140" s="10" t="inlineStr">
         <is>
-          <t>a front desk user opens Downtime pack and prints</t>
+          <t>a manager saves new booking rules</t>
         </is>
       </c>
       <c r="L140" s="10" t="inlineStr">
         <is>
-          <t>the lists show room, guest, phone, departure and the folio balance from the database, with blank lines and the paper routine</t>
+          <t>new bookings use them, bad values are refused with E_INVALID, and the change is audited with old and new values</t>
         </is>
       </c>
       <c r="M140" s="10" t="inlineStr">
         <is>
-          <t>src/routes/_authenticated/_app/downtime.tsx</t>
+          <t>set_booking_rules; Booking rules on Setup, Property</t>
         </is>
       </c>
       <c r="N140" s="10" t="inlineStr">
         <is>
-          <t>browser: downtime-pack.spec (1)</t>
+          <t>42_booking_rules (9)</t>
         </is>
       </c>
       <c r="O140" s="10" t="inlineStr">
@@ -11679,87 +11679,165 @@
       </c>
       <c r="P140" s="10" t="inlineStr">
         <is>
-          <t>No database change. Reads v_arrivals, v_in_house and v_folio_balances. Added 8 Oct 2026.</t>
+          <t>Added 8 Oct 2026. The columns existed since the reservations release; this adds the screen and the function.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
+          <t>FO-014</t>
+        </is>
+      </c>
+      <c r="B141" s="10" t="inlineStr">
+        <is>
+          <t>Front Office</t>
+        </is>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
+        <is>
+          <t>/downtime</t>
+        </is>
+      </c>
+      <c r="D141" s="10" t="inlineStr">
+        <is>
+          <t>A printable downtime pack: arrivals due, in-house guests with balance, departures due, ten blank lines for new guests on paper, and a short paper routine. Staff print it when the internet or system is down.</t>
+        </is>
+      </c>
+      <c r="E141" s="10" t="inlineStr">
+        <is>
+          <t>BR-006</t>
+        </is>
+      </c>
+      <c r="F141" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G141" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H141" s="10" t="inlineStr">
+        <is>
+          <t>fo.view</t>
+        </is>
+      </c>
+      <c r="I141" s="10" t="inlineStr"/>
+      <c r="J141" s="10" t="inlineStr">
+        <is>
+          <t>a hotel with guests in house</t>
+        </is>
+      </c>
+      <c r="K141" s="10" t="inlineStr">
+        <is>
+          <t>a front desk user opens Downtime pack and prints</t>
+        </is>
+      </c>
+      <c r="L141" s="10" t="inlineStr">
+        <is>
+          <t>the lists show room, guest, phone, departure and the folio balance from the database, with blank lines and the paper routine</t>
+        </is>
+      </c>
+      <c r="M141" s="10" t="inlineStr">
+        <is>
+          <t>src/routes/_authenticated/_app/downtime.tsx</t>
+        </is>
+      </c>
+      <c r="N141" s="10" t="inlineStr">
+        <is>
+          <t>browser: downtime-pack.spec (1)</t>
+        </is>
+      </c>
+      <c r="O141" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P141" s="10" t="inlineStr">
+        <is>
+          <t>No database change. Reads v_arrivals, v_in_house and v_folio_balances. Added 8 Oct 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
+        <is>
           <t>DAY-007</t>
         </is>
       </c>
-      <c r="B141" s="10" t="inlineStr">
+      <c r="B142" s="10" t="inlineStr">
         <is>
           <t>Business Date</t>
         </is>
       </c>
-      <c r="C141" s="10" t="inlineStr">
+      <c r="C142" s="10" t="inlineStr">
         <is>
           <t>Notifications bell</t>
         </is>
       </c>
-      <c r="D141" s="10" t="inlineStr">
+      <c r="D142" s="10" t="inlineStr">
         <is>
           <t>In the last hour before a property rolls its business date, if a cashier shift is still open, users who can run the night audit get one warning that night. The roll does not wait.</t>
         </is>
       </c>
-      <c r="E141" s="10" t="inlineStr">
+      <c r="E142" s="10" t="inlineStr">
         <is>
           <t>BR-016</t>
         </is>
       </c>
-      <c r="F141" s="10" t="inlineStr">
+      <c r="F142" s="10" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G141" s="10" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H141" s="10" t="inlineStr">
+      <c r="G142" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H142" s="10" t="inlineStr">
         <is>
           <t>fin.nightaudit.run</t>
         </is>
       </c>
-      <c r="I141" s="10" t="inlineStr">
+      <c r="I142" s="10" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="J141" s="10" t="inlineStr">
+      <c r="J142" s="10" t="inlineStr">
         <is>
           <t>a cashier shift is still open</t>
         </is>
       </c>
-      <c r="K141" s="10" t="inlineStr">
+      <c r="K142" s="10" t="inlineStr">
         <is>
           <t>the roll time is less than 60 minutes away</t>
         </is>
       </c>
-      <c r="L141" s="10" t="inlineStr">
+      <c r="L142" s="10" t="inlineStr">
         <is>
           <t>each night audit user gets one rollover_warning notification for that business date; none earlier, none after the roll time, none if no shift is open, none twice</t>
         </is>
       </c>
-      <c r="M141" s="10" t="inlineStr">
+      <c r="M142" s="10" t="inlineStr">
         <is>
           <t>app.warn_before_rollover; cron job rollover-warning</t>
         </is>
       </c>
-      <c r="N141" s="10" t="inlineStr">
+      <c r="N142" s="10" t="inlineStr">
         <is>
           <t>43_rollover_warning (9)</t>
         </is>
       </c>
-      <c r="O141" s="10" t="inlineStr">
+      <c r="O142" s="10" t="inlineStr">
         <is>
           <t>Built+tested</t>
         </is>
       </c>
-      <c r="P141" s="10" t="inlineStr">
+      <c r="P142" s="10" t="inlineStr">
         <is>
           <t>Added 8 Oct 2026. Warning only; the hard gate stays in R2 (DAY-005).</t>
         </is>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -6497,7 +6497,7 @@
       </c>
       <c r="N74" s="10" t="inlineStr">
         <is>
-          <t>48_minibar (16)</t>
+          <t>48_minibar (18)</t>
         </is>
       </c>
       <c r="O74" s="10" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="N78" s="10" t="inlineStr">
         <is>
-          <t>49_ticket_photos (17)</t>
+          <t>49_ticket_photos (20)</t>
         </is>
       </c>
       <c r="O78" s="10" t="inlineStr">

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P142"/>
+  <dimension ref="A1:P144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11840,6 +11840,162 @@
       <c r="P142" s="10" t="inlineStr">
         <is>
           <t>Added 8 Oct 2026. Warning only; the hard gate stays in R2 (DAY-005).</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>RPT-008</t>
+        </is>
+      </c>
+      <c r="B143" s="10" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="D143" s="10" t="inlineStr">
+        <is>
+          <t>A Latest activity feed on the dashboard: new bookings, check-ins, check-outs, payments and rooms marked clean, newest first. Each person sees only the kinds their rights allow.</t>
+        </is>
+      </c>
+      <c r="E143" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F143" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G143" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H143" s="10" t="inlineStr">
+        <is>
+          <t>res.view; fo.view; fin.folio.view; hk.view</t>
+        </is>
+      </c>
+      <c r="I143" s="10" t="inlineStr"/>
+      <c r="J143" s="10" t="inlineStr">
+        <is>
+          <t>a property with recent activity</t>
+        </is>
+      </c>
+      <c r="K143" s="10" t="inlineStr">
+        <is>
+          <t>a signed-in user opens the dashboard</t>
+        </is>
+      </c>
+      <c r="L143" s="10" t="inlineStr">
+        <is>
+          <t>the feed lists up to 8 recent items; payments show only with folio rights; bookings only with reservation rights; no rights is refused with E_FORBIDDEN; a room move adds no second check-in</t>
+        </is>
+      </c>
+      <c r="M143" s="10" t="inlineStr">
+        <is>
+          <t>recent_activity; Latest activity card on the dashboard</t>
+        </is>
+      </c>
+      <c r="N143" s="10" t="inlineStr">
+        <is>
+          <t>50_recent_activity (17)</t>
+        </is>
+      </c>
+      <c r="O143" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P143" s="10" t="inlineStr">
+        <is>
+          <t>Added 9 Oct 2026. Read-only; no money is changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="inlineStr">
+        <is>
+          <t>RPT-009</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>One rule for money collected. A payment, a refund, and a reversal or transfer that carries a payment method count; the Payments report, the owner summary and the invoice all use it, so a payment reversed the same day shows as zero everywhere.</t>
+        </is>
+      </c>
+      <c r="E144" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F144" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G144" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H144" s="10" t="inlineStr">
+        <is>
+          <t>rpt.finance.view</t>
+        </is>
+      </c>
+      <c r="I144" s="10" t="inlineStr"/>
+      <c r="J144" s="10" t="inlineStr">
+        <is>
+          <t>a payment taken and reversed the same day</t>
+        </is>
+      </c>
+      <c r="K144" s="10" t="inlineStr">
+        <is>
+          <t>a finance user opens the Payments report</t>
+        </is>
+      </c>
+      <c r="L144" s="10" t="inlineStr">
+        <is>
+          <t>the method nets to zero and matches the ledger; front desk without finance reports is refused with E_FORBIDDEN</t>
+        </is>
+      </c>
+      <c r="M144" s="10" t="inlineStr">
+        <is>
+          <t>report_payments; app.is_money_movement</t>
+        </is>
+      </c>
+      <c r="N144" s="10" t="inlineStr">
+        <is>
+          <t>51_money_collected (5)</t>
+        </is>
+      </c>
+      <c r="O144" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P144" s="10" t="inlineStr">
+        <is>
+          <t>Added 10 Oct 2026. The Payments report counted only payments and refunds before this. Cashier shift counts stay separate on purpose: they count what the drawer should hold.</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P144"/>
+  <dimension ref="A1:P146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11907,7 +11907,7 @@
       </c>
       <c r="N143" s="10" t="inlineStr">
         <is>
-          <t>50_recent_activity (17)</t>
+          <t>50_recent_activity (17); 52_guest_label_private (3)</t>
         </is>
       </c>
       <c r="O143" s="10" t="inlineStr">
@@ -11996,6 +11996,158 @@
       <c r="P144" s="10" t="inlineStr">
         <is>
           <t>Added 10 Oct 2026. The Payments report counted only payments and refunds before this. Cashier shift counts stay separate on purpose: they count what the drawer should hold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>FIN-021</t>
+        </is>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>Reports &gt; Collections</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>Collections list. Departed guests (checked out, no-show, cancelled) who still owe the hotel, with a follow-up log: called, promised, unreachable, disputed or note. Next follow-up is the day after a promised date, or 7 days after the last note.</t>
+        </is>
+      </c>
+      <c r="E145" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F145" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G145" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H145" s="10" t="inlineStr">
+        <is>
+          <t>rpt.finance.view; fin.payment.post</t>
+        </is>
+      </c>
+      <c r="I145" s="10" t="inlineStr"/>
+      <c r="J145" s="10" t="inlineStr">
+        <is>
+          <t>a guest left owing money</t>
+        </is>
+      </c>
+      <c r="K145" s="10" t="inlineStr">
+        <is>
+          <t>finance staff opens Reports &gt; Collections and logs a follow-up</t>
+        </is>
+      </c>
+      <c r="L145" s="10" t="inlineStr">
+        <is>
+          <t>the guest shows with balance and days since departure; a note with a promise needs a future date; guests who owe nothing or have not left are refused; front desk without finance reports is refused</t>
+        </is>
+      </c>
+      <c r="M145" s="10" t="inlineStr">
+        <is>
+          <t>collections_list; add_collection_note; collection_notes</t>
+        </is>
+      </c>
+      <c r="N145" s="10" t="inlineStr">
+        <is>
+          <t>53_collections (20)</t>
+        </is>
+      </c>
+      <c r="O145" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P145" s="10" t="inlineStr">
+        <is>
+          <t>Added 10 Oct 2026. Notes are not ledger rows; they never change a balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>DRY-001</t>
+        </is>
+      </c>
+      <c r="B146" s="10" t="inlineStr">
+        <is>
+          <t>Release readiness</t>
+        </is>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="inlineStr">
+        <is>
+          <t>One full hotel day runs from booking to night roll with the real roles: bookings, deposit, check-in, walk-in, room move, charges, discount approval, service request, extension, maintenance, the night roll, check-out, housekeeping, collections and reports.</t>
+        </is>
+      </c>
+      <c r="E146" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F146" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G146" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H146" s="10" t="inlineStr"/>
+      <c r="I146" s="10" t="inlineStr"/>
+      <c r="J146" s="10" t="inlineStr">
+        <is>
+          <t>a hotel with five kinds of staff</t>
+        </is>
+      </c>
+      <c r="K146" s="10" t="inlineStr">
+        <is>
+          <t>the day is run step by step</t>
+        </is>
+      </c>
+      <c r="L146" s="10" t="inlineStr">
+        <is>
+          <t>each step gives the expected result and each refusal fires for the wrong person; the Payments report matches the ledger</t>
+        </is>
+      </c>
+      <c r="M146" s="10" t="inlineStr">
+        <is>
+          <t>day in the life of a hotel</t>
+        </is>
+      </c>
+      <c r="N146" s="10" t="inlineStr">
+        <is>
+          <t>54_day_in_the_life (49)</t>
+        </is>
+      </c>
+      <c r="O146" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P146" s="10" t="inlineStr">
+        <is>
+          <t>Added 10 Oct 2026. Mirrors docs/pilot-dry-run.md; screens and wording still need people.</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P146"/>
+  <dimension ref="A1:P147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12148,6 +12148,88 @@
       <c r="P146" s="10" t="inlineStr">
         <is>
           <t>Added 10 Oct 2026. Mirrors docs/pilot-dry-run.md; screens and wording still need people.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="inlineStr">
+        <is>
+          <t>NFR-007</t>
+        </is>
+      </c>
+      <c r="B147" s="10" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="C147" s="10" t="inlineStr">
+        <is>
+          <t>(all)</t>
+        </is>
+      </c>
+      <c r="D147" s="10" t="inlineStr">
+        <is>
+          <t>Every function we own, helpers included, has a fixed search path so a rogue schema can never change what it does.</t>
+        </is>
+      </c>
+      <c r="E147" s="10" t="inlineStr">
+        <is>
+          <t>BR-017</t>
+        </is>
+      </c>
+      <c r="F147" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G147" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H147" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="10" t="inlineStr">
+        <is>
+          <t>Rule 4</t>
+        </is>
+      </c>
+      <c r="J147" s="10" t="inlineStr">
+        <is>
+          <t>a migration adds or changes a function</t>
+        </is>
+      </c>
+      <c r="K147" s="10" t="inlineStr">
+        <is>
+          <t>the test suite runs</t>
+        </is>
+      </c>
+      <c r="L147" s="10" t="inlineStr">
+        <is>
+          <t>it fails if any function in app or public has no fixed search path</t>
+        </is>
+      </c>
+      <c r="M147" s="10" t="inlineStr">
+        <is>
+          <t>20261018100000_helper_search_path.sql</t>
+        </is>
+      </c>
+      <c r="N147" s="10" t="inlineStr">
+        <is>
+          <t>50_helper_search_path (1)</t>
+        </is>
+      </c>
+      <c r="O147" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P147" s="10" t="inlineStr">
+        <is>
+          <t>QA-07. Fixes 14 helpers the security advisor listed. Added 10 Oct 2026.</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P147"/>
+  <dimension ref="A1:P149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12230,6 +12230,170 @@
       <c r="P147" s="10" t="inlineStr">
         <is>
           <t>QA-07. Fixes 14 helpers the security advisor listed. Added 10 Oct 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="10" t="inlineStr">
+        <is>
+          <t>PLT-014</t>
+        </is>
+      </c>
+      <c r="B148" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>(email)</t>
+        </is>
+      </c>
+      <c r="D148" s="10" t="inlineStr">
+        <is>
+          <t>A hotel is emailed before its free trial ends: 7 days before, 1 day before, and when it ends. The email says what happens, that nothing is deleted, and to contact hello@zikorahq.com. Only the hotel's active System Administrators and General Managers get it, and a hotel that has already chosen a plan gets nothing.</t>
+        </is>
+      </c>
+      <c r="E148" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F148" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G148" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H148" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="10" t="inlineStr">
+        <is>
+          <t>A13, Decision of 10 Oct 2026</t>
+        </is>
+      </c>
+      <c r="J148" s="10" t="inlineStr">
+        <is>
+          <t>a hotel on a free trial</t>
+        </is>
+      </c>
+      <c r="K148" s="10" t="inlineStr">
+        <is>
+          <t>the daily subscription clock runs</t>
+        </is>
+      </c>
+      <c r="L148" s="10" t="inlineStr">
+        <is>
+          <t>each administrator gets each notice once, however many times the clock runs</t>
+        </is>
+      </c>
+      <c r="M148" s="10" t="inlineStr">
+        <is>
+          <t>app.run_subscription_clock, app.send_subscription_notice</t>
+        </is>
+      </c>
+      <c r="N148" s="10" t="inlineStr">
+        <is>
+          <t>51_subscription_notices (12)</t>
+        </is>
+      </c>
+      <c r="O148" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P148" s="10" t="inlineStr">
+        <is>
+          <t>QA-05. No prices in the email, because billing checkout is not switched on. Product name 'Zikora' in the wording is a draft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
+          <t>PLT-015</t>
+        </is>
+      </c>
+      <c r="B149" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
+        <is>
+          <t>(email)</t>
+        </is>
+      </c>
+      <c r="D149" s="10" t="inlineStr">
+        <is>
+          <t>A hotel is emailed when payment is overdue, with 3 days of the 14-day grace left, and when it is suspended. The email says to pay by the date to keep full access, that the hotel then becomes read-only, and to contact hello@zikorahq.com. A hotel that has paid gets nothing.</t>
+        </is>
+      </c>
+      <c r="E149" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F149" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G149" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H149" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="10" t="inlineStr">
+        <is>
+          <t>D7, Decision of 10 Oct 2026</t>
+        </is>
+      </c>
+      <c r="J149" s="10" t="inlineStr">
+        <is>
+          <t>a hotel whose paid period has ended without payment</t>
+        </is>
+      </c>
+      <c r="K149" s="10" t="inlineStr">
+        <is>
+          <t>the daily subscription clock runs</t>
+        </is>
+      </c>
+      <c r="L149" s="10" t="inlineStr">
+        <is>
+          <t>each administrator gets each notice once, and the clock still marks past due and suspends as before</t>
+        </is>
+      </c>
+      <c r="M149" s="10" t="inlineStr">
+        <is>
+          <t>app.run_subscription_clock, app.send_subscription_notice</t>
+        </is>
+      </c>
+      <c r="N149" s="10" t="inlineStr">
+        <is>
+          <t>51_subscription_notices (10)</t>
+        </is>
+      </c>
+      <c r="O149" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P149" s="10" t="inlineStr">
+        <is>
+          <t>QA-05.</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P146"/>
+  <dimension ref="A1:P147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12148,6 +12148,88 @@
       <c r="P146" s="10" t="inlineStr">
         <is>
           <t>Added 10 Oct 2026. Mirrors docs/pilot-dry-run.md; screens and wording still need people.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="inlineStr">
+        <is>
+          <t>DAY-008</t>
+        </is>
+      </c>
+      <c r="B147" s="10" t="inlineStr">
+        <is>
+          <t>Business Date</t>
+        </is>
+      </c>
+      <c r="C147" s="10" t="inlineStr">
+        <is>
+          <t>Notifications bell</t>
+        </is>
+      </c>
+      <c r="D147" s="10" t="inlineStr">
+        <is>
+          <t>When the business date rolls while a cashier shift is still open, the roll goes ahead, records how many shifts were open, and tells users who can run the night audit once.</t>
+        </is>
+      </c>
+      <c r="E147" s="10" t="inlineStr">
+        <is>
+          <t>BR-016</t>
+        </is>
+      </c>
+      <c r="F147" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G147" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H147" s="10" t="inlineStr">
+        <is>
+          <t>fin.nightaudit.run</t>
+        </is>
+      </c>
+      <c r="I147" s="10" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J147" s="10" t="inlineStr">
+        <is>
+          <t>a cashier shift is still open at roll time</t>
+        </is>
+      </c>
+      <c r="K147" s="10" t="inlineStr">
+        <is>
+          <t>the date rolls</t>
+        </is>
+      </c>
+      <c r="L147" s="10" t="inlineStr">
+        <is>
+          <t>the roll succeeds; the roll log and result carry open_shifts; each night audit user gets one rollover_open_shifts notice; none if no shift was open</t>
+        </is>
+      </c>
+      <c r="M147" s="10" t="inlineStr">
+        <is>
+          <t>app.roll_property</t>
+        </is>
+      </c>
+      <c r="N147" s="10" t="inlineStr">
+        <is>
+          <t>55_roll_open_shifts (8)</t>
+        </is>
+      </c>
+      <c r="O147" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P147" s="10" t="inlineStr">
+        <is>
+          <t>Added 10 Oct 2026. Decision B: flag, do not stop (DAY-005 gate stays in R2).</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P150"/>
+  <dimension ref="A1:P151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12476,6 +12476,88 @@
       <c r="P150" s="10" t="inlineStr">
         <is>
           <t>QA-05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="10" t="inlineStr">
+        <is>
+          <t>RES-014</t>
+        </is>
+      </c>
+      <c r="B151" s="10" t="inlineStr">
+        <is>
+          <t>Reservations</t>
+        </is>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
+        <is>
+          <t>Front Desk (check-out)</t>
+        </is>
+      </c>
+      <c r="D151" s="10" t="inlineStr">
+        <is>
+          <t>When a guest checks out before the booked departure, the booking total drops to the nights kept (plus the one same-day night when it applies). Undo check-out on the same day restores the old total.</t>
+        </is>
+      </c>
+      <c r="E151" s="10" t="inlineStr">
+        <is>
+          <t>BR-006</t>
+        </is>
+      </c>
+      <c r="F151" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G151" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H151" s="10" t="inlineStr">
+        <is>
+          <t>fo.checkout</t>
+        </is>
+      </c>
+      <c r="I151" s="10" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="J151" s="10" t="inlineStr">
+        <is>
+          <t>a guest leaves before the booked departure</t>
+        </is>
+      </c>
+      <c r="K151" s="10" t="inlineStr">
+        <is>
+          <t>the check-out is made</t>
+        </is>
+      </c>
+      <c r="L151" s="10" t="inlineStr">
+        <is>
+          <t>total_amount equals the kept nights; undo check-out restores it</t>
+        </is>
+      </c>
+      <c r="M151" s="10" t="inlineStr">
+        <is>
+          <t>public.check_out; public.undo_checkout</t>
+        </is>
+      </c>
+      <c r="N151" s="10" t="inlineStr">
+        <is>
+          <t>56_early_departure_total (4)</t>
+        </is>
+      </c>
+      <c r="O151" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P151" s="10" t="inlineStr">
+        <is>
+          <t>Added 10 Oct 2026 (QA-12).</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P151"/>
+  <dimension ref="A1:Q151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -760,6 +760,7 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
@@ -838,6 +839,7 @@
         </is>
       </c>
       <c r="P2" s="10" t="inlineStr"/>
+      <c r="Q2" s="10" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -916,6 +918,7 @@
         </is>
       </c>
       <c r="P3" s="10" t="inlineStr"/>
+      <c r="Q3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -994,6 +997,7 @@
         </is>
       </c>
       <c r="P4" s="10" t="inlineStr"/>
+      <c r="Q4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -1072,6 +1076,7 @@
         </is>
       </c>
       <c r="P5" s="10" t="inlineStr"/>
+      <c r="Q5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -1150,6 +1155,7 @@
         </is>
       </c>
       <c r="P6" s="10" t="inlineStr"/>
+      <c r="Q6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -1228,6 +1234,7 @@
         </is>
       </c>
       <c r="P7" s="10" t="inlineStr"/>
+      <c r="Q7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -1310,6 +1317,7 @@
           <t>Adding a property: System Administrator and General Manager (ADM-002), within plans.max_properties.</t>
         </is>
       </c>
+      <c r="Q8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -1392,6 +1400,7 @@
           <t>Platform console /platform (wave 2 item 2): extend trial, activate or extend paid period, suspend, change plan, cancel; each with a reason, logged in subscription_history with the operator.</t>
         </is>
       </c>
+      <c r="Q9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -1474,6 +1483,7 @@
           <t>Corrected 6 Oct 2026: before wave 2 item 2 there was no platform staff role at all; the earlier "Built, no tagged test" was wrong.</t>
         </is>
       </c>
+      <c r="Q10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -1556,6 +1566,7 @@
           <t>Database done 8 Oct 2026. Screens for the hotel (Admin) and the operator (platform console) follow. New permission adm.support.manage reaches System Administrator and General Manager only.</t>
         </is>
       </c>
+      <c r="Q11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -1634,6 +1645,7 @@
         </is>
       </c>
       <c r="P12" s="10" t="inlineStr"/>
+      <c r="Q12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -1716,6 +1728,7 @@
           <t>Needs PAYSTACK_SECRET_KEY and the webhook address set in Paystack. Prices are empty until A16 is decided.</t>
         </is>
       </c>
+      <c r="Q13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -1794,6 +1807,7 @@
         </is>
       </c>
       <c r="P14" s="10" t="inlineStr"/>
+      <c r="Q14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -1876,6 +1890,7 @@
           <t>Invites are sent by a Vercel server function (not an Edge Function).</t>
         </is>
       </c>
+      <c r="Q15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -1954,6 +1969,7 @@
         </is>
       </c>
       <c r="P16" s="10" t="inlineStr"/>
+      <c r="Q16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -2032,6 +2048,7 @@
         </is>
       </c>
       <c r="P17" s="10" t="inlineStr"/>
+      <c r="Q17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -2110,6 +2127,7 @@
         </is>
       </c>
       <c r="P18" s="10" t="inlineStr"/>
+      <c r="Q18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -2188,6 +2206,7 @@
         </is>
       </c>
       <c r="P19" s="10" t="inlineStr"/>
+      <c r="Q19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
@@ -2266,6 +2285,7 @@
         </is>
       </c>
       <c r="P20" s="10" t="inlineStr"/>
+      <c r="Q20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -2344,6 +2364,7 @@
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr"/>
+      <c r="Q21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -2422,6 +2443,7 @@
         </is>
       </c>
       <c r="P22" s="10" t="inlineStr"/>
+      <c r="Q22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -2504,6 +2526,7 @@
           <t>export_data (audited), Reports &gt; Export.</t>
         </is>
       </c>
+      <c r="Q23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -2582,6 +2605,7 @@
         </is>
       </c>
       <c r="P24" s="10" t="inlineStr"/>
+      <c r="Q24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -2661,9 +2685,10 @@
       </c>
       <c r="P25" s="10" t="inlineStr">
         <is>
-          <t>Corrected 6 Oct 2026: room types and occupancy limits (save_room_type, max adults and children; Setup, Room types) exist; the overbooking allowance does not exist anywhere in the app.</t>
-        </is>
-      </c>
+          <t>Room types and occupancy limits are built (save_room_type: max adults and children; Setup, Room types). The overbooking allowance is not built: decision pending (QA-17, 11 Oct 2026). Recommended: skip it for the pilot.</t>
+        </is>
+      </c>
+      <c r="Q25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
@@ -2746,6 +2771,7 @@
           <t>A room cannot be retired while a guest is in it ([E_ROOM_OCCUPIED], checked first) or while upcoming bookings are assigned to it ([E_ROOM_BOOKED], names up to 5 booking numbers): confirmed, or tentative with an unexpired hold, from the business date forward (decisions of 6 Oct 2026). Retiring a room that is already retired is safe to repeat; renaming and floor changes still work.</t>
         </is>
       </c>
+      <c r="Q26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
@@ -2824,6 +2850,7 @@
         </is>
       </c>
       <c r="P27" s="10" t="inlineStr"/>
+      <c r="Q27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -2902,6 +2929,7 @@
         </is>
       </c>
       <c r="P28" s="10" t="inlineStr"/>
+      <c r="Q28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -2980,6 +3008,7 @@
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr"/>
+      <c r="Q29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
@@ -3058,6 +3087,7 @@
         </is>
       </c>
       <c r="P30" s="10" t="inlineStr"/>
+      <c r="Q30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
@@ -3136,6 +3166,7 @@
         </is>
       </c>
       <c r="P31" s="10" t="inlineStr"/>
+      <c r="Q31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
@@ -3214,6 +3245,7 @@
         </is>
       </c>
       <c r="P32" s="10" t="inlineStr"/>
+      <c r="Q32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
@@ -3292,6 +3324,7 @@
         </is>
       </c>
       <c r="P33" s="10" t="inlineStr"/>
+      <c r="Q33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
@@ -3370,6 +3403,7 @@
         </is>
       </c>
       <c r="P34" s="10" t="inlineStr"/>
+      <c r="Q34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
@@ -3448,6 +3482,7 @@
         </is>
       </c>
       <c r="P35" s="10" t="inlineStr"/>
+      <c r="Q35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
@@ -3526,6 +3561,7 @@
         </is>
       </c>
       <c r="P36" s="10" t="inlineStr"/>
+      <c r="Q36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
@@ -3604,6 +3640,7 @@
         </is>
       </c>
       <c r="P37" s="10" t="inlineStr"/>
+      <c r="Q37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
@@ -3682,6 +3719,7 @@
         </is>
       </c>
       <c r="P38" s="10" t="inlineStr"/>
+      <c r="Q38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -3760,6 +3798,7 @@
         </is>
       </c>
       <c r="P39" s="10" t="inlineStr"/>
+      <c r="Q39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
@@ -3838,6 +3877,7 @@
         </is>
       </c>
       <c r="P40" s="10" t="inlineStr"/>
+      <c r="Q40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
@@ -3916,6 +3956,7 @@
         </is>
       </c>
       <c r="P41" s="10" t="inlineStr"/>
+      <c r="Q41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
@@ -3994,6 +4035,7 @@
         </is>
       </c>
       <c r="P42" s="10" t="inlineStr"/>
+      <c r="Q42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
@@ -4073,7 +4115,12 @@
       </c>
       <c r="P43" s="10" t="inlineStr">
         <is>
-          <t>save_group_booking exists and the booking form picks a group; there is no screen to create a group.</t>
+          <t>save_group_booking exists. The booking form creates a group (Add group) and picks one; Reservations</t>
+        </is>
+      </c>
+      <c r="Q43" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Groups lists each group and opens it with its rooms and totals. Browser test: e2e/group-bookings.spec.ts.</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4202,12 @@
       </c>
       <c r="P44" s="10" t="inlineStr">
         <is>
-          <t>set_arrival_ready exists; no screen shows the flag yet (skipped 6 Oct 2026).</t>
+          <t>set_arrival_ready exists. The booking page has Mark ready and Not ready; the Front Desk arrivals list and the group page show Ready (QA-15</t>
+        </is>
+      </c>
+      <c r="Q44" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 11 Oct 2026).</t>
         </is>
       </c>
     </row>
@@ -4236,6 +4288,7 @@
         </is>
       </c>
       <c r="P45" s="10" t="inlineStr"/>
+      <c r="Q45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
@@ -4314,6 +4367,7 @@
         </is>
       </c>
       <c r="P46" s="10" t="inlineStr"/>
+      <c r="Q46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
@@ -4396,6 +4450,7 @@
           <t>The check-in and walk-in screens force the registration card tick; a direct database call that omits it is not refused (decision 6 Oct 2026). Drawn signature later.</t>
         </is>
       </c>
+      <c r="Q47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
@@ -4474,6 +4529,7 @@
         </is>
       </c>
       <c r="P48" s="10" t="inlineStr"/>
+      <c r="Q48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
@@ -4552,6 +4608,7 @@
         </is>
       </c>
       <c r="P49" s="10" t="inlineStr"/>
+      <c r="Q49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
@@ -4630,6 +4687,7 @@
         </is>
       </c>
       <c r="P50" s="10" t="inlineStr"/>
+      <c r="Q50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
@@ -4712,6 +4770,7 @@
           <t>Dearer room type: front desk charges the new rate; keeping it needs fo.upgrade.complimentary (SYSADMIN, GM, FOM), audited.</t>
         </is>
       </c>
+      <c r="Q51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
@@ -4790,6 +4849,7 @@
         </is>
       </c>
       <c r="P52" s="10" t="inlineStr"/>
+      <c r="Q52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
@@ -4868,6 +4928,7 @@
         </is>
       </c>
       <c r="P53" s="10" t="inlineStr"/>
+      <c r="Q53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
@@ -4946,6 +5007,7 @@
         </is>
       </c>
       <c r="P54" s="10" t="inlineStr"/>
+      <c r="Q54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
@@ -5024,6 +5086,7 @@
         </is>
       </c>
       <c r="P55" s="10" t="inlineStr"/>
+      <c r="Q55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
@@ -5102,6 +5165,7 @@
         </is>
       </c>
       <c r="P56" s="10" t="inlineStr"/>
+      <c r="Q56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
@@ -5180,6 +5244,7 @@
         </is>
       </c>
       <c r="P57" s="10" t="inlineStr"/>
+      <c r="Q57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
@@ -5258,6 +5323,7 @@
         </is>
       </c>
       <c r="P58" s="10" t="inlineStr"/>
+      <c r="Q58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
@@ -5336,6 +5402,7 @@
         </is>
       </c>
       <c r="P59" s="10" t="inlineStr"/>
+      <c r="Q59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
@@ -5414,6 +5481,7 @@
         </is>
       </c>
       <c r="P60" s="10" t="inlineStr"/>
+      <c r="Q60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
@@ -5492,6 +5560,7 @@
         </is>
       </c>
       <c r="P61" s="10" t="inlineStr"/>
+      <c r="Q61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
@@ -5570,6 +5639,7 @@
         </is>
       </c>
       <c r="P62" s="10" t="inlineStr"/>
+      <c r="Q62" s="10" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
@@ -5648,6 +5718,7 @@
         </is>
       </c>
       <c r="P63" s="10" t="inlineStr"/>
+      <c r="Q63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
@@ -5726,6 +5797,7 @@
         </is>
       </c>
       <c r="P64" s="10" t="inlineStr"/>
+      <c r="Q64" s="10" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
@@ -5804,6 +5876,7 @@
         </is>
       </c>
       <c r="P65" s="10" t="inlineStr"/>
+      <c r="Q65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
@@ -5882,6 +5955,7 @@
         </is>
       </c>
       <c r="P66" s="10" t="inlineStr"/>
+      <c r="Q66" s="10" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
@@ -5960,6 +6034,7 @@
         </is>
       </c>
       <c r="P67" s="10" t="inlineStr"/>
+      <c r="Q67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
@@ -6038,6 +6113,7 @@
         </is>
       </c>
       <c r="P68" s="10" t="inlineStr"/>
+      <c r="Q68" s="10" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
@@ -6116,6 +6192,7 @@
         </is>
       </c>
       <c r="P69" s="10" t="inlineStr"/>
+      <c r="Q69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
@@ -6194,6 +6271,7 @@
         </is>
       </c>
       <c r="P70" s="10" t="inlineStr"/>
+      <c r="Q70" s="10" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
@@ -6272,6 +6350,7 @@
         </is>
       </c>
       <c r="P71" s="10" t="inlineStr"/>
+      <c r="Q71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
@@ -6350,6 +6429,7 @@
         </is>
       </c>
       <c r="P72" s="10" t="inlineStr"/>
+      <c r="Q72" s="10" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
@@ -6428,6 +6508,7 @@
         </is>
       </c>
       <c r="P73" s="10" t="inlineStr"/>
+      <c r="Q73" s="10" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
@@ -6506,6 +6587,7 @@
         </is>
       </c>
       <c r="P74" s="10" t="inlineStr"/>
+      <c r="Q74" s="10" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
@@ -6584,6 +6666,7 @@
         </is>
       </c>
       <c r="P75" s="10" t="inlineStr"/>
+      <c r="Q75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
@@ -6662,6 +6745,7 @@
         </is>
       </c>
       <c r="P76" s="10" t="inlineStr"/>
+      <c r="Q76" s="10" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
@@ -6740,6 +6824,7 @@
         </is>
       </c>
       <c r="P77" s="10" t="inlineStr"/>
+      <c r="Q77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
@@ -6818,6 +6903,7 @@
         </is>
       </c>
       <c r="P78" s="10" t="inlineStr"/>
+      <c r="Q78" s="10" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
@@ -6896,6 +6982,7 @@
         </is>
       </c>
       <c r="P79" s="10" t="inlineStr"/>
+      <c r="Q79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
@@ -6974,6 +7061,7 @@
         </is>
       </c>
       <c r="P80" s="10" t="inlineStr"/>
+      <c r="Q80" s="10" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
@@ -7052,6 +7140,7 @@
         </is>
       </c>
       <c r="P81" s="10" t="inlineStr"/>
+      <c r="Q81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
@@ -7130,6 +7219,7 @@
         </is>
       </c>
       <c r="P82" s="10" t="inlineStr"/>
+      <c r="Q82" s="10" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
@@ -7208,6 +7298,7 @@
         </is>
       </c>
       <c r="P83" s="10" t="inlineStr"/>
+      <c r="Q83" s="10" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
@@ -7286,6 +7377,7 @@
         </is>
       </c>
       <c r="P84" s="10" t="inlineStr"/>
+      <c r="Q84" s="10" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
@@ -7364,6 +7456,7 @@
         </is>
       </c>
       <c r="P85" s="10" t="inlineStr"/>
+      <c r="Q85" s="10" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
@@ -7442,6 +7535,7 @@
         </is>
       </c>
       <c r="P86" s="10" t="inlineStr"/>
+      <c r="Q86" s="10" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
@@ -7520,6 +7614,7 @@
         </is>
       </c>
       <c r="P87" s="10" t="inlineStr"/>
+      <c r="Q87" s="10" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
@@ -7598,6 +7693,7 @@
         </is>
       </c>
       <c r="P88" s="10" t="inlineStr"/>
+      <c r="Q88" s="10" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
@@ -7676,6 +7772,7 @@
         </is>
       </c>
       <c r="P89" s="10" t="inlineStr"/>
+      <c r="Q89" s="10" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
@@ -7754,6 +7851,7 @@
         </is>
       </c>
       <c r="P90" s="10" t="inlineStr"/>
+      <c r="Q90" s="10" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
@@ -7832,6 +7930,7 @@
         </is>
       </c>
       <c r="P91" s="10" t="inlineStr"/>
+      <c r="Q91" s="10" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
@@ -7910,6 +8009,7 @@
         </is>
       </c>
       <c r="P92" s="10" t="inlineStr"/>
+      <c r="Q92" s="10" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
@@ -7988,6 +8088,7 @@
         </is>
       </c>
       <c r="P93" s="10" t="inlineStr"/>
+      <c r="Q93" s="10" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
@@ -8066,6 +8167,7 @@
         </is>
       </c>
       <c r="P94" s="10" t="inlineStr"/>
+      <c r="Q94" s="10" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
@@ -8144,6 +8246,7 @@
         </is>
       </c>
       <c r="P95" s="10" t="inlineStr"/>
+      <c r="Q95" s="10" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
@@ -8226,6 +8329,7 @@
           <t>Cashier shift page built (open, close with counts, review, reconcile). Not covered by a browser test yet. New permission fin.shift.reconcile goes to built-in roles only.</t>
         </is>
       </c>
+      <c r="Q96" s="10" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
@@ -8304,6 +8408,7 @@
         </is>
       </c>
       <c r="P97" s="10" t="inlineStr"/>
+      <c r="Q97" s="10" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
@@ -8382,6 +8487,7 @@
         </is>
       </c>
       <c r="P98" s="10" t="inlineStr"/>
+      <c r="Q98" s="10" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
@@ -8460,6 +8566,7 @@
         </is>
       </c>
       <c r="P99" s="10" t="inlineStr"/>
+      <c r="Q99" s="10" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
@@ -8538,6 +8645,7 @@
         </is>
       </c>
       <c r="P100" s="10" t="inlineStr"/>
+      <c r="Q100" s="10" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
@@ -8620,6 +8728,7 @@
           <t>Flags shown in Admin, Business date. The gate that stops the roll while a blocking flag is open is not built.</t>
         </is>
       </c>
+      <c r="Q101" s="10" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
@@ -8702,6 +8811,7 @@
           <t>Decided by Peter on 30 Sep 2026 (answer 5) and confirmed on 1 Oct 2026: same-day stays are charged one night; a manager can waive it with a reason.</t>
         </is>
       </c>
+      <c r="Q102" s="10" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
@@ -8780,6 +8890,7 @@
         </is>
       </c>
       <c r="P103" s="10" t="inlineStr"/>
+      <c r="Q103" s="10" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
@@ -8858,6 +8969,7 @@
         </is>
       </c>
       <c r="P104" s="10" t="inlineStr"/>
+      <c r="Q104" s="10" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
@@ -8936,6 +9048,7 @@
         </is>
       </c>
       <c r="P105" s="10" t="inlineStr"/>
+      <c r="Q105" s="10" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
@@ -9018,6 +9131,7 @@
           <t>Reports screen: KPIs, revenue by charge code, outstanding balances, payments, cancellations and stay length, balances by guest, export.</t>
         </is>
       </c>
+      <c r="Q106" s="10" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
@@ -9096,6 +9210,7 @@
         </is>
       </c>
       <c r="P107" s="10" t="inlineStr"/>
+      <c r="Q107" s="10" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
@@ -9174,6 +9289,7 @@
         </is>
       </c>
       <c r="P108" s="10" t="inlineStr"/>
+      <c r="Q108" s="10" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
@@ -9252,6 +9368,7 @@
         </is>
       </c>
       <c r="P109" s="10" t="inlineStr"/>
+      <c r="Q109" s="10" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
@@ -9330,6 +9447,7 @@
         </is>
       </c>
       <c r="P110" s="10" t="inlineStr"/>
+      <c r="Q110" s="10" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
@@ -9408,6 +9526,7 @@
         </is>
       </c>
       <c r="P111" s="10" t="inlineStr"/>
+      <c r="Q111" s="10" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
@@ -9486,6 +9605,7 @@
         </is>
       </c>
       <c r="P112" s="10" t="inlineStr"/>
+      <c r="Q112" s="10" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
@@ -9564,6 +9684,7 @@
         </is>
       </c>
       <c r="P113" s="10" t="inlineStr"/>
+      <c r="Q113" s="10" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
@@ -9646,6 +9767,7 @@
           <t>Method only; the accountant still signs off the rates (A11)</t>
         </is>
       </c>
+      <c r="Q114" s="10" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
@@ -9728,6 +9850,7 @@
           <t>Day totals and fields are stored in the invoice header when it is issued</t>
         </is>
       </c>
+      <c r="Q115" s="10" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
@@ -9810,6 +9933,7 @@
           <t>Month comes from the business date, not the clock. No hotel code in the number yet.</t>
         </is>
       </c>
+      <c r="Q116" s="10" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
@@ -9888,6 +10012,7 @@
         </is>
       </c>
       <c r="P117" s="10" t="inlineStr"/>
+      <c r="Q117" s="10" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
@@ -9966,6 +10091,7 @@
         </is>
       </c>
       <c r="P118" s="10" t="inlineStr"/>
+      <c r="Q118" s="10" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
@@ -10044,6 +10170,7 @@
         </is>
       </c>
       <c r="P119" s="10" t="inlineStr"/>
+      <c r="Q119" s="10" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
@@ -10122,6 +10249,7 @@
         </is>
       </c>
       <c r="P120" s="10" t="inlineStr"/>
+      <c r="Q120" s="10" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
@@ -10200,6 +10328,7 @@
         </is>
       </c>
       <c r="P121" s="10" t="inlineStr"/>
+      <c r="Q121" s="10" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
@@ -10278,6 +10407,7 @@
         </is>
       </c>
       <c r="P122" s="10" t="inlineStr"/>
+      <c r="Q122" s="10" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
@@ -10356,6 +10486,7 @@
           <t>Custom roles copied earlier do not get the new permission; say so when releasing.</t>
         </is>
       </c>
+      <c r="Q123" s="10" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
@@ -10434,6 +10565,7 @@
           <t>Figures are read from each branch own business date. No arithmetic in the browser.</t>
         </is>
       </c>
+      <c r="Q124" s="10" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
@@ -10512,6 +10644,7 @@
           <t>Access is per branch, using the existing role assignment screen.</t>
         </is>
       </c>
+      <c r="Q125" s="10" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
@@ -10590,6 +10723,7 @@
           <t>Taxes, charge codes and payment methods already arrive with every new branch.</t>
         </is>
       </c>
+      <c r="Q126" s="10" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
@@ -10668,6 +10802,7 @@
           <t>Bookings counted by arrival date; revenue by posting date.</t>
         </is>
       </c>
+      <c r="Q127" s="10" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
@@ -10746,6 +10881,7 @@
           <t>Guests still staying count as current.</t>
         </is>
       </c>
+      <c r="Q128" s="10" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
@@ -10828,6 +10964,7 @@
           <t>Email delivery waits on the sending domain and email account. Collected money nets payment reversals the same day (migration 20261015130000).</t>
         </is>
       </c>
+      <c r="Q129" s="10" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
@@ -10906,6 +11043,7 @@
           <t>Custom roles copied earlier do not get adm.ai.manage.</t>
         </is>
       </c>
+      <c r="Q130" s="10" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
@@ -10984,6 +11122,7 @@
           <t>Overdue means unpaid more than 30 days after departure.</t>
         </is>
       </c>
+      <c r="Q131" s="10" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
@@ -11058,6 +11197,7 @@
         </is>
       </c>
       <c r="P132" s="10" t="inlineStr"/>
+      <c r="Q132" s="10" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
@@ -11132,6 +11272,7 @@
         </is>
       </c>
       <c r="P133" s="10" t="inlineStr"/>
+      <c r="Q133" s="10" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
@@ -11210,6 +11351,7 @@
           <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
         </is>
       </c>
+      <c r="Q134" s="10" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
@@ -11288,6 +11430,7 @@
           <t>The AI only drafts the list. This function is the check.</t>
         </is>
       </c>
+      <c r="Q135" s="10" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
@@ -11362,6 +11505,7 @@
         </is>
       </c>
       <c r="P136" s="10" t="inlineStr"/>
+      <c r="Q136" s="10" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
@@ -11440,6 +11584,7 @@
           <t>Needs ANTHROPIC_API_KEY on the server. Not set yet.</t>
         </is>
       </c>
+      <c r="Q137" s="10" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
@@ -11522,6 +11667,7 @@
           <t>Read-only function, no stored progress. Staff step counts people with a role at the property (two or more).</t>
         </is>
       </c>
+      <c r="Q138" s="10" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
@@ -11604,6 +11750,7 @@
           <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
         </is>
       </c>
+      <c r="Q139" s="10" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
@@ -11682,6 +11829,7 @@
           <t>Added 8 Oct 2026. The columns existed since the reservations release; this adds the screen and the function.</t>
         </is>
       </c>
+      <c r="Q140" s="10" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
@@ -11760,6 +11908,7 @@
           <t>No database change. Reads v_arrivals, v_in_house and v_folio_balances. Added 8 Oct 2026.</t>
         </is>
       </c>
+      <c r="Q141" s="10" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
@@ -11842,6 +11991,7 @@
           <t>Added 8 Oct 2026. Warning only; the hard gate stays in R2 (DAY-005).</t>
         </is>
       </c>
+      <c r="Q142" s="10" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
@@ -11920,6 +12070,7 @@
           <t>Added 9 Oct 2026. Read-only; no money is changed.</t>
         </is>
       </c>
+      <c r="Q143" s="10" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
@@ -11998,6 +12149,7 @@
           <t>Added 10 Oct 2026. The Payments report counted only payments and refunds before this. Cashier shift counts stay separate on purpose: they count what the drawer should hold.</t>
         </is>
       </c>
+      <c r="Q144" s="10" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
@@ -12076,6 +12228,7 @@
           <t>Added 10 Oct 2026. Notes are not ledger rows; they never change a balance.</t>
         </is>
       </c>
+      <c r="Q145" s="10" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
@@ -12150,6 +12303,7 @@
           <t>Added 10 Oct 2026. Mirrors docs/pilot-dry-run.md; screens and wording still need people.</t>
         </is>
       </c>
+      <c r="Q146" s="10" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
@@ -12232,6 +12386,7 @@
           <t>Added 10 Oct 2026. Decision B: flag, do not stop (DAY-005 gate stays in R2).</t>
         </is>
       </c>
+      <c r="Q147" s="10" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="10" t="inlineStr">
@@ -12314,6 +12469,7 @@
           <t>QA-07. Fixes 14 helpers the security advisor listed. Added 10 Oct 2026.</t>
         </is>
       </c>
+      <c r="Q148" s="10" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
@@ -12396,6 +12552,7 @@
           <t>QA-05. No prices in the email, because billing checkout is not switched on. Product name 'Zikora' in the wording is a draft.</t>
         </is>
       </c>
+      <c r="Q149" s="10" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="10" t="inlineStr">
@@ -12478,6 +12635,7 @@
           <t>QA-05.</t>
         </is>
       </c>
+      <c r="Q150" s="10" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
@@ -12560,6 +12718,7 @@
           <t>Added 10 Oct 2026 (QA-12).</t>
         </is>
       </c>
+      <c r="Q151" s="10" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q151"/>
+  <dimension ref="A1:Q155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12719,6 +12719,338 @@
         </is>
       </c>
       <c r="Q151" s="10" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t>OFF-001</t>
+        </is>
+      </c>
+      <c r="B152" s="10" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>(all signed-in screens)</t>
+        </is>
+      </c>
+      <c r="D152" s="10" t="inlineStr">
+        <is>
+          <t>When the connection drops, the lists a signed-in user last loaded (arrivals, in house, room board, housekeeping tasks, open folios) stay readable on that device. A bar says 'No connection'.</t>
+        </is>
+      </c>
+      <c r="E152" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F152" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G152" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H152" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="10" t="inlineStr">
+        <is>
+          <t>A12; docs/offline-design.md</t>
+        </is>
+      </c>
+      <c r="J152" s="10" t="inlineStr">
+        <is>
+          <t>a user signed in on this device who loaded the front desk</t>
+        </is>
+      </c>
+      <c r="K152" s="10" t="inlineStr">
+        <is>
+          <t>the connection drops and the page is reloaded</t>
+        </is>
+      </c>
+      <c r="L152" s="10" t="inlineStr">
+        <is>
+          <t>the saved lists show and the No connection bar appears</t>
+        </is>
+      </c>
+      <c r="M152" s="10" t="inlineStr">
+        <is>
+          <t>public/sw.js; src/lib/offline/cache.ts; src/components/offline-banner.tsx</t>
+        </is>
+      </c>
+      <c r="N152" s="10" t="inlineStr">
+        <is>
+          <t>e2e/offline-read.spec.ts</t>
+        </is>
+      </c>
+      <c r="O152" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P152" s="10" t="inlineStr">
+        <is>
+          <t>Stage 1. Only data the user's role may see is saved. ID numbers and photos are never saved.</t>
+        </is>
+      </c>
+      <c r="Q152" s="10" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="10" t="inlineStr">
+        <is>
+          <t>OFF-002</t>
+        </is>
+      </c>
+      <c r="B153" s="10" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
+        <is>
+          <t>(sign-out)</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="inlineStr">
+        <is>
+          <t>Saved offline data is removed from the device on sign-out.</t>
+        </is>
+      </c>
+      <c r="E153" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F153" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G153" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H153" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="10" t="inlineStr">
+        <is>
+          <t>docs/offline-design.md</t>
+        </is>
+      </c>
+      <c r="J153" s="10" t="inlineStr">
+        <is>
+          <t>a device holding saved lists</t>
+        </is>
+      </c>
+      <c r="K153" s="10" t="inlineStr">
+        <is>
+          <t>the user signs out</t>
+        </is>
+      </c>
+      <c r="L153" s="10" t="inlineStr">
+        <is>
+          <t>the saved lists are gone</t>
+        </is>
+      </c>
+      <c r="M153" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/offline/cache.ts clearOfflineData; src/routes/__root.tsx</t>
+        </is>
+      </c>
+      <c r="N153" s="10" t="inlineStr">
+        <is>
+          <t>e2e/offline-read.spec.ts</t>
+        </is>
+      </c>
+      <c r="O153" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P153" s="10" t="inlineStr">
+        <is>
+          <t>Stage 1. Sign-out is refused while actions still wait to send (OFF-004).</t>
+        </is>
+      </c>
+      <c r="Q153" s="10" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="10" t="inlineStr">
+        <is>
+          <t>OFF-003</t>
+        </is>
+      </c>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
+        <is>
+          <t>Folio; My tasks</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="inlineStr">
+        <is>
+          <t>A charge, a payment, a cleaning task start and a cleaning task completion entered with no connection wait on the device and are sent oldest first when the connection returns. The bar shows how many wait and any that were refused, with Try again and Remove.</t>
+        </is>
+      </c>
+      <c r="E154" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F154" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G154" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H154" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" s="10" t="inlineStr">
+        <is>
+          <t>A12; docs/offline-design.md</t>
+        </is>
+      </c>
+      <c r="J154" s="10" t="inlineStr">
+        <is>
+          <t>no connection</t>
+        </is>
+      </c>
+      <c r="K154" s="10" t="inlineStr">
+        <is>
+          <t>a clerk posts a charge or starts a cleaning task</t>
+        </is>
+      </c>
+      <c r="L154" s="10" t="inlineStr">
+        <is>
+          <t>it waits on the device, then posts once when the connection returns</t>
+        </is>
+      </c>
+      <c r="M154" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/offline/queue.ts; src/lib/folios.tsx; src/lib/housekeeping.tsx</t>
+        </is>
+      </c>
+      <c r="N154" s="10" t="inlineStr">
+        <is>
+          <t>e2e/offline-write.spec.ts</t>
+        </is>
+      </c>
+      <c r="O154" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P154" s="10" t="inlineStr">
+        <is>
+          <t>Stage 2. Approvals, check-in, check-out and room moves stay online only (stage 3 is not built).</t>
+        </is>
+      </c>
+      <c r="Q154" s="10" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="10" t="inlineStr">
+        <is>
+          <t>OFF-004</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="C155" s="10" t="inlineStr">
+        <is>
+          <t>Folio</t>
+        </is>
+      </c>
+      <c r="D155" s="10" t="inlineStr">
+        <is>
+          <t>A charge or payment that waits on the device carries its repeat-safe key, so sending it twice never posts twice.</t>
+        </is>
+      </c>
+      <c r="E155" s="10" t="inlineStr">
+        <is>
+          <t>FIN-008</t>
+        </is>
+      </c>
+      <c r="F155" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G155" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H155" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="10" t="inlineStr">
+        <is>
+          <t>Rule: idempotency keys</t>
+        </is>
+      </c>
+      <c r="J155" s="10" t="inlineStr">
+        <is>
+          <t>a queued charge</t>
+        </is>
+      </c>
+      <c r="K155" s="10" t="inlineStr">
+        <is>
+          <t>it is sent twice</t>
+        </is>
+      </c>
+      <c r="L155" s="10" t="inlineStr">
+        <is>
+          <t>the balance rises once</t>
+        </is>
+      </c>
+      <c r="M155" s="10" t="inlineStr">
+        <is>
+          <t>queue keeps the idempotency key; post_charge key check</t>
+        </is>
+      </c>
+      <c r="N155" s="10" t="inlineStr">
+        <is>
+          <t>e2e/offline-write.spec.ts</t>
+        </is>
+      </c>
+      <c r="O155" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P155" s="10" t="inlineStr">
+        <is>
+          <t>Stage 2.</t>
+        </is>
+      </c>
+      <c r="Q155" s="10" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'R1 Requirements'!$A$1:$O$108</definedName>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q151"/>
+  <dimension ref="A1:Q152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12719,6 +12719,89 @@
         </is>
       </c>
       <c r="Q151" s="10" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t>NFR-008</t>
+        </is>
+      </c>
+      <c r="B152" s="10" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>(all)</t>
+        </is>
+      </c>
+      <c r="D152" s="10" t="inlineStr">
+        <is>
+          <t>Every screen works on a phone (360 pixels wide) and a tablet (768): the page title is readable, nothing scrolls sideways, tables show every column as cards on a phone, tabs, buttons, links and switches are easy to hit, text is at least 12 pixels, fields are 16 pixels so an iPhone does not zoom in, and pop-up forms fit the screen.</t>
+        </is>
+      </c>
+      <c r="E152" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F152" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G152" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H152" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="10" t="inlineStr">
+        <is>
+          <t>Mobile layout (10 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="J152" s="10" t="inlineStr">
+        <is>
+          <t>a busy hotel (long names, a folio with charges, tasks, tickets, a shift)</t>
+        </is>
+      </c>
+      <c r="K152" s="10" t="inlineStr">
+        <is>
+          <t>every screen and the main pop-up forms are opened at 360 and 768 pixels wide</t>
+        </is>
+      </c>
+      <c r="L152" s="10" t="inlineStr">
+        <is>
+          <t>the title fills the width, nothing scrolls sideways, phone tables are cards, targets are 24 to 40 pixels or more, text is 12 pixels or more, fields are 16 pixels, and pop-ups keep a margin and their buttons in reach</t>
+        </is>
+      </c>
+      <c r="M152" s="10" t="inlineStr">
+        <is>
+          <t>PageHeader stacks on a phone; Table shows cards under 768 pixels (src/styles.css) and a scroll shadow above that; tabs, checkboxes, switches and links get larger targets; fields are 16 pixels on a phone; dialogs fit the screen with pinned buttons</t>
+        </is>
+      </c>
+      <c r="N152" s="10" t="inlineStr">
+        <is>
+          <t>phone-layout (2); phone-width (3)</t>
+        </is>
+      </c>
+      <c r="O152" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P152" s="10" t="inlineStr">
+        <is>
+          <t>Added 11 Oct 2026. The availability calendar and the downtime pack are true grids and scroll inside their own box on purpose.</t>
+        </is>
+      </c>
+      <c r="Q152" s="10" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'R1 Requirements'!$A$1:$O$108</definedName>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q158"/>
+  <dimension ref="A1:Q159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>a tenant, a 30-day trial, one property with country defaults, and the System Administrator and General Manager roles exist for them</t>
+          <t>a tenant, a 60-day trial, one property with country defaults, and the System Administrator and General Manager roles exist for them</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
@@ -13300,6 +13300,89 @@
         </is>
       </c>
       <c r="Q158" s="10" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="10" t="inlineStr">
+        <is>
+          <t>PLT-016</t>
+        </is>
+      </c>
+      <c r="B159" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
+          <t>(signup page), (banner), pricing page</t>
+        </is>
+      </c>
+      <c r="D159" s="10" t="inlineStr">
+        <is>
+          <t>A new hotel gets a 60-day free trial with every feature and no card. After it, the hotel becomes read-only until a plan is switched on.</t>
+        </is>
+      </c>
+      <c r="E159" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F159" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G159" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H159" s="10" t="inlineStr">
+        <is>
+          <t>(any signed-in user)</t>
+        </is>
+      </c>
+      <c r="I159" s="10" t="inlineStr">
+        <is>
+          <t>A13, Decision of 12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="J159" s="10" t="inlineStr">
+        <is>
+          <t>a signed-in user with a confirmed email and no hotel</t>
+        </is>
+      </c>
+      <c r="K159" s="10" t="inlineStr">
+        <is>
+          <t>they create their hotel</t>
+        </is>
+      </c>
+      <c r="L159" s="10" t="inlineStr">
+        <is>
+          <t>the trial ends 60 days after the hotel was created, and the status is trial</t>
+        </is>
+      </c>
+      <c r="M159" s="10" t="inlineStr">
+        <is>
+          <t>create_hotel</t>
+        </is>
+      </c>
+      <c r="N159" s="10" t="inlineStr">
+        <is>
+          <t>17_more_features (1)</t>
+        </is>
+      </c>
+      <c r="O159" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P159" s="10" t="inlineStr">
+        <is>
+          <t>Peter decided on 12 Oct 2026 (was 30 days). Hotels already on trial keep their dates; platform staff can extend one by hand. Plan choice at signup is not built: every new hotel starts on Starter (20 rooms).</t>
+        </is>
+      </c>
+      <c r="Q159" s="10" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q159"/>
+  <dimension ref="A1:Q160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13383,6 +13383,89 @@
         </is>
       </c>
       <c r="Q159" s="10" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="10" t="inlineStr">
+        <is>
+          <t>PLT-017</t>
+        </is>
+      </c>
+      <c r="B160" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>(signup page), (banner), pricing page</t>
+        </is>
+      </c>
+      <c r="D160" s="10" t="inlineStr">
+        <is>
+          <t>Plan prices are set in naira: Starter 20,000, Standard 45,000, Pro 80,000 a month; a year costs ten months; Enterprise is quoted and has no online price.</t>
+        </is>
+      </c>
+      <c r="E160" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F160" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G160" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H160" s="10" t="inlineStr">
+        <is>
+          <t>(any signed-in user)</t>
+        </is>
+      </c>
+      <c r="I160" s="10" t="inlineStr">
+        <is>
+          <t>A16, Decision of 12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="J160" s="10" t="inlineStr">
+        <is>
+          <t>a hotel administrator on trial</t>
+        </is>
+      </c>
+      <c r="K160" s="10" t="inlineStr">
+        <is>
+          <t>they start a payment for a plan</t>
+        </is>
+      </c>
+      <c r="L160" s="10" t="inlineStr">
+        <is>
+          <t>the amount comes from the plans table in kobo; Enterprise is refused with E_NO_PRICE</t>
+        </is>
+      </c>
+      <c r="M160" s="10" t="inlineStr">
+        <is>
+          <t>start_subscription_payment (migration 20261020130000)</t>
+        </is>
+      </c>
+      <c r="N160" s="10" t="inlineStr">
+        <is>
+          <t>59_plan_prices (1)</t>
+        </is>
+      </c>
+      <c r="O160" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P160" s="10" t="inlineStr">
+        <is>
+          <t>Starter 20,000 is the launch price. List price 30,000 and the 12-month lock for early hotels are not built: raising the price later raises it for every hotel. Features by plan are not built; plans cap rooms, properties and users only. Billing stays off until the Paystack key and webhook are set.</t>
+        </is>
+      </c>
+      <c r="Q160" s="10" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -13402,7 +13402,7 @@
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>Plan prices are set in naira: Starter 20,000, Standard 45,000, Pro 80,000 a month; a year costs ten months; Enterprise is quoted and has no online price.</t>
+          <t>Plan prices are set in naira: Starter 30,000, Standard 45,000, Pro 80,000 a month; a year costs ten months; Enterprise is quoted and has no online price.</t>
         </is>
       </c>
       <c r="E160" s="10" t="inlineStr">
@@ -13462,7 +13462,7 @@
       </c>
       <c r="P160" s="10" t="inlineStr">
         <is>
-          <t>Starter 20,000 is the launch price. List price 30,000 and the 12-month lock for early hotels are not built: raising the price later raises it for every hotel. Features by plan are not built; plans cap rooms, properties and users only. Billing stays off until the Paystack key and webhook are set.</t>
+          <t>One price for every hotel: no launch price and no price lock (Peter, 12 Oct 2026). Features by plan are not built; plans cap rooms, properties and users only. Billing stays off until the Paystack key and webhook are set.</t>
         </is>
       </c>
       <c r="Q160" s="10" t="n"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q160"/>
+  <dimension ref="A1:Q162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="P154" s="10" t="inlineStr">
         <is>
-          <t>Stage 2. Approvals, check-in, check-out and room moves stay online only (stage 3 is not built).</t>
+          <t>Stage 2. Approvals and check-in stay online only. Check-out and room moves: see OFF-005 and OFF-006.</t>
         </is>
       </c>
       <c r="Q154" s="10" t="n"/>
@@ -13466,6 +13466,172 @@
         </is>
       </c>
       <c r="Q160" s="10" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="10" t="inlineStr">
+        <is>
+          <t>OFF-005</t>
+        </is>
+      </c>
+      <c r="B161" s="10" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>Check-out</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="inlineStr">
+        <is>
+          <t>A check-out entered with no connection waits on the device and is sent when the connection returns. The screen does not offer it twice while it waits. The database applies its usual rule at send time: a balance that is not zero is accepted only from someone who may check out with a balance, and it then appears in Collections for Finance. Anyone else sees it under Needs attention.</t>
+        </is>
+      </c>
+      <c r="E161" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F161" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G161" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H161" s="10" t="inlineStr">
+        <is>
+          <t>fo.checkout; fo.checkout.unsettled</t>
+        </is>
+      </c>
+      <c r="I161" s="10" t="inlineStr">
+        <is>
+          <t>A12; docs/offline-design.md</t>
+        </is>
+      </c>
+      <c r="J161" s="10" t="inlineStr">
+        <is>
+          <t>no connection and a guest in house</t>
+        </is>
+      </c>
+      <c r="K161" s="10" t="inlineStr">
+        <is>
+          <t>a clerk checks the guest out</t>
+        </is>
+      </c>
+      <c r="L161" s="10" t="inlineStr">
+        <is>
+          <t>it waits on the device, then the guest is checked out once when the connection returns</t>
+        </is>
+      </c>
+      <c r="M161" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/offline/queue.ts; src/lib/checkout.tsx; src/lib/offline/warm.ts</t>
+        </is>
+      </c>
+      <c r="N161" s="10" t="inlineStr">
+        <is>
+          <t>e2e/offline-stage3.spec.ts</t>
+        </is>
+      </c>
+      <c r="O161" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P161" s="10" t="inlineStr">
+        <is>
+          <t>Stage 3a. Reason recorded: Checked out with no connection. Approvals stay online only.</t>
+        </is>
+      </c>
+      <c r="Q161" s="10" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="10" t="inlineStr">
+        <is>
+          <t>OFF-006</t>
+        </is>
+      </c>
+      <c r="B162" s="10" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
+          <t>Front Desk</t>
+        </is>
+      </c>
+      <c r="D162" s="10" t="inlineStr">
+        <is>
+          <t>A room move entered with no connection waits on the device and is sent when the connection returns. If the database refuses it (for example the room was taken), it moves to Needs attention with the plain message and nothing is lost.</t>
+        </is>
+      </c>
+      <c r="E162" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F162" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G162" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H162" s="10" t="inlineStr">
+        <is>
+          <t>fo.room.move</t>
+        </is>
+      </c>
+      <c r="I162" s="10" t="inlineStr">
+        <is>
+          <t>A12; docs/offline-design.md</t>
+        </is>
+      </c>
+      <c r="J162" s="10" t="inlineStr">
+        <is>
+          <t>no connection and a guest in house</t>
+        </is>
+      </c>
+      <c r="K162" s="10" t="inlineStr">
+        <is>
+          <t>a clerk moves the guest to another room</t>
+        </is>
+      </c>
+      <c r="L162" s="10" t="inlineStr">
+        <is>
+          <t>it waits on the device and moves the guest when the connection returns, or shows Needs attention if refused</t>
+        </is>
+      </c>
+      <c r="M162" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/offline/queue.ts; src/lib/front-desk.tsx; src/lib/offline/warm.ts</t>
+        </is>
+      </c>
+      <c r="N162" s="10" t="inlineStr">
+        <is>
+          <t>e2e/offline-stage3.spec.ts</t>
+        </is>
+      </c>
+      <c r="O162" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P162" s="10" t="inlineStr">
+        <is>
+          <t>Stage 3a. Check-in and walk-in are stage 3b (waiting on the ID number decision).</t>
+        </is>
+      </c>
+      <c r="Q162" s="10" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q160"/>
+  <dimension ref="A1:Q161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>A trial ends automatically and the hotel becomes read-only.</t>
+          <t>A trial ends automatically. The hotel moves to a paid plan and has 14 days to pay (see PLT-018).</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>the subscription is Expired, the change is in the subscription history, and the hotel can read but not create</t>
+          <t>the subscription is Past due, the change is in the subscription history, and the hotel keeps working during the 14 days</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="P149" s="10" t="inlineStr">
         <is>
-          <t>QA-05. No prices in the email, because billing checkout is not switched on. Product name 'Zikora' in the wording is a draft.</t>
+          <t>QA-05. The warnings name the plan and price (PLT-018). Product name 'Zikora' in the wording is a draft.</t>
         </is>
       </c>
       <c r="Q149" s="10" t="n"/>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>A new hotel gets a 60-day free trial with every feature and no card. After it, the hotel becomes read-only until a plan is switched on.</t>
+          <t>A new hotel gets a 60-day free trial with every feature and no card. After it, the hotel moves to a paid plan with 14 days to pay (PLT-018).</t>
         </is>
       </c>
       <c r="E159" s="10" t="inlineStr">
@@ -13466,6 +13466,89 @@
         </is>
       </c>
       <c r="Q160" s="10" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="10" t="inlineStr">
+        <is>
+          <t>PLT-018</t>
+        </is>
+      </c>
+      <c r="B161" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>(email), (banner), pricing page</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="inlineStr">
+        <is>
+          <t>When the 60-day trial ends, the hotel moves to the cheapest plan it fits (Starter, Standard, Pro, else Enterprise), becomes Past due and has 14 days to pay, counted from the day the trial ended. It keeps working. One email names the plan and the monthly price from the plans table; a hotel too big for every priced plan is told to contact us for a quote. Unpaid after 14 days, the hotel becomes read-only (suspended). Nothing is deleted. The 7 and 1 day warnings name the plan and price.</t>
+        </is>
+      </c>
+      <c r="E161" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F161" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G161" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H161" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="10" t="inlineStr">
+        <is>
+          <t>A13, A16, Decision of 12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="J161" s="10" t="inlineStr">
+        <is>
+          <t>a hotel whose trial end date has passed</t>
+        </is>
+      </c>
+      <c r="K161" s="10" t="inlineStr">
+        <is>
+          <t>the daily clock runs</t>
+        </is>
+      </c>
+      <c r="L161" s="10" t="inlineStr">
+        <is>
+          <t>the hotel is on its plan, Past due, still working, with one email; after 14 days unpaid it is read-only</t>
+        </is>
+      </c>
+      <c r="M161" s="10" t="inlineStr">
+        <is>
+          <t>app.run_subscription_clock; app.trial_plan; app.plan_price_text; app.trial_plan_sentence</t>
+        </is>
+      </c>
+      <c r="N161" s="10" t="inlineStr">
+        <is>
+          <t>60_trial_to_paid_plan; 15_accounts; 51_subscription_notices</t>
+        </is>
+      </c>
+      <c r="O161" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P161" s="10" t="inlineStr">
+        <is>
+          <t>Billing checkout (Paystack) is off until the key and webhook are set, so payment is arranged by email to hello@zikorahq.com. The Terms (section 4) still say read-only at trial end and need counsel to reword.</t>
+        </is>
+      </c>
+      <c r="Q161" s="10" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q162"/>
+  <dimension ref="A1:Q164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13628,10 +13628,176 @@
       </c>
       <c r="P162" s="10" t="inlineStr">
         <is>
-          <t>Stage 3a. Check-in and walk-in are stage 3b (waiting on the ID number decision).</t>
+          <t>Stage 3a. Check-in is OFF-007 and OFF-008. Walk-in is not built.</t>
         </is>
       </c>
       <c r="Q162" s="10" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="10" t="inlineStr">
+        <is>
+          <t>OFF-007</t>
+        </is>
+      </c>
+      <c r="B163" s="10" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
+        <is>
+          <t>Front Desk</t>
+        </is>
+      </c>
+      <c r="D163" s="10" t="inlineStr">
+        <is>
+          <t>A check-in entered with no connection waits on the device and is sent when the connection returns. The guest's ID number waits on the device only until the entry is sent, then it is gone.</t>
+        </is>
+      </c>
+      <c r="E163" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F163" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G163" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H163" s="10" t="inlineStr">
+        <is>
+          <t>fo.checkin</t>
+        </is>
+      </c>
+      <c r="I163" s="10" t="inlineStr">
+        <is>
+          <t>A12; docs/offline-design.md; Peter 12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="J163" s="10" t="inlineStr">
+        <is>
+          <t>no connection and an arrival today</t>
+        </is>
+      </c>
+      <c r="K163" s="10" t="inlineStr">
+        <is>
+          <t>a clerk checks the guest in</t>
+        </is>
+      </c>
+      <c r="L163" s="10" t="inlineStr">
+        <is>
+          <t>it waits on the device, then the guest is checked in once when the connection returns, and the ID number is no longer saved on the device</t>
+        </is>
+      </c>
+      <c r="M163" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/offline/queue.ts; src/lib/front-desk.tsx; src/lib/offline/warm.ts</t>
+        </is>
+      </c>
+      <c r="N163" s="10" t="inlineStr">
+        <is>
+          <t>e2e/offline-stage3.spec.ts</t>
+        </is>
+      </c>
+      <c r="O163" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P163" s="10" t="inlineStr">
+        <is>
+          <t>Stage 3b, check-in of an existing booking. Walk-in is not built (needs a new guest to be made offline). ID photos need a connection.</t>
+        </is>
+      </c>
+      <c r="Q163" s="10" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="10" t="inlineStr">
+        <is>
+          <t>OFF-008</t>
+        </is>
+      </c>
+      <c r="B164" s="10" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="C164" s="10" t="inlineStr">
+        <is>
+          <t>Front Desk</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="inlineStr">
+        <is>
+          <t>A check-in the database refuses (for example the room is taken) moves to Needs attention with the plain message. Its ID number is erased from the device at that moment, it cannot be sent again as it was, and staff check the guest in again online.</t>
+        </is>
+      </c>
+      <c r="E164" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F164" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G164" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H164" s="10" t="inlineStr">
+        <is>
+          <t>fo.checkin</t>
+        </is>
+      </c>
+      <c r="I164" s="10" t="inlineStr">
+        <is>
+          <t>docs/offline-design.md; Peter 12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="J164" s="10" t="inlineStr">
+        <is>
+          <t>a check-in waiting on the device</t>
+        </is>
+      </c>
+      <c r="K164" s="10" t="inlineStr">
+        <is>
+          <t>the database refuses it</t>
+        </is>
+      </c>
+      <c r="L164" s="10" t="inlineStr">
+        <is>
+          <t>the entry shows Needs attention with Remove only, and no ID number is saved on the device</t>
+        </is>
+      </c>
+      <c r="M164" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/offline/queue.ts; src/components/offline-banner.tsx</t>
+        </is>
+      </c>
+      <c r="N164" s="10" t="inlineStr">
+        <is>
+          <t>e2e/offline-stage3.spec.ts</t>
+        </is>
+      </c>
+      <c r="O164" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P164" s="10" t="inlineStr">
+        <is>
+          <t>Stage 3b.</t>
+        </is>
+      </c>
+      <c r="Q164" s="10" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q165"/>
+  <dimension ref="A1:Q166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13881,6 +13881,89 @@
         </is>
       </c>
       <c r="Q165" s="10" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="10" t="inlineStr">
+        <is>
+          <t>PLT-019</t>
+        </is>
+      </c>
+      <c r="B166" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C166" s="10" t="inlineStr">
+        <is>
+          <t>Contact page</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="inlineStr">
+        <is>
+          <t>The website contact form emails the enquiry to hello@zikorahq.com through the email service and says thank you only when the service confirms. If the service is not set up or fails, the form opens the visitor's email app and says nothing has been received. A hidden field turns bots away. Nothing is stored.</t>
+        </is>
+      </c>
+      <c r="E166" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F166" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G166" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H166" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" s="10" t="inlineStr">
+        <is>
+          <t>Audit 12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="J166" s="10" t="inlineStr">
+        <is>
+          <t>a visitor fills the contact form</t>
+        </is>
+      </c>
+      <c r="K166" s="10" t="inlineStr">
+        <is>
+          <t>they send it</t>
+        </is>
+      </c>
+      <c r="L166" s="10" t="inlineStr">
+        <is>
+          <t>one email reaches the contact address with the visitor as reply-to; with no email key the form says it did not send</t>
+        </is>
+      </c>
+      <c r="M166" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/enquiry.ts; src/lib/enquiry.functions.ts; src/components/public/enquiry-form.tsx</t>
+        </is>
+      </c>
+      <c r="N166" s="10" t="inlineStr">
+        <is>
+          <t>e2e/enquiry-unit.spec.ts</t>
+        </is>
+      </c>
+      <c r="O166" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P166" s="10" t="inlineStr">
+        <is>
+          <t>Real sending starts when RESEND_API_KEY and OUTBOX_FROM_EMAIL are set in Vercel. Until then the form uses the email app fallback. No rate limit yet.</t>
+        </is>
+      </c>
+      <c r="Q166" s="10" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q166"/>
+  <dimension ref="A1:Q167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13964,6 +13964,89 @@
         </is>
       </c>
       <c r="Q166" s="10" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="10" t="inlineStr">
+        <is>
+          <t>PLT-020</t>
+        </is>
+      </c>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C167" s="10" t="inlineStr">
+        <is>
+          <t>All pages</t>
+        </is>
+      </c>
+      <c r="D167" s="10" t="inlineStr">
+        <is>
+          <t>Every page and answer from the live site carries security headers: no framing by other sites, no file type guessing, limited referrer, microphone and location off, camera allowed for the same site only (ID and ticket photos). No script policy yet, because the app needs inline scripts to start.</t>
+        </is>
+      </c>
+      <c r="E167" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F167" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G167" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H167" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="10" t="inlineStr">
+        <is>
+          <t>Audit 12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="J167" s="10" t="inlineStr">
+        <is>
+          <t>a visitor or a hijacking site loads Zikora</t>
+        </is>
+      </c>
+      <c r="K167" s="10" t="inlineStr">
+        <is>
+          <t>the page is served</t>
+        </is>
+      </c>
+      <c r="L167" s="10" t="inlineStr">
+        <is>
+          <t>other sites cannot frame it and the browser applies the limits</t>
+        </is>
+      </c>
+      <c r="M167" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/security-headers.ts; vite.config.ts</t>
+        </is>
+      </c>
+      <c r="N167" s="10" t="inlineStr">
+        <is>
+          <t>e2e/security-headers-unit.spec.ts</t>
+        </is>
+      </c>
+      <c r="O167" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P167" s="10" t="inlineStr">
+        <is>
+          <t>Headers apply on the Vercel build only (not the local dev server). Full script policy (CSP) is a later job.</t>
+        </is>
+      </c>
+      <c r="Q167" s="10" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q166"/>
+  <dimension ref="A1:Q167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13553,22 +13553,22 @@
     <row r="162">
       <c r="A162" s="10" t="inlineStr">
         <is>
-          <t>OFF-005</t>
+          <t>PLT-021</t>
         </is>
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>Platform &amp; Tenancy</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>Check-out</t>
+          <t>All pages</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>A check-out entered with no connection waits on the device and is sent when the connection returns. The screen does not offer it twice while it waits. The database applies its usual rule at send time: a balance that is not zero is accepted only from someone who may check out with a balance, and it then appears in Collections for Finance. Anyone else sees it under Needs attention.</t>
+          <t>Zikora can be added to a phone or tablet home screen and opens as its own app window, with the Zikora name, icon and colours. It opens on the sign-in page.</t>
         </is>
       </c>
       <c r="E162" s="10" t="inlineStr">
@@ -13588,37 +13588,37 @@
       </c>
       <c r="H162" s="10" t="inlineStr">
         <is>
-          <t>fo.checkout; fo.checkout.unsettled</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I162" s="10" t="inlineStr">
         <is>
-          <t>A12; docs/offline-design.md</t>
+          <t>Audit 12 Oct 2026</t>
         </is>
       </c>
       <c r="J162" s="10" t="inlineStr">
         <is>
-          <t>no connection and a guest in house</t>
+          <t>a staff member opens Zikora on a phone</t>
         </is>
       </c>
       <c r="K162" s="10" t="inlineStr">
         <is>
-          <t>a clerk checks the guest out</t>
+          <t>they choose Add to home screen (or Install)</t>
         </is>
       </c>
       <c r="L162" s="10" t="inlineStr">
         <is>
-          <t>it waits on the device, then the guest is checked out once when the connection returns</t>
+          <t>the icon appears with the name Zikora and it opens full screen on the sign-in page</t>
         </is>
       </c>
       <c r="M162" s="10" t="inlineStr">
         <is>
-          <t>src/lib/offline/queue.ts; src/lib/checkout.tsx; src/lib/offline/warm.ts</t>
+          <t>public/manifest.webmanifest; src/routes/__root.tsx</t>
         </is>
       </c>
       <c r="N162" s="10" t="inlineStr">
         <is>
-          <t>e2e/offline-stage3.spec.ts</t>
+          <t>e2e/web-manifest-unit.spec.ts</t>
         </is>
       </c>
       <c r="O162" s="10" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="P162" s="10" t="inlineStr">
         <is>
-          <t>Stage 3a. Reason recorded: Checked out with no connection. Approvals stay online only.</t>
+          <t>Needs a real phone check (iPhone Safari and Android Chrome). Works with the offline service worker already in place.</t>
         </is>
       </c>
       <c r="Q162" s="10" t="n"/>
@@ -13636,7 +13636,7 @@
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
         <is>
-          <t>OFF-006</t>
+          <t>OFF-005</t>
         </is>
       </c>
       <c r="B163" s="10" t="inlineStr">
@@ -13646,12 +13646,12 @@
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>Front Desk</t>
+          <t>Check-out</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>A room move entered with no connection waits on the device and is sent when the connection returns. If the database refuses it (for example the room was taken), it moves to Needs attention with the plain message and nothing is lost.</t>
+          <t>A check-out entered with no connection waits on the device and is sent when the connection returns. The screen does not offer it twice while it waits. The database applies its usual rule at send time: a balance that is not zero is accepted only from someone who may check out with a balance, and it then appears in Collections for Finance. Anyone else sees it under Needs attention.</t>
         </is>
       </c>
       <c r="E163" s="10" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="H163" s="10" t="inlineStr">
         <is>
-          <t>fo.room.move</t>
+          <t>fo.checkout; fo.checkout.unsettled</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
@@ -13686,17 +13686,17 @@
       </c>
       <c r="K163" s="10" t="inlineStr">
         <is>
-          <t>a clerk moves the guest to another room</t>
+          <t>a clerk checks the guest out</t>
         </is>
       </c>
       <c r="L163" s="10" t="inlineStr">
         <is>
-          <t>it waits on the device and moves the guest when the connection returns, or shows Needs attention if refused</t>
+          <t>it waits on the device, then the guest is checked out once when the connection returns</t>
         </is>
       </c>
       <c r="M163" s="10" t="inlineStr">
         <is>
-          <t>src/lib/offline/queue.ts; src/lib/front-desk.tsx; src/lib/offline/warm.ts</t>
+          <t>src/lib/offline/queue.ts; src/lib/checkout.tsx; src/lib/offline/warm.ts</t>
         </is>
       </c>
       <c r="N163" s="10" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="P163" s="10" t="inlineStr">
         <is>
-          <t>Stage 3a. Check-in is OFF-007 and OFF-008. Walk-in is not built.</t>
+          <t>Stage 3a. Reason recorded: Checked out with no connection. Approvals stay online only.</t>
         </is>
       </c>
       <c r="Q163" s="10" t="n"/>
@@ -13719,7 +13719,7 @@
     <row r="164">
       <c r="A164" s="10" t="inlineStr">
         <is>
-          <t>OFF-007</t>
+          <t>OFF-006</t>
         </is>
       </c>
       <c r="B164" s="10" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>A check-in entered with no connection waits on the device and is sent when the connection returns. The guest's ID number waits on the device only until the entry is sent, then it is gone.</t>
+          <t>A room move entered with no connection waits on the device and is sent when the connection returns. If the database refuses it (for example the room was taken), it moves to Needs attention with the plain message and nothing is lost.</t>
         </is>
       </c>
       <c r="E164" s="10" t="inlineStr">
@@ -13754,27 +13754,27 @@
       </c>
       <c r="H164" s="10" t="inlineStr">
         <is>
-          <t>fo.checkin</t>
+          <t>fo.room.move</t>
         </is>
       </c>
       <c r="I164" s="10" t="inlineStr">
         <is>
-          <t>A12; docs/offline-design.md; Peter 12 Oct 2026</t>
+          <t>A12; docs/offline-design.md</t>
         </is>
       </c>
       <c r="J164" s="10" t="inlineStr">
         <is>
-          <t>no connection and an arrival today</t>
+          <t>no connection and a guest in house</t>
         </is>
       </c>
       <c r="K164" s="10" t="inlineStr">
         <is>
-          <t>a clerk checks the guest in</t>
+          <t>a clerk moves the guest to another room</t>
         </is>
       </c>
       <c r="L164" s="10" t="inlineStr">
         <is>
-          <t>it waits on the device, then the guest is checked in once when the connection returns, and the ID number is no longer saved on the device</t>
+          <t>it waits on the device and moves the guest when the connection returns, or shows Needs attention if refused</t>
         </is>
       </c>
       <c r="M164" s="10" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="P164" s="10" t="inlineStr">
         <is>
-          <t>Stage 3b, check-in of an existing booking. Walk-in is not built (needs a new guest to be made offline). ID photos need a connection.</t>
+          <t>Stage 3a. Check-in is OFF-007 and OFF-008. Walk-in is not built.</t>
         </is>
       </c>
       <c r="Q164" s="10" t="n"/>
@@ -13802,7 +13802,7 @@
     <row r="165">
       <c r="A165" s="10" t="inlineStr">
         <is>
-          <t>OFF-008</t>
+          <t>OFF-007</t>
         </is>
       </c>
       <c r="B165" s="10" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>A check-in the database refuses (for example the room is taken) moves to Needs attention with the plain message. Its ID number is erased from the device at that moment, it cannot be sent again as it was, and staff check the guest in again online.</t>
+          <t>A check-in entered with no connection waits on the device and is sent when the connection returns. The guest's ID number waits on the device only until the entry is sent, then it is gone.</t>
         </is>
       </c>
       <c r="E165" s="10" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="F165" s="10" t="inlineStr">
         <is>
-          <t>Must</t>
+          <t>Should</t>
         </is>
       </c>
       <c r="G165" s="10" t="inlineStr">
@@ -13842,27 +13842,27 @@
       </c>
       <c r="I165" s="10" t="inlineStr">
         <is>
-          <t>docs/offline-design.md; Peter 12 Oct 2026</t>
+          <t>A12; docs/offline-design.md; Peter 12 Oct 2026</t>
         </is>
       </c>
       <c r="J165" s="10" t="inlineStr">
         <is>
-          <t>a check-in waiting on the device</t>
+          <t>no connection and an arrival today</t>
         </is>
       </c>
       <c r="K165" s="10" t="inlineStr">
         <is>
-          <t>the database refuses it</t>
+          <t>a clerk checks the guest in</t>
         </is>
       </c>
       <c r="L165" s="10" t="inlineStr">
         <is>
-          <t>the entry shows Needs attention with Remove only, and no ID number is saved on the device</t>
+          <t>it waits on the device, then the guest is checked in once when the connection returns, and the ID number is no longer saved on the device</t>
         </is>
       </c>
       <c r="M165" s="10" t="inlineStr">
         <is>
-          <t>src/lib/offline/queue.ts; src/components/offline-banner.tsx</t>
+          <t>src/lib/offline/queue.ts; src/lib/front-desk.tsx; src/lib/offline/warm.ts</t>
         </is>
       </c>
       <c r="N165" s="10" t="inlineStr">
@@ -13877,7 +13877,7 @@
       </c>
       <c r="P165" s="10" t="inlineStr">
         <is>
-          <t>Stage 3b.</t>
+          <t>Stage 3b, check-in of an existing booking. Walk-in is not built (needs a new guest to be made offline). ID photos need a connection.</t>
         </is>
       </c>
       <c r="Q165" s="10" t="n"/>
@@ -13885,85 +13885,168 @@
     <row r="166">
       <c r="A166" s="10" t="inlineStr">
         <is>
+          <t>OFF-008</t>
+        </is>
+      </c>
+      <c r="B166" s="10" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="C166" s="10" t="inlineStr">
+        <is>
+          <t>Front Desk</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="inlineStr">
+        <is>
+          <t>A check-in the database refuses (for example the room is taken) moves to Needs attention with the plain message. Its ID number is erased from the device at that moment, it cannot be sent again as it was, and staff check the guest in again online.</t>
+        </is>
+      </c>
+      <c r="E166" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F166" s="10" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="G166" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H166" s="10" t="inlineStr">
+        <is>
+          <t>fo.checkin</t>
+        </is>
+      </c>
+      <c r="I166" s="10" t="inlineStr">
+        <is>
+          <t>docs/offline-design.md; Peter 12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="J166" s="10" t="inlineStr">
+        <is>
+          <t>a check-in waiting on the device</t>
+        </is>
+      </c>
+      <c r="K166" s="10" t="inlineStr">
+        <is>
+          <t>the database refuses it</t>
+        </is>
+      </c>
+      <c r="L166" s="10" t="inlineStr">
+        <is>
+          <t>the entry shows Needs attention with Remove only, and no ID number is saved on the device</t>
+        </is>
+      </c>
+      <c r="M166" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/offline/queue.ts; src/components/offline-banner.tsx</t>
+        </is>
+      </c>
+      <c r="N166" s="10" t="inlineStr">
+        <is>
+          <t>e2e/offline-stage3.spec.ts</t>
+        </is>
+      </c>
+      <c r="O166" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P166" s="10" t="inlineStr">
+        <is>
+          <t>Stage 3b.</t>
+        </is>
+      </c>
+      <c r="Q166" s="10" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="10" t="inlineStr">
+        <is>
           <t>PLT-019</t>
         </is>
       </c>
-      <c r="B166" s="10" t="inlineStr">
+      <c r="B167" s="10" t="inlineStr">
         <is>
           <t>Platform &amp; Tenancy</t>
         </is>
       </c>
-      <c r="C166" s="10" t="inlineStr">
+      <c r="C167" s="10" t="inlineStr">
         <is>
           <t>Contact page</t>
         </is>
       </c>
-      <c r="D166" s="10" t="inlineStr">
+      <c r="D167" s="10" t="inlineStr">
         <is>
           <t>The website contact form emails the enquiry to hello@zikorahq.com through the email service and says thank you only when the service confirms. If the service is not set up or fails, the form opens the visitor's email app and says nothing has been received. A hidden field turns bots away. Nothing is stored.</t>
         </is>
       </c>
-      <c r="E166" s="10" t="inlineStr">
+      <c r="E167" s="10" t="inlineStr">
         <is>
           <t>BR-001</t>
         </is>
       </c>
-      <c r="F166" s="10" t="inlineStr">
+      <c r="F167" s="10" t="inlineStr">
         <is>
           <t>Should</t>
         </is>
       </c>
-      <c r="G166" s="10" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H166" s="10" t="inlineStr">
+      <c r="G167" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H167" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I166" s="10" t="inlineStr">
+      <c r="I167" s="10" t="inlineStr">
         <is>
           <t>Audit 12 Oct 2026</t>
         </is>
       </c>
-      <c r="J166" s="10" t="inlineStr">
+      <c r="J167" s="10" t="inlineStr">
         <is>
           <t>a visitor fills the contact form</t>
         </is>
       </c>
-      <c r="K166" s="10" t="inlineStr">
+      <c r="K167" s="10" t="inlineStr">
         <is>
           <t>they send it</t>
         </is>
       </c>
-      <c r="L166" s="10" t="inlineStr">
+      <c r="L167" s="10" t="inlineStr">
         <is>
           <t>one email reaches the contact address with the visitor as reply-to; with no email key the form says it did not send</t>
         </is>
       </c>
-      <c r="M166" s="10" t="inlineStr">
+      <c r="M167" s="10" t="inlineStr">
         <is>
           <t>src/lib/enquiry.ts; src/lib/enquiry.functions.ts; src/components/public/enquiry-form.tsx</t>
         </is>
       </c>
-      <c r="N166" s="10" t="inlineStr">
+      <c r="N167" s="10" t="inlineStr">
         <is>
           <t>e2e/enquiry-unit.spec.ts</t>
         </is>
       </c>
-      <c r="O166" s="10" t="inlineStr">
-        <is>
-          <t>Built+tested</t>
-        </is>
-      </c>
-      <c r="P166" s="10" t="inlineStr">
+      <c r="O167" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P167" s="10" t="inlineStr">
         <is>
           <t>Real sending starts when RESEND_API_KEY and OUTBOX_FROM_EMAIL are set in Vercel. Until then the form uses the email app fallback. No rate limit yet.</t>
         </is>
       </c>
-      <c r="Q166" s="10" t="n"/>
+      <c r="Q167" s="10" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'R1 Requirements'!$A$1:$O$108</definedName>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q168"/>
+  <dimension ref="A1:Q169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14130,6 +14130,89 @@
         </is>
       </c>
       <c r="Q168" s="10" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="10" t="inlineStr">
+        <is>
+          <t>PLT-022</t>
+        </is>
+      </c>
+      <c r="B169" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C169" s="10" t="inlineStr">
+        <is>
+          <t>All public pages</t>
+        </is>
+      </c>
+      <c r="D169" s="10" t="inlineStr">
+        <is>
+          <t>Every public page names its own canonical address, and the site publishes a security.txt so a researcher knows how to report a problem.</t>
+        </is>
+      </c>
+      <c r="E169" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F169" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G169" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H169" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="10" t="inlineStr">
+        <is>
+          <t>Audit 12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="J169" s="10" t="inlineStr">
+        <is>
+          <t>a search engine or a security researcher visits the site</t>
+        </is>
+      </c>
+      <c r="K169" s="10" t="inlineStr">
+        <is>
+          <t>it reads a public page or /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="L169" s="10" t="inlineStr">
+        <is>
+          <t>each indexed page names itself as canonical (Privacy and Terms did not), and security.txt gives a contact, an expiry date within a year and its own address</t>
+        </is>
+      </c>
+      <c r="M169" s="10" t="inlineStr">
+        <is>
+          <t>pageHead path on Privacy and Terms; public/.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="N169" s="10" t="inlineStr">
+        <is>
+          <t>site-basics (2)</t>
+        </is>
+      </c>
+      <c r="O169" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P169" s="10" t="inlineStr">
+        <is>
+          <t>Added 12 Oct 2026. security.txt expires 1 Oct 2027: renew it before then. Its contact is the website contact page until the hello@ mailbox can receive mail.</t>
+        </is>
+      </c>
+      <c r="Q169" s="10" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="R1 Requirements" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BR Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Build Gaps" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'R1 Requirements'!$A$1:$O$108</definedName>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q168"/>
+  <dimension ref="A1:P168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -760,7 +760,6 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
@@ -839,7 +838,6 @@
         </is>
       </c>
       <c r="P2" s="10" t="inlineStr"/>
-      <c r="Q2" s="10" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -918,7 +916,6 @@
         </is>
       </c>
       <c r="P3" s="10" t="inlineStr"/>
-      <c r="Q3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -997,7 +994,6 @@
         </is>
       </c>
       <c r="P4" s="10" t="inlineStr"/>
-      <c r="Q4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -1076,7 +1072,6 @@
         </is>
       </c>
       <c r="P5" s="10" t="inlineStr"/>
-      <c r="Q5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -1155,7 +1150,6 @@
         </is>
       </c>
       <c r="P6" s="10" t="inlineStr"/>
-      <c r="Q6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -1234,7 +1228,6 @@
         </is>
       </c>
       <c r="P7" s="10" t="inlineStr"/>
-      <c r="Q7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -1317,7 +1310,6 @@
           <t>Adding a property: System Administrator and General Manager (ADM-002), within plans.max_properties.</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -1400,7 +1392,6 @@
           <t>Platform console /platform (wave 2 item 2): extend trial, activate or extend paid period, suspend, change plan, cancel; each with a reason, logged in subscription_history with the operator.</t>
         </is>
       </c>
-      <c r="Q9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -1483,7 +1474,6 @@
           <t>Corrected 6 Oct 2026: before wave 2 item 2 there was no platform staff role at all; the earlier "Built, no tagged test" was wrong.</t>
         </is>
       </c>
-      <c r="Q10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -1566,7 +1556,6 @@
           <t>Database done 8 Oct 2026. Screens for the hotel (Admin) and the operator (platform console) follow. New permission adm.support.manage reaches System Administrator and General Manager only.</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -1645,7 +1634,6 @@
         </is>
       </c>
       <c r="P12" s="10" t="inlineStr"/>
-      <c r="Q12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -1728,7 +1716,6 @@
           <t>Needs PAYSTACK_SECRET_KEY and the webhook address set in Paystack. Prices are empty until A16 is decided.</t>
         </is>
       </c>
-      <c r="Q13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -1807,7 +1794,6 @@
         </is>
       </c>
       <c r="P14" s="10" t="inlineStr"/>
-      <c r="Q14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -1890,7 +1876,6 @@
           <t>Invites are sent by a Vercel server function (not an Edge Function).</t>
         </is>
       </c>
-      <c r="Q15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -1969,7 +1954,6 @@
         </is>
       </c>
       <c r="P16" s="10" t="inlineStr"/>
-      <c r="Q16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -2048,7 +2032,6 @@
         </is>
       </c>
       <c r="P17" s="10" t="inlineStr"/>
-      <c r="Q17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -2127,7 +2110,6 @@
         </is>
       </c>
       <c r="P18" s="10" t="inlineStr"/>
-      <c r="Q18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -2206,7 +2188,6 @@
         </is>
       </c>
       <c r="P19" s="10" t="inlineStr"/>
-      <c r="Q19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
@@ -2285,7 +2266,6 @@
         </is>
       </c>
       <c r="P20" s="10" t="inlineStr"/>
-      <c r="Q20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -2364,7 +2344,6 @@
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr"/>
-      <c r="Q21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -2443,7 +2422,6 @@
         </is>
       </c>
       <c r="P22" s="10" t="inlineStr"/>
-      <c r="Q22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -2526,7 +2504,6 @@
           <t>export_data (audited), Reports &gt; Export.</t>
         </is>
       </c>
-      <c r="Q23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -2605,7 +2582,6 @@
         </is>
       </c>
       <c r="P24" s="10" t="inlineStr"/>
-      <c r="Q24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -2688,7 +2664,6 @@
           <t>Room types and occupancy limits are built (save_room_type: max adults and children; Setup, Room types). The overbooking allowance is not built: decision pending (QA-17, 11 Oct 2026). Recommended: skip it for the pilot.</t>
         </is>
       </c>
-      <c r="Q25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
@@ -2771,7 +2746,6 @@
           <t>A room cannot be retired while a guest is in it ([E_ROOM_OCCUPIED], checked first) or while upcoming bookings are assigned to it ([E_ROOM_BOOKED], names up to 5 booking numbers): confirmed, or tentative with an unexpired hold, from the business date forward (decisions of 6 Oct 2026). Retiring a room that is already retired is safe to repeat; renaming and floor changes still work.</t>
         </is>
       </c>
-      <c r="Q26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
@@ -2850,7 +2824,6 @@
         </is>
       </c>
       <c r="P27" s="10" t="inlineStr"/>
-      <c r="Q27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -2929,7 +2902,6 @@
         </is>
       </c>
       <c r="P28" s="10" t="inlineStr"/>
-      <c r="Q28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -3008,7 +2980,6 @@
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr"/>
-      <c r="Q29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
@@ -3087,7 +3058,6 @@
         </is>
       </c>
       <c r="P30" s="10" t="inlineStr"/>
-      <c r="Q30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
@@ -3166,7 +3136,6 @@
         </is>
       </c>
       <c r="P31" s="10" t="inlineStr"/>
-      <c r="Q31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
@@ -3245,7 +3214,6 @@
         </is>
       </c>
       <c r="P32" s="10" t="inlineStr"/>
-      <c r="Q32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
@@ -3324,7 +3292,6 @@
         </is>
       </c>
       <c r="P33" s="10" t="inlineStr"/>
-      <c r="Q33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
@@ -3403,7 +3370,6 @@
         </is>
       </c>
       <c r="P34" s="10" t="inlineStr"/>
-      <c r="Q34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
@@ -3482,7 +3448,6 @@
         </is>
       </c>
       <c r="P35" s="10" t="inlineStr"/>
-      <c r="Q35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
@@ -3561,7 +3526,6 @@
         </is>
       </c>
       <c r="P36" s="10" t="inlineStr"/>
-      <c r="Q36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
@@ -3640,7 +3604,6 @@
         </is>
       </c>
       <c r="P37" s="10" t="inlineStr"/>
-      <c r="Q37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
@@ -3719,7 +3682,6 @@
         </is>
       </c>
       <c r="P38" s="10" t="inlineStr"/>
-      <c r="Q38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -3798,7 +3760,6 @@
         </is>
       </c>
       <c r="P39" s="10" t="inlineStr"/>
-      <c r="Q39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
@@ -3877,7 +3838,6 @@
         </is>
       </c>
       <c r="P40" s="10" t="inlineStr"/>
-      <c r="Q40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
@@ -3956,7 +3916,6 @@
         </is>
       </c>
       <c r="P41" s="10" t="inlineStr"/>
-      <c r="Q41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
@@ -4035,7 +3994,6 @@
         </is>
       </c>
       <c r="P42" s="10" t="inlineStr"/>
-      <c r="Q42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
@@ -4105,22 +4063,17 @@
       </c>
       <c r="N43" s="10" t="inlineStr">
         <is>
-          <t>29_untagged_rows (7)</t>
+          <t>29_untagged_rows (7); browser: group-bookings (QA-11)</t>
         </is>
       </c>
       <c r="O43" s="10" t="inlineStr">
         <is>
-          <t>Built+tested (database only)</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P43" s="10" t="inlineStr">
         <is>
-          <t>save_group_booking exists. The booking form creates a group (Add group) and picks one; Reservations</t>
-        </is>
-      </c>
-      <c r="Q43" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Groups lists each group and opens it with its rooms and totals. Browser test: e2e/group-bookings.spec.ts.</t>
+          <t>save_group_booking exists. The booking form creates a group (Add group) and picks one; Reservations, Groups lists each group and opens it with its rooms and totals. Browser test: e2e/group-bookings.spec.ts.</t>
         </is>
       </c>
     </row>
@@ -4192,22 +4145,17 @@
       </c>
       <c r="N44" s="10" t="inlineStr">
         <is>
-          <t>17_more_features (2); 26_small_fixes (4); 29_untagged_rows (6)</t>
+          <t>17_more_features (2); 26_small_fixes (4); 29_untagged_rows (6); browser: arrival-ready</t>
         </is>
       </c>
       <c r="O44" s="10" t="inlineStr">
         <is>
-          <t>Built+tested (database only)</t>
+          <t>Built+tested</t>
         </is>
       </c>
       <c r="P44" s="10" t="inlineStr">
         <is>
-          <t>set_arrival_ready exists. The booking page has Mark ready and Not ready; the Front Desk arrivals list and the group page show Ready (QA-15</t>
-        </is>
-      </c>
-      <c r="Q44" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 11 Oct 2026).</t>
+          <t>set_arrival_ready exists. The booking page has Mark ready and Not ready; the Front Desk arrivals list and the group page show Ready (QA-15, 11 Oct 2026). Browser test e2e/arrival-ready.spec.ts (12 Oct 2026): Mark ready shows Ready for arrival on the booking page and Ready on the Front Desk arrivals list; Not ready clears it.</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4236,6 @@
         </is>
       </c>
       <c r="P45" s="10" t="inlineStr"/>
-      <c r="Q45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
@@ -4367,7 +4314,6 @@
         </is>
       </c>
       <c r="P46" s="10" t="inlineStr"/>
-      <c r="Q46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
@@ -4450,7 +4396,6 @@
           <t>The check-in and walk-in screens force the registration card tick; a direct database call that omits it is not refused (decision 6 Oct 2026). Drawn signature later.</t>
         </is>
       </c>
-      <c r="Q47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
@@ -4529,7 +4474,6 @@
         </is>
       </c>
       <c r="P48" s="10" t="inlineStr"/>
-      <c r="Q48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
@@ -4608,7 +4552,6 @@
         </is>
       </c>
       <c r="P49" s="10" t="inlineStr"/>
-      <c r="Q49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
@@ -4687,7 +4630,6 @@
         </is>
       </c>
       <c r="P50" s="10" t="inlineStr"/>
-      <c r="Q50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
@@ -4770,7 +4712,6 @@
           <t>Dearer room type: front desk charges the new rate; keeping it needs fo.upgrade.complimentary (SYSADMIN, GM, FOM), audited.</t>
         </is>
       </c>
-      <c r="Q51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
@@ -4849,7 +4790,6 @@
         </is>
       </c>
       <c r="P52" s="10" t="inlineStr"/>
-      <c r="Q52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
@@ -4928,7 +4868,6 @@
         </is>
       </c>
       <c r="P53" s="10" t="inlineStr"/>
-      <c r="Q53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
@@ -5007,7 +4946,6 @@
         </is>
       </c>
       <c r="P54" s="10" t="inlineStr"/>
-      <c r="Q54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
@@ -5086,7 +5024,6 @@
         </is>
       </c>
       <c r="P55" s="10" t="inlineStr"/>
-      <c r="Q55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
@@ -5165,7 +5102,6 @@
         </is>
       </c>
       <c r="P56" s="10" t="inlineStr"/>
-      <c r="Q56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
@@ -5244,7 +5180,6 @@
         </is>
       </c>
       <c r="P57" s="10" t="inlineStr"/>
-      <c r="Q57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
@@ -5323,7 +5258,6 @@
         </is>
       </c>
       <c r="P58" s="10" t="inlineStr"/>
-      <c r="Q58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
@@ -5402,7 +5336,6 @@
         </is>
       </c>
       <c r="P59" s="10" t="inlineStr"/>
-      <c r="Q59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
@@ -5481,7 +5414,6 @@
         </is>
       </c>
       <c r="P60" s="10" t="inlineStr"/>
-      <c r="Q60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
@@ -5560,7 +5492,6 @@
         </is>
       </c>
       <c r="P61" s="10" t="inlineStr"/>
-      <c r="Q61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
@@ -5639,7 +5570,6 @@
         </is>
       </c>
       <c r="P62" s="10" t="inlineStr"/>
-      <c r="Q62" s="10" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
@@ -5718,7 +5648,6 @@
         </is>
       </c>
       <c r="P63" s="10" t="inlineStr"/>
-      <c r="Q63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
@@ -5797,7 +5726,6 @@
         </is>
       </c>
       <c r="P64" s="10" t="inlineStr"/>
-      <c r="Q64" s="10" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
@@ -5876,7 +5804,6 @@
         </is>
       </c>
       <c r="P65" s="10" t="inlineStr"/>
-      <c r="Q65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
@@ -5955,7 +5882,6 @@
         </is>
       </c>
       <c r="P66" s="10" t="inlineStr"/>
-      <c r="Q66" s="10" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
@@ -6034,7 +5960,6 @@
         </is>
       </c>
       <c r="P67" s="10" t="inlineStr"/>
-      <c r="Q67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
@@ -6113,7 +6038,6 @@
         </is>
       </c>
       <c r="P68" s="10" t="inlineStr"/>
-      <c r="Q68" s="10" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
@@ -6192,7 +6116,6 @@
         </is>
       </c>
       <c r="P69" s="10" t="inlineStr"/>
-      <c r="Q69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
@@ -6271,7 +6194,6 @@
         </is>
       </c>
       <c r="P70" s="10" t="inlineStr"/>
-      <c r="Q70" s="10" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
@@ -6350,7 +6272,6 @@
         </is>
       </c>
       <c r="P71" s="10" t="inlineStr"/>
-      <c r="Q71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
@@ -6429,7 +6350,6 @@
         </is>
       </c>
       <c r="P72" s="10" t="inlineStr"/>
-      <c r="Q72" s="10" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
@@ -6508,7 +6428,6 @@
         </is>
       </c>
       <c r="P73" s="10" t="inlineStr"/>
-      <c r="Q73" s="10" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
@@ -6587,7 +6506,6 @@
         </is>
       </c>
       <c r="P74" s="10" t="inlineStr"/>
-      <c r="Q74" s="10" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
@@ -6666,7 +6584,6 @@
         </is>
       </c>
       <c r="P75" s="10" t="inlineStr"/>
-      <c r="Q75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
@@ -6745,7 +6662,6 @@
         </is>
       </c>
       <c r="P76" s="10" t="inlineStr"/>
-      <c r="Q76" s="10" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
@@ -6824,7 +6740,6 @@
         </is>
       </c>
       <c r="P77" s="10" t="inlineStr"/>
-      <c r="Q77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
@@ -6903,7 +6818,6 @@
         </is>
       </c>
       <c r="P78" s="10" t="inlineStr"/>
-      <c r="Q78" s="10" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
@@ -6982,7 +6896,6 @@
         </is>
       </c>
       <c r="P79" s="10" t="inlineStr"/>
-      <c r="Q79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
@@ -7061,7 +6974,6 @@
         </is>
       </c>
       <c r="P80" s="10" t="inlineStr"/>
-      <c r="Q80" s="10" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
@@ -7140,7 +7052,6 @@
         </is>
       </c>
       <c r="P81" s="10" t="inlineStr"/>
-      <c r="Q81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
@@ -7219,7 +7130,6 @@
         </is>
       </c>
       <c r="P82" s="10" t="inlineStr"/>
-      <c r="Q82" s="10" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
@@ -7298,7 +7208,6 @@
         </is>
       </c>
       <c r="P83" s="10" t="inlineStr"/>
-      <c r="Q83" s="10" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
@@ -7377,7 +7286,6 @@
         </is>
       </c>
       <c r="P84" s="10" t="inlineStr"/>
-      <c r="Q84" s="10" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
@@ -7456,7 +7364,6 @@
         </is>
       </c>
       <c r="P85" s="10" t="inlineStr"/>
-      <c r="Q85" s="10" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
@@ -7535,7 +7442,6 @@
         </is>
       </c>
       <c r="P86" s="10" t="inlineStr"/>
-      <c r="Q86" s="10" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
@@ -7614,7 +7520,6 @@
         </is>
       </c>
       <c r="P87" s="10" t="inlineStr"/>
-      <c r="Q87" s="10" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
@@ -7693,7 +7598,6 @@
         </is>
       </c>
       <c r="P88" s="10" t="inlineStr"/>
-      <c r="Q88" s="10" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
@@ -7772,7 +7676,6 @@
         </is>
       </c>
       <c r="P89" s="10" t="inlineStr"/>
-      <c r="Q89" s="10" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
@@ -7851,7 +7754,6 @@
         </is>
       </c>
       <c r="P90" s="10" t="inlineStr"/>
-      <c r="Q90" s="10" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
@@ -7930,7 +7832,6 @@
         </is>
       </c>
       <c r="P91" s="10" t="inlineStr"/>
-      <c r="Q91" s="10" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
@@ -8009,7 +7910,6 @@
         </is>
       </c>
       <c r="P92" s="10" t="inlineStr"/>
-      <c r="Q92" s="10" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
@@ -8088,7 +7988,6 @@
         </is>
       </c>
       <c r="P93" s="10" t="inlineStr"/>
-      <c r="Q93" s="10" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
@@ -8167,7 +8066,6 @@
         </is>
       </c>
       <c r="P94" s="10" t="inlineStr"/>
-      <c r="Q94" s="10" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
@@ -8246,7 +8144,6 @@
         </is>
       </c>
       <c r="P95" s="10" t="inlineStr"/>
-      <c r="Q95" s="10" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
@@ -8316,7 +8213,7 @@
       </c>
       <c r="N96" s="10" t="inlineStr">
         <is>
-          <t>34_cashier_shifts (45)</t>
+          <t>34_cashier_shifts (45); browser: screens-actions (opening a shift)</t>
         </is>
       </c>
       <c r="O96" s="10" t="inlineStr">
@@ -8326,10 +8223,9 @@
       </c>
       <c r="P96" s="10" t="inlineStr">
         <is>
-          <t>Cashier shift page built (open, close with counts, review, reconcile). Not covered by a browser test yet. New permission fin.shift.reconcile goes to built-in roles only.</t>
-        </is>
-      </c>
-      <c r="Q96" s="10" t="n"/>
+          <t>Cashier shift page built (open, close with counts, review, reconcile). A browser test (QA-11) covers opening a shift. Closing with counts, review and reconcile are covered by the database tests only (checked 12 Oct 2026). New permission fin.shift.reconcile goes to built-in roles only.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
@@ -8408,7 +8304,6 @@
         </is>
       </c>
       <c r="P97" s="10" t="inlineStr"/>
-      <c r="Q97" s="10" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
@@ -8487,7 +8382,6 @@
         </is>
       </c>
       <c r="P98" s="10" t="inlineStr"/>
-      <c r="Q98" s="10" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
@@ -8566,7 +8460,6 @@
         </is>
       </c>
       <c r="P99" s="10" t="inlineStr"/>
-      <c r="Q99" s="10" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
@@ -8645,7 +8538,6 @@
         </is>
       </c>
       <c r="P100" s="10" t="inlineStr"/>
-      <c r="Q100" s="10" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
@@ -8728,7 +8620,6 @@
           <t>Flags shown in Admin, Business date. The gate that stops the roll while a blocking flag is open is not built.</t>
         </is>
       </c>
-      <c r="Q101" s="10" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
@@ -8811,7 +8702,6 @@
           <t>Decided by Peter on 30 Sep 2026 (answer 5) and confirmed on 1 Oct 2026: same-day stays are charged one night; a manager can waive it with a reason.</t>
         </is>
       </c>
-      <c r="Q102" s="10" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
@@ -8890,7 +8780,6 @@
         </is>
       </c>
       <c r="P103" s="10" t="inlineStr"/>
-      <c r="Q103" s="10" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
@@ -8969,7 +8858,6 @@
         </is>
       </c>
       <c r="P104" s="10" t="inlineStr"/>
-      <c r="Q104" s="10" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
@@ -9048,7 +8936,6 @@
         </is>
       </c>
       <c r="P105" s="10" t="inlineStr"/>
-      <c r="Q105" s="10" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
@@ -9131,7 +9018,6 @@
           <t>Reports screen: KPIs, revenue by charge code, outstanding balances, payments, cancellations and stay length, balances by guest, export.</t>
         </is>
       </c>
-      <c r="Q106" s="10" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
@@ -9210,7 +9096,6 @@
         </is>
       </c>
       <c r="P107" s="10" t="inlineStr"/>
-      <c r="Q107" s="10" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
@@ -9289,7 +9174,6 @@
         </is>
       </c>
       <c r="P108" s="10" t="inlineStr"/>
-      <c r="Q108" s="10" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
@@ -9368,7 +9252,6 @@
         </is>
       </c>
       <c r="P109" s="10" t="inlineStr"/>
-      <c r="Q109" s="10" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
@@ -9447,7 +9330,6 @@
         </is>
       </c>
       <c r="P110" s="10" t="inlineStr"/>
-      <c r="Q110" s="10" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
@@ -9526,7 +9408,6 @@
         </is>
       </c>
       <c r="P111" s="10" t="inlineStr"/>
-      <c r="Q111" s="10" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
@@ -9605,7 +9486,6 @@
         </is>
       </c>
       <c r="P112" s="10" t="inlineStr"/>
-      <c r="Q112" s="10" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
@@ -9684,7 +9564,6 @@
         </is>
       </c>
       <c r="P113" s="10" t="inlineStr"/>
-      <c r="Q113" s="10" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
@@ -9767,7 +9646,6 @@
           <t>Method only; the accountant still signs off the rates (A11)</t>
         </is>
       </c>
-      <c r="Q114" s="10" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
@@ -9850,7 +9728,6 @@
           <t>Day totals and fields are stored in the invoice header when it is issued</t>
         </is>
       </c>
-      <c r="Q115" s="10" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
@@ -9933,7 +9810,6 @@
           <t>Month comes from the business date, not the clock. No hotel code in the number yet.</t>
         </is>
       </c>
-      <c r="Q116" s="10" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
@@ -10012,7 +9888,6 @@
         </is>
       </c>
       <c r="P117" s="10" t="inlineStr"/>
-      <c r="Q117" s="10" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
@@ -10091,7 +9966,6 @@
         </is>
       </c>
       <c r="P118" s="10" t="inlineStr"/>
-      <c r="Q118" s="10" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
@@ -10170,7 +10044,6 @@
         </is>
       </c>
       <c r="P119" s="10" t="inlineStr"/>
-      <c r="Q119" s="10" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
@@ -10249,7 +10122,6 @@
         </is>
       </c>
       <c r="P120" s="10" t="inlineStr"/>
-      <c r="Q120" s="10" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
@@ -10328,7 +10200,6 @@
         </is>
       </c>
       <c r="P121" s="10" t="inlineStr"/>
-      <c r="Q121" s="10" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
@@ -10407,7 +10278,6 @@
         </is>
       </c>
       <c r="P122" s="10" t="inlineStr"/>
-      <c r="Q122" s="10" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
@@ -10486,7 +10356,6 @@
           <t>Custom roles copied earlier do not get the new permission; say so when releasing.</t>
         </is>
       </c>
-      <c r="Q123" s="10" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
@@ -10565,7 +10434,6 @@
           <t>Figures are read from each branch own business date. No arithmetic in the browser.</t>
         </is>
       </c>
-      <c r="Q124" s="10" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
@@ -10644,7 +10512,6 @@
           <t>Access is per branch, using the existing role assignment screen.</t>
         </is>
       </c>
-      <c r="Q125" s="10" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
@@ -10723,7 +10590,6 @@
           <t>Taxes, charge codes and payment methods already arrive with every new branch.</t>
         </is>
       </c>
-      <c r="Q126" s="10" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
@@ -10802,7 +10668,6 @@
           <t>Bookings counted by arrival date; revenue by posting date.</t>
         </is>
       </c>
-      <c r="Q127" s="10" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
@@ -10881,7 +10746,6 @@
           <t>Guests still staying count as current.</t>
         </is>
       </c>
-      <c r="Q128" s="10" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
@@ -10964,7 +10828,6 @@
           <t>Email delivery waits on the sending domain and email account. Collected money nets payment reversals the same day (migration 20261015130000).</t>
         </is>
       </c>
-      <c r="Q129" s="10" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
@@ -11043,7 +10906,6 @@
           <t>Custom roles copied earlier do not get adm.ai.manage.</t>
         </is>
       </c>
-      <c r="Q130" s="10" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
@@ -11122,7 +10984,6 @@
           <t>Overdue means unpaid more than 30 days after departure.</t>
         </is>
       </c>
-      <c r="Q131" s="10" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
@@ -11197,7 +11058,6 @@
         </is>
       </c>
       <c r="P132" s="10" t="inlineStr"/>
-      <c r="Q132" s="10" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
@@ -11272,7 +11132,6 @@
         </is>
       </c>
       <c r="P133" s="10" t="inlineStr"/>
-      <c r="Q133" s="10" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
@@ -11351,7 +11210,6 @@
           <t>Needs ANTHROPIC_API_KEY on the server (Vercel settings). Not set yet.</t>
         </is>
       </c>
-      <c r="Q134" s="10" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
@@ -11430,7 +11288,6 @@
           <t>The AI only drafts the list. This function is the check.</t>
         </is>
       </c>
-      <c r="Q135" s="10" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
@@ -11505,7 +11362,6 @@
         </is>
       </c>
       <c r="P136" s="10" t="inlineStr"/>
-      <c r="Q136" s="10" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
@@ -11584,7 +11440,6 @@
           <t>Needs ANTHROPIC_API_KEY on the server. Not set yet.</t>
         </is>
       </c>
-      <c r="Q137" s="10" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
@@ -11667,7 +11522,6 @@
           <t>Read-only function, no stored progress. Staff step counts people with a role at the property (two or more).</t>
         </is>
       </c>
-      <c r="Q138" s="10" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
@@ -11750,7 +11604,6 @@
           <t>Runs 8 separate database sessions at once. Added 7 Oct 2026.</t>
         </is>
       </c>
-      <c r="Q139" s="10" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
@@ -11829,7 +11682,6 @@
           <t>Added 8 Oct 2026. The columns existed since the reservations release; this adds the screen and the function.</t>
         </is>
       </c>
-      <c r="Q140" s="10" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
@@ -11908,7 +11760,6 @@
           <t>No database change. Reads v_arrivals, v_in_house and v_folio_balances. Added 8 Oct 2026.</t>
         </is>
       </c>
-      <c r="Q141" s="10" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
@@ -11991,7 +11842,6 @@
           <t>Added 8 Oct 2026. Warning only; the hard gate stays in R2 (DAY-005).</t>
         </is>
       </c>
-      <c r="Q142" s="10" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
@@ -12070,7 +11920,6 @@
           <t>Added 9 Oct 2026. Read-only; no money is changed.</t>
         </is>
       </c>
-      <c r="Q143" s="10" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
@@ -12149,7 +11998,6 @@
           <t>Added 10 Oct 2026. The Payments report counted only payments and refunds before this. Cashier shift counts stay separate on purpose: they count what the drawer should hold.</t>
         </is>
       </c>
-      <c r="Q144" s="10" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
@@ -12228,7 +12076,6 @@
           <t>Added 10 Oct 2026. Notes are not ledger rows; they never change a balance.</t>
         </is>
       </c>
-      <c r="Q145" s="10" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
@@ -12303,7 +12150,6 @@
           <t>Added 10 Oct 2026. Mirrors docs/pilot-dry-run.md; screens and wording still need people.</t>
         </is>
       </c>
-      <c r="Q146" s="10" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
@@ -12386,7 +12232,6 @@
           <t>Added 10 Oct 2026. Decision B: flag, do not stop (DAY-005 gate stays in R2).</t>
         </is>
       </c>
-      <c r="Q147" s="10" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="10" t="inlineStr">
@@ -12469,7 +12314,6 @@
           <t>QA-07. Fixes 14 helpers the security advisor listed. Added 10 Oct 2026.</t>
         </is>
       </c>
-      <c r="Q148" s="10" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
@@ -12552,7 +12396,6 @@
           <t>QA-05. The warnings name the plan and price (PLT-018). Product name 'Zikora' in the wording is a draft.</t>
         </is>
       </c>
-      <c r="Q149" s="10" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="10" t="inlineStr">
@@ -12635,7 +12478,6 @@
           <t>QA-05.</t>
         </is>
       </c>
-      <c r="Q150" s="10" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
@@ -12718,7 +12560,6 @@
           <t>Added 10 Oct 2026 (QA-12).</t>
         </is>
       </c>
-      <c r="Q151" s="10" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="10" t="inlineStr">
@@ -12801,7 +12642,6 @@
           <t>Stage 1. Only data the user's role may see is saved. ID numbers and photos are never saved.</t>
         </is>
       </c>
-      <c r="Q152" s="10" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
@@ -12884,7 +12724,6 @@
           <t>Stage 1. Sign-out is refused while actions still wait to send (OFF-004).</t>
         </is>
       </c>
-      <c r="Q153" s="10" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="10" t="inlineStr">
@@ -12967,7 +12806,6 @@
           <t>Stage 2. Approvals and check-in stay online only. Check-out and room moves: see OFF-005 and OFF-006.</t>
         </is>
       </c>
-      <c r="Q154" s="10" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
@@ -13050,7 +12888,6 @@
           <t>Stage 2.</t>
         </is>
       </c>
-      <c r="Q155" s="10" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="10" t="inlineStr">
@@ -13133,7 +12970,6 @@
           <t>QA-22. Page sizes: 100 bookings, 50 guests, 200 folios, 100 audit rows.</t>
         </is>
       </c>
-      <c r="Q156" s="10" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
@@ -13216,7 +13052,6 @@
           <t>Needs a connection. Not saved for offline use.</t>
         </is>
       </c>
-      <c r="Q157" s="10" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="10" t="inlineStr">
@@ -13299,7 +13134,6 @@
           <t>Added 11 Oct 2026. The availability calendar and the downtime pack are true grids and scroll inside their own box on purpose.</t>
         </is>
       </c>
-      <c r="Q158" s="10" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
@@ -13382,7 +13216,6 @@
           <t>Peter decided on 12 Oct 2026 (was 30 days). Hotels already on trial keep their dates; platform staff can extend one by hand. Plan choice at signup is not built: every new hotel starts on Starter (20 rooms).</t>
         </is>
       </c>
-      <c r="Q159" s="10" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="10" t="inlineStr">
@@ -13465,7 +13298,6 @@
           <t>One price for every hotel: no launch price and no price lock (Peter, 12 Oct 2026). Features by plan are not built; plans cap rooms, properties and users only. Billing stays off until the Paystack key and webhook are set.</t>
         </is>
       </c>
-      <c r="Q160" s="10" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
@@ -13548,7 +13380,6 @@
           <t>Billing checkout (Paystack) is off until the key and webhook are set, so payment is arranged by email to hello@zikorahq.com. The Terms (section 4) still say read-only at trial end and need counsel to reword.</t>
         </is>
       </c>
-      <c r="Q161" s="10" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="10" t="inlineStr">
@@ -13631,7 +13462,6 @@
           <t>Needs a real phone check (iPhone Safari and Android Chrome). Works with the offline service worker already in place.</t>
         </is>
       </c>
-      <c r="Q162" s="10" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
@@ -13714,7 +13544,6 @@
           <t>Stage 3a. Reason recorded: Checked out with no connection. Approvals stay online only.</t>
         </is>
       </c>
-      <c r="Q163" s="10" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="10" t="inlineStr">
@@ -13797,7 +13626,6 @@
           <t>Stage 3a. Check-in is OFF-007 and OFF-008. Walk-in is not built.</t>
         </is>
       </c>
-      <c r="Q164" s="10" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="10" t="inlineStr">
@@ -13880,7 +13708,6 @@
           <t>Stage 3b, check-in of an existing booking. Walk-in is not built (needs a new guest to be made offline). ID photos need a connection.</t>
         </is>
       </c>
-      <c r="Q165" s="10" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="10" t="inlineStr">
@@ -13963,7 +13790,6 @@
           <t>Stage 3b.</t>
         </is>
       </c>
-      <c r="Q166" s="10" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="10" t="inlineStr">
@@ -14046,7 +13872,6 @@
           <t>Real sending starts when RESEND_API_KEY and OUTBOX_FROM_EMAIL are set in Vercel. Until then the form uses the email app fallback. No rate limit yet.</t>
         </is>
       </c>
-      <c r="Q167" s="10" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="10" t="inlineStr">
@@ -14129,7 +13954,6 @@
           <t>Headers apply on the Vercel build only (not the local dev server). Full script policy (CSP) is a later job.</t>
         </is>
       </c>
-      <c r="Q168" s="10" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O108"/>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P169"/>
+  <dimension ref="A1:P170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14034,6 +14034,88 @@
       <c r="P169" s="10" t="inlineStr">
         <is>
           <t>Added 12 Oct 2026. security.txt expires 1 Oct 2027: renew it before then. Its contact is the website contact page until the hello@ mailbox can receive mail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="10" t="inlineStr">
+        <is>
+          <t>PLT-023</t>
+        </is>
+      </c>
+      <c r="B170" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C170" s="10" t="inlineStr">
+        <is>
+          <t>All pages</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="inlineStr">
+        <is>
+          <t>The first page load stays small. Public pages do not download the sign-in library, the form checker or the toast library; those load only when someone signs in, sends a form or reaches a signed-in screen. The first load went from 823 KB to 423 KB (243 KB to 134 KB compressed).</t>
+        </is>
+      </c>
+      <c r="E170" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F170" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G170" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H170" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="10" t="inlineStr">
+        <is>
+          <t>Audit 12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="J170" s="10" t="inlineStr">
+        <is>
+          <t>a hotel owner opens the home page on mobile data</t>
+        </is>
+      </c>
+      <c r="K170" s="10" t="inlineStr">
+        <is>
+          <t>the page loads</t>
+        </is>
+      </c>
+      <c r="L170" s="10" t="inlineStr">
+        <is>
+          <t>the first scripts total under 470 KB and include none of the app-only libraries</t>
+        </is>
+      </c>
+      <c r="M170" s="10" t="inlineStr">
+        <is>
+          <t>scripts/bundle-size.mjs; scripts/check-bundle.mjs; src/lib/auth-watch.ts; src/lib/queries.ts; src/routes/__root.tsx</t>
+        </is>
+      </c>
+      <c r="N170" s="10" t="inlineStr">
+        <is>
+          <t>e2e/bundle-size-unit.spec.ts</t>
+        </is>
+      </c>
+      <c r="O170" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P170" s="10" t="inlineStr">
+        <is>
+          <t>Checked in CI after the build (npm run check:bundle). The 470 KB limit is raw size. React itself is about 200 KB of it.</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -14055,7 +14055,7 @@
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>The first page load stays small. Public pages do not download the sign-in library, the form checker or the toast library; those load only when someone signs in, sends a form or reaches a signed-in screen. The first load went from 823 KB to 423 KB (243 KB to 134 KB compressed).</t>
+          <t>The first page load stays small. Public pages do not download the sign-in library or the form checker; those load only when someone signs in, sends a form or reaches a signed-in screen. The first load went from 823 KB to 456 KB (243 KB to 142 KB compressed).</t>
         </is>
       </c>
       <c r="E170" s="10" t="inlineStr">

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P170"/>
+  <dimension ref="A1:P171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14116,6 +14116,88 @@
       <c r="P170" s="10" t="inlineStr">
         <is>
           <t>Checked in CI after the build (npm run check:bundle). The 470 KB limit is raw size. React itself is about 200 KB of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="10" t="inlineStr">
+        <is>
+          <t>PLT-024</t>
+        </is>
+      </c>
+      <c r="B171" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>Platform console</t>
+        </is>
+      </c>
+      <c r="D171" s="10" t="inlineStr">
+        <is>
+          <t>The owner sees a summary at the top of the platform console: hotels by status, new hotels this week and month, trials ending within 14 days, hotels gone quiet, and the monthly list price of active hotels. Account data only.</t>
+        </is>
+      </c>
+      <c r="E171" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F171" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G171" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H171" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="10" t="inlineStr">
+        <is>
+          <t>Owner request 13 Oct 2026</t>
+        </is>
+      </c>
+      <c r="J171" s="10" t="inlineStr">
+        <is>
+          <t>a platform operator signed in with two-step sign-in</t>
+        </is>
+      </c>
+      <c r="K171" s="10" t="inlineStr">
+        <is>
+          <t>they open the platform console</t>
+        </is>
+      </c>
+      <c r="L171" s="10" t="inlineStr">
+        <is>
+          <t>they see the counts, the trials about to end, the quiet hotels and the monthly value of active hotels, with no guest, booking or balance data</t>
+        </is>
+      </c>
+      <c r="M171" s="10" t="inlineStr">
+        <is>
+          <t>platform_summary; src/routes/_authenticated/platform.tsx; src/components/platform-summary.tsx</t>
+        </is>
+      </c>
+      <c r="N171" s="10" t="inlineStr">
+        <is>
+          <t>supabase/tests/db/62_platform_summary.sql</t>
+        </is>
+      </c>
+      <c r="O171" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P171" s="10" t="inlineStr">
+        <is>
+          <t>Monthly value is list price of hotels with Active status. Pilot hotels invoiced by hand or free still count if set to Active.</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P171"/>
+  <dimension ref="A1:P172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14198,6 +14198,88 @@
       <c r="P171" s="10" t="inlineStr">
         <is>
           <t>Monthly value is list price of hotels with Active status. Pilot hotels invoiced by hand or free still count if set to Active.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="10" t="inlineStr">
+        <is>
+          <t>PLT-025</t>
+        </is>
+      </c>
+      <c r="B172" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C172" s="10" t="inlineStr">
+        <is>
+          <t>Operations (not a screen)</t>
+        </is>
+      </c>
+      <c r="D172" s="10" t="inlineStr">
+        <is>
+          <t>Demo hotels can be removed completely, with their ledger, audit log and staff sign-ins, by a one-time script that Claude prepares and the owner runs. A dry run shows every count and changes nothing. It never touches other hotels or platform operators, and it rolls back if anything is left behind.</t>
+        </is>
+      </c>
+      <c r="E172" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F172" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G172" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H172" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="10" t="inlineStr">
+        <is>
+          <t>Owner request 13 Oct 2026</t>
+        </is>
+      </c>
+      <c r="J172" s="10" t="inlineStr">
+        <is>
+          <t>a demo hotel that holds no real guest or money data</t>
+        </is>
+      </c>
+      <c r="K172" s="10" t="inlineStr">
+        <is>
+          <t>the owner runs the removal script with the hotel id</t>
+        </is>
+      </c>
+      <c r="L172" s="10" t="inlineStr">
+        <is>
+          <t>the hotel and everything it owns is gone, other hotels and operators are unchanged, and the ledger locks are back on</t>
+        </is>
+      </c>
+      <c r="M172" s="10" t="inlineStr">
+        <is>
+          <t>scripts/remove-hotels.sql; docs/runbook-remove-hotels.md</t>
+        </is>
+      </c>
+      <c r="N172" s="10" t="inlineStr">
+        <is>
+          <t>supabase/tests/db/63_remove_hotels.sql</t>
+        </is>
+      </c>
+      <c r="O172" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P172" s="10" t="inlineStr">
+        <is>
+          <t>One-time tool, not a migration. Live needs a backup first and the owner's typed yes, live.</t>
         </is>
       </c>
     </row>

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -14219,7 +14219,7 @@
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>Demo hotels can be removed completely, with their ledger, audit log and staff sign-ins, by a one-time script that Claude prepares and the owner runs. A dry run shows every count and changes nothing. It never touches other hotels or platform operators, and it rolls back if anything is left behind.</t>
+          <t>Demo hotels can be removed completely, with their ledger, audit log and staff sign-ins, by a one-time script that Claude prepares and the owner runs. A dry run shows every count and changes nothing. A second function removes a named platform operator on request. Hotel removal never touches other hotels or operators, and it rolls back if anything is left behind.</t>
         </is>
       </c>
       <c r="E172" s="10" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="L172" s="10" t="inlineStr">
         <is>
-          <t>the hotel and everything it owns is gone, other hotels and operators are unchanged, and the ledger locks are back on</t>
+          <t>the hotel and everything it owns is gone, other hotels and operators are unchanged, and a named operator can be removed on its own, and the ledger locks are back on</t>
         </is>
       </c>
       <c r="M172" s="10" t="inlineStr">

--- a/docs/HMS_R1_Requirements.xlsx
+++ b/docs/HMS_R1_Requirements.xlsx
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P172"/>
+  <dimension ref="A1:P173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14280,6 +14280,88 @@
       <c r="P172" s="10" t="inlineStr">
         <is>
           <t>One-time tool, not a migration. Live needs a backup first and the owner's typed yes, live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="10" t="inlineStr">
+        <is>
+          <t>PLT-026</t>
+        </is>
+      </c>
+      <c r="B173" s="10" t="inlineStr">
+        <is>
+          <t>Platform &amp; Tenancy</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>Sign up, Sign in, Reset password</t>
+        </is>
+      </c>
+      <c r="D173" s="10" t="inlineStr">
+        <is>
+          <t>Open sign-up has a safety check (Cloudflare Turnstile) that stops bots from creating accounts in bulk. The check also guards sign-in and password reset, because Supabase applies it to all three. It is off until a site key is set, and the secret key stays in the Supabase dashboard only.</t>
+        </is>
+      </c>
+      <c r="E173" s="10" t="inlineStr">
+        <is>
+          <t>BR-001</t>
+        </is>
+      </c>
+      <c r="F173" s="10" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="G173" s="10" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H173" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="10" t="inlineStr">
+        <is>
+          <t>Owner decision 13 Oct 2026</t>
+        </is>
+      </c>
+      <c r="J173" s="10" t="inlineStr">
+        <is>
+          <t>a visitor on the sign-up page with the check switched on</t>
+        </is>
+      </c>
+      <c r="K173" s="10" t="inlineStr">
+        <is>
+          <t>they send the form</t>
+        </is>
+      </c>
+      <c r="L173" s="10" t="inlineStr">
+        <is>
+          <t>the safety check token goes with the request and the account is created only if it passes; with no site key the form works as before</t>
+        </is>
+      </c>
+      <c r="M173" s="10" t="inlineStr">
+        <is>
+          <t>src/lib/captcha.ts; src/components/turnstile.tsx; src/routes/auth.tsx; src/routes/forgot-password.tsx</t>
+        </is>
+      </c>
+      <c r="N173" s="10" t="inlineStr">
+        <is>
+          <t>e2e/captcha-unit.spec.ts</t>
+        </is>
+      </c>
+      <c r="O173" s="10" t="inlineStr">
+        <is>
+          <t>Built+tested</t>
+        </is>
+      </c>
+      <c r="P173" s="10" t="inlineStr">
+        <is>
+          <t>Switch-on order matters: set the site key in Vercel and deploy first, then turn on CAPTCHA protection in Supabase. The other way round, nobody can sign in. See docs/setup-checklist.md.</t>
         </is>
       </c>
     </row>
